--- a/Adjusted_Close_FPT_VNM.xlsx
+++ b/Adjusted_Close_FPT_VNM.xlsx
@@ -444,10 +444,10 @@
         <v>45196</v>
       </c>
       <c r="B2" t="n">
-        <v>61812.1171875</v>
+        <v>61812.12109375</v>
       </c>
       <c r="C2" t="n">
-        <v>64295.93359375</v>
+        <v>64295.9296875</v>
       </c>
     </row>
     <row r="3">
@@ -466,10 +466,10 @@
         <v>45198</v>
       </c>
       <c r="B4" t="n">
-        <v>60828.89453125</v>
+        <v>60828.8984375</v>
       </c>
       <c r="C4" t="n">
-        <v>62281.4375</v>
+        <v>62281.44140625</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         <v>45201</v>
       </c>
       <c r="B5" t="n">
-        <v>61091.0859375</v>
+        <v>61091.08984375</v>
       </c>
       <c r="C5" t="n">
         <v>63456.5546875</v>
@@ -491,7 +491,7 @@
         <v>60435.60546875</v>
       </c>
       <c r="C6" t="n">
-        <v>62113.56640625</v>
+        <v>62113.5625</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +502,7 @@
         <v>60632.25</v>
       </c>
       <c r="C7" t="n">
-        <v>62449.32421875</v>
+        <v>62449.3125</v>
       </c>
     </row>
     <row r="8">
@@ -510,7 +510,7 @@
         <v>45204</v>
       </c>
       <c r="B8" t="n">
-        <v>60042.3125</v>
+        <v>60042.31640625</v>
       </c>
       <c r="C8" t="n">
         <v>61022.37890625</v>
@@ -524,7 +524,7 @@
         <v>60763.34765625</v>
       </c>
       <c r="C9" t="n">
-        <v>62281.4375</v>
+        <v>62281.44140625</v>
       </c>
     </row>
     <row r="10">
@@ -532,10 +532,10 @@
         <v>45208</v>
       </c>
       <c r="B10" t="n">
-        <v>62664.24609375</v>
+        <v>62664.25</v>
       </c>
       <c r="C10" t="n">
-        <v>61861.75</v>
+        <v>61861.765625</v>
       </c>
     </row>
     <row r="11">
@@ -546,7 +546,7 @@
         <v>63123.0859375</v>
       </c>
       <c r="C11" t="n">
-        <v>62449.32421875</v>
+        <v>62449.3125</v>
       </c>
     </row>
     <row r="12">
@@ -557,7 +557,7 @@
         <v>63581.92578125</v>
       </c>
       <c r="C12" t="n">
-        <v>62449.32421875</v>
+        <v>62449.3125</v>
       </c>
     </row>
     <row r="13">
@@ -565,10 +565,10 @@
         <v>45211</v>
       </c>
       <c r="B13" t="n">
-        <v>63188.63671875</v>
+        <v>63188.640625</v>
       </c>
       <c r="C13" t="n">
-        <v>63372.625</v>
+        <v>63372.62109375</v>
       </c>
     </row>
     <row r="14">
@@ -587,7 +587,7 @@
         <v>45215</v>
       </c>
       <c r="B15" t="n">
-        <v>63450.8359375</v>
+        <v>63450.83203125</v>
       </c>
       <c r="C15" t="n">
         <v>63120.8125</v>
@@ -609,10 +609,10 @@
         <v>45217</v>
       </c>
       <c r="B17" t="n">
-        <v>60959.9921875</v>
+        <v>60959.99609375</v>
       </c>
       <c r="C17" t="n">
-        <v>62029.625</v>
+        <v>62029.62109375</v>
       </c>
     </row>
     <row r="18">
@@ -623,7 +623,7 @@
         <v>60304.5078125</v>
       </c>
       <c r="C18" t="n">
-        <v>59931.19921875</v>
+        <v>59931.203125</v>
       </c>
     </row>
     <row r="19">
@@ -642,10 +642,10 @@
         <v>45222</v>
       </c>
       <c r="B20" t="n">
-        <v>59649.0234375</v>
+        <v>59649.02734375</v>
       </c>
       <c r="C20" t="n">
-        <v>58923.94921875</v>
+        <v>58923.953125</v>
       </c>
     </row>
     <row r="21">
@@ -667,7 +667,7 @@
         <v>59583.48046875</v>
       </c>
       <c r="C22" t="n">
-        <v>57916.69921875</v>
+        <v>57916.70703125</v>
       </c>
     </row>
     <row r="23">
@@ -675,7 +675,7 @@
         <v>45225</v>
       </c>
       <c r="B23" t="n">
-        <v>56895.9921875</v>
+        <v>56895.99609375</v>
       </c>
       <c r="C23" t="n">
         <v>56237.95703125</v>
@@ -689,7 +689,7 @@
         <v>57027.08984375</v>
       </c>
       <c r="C24" t="n">
-        <v>57077.33203125</v>
+        <v>57077.328125</v>
       </c>
     </row>
     <row r="25">
@@ -708,10 +708,10 @@
         <v>45230</v>
       </c>
       <c r="B26" t="n">
-        <v>54405.15234375</v>
+        <v>54405.1484375</v>
       </c>
       <c r="C26" t="n">
-        <v>57077.33203125</v>
+        <v>57077.328125</v>
       </c>
     </row>
     <row r="27">
@@ -722,7 +722,7 @@
         <v>55978.31640625</v>
       </c>
       <c r="C27" t="n">
-        <v>59091.81640625</v>
+        <v>59091.82421875</v>
       </c>
     </row>
     <row r="28">
@@ -730,10 +730,10 @@
         <v>45232</v>
       </c>
       <c r="B28" t="n">
-        <v>58338.05859375</v>
+        <v>58338.0625</v>
       </c>
       <c r="C28" t="n">
-        <v>59511.5078125</v>
+        <v>59511.51171875</v>
       </c>
     </row>
     <row r="29">
@@ -752,7 +752,7 @@
         <v>45236</v>
       </c>
       <c r="B30" t="n">
-        <v>58010.31640625</v>
+        <v>58010.3125</v>
       </c>
       <c r="C30" t="n">
         <v>59595.44921875</v>
@@ -763,10 +763,10 @@
         <v>45237</v>
       </c>
       <c r="B31" t="n">
-        <v>57879.21484375</v>
+        <v>57879.21875</v>
       </c>
       <c r="C31" t="n">
-        <v>59427.56640625</v>
+        <v>59427.57421875</v>
       </c>
     </row>
     <row r="32">
@@ -774,10 +774,10 @@
         <v>45238</v>
       </c>
       <c r="B32" t="n">
-        <v>60697.79296875</v>
+        <v>60697.796875</v>
       </c>
       <c r="C32" t="n">
-        <v>59931.19921875</v>
+        <v>59931.203125</v>
       </c>
     </row>
     <row r="33">
@@ -788,7 +788,7 @@
         <v>60632.25</v>
       </c>
       <c r="C33" t="n">
-        <v>59343.6328125</v>
+        <v>59343.63671875</v>
       </c>
     </row>
     <row r="34">
@@ -796,7 +796,7 @@
         <v>45240</v>
       </c>
       <c r="B34" t="n">
-        <v>59976.765625</v>
+        <v>59976.76953125</v>
       </c>
       <c r="C34" t="n">
         <v>58420.32421875</v>
@@ -818,10 +818,10 @@
         <v>45244</v>
       </c>
       <c r="B36" t="n">
-        <v>60697.79296875</v>
+        <v>60697.796875</v>
       </c>
       <c r="C36" t="n">
-        <v>57832.76953125</v>
+        <v>57832.765625</v>
       </c>
     </row>
     <row r="37">
@@ -829,10 +829,10 @@
         <v>45245</v>
       </c>
       <c r="B37" t="n">
-        <v>60566.6953125</v>
+        <v>60566.69921875</v>
       </c>
       <c r="C37" t="n">
-        <v>59343.6328125</v>
+        <v>59343.63671875</v>
       </c>
     </row>
     <row r="38">
@@ -840,7 +840,7 @@
         <v>45246</v>
       </c>
       <c r="B38" t="n">
-        <v>60959.9921875</v>
+        <v>60959.99609375</v>
       </c>
       <c r="C38" t="n">
         <v>59007.890625</v>
@@ -851,7 +851,7 @@
         <v>45247</v>
       </c>
       <c r="B39" t="n">
-        <v>59649.0234375</v>
+        <v>59649.02734375</v>
       </c>
       <c r="C39" t="n">
         <v>58756.07421875</v>
@@ -865,7 +865,7 @@
         <v>59452.37890625</v>
       </c>
       <c r="C40" t="n">
-        <v>58168.51953125</v>
+        <v>58168.515625</v>
       </c>
     </row>
     <row r="41">
@@ -876,7 +876,7 @@
         <v>60238.9609375</v>
       </c>
       <c r="C41" t="n">
-        <v>58336.390625</v>
+        <v>58336.38671875</v>
       </c>
     </row>
     <row r="42">
@@ -884,7 +884,7 @@
         <v>45252</v>
       </c>
       <c r="B42" t="n">
-        <v>60959.9921875</v>
+        <v>60959.99609375</v>
       </c>
       <c r="C42" t="n">
         <v>58252.44921875</v>
@@ -895,7 +895,7 @@
         <v>45253</v>
       </c>
       <c r="B43" t="n">
-        <v>59517.92578125</v>
+        <v>59517.9296875</v>
       </c>
       <c r="C43" t="n">
         <v>57664.890625</v>
@@ -920,7 +920,7 @@
         <v>59452.37890625</v>
       </c>
       <c r="C45" t="n">
-        <v>57161.26171875</v>
+        <v>57161.2734375</v>
       </c>
     </row>
     <row r="46">
@@ -928,7 +928,7 @@
         <v>45258</v>
       </c>
       <c r="B46" t="n">
-        <v>59714.5703125</v>
+        <v>59714.57421875</v>
       </c>
       <c r="C46" t="n">
         <v>57497.015625</v>
@@ -939,7 +939,7 @@
         <v>45259</v>
       </c>
       <c r="B47" t="n">
-        <v>60107.86328125</v>
+        <v>60107.8671875</v>
       </c>
       <c r="C47" t="n">
         <v>57413.078125</v>
@@ -961,7 +961,7 @@
         <v>45261</v>
       </c>
       <c r="B49" t="n">
-        <v>60566.6953125</v>
+        <v>60566.69921875</v>
       </c>
       <c r="C49" t="n">
         <v>57413.078125</v>
@@ -975,7 +975,7 @@
         <v>61353.28125</v>
       </c>
       <c r="C50" t="n">
-        <v>57748.82421875</v>
+        <v>57748.828125</v>
       </c>
     </row>
     <row r="51">
@@ -986,7 +986,7 @@
         <v>62139.86328125</v>
       </c>
       <c r="C51" t="n">
-        <v>57161.26171875</v>
+        <v>57161.2734375</v>
       </c>
     </row>
     <row r="52">
@@ -994,7 +994,7 @@
         <v>45266</v>
       </c>
       <c r="B52" t="n">
-        <v>62270.96484375</v>
+        <v>62270.9609375</v>
       </c>
       <c r="C52" t="n">
         <v>57497.015625</v>
@@ -1005,7 +1005,7 @@
         <v>45267</v>
       </c>
       <c r="B53" t="n">
-        <v>61812.1171875</v>
+        <v>61812.12109375</v>
       </c>
       <c r="C53" t="n">
         <v>57413.078125</v>
@@ -1019,7 +1019,7 @@
         <v>61746.57421875</v>
       </c>
       <c r="C54" t="n">
-        <v>57916.69921875</v>
+        <v>57916.70703125</v>
       </c>
     </row>
     <row r="55">
@@ -1027,7 +1027,7 @@
         <v>45271</v>
       </c>
       <c r="B55" t="n">
-        <v>62270.96484375</v>
+        <v>62270.9609375</v>
       </c>
       <c r="C55" t="n">
         <v>58756.07421875</v>
@@ -1038,7 +1038,7 @@
         <v>45272</v>
       </c>
       <c r="B56" t="n">
-        <v>63450.8359375</v>
+        <v>63450.83203125</v>
       </c>
       <c r="C56" t="n">
         <v>58252.44921875</v>
@@ -1060,10 +1060,10 @@
         <v>45275</v>
       </c>
       <c r="B58" t="n">
-        <v>63057.54296875</v>
+        <v>63057.5390625</v>
       </c>
       <c r="C58" t="n">
-        <v>57161.26171875</v>
+        <v>57161.2734375</v>
       </c>
     </row>
     <row r="59">
@@ -1096,7 +1096,7 @@
         <v>62074.31640625</v>
       </c>
       <c r="C61" t="n">
-        <v>57161.26171875</v>
+        <v>57161.2734375</v>
       </c>
     </row>
     <row r="62">
@@ -1104,10 +1104,10 @@
         <v>45281</v>
       </c>
       <c r="B62" t="n">
-        <v>62336.5078125</v>
+        <v>62336.51171875</v>
       </c>
       <c r="C62" t="n">
-        <v>56909.453125</v>
+        <v>56909.45703125</v>
       </c>
     </row>
     <row r="63">
@@ -1129,7 +1129,7 @@
         <v>62926.44140625</v>
       </c>
       <c r="C64" t="n">
-        <v>56993.3984375</v>
+        <v>56993.39453125</v>
       </c>
     </row>
     <row r="65">
@@ -1140,7 +1140,7 @@
         <v>63713.01953125</v>
       </c>
       <c r="C65" t="n">
-        <v>57077.33203125</v>
+        <v>57077.328125</v>
       </c>
     </row>
     <row r="66">
@@ -1148,10 +1148,10 @@
         <v>45287</v>
       </c>
       <c r="B66" t="n">
-        <v>63516.3828125</v>
+        <v>63516.38671875</v>
       </c>
       <c r="C66" t="n">
-        <v>57077.33203125</v>
+        <v>57077.3359375</v>
       </c>
     </row>
     <row r="67">
@@ -1162,7 +1162,7 @@
         <v>63319.73828125</v>
       </c>
       <c r="C67" t="n">
-        <v>57922.921875</v>
+        <v>57922.91796875</v>
       </c>
     </row>
     <row r="68">
@@ -1173,7 +1173,7 @@
         <v>62991.9921875</v>
       </c>
       <c r="C68" t="n">
-        <v>57161.88671875</v>
+        <v>57161.890625</v>
       </c>
     </row>
     <row r="69">
@@ -1181,10 +1181,10 @@
         <v>45293</v>
       </c>
       <c r="B69" t="n">
-        <v>62860.89453125</v>
+        <v>62860.890625</v>
       </c>
       <c r="C69" t="n">
-        <v>57753.8046875</v>
+        <v>57753.80078125</v>
       </c>
     </row>
     <row r="70">
@@ -1195,7 +1195,7 @@
         <v>63123.0859375</v>
       </c>
       <c r="C70" t="n">
-        <v>58345.71484375</v>
+        <v>58345.71875</v>
       </c>
     </row>
     <row r="71">
@@ -1206,7 +1206,7 @@
         <v>63713.01953125</v>
       </c>
       <c r="C71" t="n">
-        <v>58345.71484375</v>
+        <v>58345.71875</v>
       </c>
     </row>
     <row r="72">
@@ -1217,7 +1217,7 @@
         <v>63844.1171875</v>
       </c>
       <c r="C72" t="n">
-        <v>58176.59375</v>
+        <v>58176.59765625</v>
       </c>
     </row>
     <row r="73">
@@ -1225,7 +1225,7 @@
         <v>45299</v>
       </c>
       <c r="B73" t="n">
-        <v>63778.56640625</v>
+        <v>63778.5703125</v>
       </c>
       <c r="C73" t="n">
         <v>57669.2421875</v>
@@ -1239,7 +1239,7 @@
         <v>63319.73828125</v>
       </c>
       <c r="C74" t="n">
-        <v>57584.68359375</v>
+        <v>57584.69140625</v>
       </c>
     </row>
     <row r="75">
@@ -1250,7 +1250,7 @@
         <v>62074.31640625</v>
       </c>
       <c r="C75" t="n">
-        <v>57077.33203125</v>
+        <v>57077.3359375</v>
       </c>
     </row>
     <row r="76">
@@ -1258,10 +1258,10 @@
         <v>45302</v>
       </c>
       <c r="B76" t="n">
-        <v>62270.96484375</v>
+        <v>62270.9609375</v>
       </c>
       <c r="C76" t="n">
-        <v>57415.5703125</v>
+        <v>57415.56640625</v>
       </c>
     </row>
     <row r="77">
@@ -1291,10 +1291,10 @@
         <v>45308</v>
       </c>
       <c r="B79" t="n">
-        <v>62729.80078125</v>
+        <v>62729.796875</v>
       </c>
       <c r="C79" t="n">
-        <v>56739.09765625</v>
+        <v>56739.08984375</v>
       </c>
     </row>
     <row r="80">
@@ -1305,7 +1305,7 @@
         <v>63123.0859375</v>
       </c>
       <c r="C80" t="n">
-        <v>57500.12890625</v>
+        <v>57500.125</v>
       </c>
     </row>
     <row r="81">
@@ -1313,10 +1313,10 @@
         <v>45313</v>
       </c>
       <c r="B81" t="n">
-        <v>63188.63671875</v>
+        <v>63188.640625</v>
       </c>
       <c r="C81" t="n">
-        <v>57753.8046875</v>
+        <v>57753.80078125</v>
       </c>
     </row>
     <row r="82">
@@ -1324,7 +1324,7 @@
         <v>45314</v>
       </c>
       <c r="B82" t="n">
-        <v>62664.24609375</v>
+        <v>62664.25</v>
       </c>
       <c r="C82" t="n">
         <v>57246.44921875</v>
@@ -1335,10 +1335,10 @@
         <v>45315</v>
       </c>
       <c r="B83" t="n">
-        <v>62270.96484375</v>
+        <v>62270.9609375</v>
       </c>
       <c r="C83" t="n">
-        <v>56908.21484375</v>
+        <v>56908.2109375</v>
       </c>
     </row>
     <row r="84">
@@ -1346,10 +1346,10 @@
         <v>45316</v>
       </c>
       <c r="B84" t="n">
-        <v>62270.96484375</v>
+        <v>62270.9609375</v>
       </c>
       <c r="C84" t="n">
-        <v>56908.21484375</v>
+        <v>56908.2109375</v>
       </c>
     </row>
     <row r="85">
@@ -1357,7 +1357,7 @@
         <v>45317</v>
       </c>
       <c r="B85" t="n">
-        <v>62860.89453125</v>
+        <v>62860.890625</v>
       </c>
       <c r="C85" t="n">
         <v>56654.53515625</v>
@@ -1368,7 +1368,7 @@
         <v>45320</v>
       </c>
       <c r="B86" t="n">
-        <v>62860.89453125</v>
+        <v>62860.890625</v>
       </c>
       <c r="C86" t="n">
         <v>56654.53515625</v>
@@ -1379,10 +1379,10 @@
         <v>45321</v>
       </c>
       <c r="B87" t="n">
-        <v>62664.24609375</v>
+        <v>62664.25</v>
       </c>
       <c r="C87" t="n">
-        <v>56569.98046875</v>
+        <v>56569.9765625</v>
       </c>
     </row>
     <row r="88">
@@ -1390,7 +1390,7 @@
         <v>45322</v>
       </c>
       <c r="B88" t="n">
-        <v>62729.80078125</v>
+        <v>62729.796875</v>
       </c>
       <c r="C88" t="n">
         <v>56654.53515625</v>
@@ -1401,10 +1401,10 @@
         <v>45323</v>
       </c>
       <c r="B89" t="n">
-        <v>65482.828125</v>
+        <v>65482.83203125</v>
       </c>
       <c r="C89" t="n">
-        <v>57077.33203125</v>
+        <v>57077.3359375</v>
       </c>
     </row>
     <row r="90">
@@ -1412,10 +1412,10 @@
         <v>45324</v>
       </c>
       <c r="B90" t="n">
-        <v>65482.828125</v>
+        <v>65482.83203125</v>
       </c>
       <c r="C90" t="n">
-        <v>57077.33203125</v>
+        <v>57077.3359375</v>
       </c>
     </row>
     <row r="91">
@@ -1423,10 +1423,10 @@
         <v>45327</v>
       </c>
       <c r="B91" t="n">
-        <v>67842.5703125</v>
+        <v>67842.5625</v>
       </c>
       <c r="C91" t="n">
-        <v>57500.12890625</v>
+        <v>57500.125</v>
       </c>
     </row>
     <row r="92">
@@ -1434,10 +1434,10 @@
         <v>45328</v>
       </c>
       <c r="B92" t="n">
-        <v>68235.8671875</v>
+        <v>68235.859375</v>
       </c>
       <c r="C92" t="n">
-        <v>57161.88671875</v>
+        <v>57161.890625</v>
       </c>
     </row>
     <row r="93">
@@ -1448,7 +1448,7 @@
         <v>68760.25</v>
       </c>
       <c r="C93" t="n">
-        <v>57161.88671875</v>
+        <v>57161.890625</v>
       </c>
     </row>
     <row r="94">
@@ -1456,10 +1456,10 @@
         <v>45337</v>
       </c>
       <c r="B94" t="n">
-        <v>68170.3046875</v>
+        <v>68170.3203125</v>
       </c>
       <c r="C94" t="n">
-        <v>57161.88671875</v>
+        <v>57161.890625</v>
       </c>
     </row>
     <row r="95">
@@ -1467,10 +1467,10 @@
         <v>45338</v>
       </c>
       <c r="B95" t="n">
-        <v>68891.34375</v>
+        <v>68891.3515625</v>
       </c>
       <c r="C95" t="n">
-        <v>59191.30078125</v>
+        <v>59191.3046875</v>
       </c>
     </row>
     <row r="96">
@@ -1492,7 +1492,7 @@
         <v>68366.9609375</v>
       </c>
       <c r="C97" t="n">
-        <v>60459.69140625</v>
+        <v>60459.6953125</v>
       </c>
     </row>
     <row r="98">
@@ -1500,10 +1500,10 @@
         <v>45343</v>
       </c>
       <c r="B98" t="n">
-        <v>69415.734375</v>
+        <v>69415.7265625</v>
       </c>
       <c r="C98" t="n">
-        <v>60290.57421875</v>
+        <v>60290.5703125</v>
       </c>
     </row>
     <row r="99">
@@ -1522,10 +1522,10 @@
         <v>45345</v>
       </c>
       <c r="B100" t="n">
-        <v>68104.765625</v>
+        <v>68104.7578125</v>
       </c>
       <c r="C100" t="n">
-        <v>60036.890625</v>
+        <v>60036.8984375</v>
       </c>
     </row>
     <row r="101">
@@ -1533,10 +1533,10 @@
         <v>45348</v>
       </c>
       <c r="B101" t="n">
-        <v>70792.2421875</v>
+        <v>70792.25</v>
       </c>
       <c r="C101" t="n">
-        <v>60036.890625</v>
+        <v>60036.8984375</v>
       </c>
     </row>
     <row r="102">
@@ -1547,7 +1547,7 @@
         <v>70726.703125</v>
       </c>
       <c r="C102" t="n">
-        <v>60882.484375</v>
+        <v>60882.48828125</v>
       </c>
     </row>
     <row r="103">
@@ -1555,10 +1555,10 @@
         <v>45350</v>
       </c>
       <c r="B103" t="n">
-        <v>71120</v>
+        <v>71119.9921875</v>
       </c>
       <c r="C103" t="n">
-        <v>61051.6015625</v>
+        <v>61051.59375</v>
       </c>
     </row>
     <row r="104">
@@ -1566,10 +1566,10 @@
         <v>45351</v>
       </c>
       <c r="B104" t="n">
-        <v>71447.7421875</v>
+        <v>71447.7265625</v>
       </c>
       <c r="C104" t="n">
-        <v>60882.484375</v>
+        <v>60882.48828125</v>
       </c>
     </row>
     <row r="105">
@@ -1577,10 +1577,10 @@
         <v>45352</v>
       </c>
       <c r="B105" t="n">
-        <v>72627.609375</v>
+        <v>72627.6015625</v>
       </c>
       <c r="C105" t="n">
-        <v>60459.69140625</v>
+        <v>60459.6953125</v>
       </c>
     </row>
     <row r="106">
@@ -1588,10 +1588,10 @@
         <v>45355</v>
       </c>
       <c r="B106" t="n">
-        <v>73020.90625</v>
+        <v>73020.8984375</v>
       </c>
       <c r="C106" t="n">
-        <v>60882.484375</v>
+        <v>60882.48828125</v>
       </c>
     </row>
     <row r="107">
@@ -1599,7 +1599,7 @@
         <v>45356</v>
       </c>
       <c r="B107" t="n">
-        <v>72562.046875</v>
+        <v>72562.0546875</v>
       </c>
       <c r="C107" t="n">
         <v>61728.078125</v>
@@ -1613,7 +1613,7 @@
         <v>71513.28125</v>
       </c>
       <c r="C108" t="n">
-        <v>60713.375</v>
+        <v>60713.3671875</v>
       </c>
     </row>
     <row r="109">
@@ -1621,10 +1621,10 @@
         <v>45358</v>
       </c>
       <c r="B109" t="n">
-        <v>72955.3515625</v>
+        <v>72955.34375</v>
       </c>
       <c r="C109" t="n">
-        <v>60882.484375</v>
+        <v>60882.48828125</v>
       </c>
     </row>
     <row r="110">
@@ -1635,7 +1635,7 @@
         <v>72103.2109375</v>
       </c>
       <c r="C110" t="n">
-        <v>59191.30078125</v>
+        <v>59191.3046875</v>
       </c>
     </row>
     <row r="111">
@@ -1657,7 +1657,7 @@
         <v>73348.6328125</v>
       </c>
       <c r="C112" t="n">
-        <v>59191.30078125</v>
+        <v>59191.3046875</v>
       </c>
     </row>
     <row r="113">
@@ -1665,10 +1665,10 @@
         <v>45364</v>
       </c>
       <c r="B113" t="n">
-        <v>76691.6015625</v>
+        <v>76691.59375</v>
       </c>
       <c r="C113" t="n">
-        <v>59867.76953125</v>
+        <v>59867.77734375</v>
       </c>
     </row>
     <row r="114">
@@ -1676,10 +1676,10 @@
         <v>45365</v>
       </c>
       <c r="B114" t="n">
-        <v>76691.6015625</v>
+        <v>76691.59375</v>
       </c>
       <c r="C114" t="n">
-        <v>59614.10546875</v>
+        <v>59614.09765625</v>
       </c>
     </row>
     <row r="115">
@@ -1698,7 +1698,7 @@
         <v>45369</v>
       </c>
       <c r="B116" t="n">
-        <v>74069.671875</v>
+        <v>74069.6640625</v>
       </c>
       <c r="C116" t="n">
         <v>58158.0078125</v>
@@ -1720,7 +1720,7 @@
         <v>45371</v>
       </c>
       <c r="B118" t="n">
-        <v>75052.890625</v>
+        <v>75052.8984375</v>
       </c>
       <c r="C118" t="n">
         <v>58243.66015625</v>
@@ -1734,7 +1734,7 @@
         <v>76167.2109375</v>
       </c>
       <c r="C119" t="n">
-        <v>58586.2734375</v>
+        <v>58586.26953125</v>
       </c>
     </row>
     <row r="120">
@@ -1764,7 +1764,7 @@
         <v>45377</v>
       </c>
       <c r="B122" t="n">
-        <v>75380.640625</v>
+        <v>75380.6328125</v>
       </c>
       <c r="C122" t="n">
         <v>57986.703125</v>
@@ -1786,7 +1786,7 @@
         <v>45379</v>
       </c>
       <c r="B124" t="n">
-        <v>76757.140625</v>
+        <v>76757.15625</v>
       </c>
       <c r="C124" t="n">
         <v>57986.703125</v>
@@ -1808,7 +1808,7 @@
         <v>45383</v>
       </c>
       <c r="B126" t="n">
-        <v>76560.515625</v>
+        <v>76560.5</v>
       </c>
       <c r="C126" t="n">
         <v>57387.13671875</v>
@@ -1819,7 +1819,7 @@
         <v>45384</v>
       </c>
       <c r="B127" t="n">
-        <v>76691.6015625</v>
+        <v>76691.59375</v>
       </c>
       <c r="C127" t="n">
         <v>57644.09375</v>
@@ -1830,7 +1830,7 @@
         <v>45385</v>
       </c>
       <c r="B128" t="n">
-        <v>75446.1875</v>
+        <v>75446.1953125</v>
       </c>
       <c r="C128" t="n">
         <v>57130.1796875</v>
@@ -1863,7 +1863,7 @@
         <v>45390</v>
       </c>
       <c r="B131" t="n">
-        <v>73807.4765625</v>
+        <v>73807.46875</v>
       </c>
       <c r="C131" t="n">
         <v>57387.13671875</v>
@@ -1874,7 +1874,7 @@
         <v>45391</v>
       </c>
       <c r="B132" t="n">
-        <v>74069.671875</v>
+        <v>74069.6640625</v>
       </c>
       <c r="C132" t="n">
         <v>57387.13671875</v>
@@ -1885,7 +1885,7 @@
         <v>45392</v>
       </c>
       <c r="B133" t="n">
-        <v>74594.0546875</v>
+        <v>74594.0625</v>
       </c>
       <c r="C133" t="n">
         <v>57215.828125</v>
@@ -1899,7 +1899,7 @@
         <v>75315.0859375</v>
       </c>
       <c r="C134" t="n">
-        <v>57044.53125</v>
+        <v>57044.52734375</v>
       </c>
     </row>
     <row r="135">
@@ -1907,7 +1907,7 @@
         <v>45394</v>
       </c>
       <c r="B135" t="n">
-        <v>75708.3828125</v>
+        <v>75708.375</v>
       </c>
       <c r="C135" t="n">
         <v>57130.1796875</v>
@@ -1918,10 +1918,10 @@
         <v>45397</v>
       </c>
       <c r="B136" t="n">
-        <v>73151.9921875</v>
+        <v>73151.984375</v>
       </c>
       <c r="C136" t="n">
-        <v>55588.43359375</v>
+        <v>55588.4375</v>
       </c>
     </row>
     <row r="137">
@@ -1929,7 +1929,7 @@
         <v>45398</v>
       </c>
       <c r="B137" t="n">
-        <v>74069.671875</v>
+        <v>74069.6640625</v>
       </c>
       <c r="C137" t="n">
         <v>54817.5625</v>
@@ -1940,7 +1940,7 @@
         <v>45399</v>
       </c>
       <c r="B138" t="n">
-        <v>73283.078125</v>
+        <v>73283.0859375</v>
       </c>
       <c r="C138" t="n">
         <v>54988.8671875</v>
@@ -1951,7 +1951,7 @@
         <v>45401</v>
       </c>
       <c r="B139" t="n">
-        <v>71447.7421875</v>
+        <v>71447.7265625</v>
       </c>
       <c r="C139" t="n">
         <v>54988.8671875</v>
@@ -1962,7 +1962,7 @@
         <v>45404</v>
       </c>
       <c r="B140" t="n">
-        <v>72299.8671875</v>
+        <v>72299.8515625</v>
       </c>
       <c r="C140" t="n">
         <v>54817.5625</v>
@@ -1976,7 +1976,7 @@
         <v>73610.8203125</v>
       </c>
       <c r="C141" t="n">
-        <v>54389.296875</v>
+        <v>54389.30078125</v>
       </c>
     </row>
     <row r="142">
@@ -1984,7 +1984,7 @@
         <v>45406</v>
       </c>
       <c r="B142" t="n">
-        <v>78723.59375</v>
+        <v>78723.6015625</v>
       </c>
       <c r="C142" t="n">
         <v>54817.5625</v>
@@ -1995,7 +1995,7 @@
         <v>45407</v>
       </c>
       <c r="B143" t="n">
-        <v>80755.6171875</v>
+        <v>80755.609375</v>
       </c>
       <c r="C143" t="n">
         <v>55417.12890625</v>
@@ -2006,10 +2006,10 @@
         <v>45408</v>
       </c>
       <c r="B144" t="n">
-        <v>80755.6171875</v>
+        <v>80755.609375</v>
       </c>
       <c r="C144" t="n">
-        <v>55674.08984375</v>
+        <v>55674.0859375</v>
       </c>
     </row>
     <row r="145">
@@ -2017,10 +2017,10 @@
         <v>45414</v>
       </c>
       <c r="B145" t="n">
-        <v>83443.078125</v>
+        <v>83443.0859375</v>
       </c>
       <c r="C145" t="n">
-        <v>56016.69921875</v>
+        <v>56016.6953125</v>
       </c>
     </row>
     <row r="146">
@@ -2028,10 +2028,10 @@
         <v>45415</v>
       </c>
       <c r="B146" t="n">
-        <v>82525.4140625</v>
+        <v>82525.421875</v>
       </c>
       <c r="C146" t="n">
-        <v>56188.00390625</v>
+        <v>56188</v>
       </c>
     </row>
     <row r="147">
@@ -2039,7 +2039,7 @@
         <v>45418</v>
       </c>
       <c r="B147" t="n">
-        <v>83639.734375</v>
+        <v>83639.7265625</v>
       </c>
       <c r="C147" t="n">
         <v>56359.30859375</v>
@@ -2072,10 +2072,10 @@
         <v>45421</v>
       </c>
       <c r="B150" t="n">
-        <v>85409.53125</v>
+        <v>85409.5390625</v>
       </c>
       <c r="C150" t="n">
-        <v>57044.53125</v>
+        <v>57044.52734375</v>
       </c>
     </row>
     <row r="151">
@@ -2086,7 +2086,7 @@
         <v>85868.375</v>
       </c>
       <c r="C151" t="n">
-        <v>56958.875</v>
+        <v>56958.87109375</v>
       </c>
     </row>
     <row r="152">
@@ -2105,10 +2105,10 @@
         <v>45426</v>
       </c>
       <c r="B153" t="n">
-        <v>85540.6328125</v>
+        <v>85540.625</v>
       </c>
       <c r="C153" t="n">
-        <v>56958.875</v>
+        <v>56958.87109375</v>
       </c>
     </row>
     <row r="154">
@@ -2130,7 +2130,7 @@
         <v>88752.5078125</v>
       </c>
       <c r="C155" t="n">
-        <v>57558.44140625</v>
+        <v>57558.4453125</v>
       </c>
     </row>
     <row r="156">
@@ -2152,7 +2152,7 @@
         <v>87179.34375</v>
       </c>
       <c r="C157" t="n">
-        <v>56873.2265625</v>
+        <v>56873.22265625</v>
       </c>
     </row>
     <row r="158">
@@ -2163,7 +2163,7 @@
         <v>89145.796875</v>
       </c>
       <c r="C158" t="n">
-        <v>56701.9140625</v>
+        <v>56701.921875</v>
       </c>
     </row>
     <row r="159">
@@ -2171,7 +2171,7 @@
         <v>45434</v>
       </c>
       <c r="B159" t="n">
-        <v>90456.75</v>
+        <v>90456.7578125</v>
       </c>
       <c r="C159" t="n">
         <v>56359.30859375</v>
@@ -2226,10 +2226,10 @@
         <v>45441</v>
       </c>
       <c r="B164" t="n">
-        <v>88949.1484375</v>
+        <v>88949.15625</v>
       </c>
       <c r="C164" t="n">
-        <v>56787.56640625</v>
+        <v>56787.5703125</v>
       </c>
     </row>
     <row r="165">
@@ -2237,10 +2237,10 @@
         <v>45442</v>
       </c>
       <c r="B165" t="n">
-        <v>88490.3125</v>
+        <v>88490.3203125</v>
       </c>
       <c r="C165" t="n">
-        <v>56273.65625</v>
+        <v>56273.65234375</v>
       </c>
     </row>
     <row r="166">
@@ -2251,7 +2251,7 @@
         <v>88228.1171875</v>
       </c>
       <c r="C166" t="n">
-        <v>56016.69921875</v>
+        <v>56016.6953125</v>
       </c>
     </row>
     <row r="167">
@@ -2262,7 +2262,7 @@
         <v>88228.1171875</v>
       </c>
       <c r="C167" t="n">
-        <v>56016.69921875</v>
+        <v>56016.6953125</v>
       </c>
     </row>
     <row r="168">
@@ -2295,7 +2295,7 @@
         <v>91505.5390625</v>
       </c>
       <c r="C170" t="n">
-        <v>57558.44140625</v>
+        <v>57558.4453125</v>
       </c>
     </row>
     <row r="171">
@@ -2317,7 +2317,7 @@
         <v>94389.65625</v>
       </c>
       <c r="C172" t="n">
-        <v>57558.44140625</v>
+        <v>57558.4453125</v>
       </c>
     </row>
     <row r="173">
@@ -2325,10 +2325,10 @@
         <v>45454</v>
       </c>
       <c r="B173" t="n">
-        <v>96028.3828125</v>
+        <v>96028.375</v>
       </c>
       <c r="C173" t="n">
-        <v>56958.875</v>
+        <v>56958.87109375</v>
       </c>
     </row>
     <row r="174">
@@ -2347,10 +2347,10 @@
         <v>45456</v>
       </c>
       <c r="B175" t="n">
-        <v>98770.15625</v>
+        <v>98770.1484375</v>
       </c>
       <c r="C175" t="n">
-        <v>57301.48828125</v>
+        <v>57301.484375</v>
       </c>
     </row>
     <row r="176">
@@ -2358,10 +2358,10 @@
         <v>45457</v>
       </c>
       <c r="B176" t="n">
-        <v>99529.9296875</v>
+        <v>99529.921875</v>
       </c>
       <c r="C176" t="n">
-        <v>56701.9140625</v>
+        <v>56701.921875</v>
       </c>
     </row>
     <row r="177">
@@ -2369,7 +2369,7 @@
         <v>45460</v>
       </c>
       <c r="B177" t="n">
-        <v>97858.421875</v>
+        <v>97858.4296875</v>
       </c>
       <c r="C177" t="n">
         <v>56530.61328125</v>
@@ -2380,10 +2380,10 @@
         <v>45461</v>
       </c>
       <c r="B178" t="n">
-        <v>97250.6171875</v>
+        <v>97250.609375</v>
       </c>
       <c r="C178" t="n">
-        <v>56444.9609375</v>
+        <v>56444.95703125</v>
       </c>
     </row>
     <row r="179">
@@ -2413,7 +2413,7 @@
         <v>45464</v>
       </c>
       <c r="B181" t="n">
-        <v>103404.7578125</v>
+        <v>103404.75</v>
       </c>
       <c r="C181" t="n">
         <v>56530.61328125</v>
@@ -2424,10 +2424,10 @@
         <v>45467</v>
       </c>
       <c r="B182" t="n">
-        <v>100365.6640625</v>
+        <v>100365.671875</v>
       </c>
       <c r="C182" t="n">
-        <v>56102.35546875</v>
+        <v>56102.3515625</v>
       </c>
     </row>
     <row r="183">
@@ -2435,10 +2435,10 @@
         <v>45468</v>
       </c>
       <c r="B183" t="n">
-        <v>98770.15625</v>
+        <v>98770.1484375</v>
       </c>
       <c r="C183" t="n">
-        <v>56102.35546875</v>
+        <v>56102.3515625</v>
       </c>
     </row>
     <row r="184">
@@ -2471,7 +2471,7 @@
         <v>99150.03125</v>
       </c>
       <c r="C186" t="n">
-        <v>56102.35546875</v>
+        <v>56102.3515625</v>
       </c>
     </row>
     <row r="187">
@@ -2490,10 +2490,10 @@
         <v>45475</v>
       </c>
       <c r="B188" t="n">
-        <v>97250.6171875</v>
+        <v>97250.609375</v>
       </c>
       <c r="C188" t="n">
-        <v>56701.9140625</v>
+        <v>56701.921875</v>
       </c>
     </row>
     <row r="189">
@@ -2501,10 +2501,10 @@
         <v>45476</v>
       </c>
       <c r="B189" t="n">
-        <v>99529.9296875</v>
+        <v>99529.921875</v>
       </c>
       <c r="C189" t="n">
-        <v>56701.9140625</v>
+        <v>56701.921875</v>
       </c>
     </row>
     <row r="190">
@@ -2512,10 +2512,10 @@
         <v>45477</v>
       </c>
       <c r="B190" t="n">
-        <v>103176.8203125</v>
+        <v>103176.828125</v>
       </c>
       <c r="C190" t="n">
-        <v>56873.2265625</v>
+        <v>56873.22265625</v>
       </c>
     </row>
     <row r="191">
@@ -2526,7 +2526,7 @@
         <v>105380.15625</v>
       </c>
       <c r="C191" t="n">
-        <v>57558.44140625</v>
+        <v>57558.4453125</v>
       </c>
     </row>
     <row r="192">
@@ -2556,7 +2556,7 @@
         <v>45483</v>
       </c>
       <c r="B194" t="n">
-        <v>101809.2265625</v>
+        <v>101809.234375</v>
       </c>
       <c r="C194" t="n">
         <v>57215.828125</v>
@@ -2570,7 +2570,7 @@
         <v>101049.46875</v>
       </c>
       <c r="C195" t="n">
-        <v>56787.56640625</v>
+        <v>56787.5703125</v>
       </c>
     </row>
     <row r="196">
@@ -2581,7 +2581,7 @@
         <v>101657.28125</v>
       </c>
       <c r="C196" t="n">
-        <v>56787.56640625</v>
+        <v>56787.5703125</v>
       </c>
     </row>
     <row r="197">
@@ -2589,10 +2589,10 @@
         <v>45488</v>
       </c>
       <c r="B197" t="n">
-        <v>100821.53125</v>
+        <v>100821.5390625</v>
       </c>
       <c r="C197" t="n">
-        <v>56701.9140625</v>
+        <v>56701.921875</v>
       </c>
     </row>
     <row r="198">
@@ -2600,7 +2600,7 @@
         <v>45489</v>
       </c>
       <c r="B198" t="n">
-        <v>101809.2265625</v>
+        <v>101809.234375</v>
       </c>
       <c r="C198" t="n">
         <v>56616.265625</v>
@@ -2614,7 +2614,7 @@
         <v>100213.71875</v>
       </c>
       <c r="C199" t="n">
-        <v>56273.65625</v>
+        <v>56273.65234375</v>
       </c>
     </row>
     <row r="200">
@@ -2622,10 +2622,10 @@
         <v>45491</v>
       </c>
       <c r="B200" t="n">
-        <v>97174.6328125</v>
+        <v>97174.640625</v>
       </c>
       <c r="C200" t="n">
-        <v>56444.9609375</v>
+        <v>56444.95703125</v>
       </c>
     </row>
     <row r="201">
@@ -2644,10 +2644,10 @@
         <v>45495</v>
       </c>
       <c r="B202" t="n">
-        <v>94287.5078125</v>
+        <v>94287.5</v>
       </c>
       <c r="C202" t="n">
-        <v>56016.69921875</v>
+        <v>56016.6953125</v>
       </c>
     </row>
     <row r="203">
@@ -2658,7 +2658,7 @@
         <v>95351.1875</v>
       </c>
       <c r="C203" t="n">
-        <v>56444.9609375</v>
+        <v>56444.95703125</v>
       </c>
     </row>
     <row r="204">
@@ -2669,7 +2669,7 @@
         <v>95731.0625</v>
       </c>
       <c r="C204" t="n">
-        <v>56188.00390625</v>
+        <v>56188</v>
       </c>
     </row>
     <row r="205">
@@ -2677,10 +2677,10 @@
         <v>45498</v>
       </c>
       <c r="B205" t="n">
-        <v>94971.296875</v>
+        <v>94971.2890625</v>
       </c>
       <c r="C205" t="n">
-        <v>56188.00390625</v>
+        <v>56188</v>
       </c>
     </row>
     <row r="206">
@@ -2688,10 +2688,10 @@
         <v>45502</v>
       </c>
       <c r="B206" t="n">
-        <v>98010.3828125</v>
+        <v>98010.375</v>
       </c>
       <c r="C206" t="n">
-        <v>57558.44140625</v>
+        <v>57558.4453125</v>
       </c>
     </row>
     <row r="207">
@@ -2699,7 +2699,7 @@
         <v>45503</v>
       </c>
       <c r="B207" t="n">
-        <v>97250.6171875</v>
+        <v>97250.609375</v>
       </c>
       <c r="C207" t="n">
         <v>57986.703125</v>
@@ -2724,7 +2724,7 @@
         <v>94819.3515625</v>
       </c>
       <c r="C209" t="n">
-        <v>60213.66796875</v>
+        <v>60213.671875</v>
       </c>
     </row>
     <row r="210">
@@ -2732,10 +2732,10 @@
         <v>45506</v>
       </c>
       <c r="B210" t="n">
-        <v>93603.7109375</v>
+        <v>93603.71875</v>
       </c>
       <c r="C210" t="n">
-        <v>61241.49609375</v>
+        <v>61241.5</v>
       </c>
     </row>
     <row r="211">
@@ -2757,7 +2757,7 @@
         <v>91780.265625</v>
       </c>
       <c r="C212" t="n">
-        <v>62269.328125</v>
+        <v>62269.32421875</v>
       </c>
     </row>
     <row r="213">
@@ -2768,7 +2768,7 @@
         <v>92691.9921875</v>
       </c>
       <c r="C213" t="n">
-        <v>63211.5</v>
+        <v>63211.5078125</v>
       </c>
     </row>
     <row r="214">
@@ -2779,7 +2779,7 @@
         <v>92236.125</v>
       </c>
       <c r="C214" t="n">
-        <v>62269.328125</v>
+        <v>62269.32421875</v>
       </c>
     </row>
     <row r="215">
@@ -2787,10 +2787,10 @@
         <v>45513</v>
       </c>
       <c r="B215" t="n">
-        <v>96414.8515625</v>
+        <v>96414.8671875</v>
       </c>
       <c r="C215" t="n">
-        <v>62783.23828125</v>
+        <v>62783.234375</v>
       </c>
     </row>
     <row r="216">
@@ -2798,7 +2798,7 @@
         <v>45516</v>
       </c>
       <c r="B216" t="n">
-        <v>98770.15625</v>
+        <v>98770.1484375</v>
       </c>
       <c r="C216" t="n">
         <v>62526.28515625</v>
@@ -2812,7 +2812,7 @@
         <v>98542.21875</v>
       </c>
       <c r="C217" t="n">
-        <v>63211.5</v>
+        <v>63211.5078125</v>
       </c>
     </row>
     <row r="218">
@@ -2823,7 +2823,7 @@
         <v>98390.265625</v>
       </c>
       <c r="C218" t="n">
-        <v>63382.80859375</v>
+        <v>63382.8046875</v>
       </c>
     </row>
     <row r="219">
@@ -2831,10 +2831,10 @@
         <v>45519</v>
       </c>
       <c r="B219" t="n">
-        <v>97782.453125</v>
+        <v>97782.4453125</v>
       </c>
       <c r="C219" t="n">
-        <v>63211.5</v>
+        <v>63211.5078125</v>
       </c>
     </row>
     <row r="220">
@@ -2842,10 +2842,10 @@
         <v>45520</v>
       </c>
       <c r="B220" t="n">
-        <v>99226.015625</v>
+        <v>99226.0234375</v>
       </c>
       <c r="C220" t="n">
-        <v>63211.5</v>
+        <v>63211.5078125</v>
       </c>
     </row>
     <row r="221">
@@ -2856,7 +2856,7 @@
         <v>99150.03125</v>
       </c>
       <c r="C221" t="n">
-        <v>65095.85546875</v>
+        <v>65095.859375</v>
       </c>
     </row>
     <row r="222">
@@ -2867,7 +2867,7 @@
         <v>99909.8046875</v>
       </c>
       <c r="C222" t="n">
-        <v>64753.24609375</v>
+        <v>64753.2421875</v>
       </c>
     </row>
     <row r="223">
@@ -2878,7 +2878,7 @@
         <v>101429.34375</v>
       </c>
       <c r="C223" t="n">
-        <v>64496.28515625</v>
+        <v>64496.2890625</v>
       </c>
     </row>
     <row r="224">
@@ -2889,7 +2889,7 @@
         <v>101657.28125</v>
       </c>
       <c r="C224" t="n">
-        <v>63554.1171875</v>
+        <v>63554.11328125</v>
       </c>
     </row>
     <row r="225">
@@ -2900,7 +2900,7 @@
         <v>101125.4375</v>
       </c>
       <c r="C225" t="n">
-        <v>64153.671875</v>
+        <v>64153.6875</v>
       </c>
     </row>
     <row r="226">
@@ -2911,7 +2911,7 @@
         <v>99909.8046875</v>
       </c>
       <c r="C226" t="n">
-        <v>62868.89453125</v>
+        <v>62868.890625</v>
       </c>
     </row>
     <row r="227">
@@ -2922,7 +2922,7 @@
         <v>101277.390625</v>
       </c>
       <c r="C227" t="n">
-        <v>63297.14453125</v>
+        <v>63297.1484375</v>
       </c>
     </row>
     <row r="228">
@@ -2944,7 +2944,7 @@
         <v>102417.046875</v>
       </c>
       <c r="C229" t="n">
-        <v>63297.14453125</v>
+        <v>63297.1484375</v>
       </c>
     </row>
     <row r="230">
@@ -2955,7 +2955,7 @@
         <v>101049.46875</v>
       </c>
       <c r="C230" t="n">
-        <v>63639.76171875</v>
+        <v>63639.76953125</v>
       </c>
     </row>
     <row r="231">
@@ -2963,7 +2963,7 @@
         <v>45540</v>
       </c>
       <c r="B231" t="n">
-        <v>99226.015625</v>
+        <v>99226.0234375</v>
       </c>
       <c r="C231" t="n">
         <v>63982.375</v>
@@ -2974,10 +2974,10 @@
         <v>45541</v>
       </c>
       <c r="B232" t="n">
-        <v>100365.6640625</v>
+        <v>100365.671875</v>
       </c>
       <c r="C232" t="n">
-        <v>64581.9375</v>
+        <v>64581.94921875</v>
       </c>
     </row>
     <row r="233">
@@ -2988,7 +2988,7 @@
         <v>99757.8515625</v>
       </c>
       <c r="C233" t="n">
-        <v>64068.02734375</v>
+        <v>64068.03125</v>
       </c>
     </row>
     <row r="234">
@@ -2996,10 +2996,10 @@
         <v>45545</v>
       </c>
       <c r="B234" t="n">
-        <v>98770.15625</v>
+        <v>98770.1484375</v>
       </c>
       <c r="C234" t="n">
-        <v>64153.671875</v>
+        <v>64153.6875</v>
       </c>
     </row>
     <row r="235">
@@ -3007,10 +3007,10 @@
         <v>45546</v>
       </c>
       <c r="B235" t="n">
-        <v>99226.015625</v>
+        <v>99226.0234375</v>
       </c>
       <c r="C235" t="n">
-        <v>63896.7265625</v>
+        <v>63896.71484375</v>
       </c>
     </row>
     <row r="236">
@@ -3032,7 +3032,7 @@
         <v>101049.46875</v>
       </c>
       <c r="C237" t="n">
-        <v>62440.6328125</v>
+        <v>62440.62890625</v>
       </c>
     </row>
     <row r="238">
@@ -3043,7 +3043,7 @@
         <v>99605.8984375</v>
       </c>
       <c r="C238" t="n">
-        <v>61584.1015625</v>
+        <v>61584.10546875</v>
       </c>
     </row>
     <row r="239">
@@ -3054,7 +3054,7 @@
         <v>100973.4921875</v>
       </c>
       <c r="C239" t="n">
-        <v>62868.89453125</v>
+        <v>62868.890625</v>
       </c>
     </row>
     <row r="240">
@@ -3065,7 +3065,7 @@
         <v>102265.09375</v>
       </c>
       <c r="C240" t="n">
-        <v>62783.23828125</v>
+        <v>62783.234375</v>
       </c>
     </row>
     <row r="241">
@@ -3073,10 +3073,10 @@
         <v>45554</v>
       </c>
       <c r="B241" t="n">
-        <v>102720.96875</v>
+        <v>102720.9609375</v>
       </c>
       <c r="C241" t="n">
-        <v>62783.23828125</v>
+        <v>62783.234375</v>
       </c>
     </row>
     <row r="242">
@@ -3087,7 +3087,7 @@
         <v>102796.9375</v>
       </c>
       <c r="C242" t="n">
-        <v>62269.328125</v>
+        <v>62269.32421875</v>
       </c>
     </row>
     <row r="243">
@@ -3095,10 +3095,10 @@
         <v>45558</v>
       </c>
       <c r="B243" t="n">
-        <v>101809.2265625</v>
+        <v>101809.234375</v>
       </c>
       <c r="C243" t="n">
-        <v>62440.6328125</v>
+        <v>62440.62890625</v>
       </c>
     </row>
     <row r="244">
@@ -3109,7 +3109,7 @@
         <v>102189.125</v>
       </c>
       <c r="C244" t="n">
-        <v>62307.68359375</v>
+        <v>62307.6875</v>
       </c>
     </row>
     <row r="245">
@@ -3128,7 +3128,7 @@
         <v>45561</v>
       </c>
       <c r="B246" t="n">
-        <v>102037.1640625</v>
+        <v>102037.171875</v>
       </c>
       <c r="C246" t="n">
         <v>62662.20703125</v>
@@ -3142,7 +3142,7 @@
         <v>101961.1796875</v>
       </c>
       <c r="C247" t="n">
-        <v>62928.1015625</v>
+        <v>62928.09765625</v>
       </c>
     </row>
     <row r="248">
@@ -3153,7 +3153,7 @@
         <v>102189.125</v>
       </c>
       <c r="C248" t="n">
-        <v>62130.421875</v>
+        <v>62130.42578125</v>
       </c>
     </row>
     <row r="249">
@@ -3161,10 +3161,10 @@
         <v>45566</v>
       </c>
       <c r="B249" t="n">
-        <v>103252.796875</v>
+        <v>103252.7890625</v>
       </c>
       <c r="C249" t="n">
-        <v>62130.421875</v>
+        <v>62130.42578125</v>
       </c>
     </row>
     <row r="250">
@@ -3175,7 +3175,7 @@
         <v>102872.9140625</v>
       </c>
       <c r="C250" t="n">
-        <v>62130.421875</v>
+        <v>62130.42578125</v>
       </c>
     </row>
     <row r="251">
@@ -3183,10 +3183,10 @@
         <v>45568</v>
       </c>
       <c r="B251" t="n">
-        <v>101809.2265625</v>
+        <v>101809.234375</v>
       </c>
       <c r="C251" t="n">
-        <v>62307.68359375</v>
+        <v>62307.6875</v>
       </c>
     </row>
     <row r="252">
@@ -3194,7 +3194,7 @@
         <v>45569</v>
       </c>
       <c r="B252" t="n">
-        <v>101885.2109375</v>
+        <v>101885.21875</v>
       </c>
       <c r="C252" t="n">
         <v>60712.3203125</v>
@@ -3205,10 +3205,10 @@
         <v>45572</v>
       </c>
       <c r="B253" t="n">
-        <v>101885.2109375</v>
+        <v>101885.21875</v>
       </c>
       <c r="C253" t="n">
-        <v>59471.484375</v>
+        <v>59471.48828125</v>
       </c>
     </row>
     <row r="254">
@@ -3219,7 +3219,7 @@
         <v>102872.9140625</v>
       </c>
       <c r="C254" t="n">
-        <v>60091.90625</v>
+        <v>60091.90234375</v>
       </c>
     </row>
     <row r="255">
@@ -3230,7 +3230,7 @@
         <v>106063.953125</v>
       </c>
       <c r="C255" t="n">
-        <v>60003.26953125</v>
+        <v>60003.27734375</v>
       </c>
     </row>
     <row r="256">
@@ -3238,10 +3238,10 @@
         <v>45579</v>
       </c>
       <c r="B256" t="n">
-        <v>104544.40625</v>
+        <v>104544.4140625</v>
       </c>
       <c r="C256" t="n">
-        <v>59560.11328125</v>
+        <v>59560.1171875</v>
       </c>
     </row>
     <row r="257">
@@ -3249,10 +3249,10 @@
         <v>45580</v>
       </c>
       <c r="B257" t="n">
-        <v>104088.546875</v>
+        <v>104088.5546875</v>
       </c>
       <c r="C257" t="n">
-        <v>59205.59375</v>
+        <v>59205.58984375</v>
       </c>
     </row>
     <row r="258">
@@ -3271,7 +3271,7 @@
         <v>45582</v>
       </c>
       <c r="B259" t="n">
-        <v>104088.546875</v>
+        <v>104088.5546875</v>
       </c>
       <c r="C259" t="n">
         <v>59914.640625</v>
@@ -3282,10 +3282,10 @@
         <v>45583</v>
       </c>
       <c r="B260" t="n">
-        <v>104088.546875</v>
+        <v>104088.5546875</v>
       </c>
       <c r="C260" t="n">
-        <v>59737.3828125</v>
+        <v>59737.37890625</v>
       </c>
     </row>
     <row r="261">
@@ -3326,7 +3326,7 @@
         <v>45589</v>
       </c>
       <c r="B264" t="n">
-        <v>102037.1640625</v>
+        <v>102037.171875</v>
       </c>
       <c r="C264" t="n">
         <v>60623.69140625</v>
@@ -3337,7 +3337,7 @@
         <v>45590</v>
       </c>
       <c r="B265" t="n">
-        <v>101809.2265625</v>
+        <v>101809.234375</v>
       </c>
       <c r="C265" t="n">
         <v>60269.1640625</v>
@@ -3351,7 +3351,7 @@
         <v>102493.0234375</v>
       </c>
       <c r="C266" t="n">
-        <v>59560.11328125</v>
+        <v>59560.1171875</v>
       </c>
     </row>
     <row r="267">
@@ -3362,7 +3362,7 @@
         <v>102872.9140625</v>
       </c>
       <c r="C267" t="n">
-        <v>59382.85546875</v>
+        <v>59382.8515625</v>
       </c>
     </row>
     <row r="268">
@@ -3370,10 +3370,10 @@
         <v>45596</v>
       </c>
       <c r="B268" t="n">
-        <v>103252.796875</v>
+        <v>103252.7890625</v>
       </c>
       <c r="C268" t="n">
-        <v>58585.171875</v>
+        <v>58585.17578125</v>
       </c>
     </row>
     <row r="269">
@@ -3384,7 +3384,7 @@
         <v>102265.09375</v>
       </c>
       <c r="C269" t="n">
-        <v>58319.28515625</v>
+        <v>58319.28125</v>
       </c>
     </row>
     <row r="270">
@@ -3406,7 +3406,7 @@
         <v>102265.09375</v>
       </c>
       <c r="C271" t="n">
-        <v>58319.28515625</v>
+        <v>58319.28125</v>
       </c>
     </row>
     <row r="272">
@@ -3414,7 +3414,7 @@
         <v>45603</v>
       </c>
       <c r="B272" t="n">
-        <v>102644.984375</v>
+        <v>102644.9765625</v>
       </c>
       <c r="C272" t="n">
         <v>58407.9140625</v>
@@ -3439,7 +3439,7 @@
         <v>103936.5859375</v>
       </c>
       <c r="C274" t="n">
-        <v>57521.59765625</v>
+        <v>57521.6015625</v>
       </c>
     </row>
     <row r="275">
@@ -3458,7 +3458,7 @@
         <v>45610</v>
       </c>
       <c r="B276" t="n">
-        <v>103328.7734375</v>
+        <v>103328.78125</v>
       </c>
       <c r="C276" t="n">
         <v>57610.234375</v>
@@ -3480,7 +3480,7 @@
         <v>45614</v>
       </c>
       <c r="B278" t="n">
-        <v>101809.2265625</v>
+        <v>101809.234375</v>
       </c>
       <c r="C278" t="n">
         <v>56014.87109375</v>
@@ -3491,10 +3491,10 @@
         <v>45615</v>
       </c>
       <c r="B279" t="n">
-        <v>98770.15625</v>
+        <v>98770.1484375</v>
       </c>
       <c r="C279" t="n">
-        <v>55837.61328125</v>
+        <v>55837.609375</v>
       </c>
     </row>
     <row r="280">
@@ -3502,10 +3502,10 @@
         <v>45616</v>
       </c>
       <c r="B280" t="n">
-        <v>100593.59375</v>
+        <v>100593.6015625</v>
       </c>
       <c r="C280" t="n">
-        <v>56369.3984375</v>
+        <v>56369.39453125</v>
       </c>
     </row>
     <row r="281">
@@ -3527,7 +3527,7 @@
         <v>101733.265625</v>
       </c>
       <c r="C282" t="n">
-        <v>56989.8125</v>
+        <v>56989.81640625</v>
       </c>
     </row>
     <row r="283">
@@ -3538,7 +3538,7 @@
         <v>101733.265625</v>
       </c>
       <c r="C283" t="n">
-        <v>56989.8125</v>
+        <v>56989.81640625</v>
       </c>
     </row>
     <row r="284">
@@ -3546,7 +3546,7 @@
         <v>45622</v>
       </c>
       <c r="B284" t="n">
-        <v>102720.96875</v>
+        <v>102720.9609375</v>
       </c>
       <c r="C284" t="n">
         <v>57432.96875</v>
@@ -3560,7 +3560,7 @@
         <v>105532.1171875</v>
       </c>
       <c r="C285" t="n">
-        <v>57255.7109375</v>
+        <v>57255.703125</v>
       </c>
     </row>
     <row r="286">
@@ -3571,7 +3571,7 @@
         <v>105911.984375</v>
       </c>
       <c r="C286" t="n">
-        <v>57167.07421875</v>
+        <v>57167.078125</v>
       </c>
     </row>
     <row r="287">
@@ -3579,10 +3579,10 @@
         <v>45625</v>
       </c>
       <c r="B287" t="n">
-        <v>109634.875</v>
+        <v>109634.8671875</v>
       </c>
       <c r="C287" t="n">
-        <v>57255.7109375</v>
+        <v>57255.703125</v>
       </c>
     </row>
     <row r="288">
@@ -3593,7 +3593,7 @@
         <v>108793.2890625</v>
       </c>
       <c r="C288" t="n">
-        <v>57167.07421875</v>
+        <v>57167.078125</v>
       </c>
     </row>
     <row r="289">
@@ -3601,7 +3601,7 @@
         <v>45629</v>
       </c>
       <c r="B289" t="n">
-        <v>110935.5</v>
+        <v>110935.4921875</v>
       </c>
       <c r="C289" t="n">
         <v>56635.2890625</v>
@@ -3615,7 +3615,7 @@
         <v>109787.8828125</v>
       </c>
       <c r="C290" t="n">
-        <v>56103.5</v>
+        <v>56103.50390625</v>
       </c>
     </row>
     <row r="291">
@@ -3626,7 +3626,7 @@
         <v>113613.2421875</v>
       </c>
       <c r="C291" t="n">
-        <v>56989.8125</v>
+        <v>56989.81640625</v>
       </c>
     </row>
     <row r="292">
@@ -3645,7 +3645,7 @@
         <v>45636</v>
       </c>
       <c r="B293" t="n">
-        <v>114378.328125</v>
+        <v>114378.3203125</v>
       </c>
       <c r="C293" t="n">
         <v>56635.2890625</v>
@@ -3656,10 +3656,10 @@
         <v>45637</v>
       </c>
       <c r="B294" t="n">
-        <v>115143.390625</v>
+        <v>115143.3828125</v>
       </c>
       <c r="C294" t="n">
-        <v>56901.18359375</v>
+        <v>56901.1796875</v>
       </c>
     </row>
     <row r="295">
@@ -3670,7 +3670,7 @@
         <v>114913.8671875</v>
       </c>
       <c r="C295" t="n">
-        <v>57255.7109375</v>
+        <v>57255.703125</v>
       </c>
     </row>
     <row r="296">
@@ -3678,10 +3678,10 @@
         <v>45639</v>
       </c>
       <c r="B296" t="n">
-        <v>114378.328125</v>
+        <v>114378.3203125</v>
       </c>
       <c r="C296" t="n">
-        <v>56901.18359375</v>
+        <v>56901.1796875</v>
       </c>
     </row>
     <row r="297">
@@ -3689,7 +3689,7 @@
         <v>45642</v>
       </c>
       <c r="B297" t="n">
-        <v>114684.34375</v>
+        <v>114684.3515625</v>
       </c>
       <c r="C297" t="n">
         <v>57610.234375</v>
@@ -3700,7 +3700,7 @@
         <v>45644</v>
       </c>
       <c r="B298" t="n">
-        <v>113766.2578125</v>
+        <v>113766.25</v>
       </c>
       <c r="C298" t="n">
         <v>57344.33984375</v>
@@ -3722,7 +3722,7 @@
         <v>45646</v>
       </c>
       <c r="B300" t="n">
-        <v>114378.328125</v>
+        <v>114378.3203125</v>
       </c>
       <c r="C300" t="n">
         <v>57610.234375</v>
@@ -3733,7 +3733,7 @@
         <v>45649</v>
       </c>
       <c r="B301" t="n">
-        <v>114607.8359375</v>
+        <v>114607.828125</v>
       </c>
       <c r="C301" t="n">
         <v>57078.44140625</v>
@@ -3744,10 +3744,10 @@
         <v>45650</v>
       </c>
       <c r="B302" t="n">
-        <v>115066.8828125</v>
+        <v>115066.875</v>
       </c>
       <c r="C302" t="n">
-        <v>56989.8125</v>
+        <v>56989.81640625</v>
       </c>
     </row>
     <row r="303">
@@ -3755,7 +3755,7 @@
         <v>45651</v>
       </c>
       <c r="B303" t="n">
-        <v>115372.9140625</v>
+        <v>115372.90625</v>
       </c>
       <c r="C303" t="n">
         <v>57078.44140625</v>
@@ -3766,7 +3766,7 @@
         <v>45652</v>
       </c>
       <c r="B304" t="n">
-        <v>114607.8359375</v>
+        <v>114607.828125</v>
       </c>
       <c r="C304" t="n">
         <v>56989.12109375</v>
@@ -3788,10 +3788,10 @@
         <v>45656</v>
       </c>
       <c r="B306" t="n">
-        <v>115143.390625</v>
+        <v>115143.3828125</v>
       </c>
       <c r="C306" t="n">
-        <v>56542.49609375</v>
+        <v>56542.5</v>
       </c>
     </row>
     <row r="307">
@@ -3799,7 +3799,7 @@
         <v>45657</v>
       </c>
       <c r="B307" t="n">
-        <v>116673.5390625</v>
+        <v>116673.53125</v>
       </c>
       <c r="C307" t="n">
         <v>56631.8203125</v>
@@ -3810,7 +3810,7 @@
         <v>45659</v>
       </c>
       <c r="B308" t="n">
-        <v>116290.9921875</v>
+        <v>116291</v>
       </c>
       <c r="C308" t="n">
         <v>56363.84765625</v>
@@ -3821,7 +3821,7 @@
         <v>45660</v>
       </c>
       <c r="B309" t="n">
-        <v>113995.78125</v>
+        <v>113995.7890625</v>
       </c>
       <c r="C309" t="n">
         <v>56274.5234375</v>
@@ -3832,7 +3832,7 @@
         <v>45663</v>
       </c>
       <c r="B310" t="n">
-        <v>114225.296875</v>
+        <v>114225.3046875</v>
       </c>
       <c r="C310" t="n">
         <v>55827.90234375</v>
@@ -3854,7 +3854,7 @@
         <v>45665</v>
       </c>
       <c r="B312" t="n">
-        <v>113460.2265625</v>
+        <v>113460.234375</v>
       </c>
       <c r="C312" t="n">
         <v>55113.3046875</v>
@@ -3865,7 +3865,7 @@
         <v>45666</v>
       </c>
       <c r="B313" t="n">
-        <v>113842.7734375</v>
+        <v>113842.765625</v>
       </c>
       <c r="C313" t="n">
         <v>55202.6328125</v>
@@ -3890,7 +3890,7 @@
         <v>111012</v>
       </c>
       <c r="C315" t="n">
-        <v>55023.98046875</v>
+        <v>55023.984375</v>
       </c>
     </row>
     <row r="316">
@@ -3920,7 +3920,7 @@
         <v>45674</v>
       </c>
       <c r="B318" t="n">
-        <v>113995.78125</v>
+        <v>113995.7890625</v>
       </c>
       <c r="C318" t="n">
         <v>55381.28125</v>
@@ -3931,10 +3931,10 @@
         <v>45677</v>
       </c>
       <c r="B319" t="n">
-        <v>114760.8515625</v>
+        <v>114760.859375</v>
       </c>
       <c r="C319" t="n">
-        <v>55291.95703125</v>
+        <v>55291.953125</v>
       </c>
     </row>
     <row r="320">
@@ -3942,7 +3942,7 @@
         <v>45678</v>
       </c>
       <c r="B320" t="n">
-        <v>114684.34375</v>
+        <v>114684.3515625</v>
       </c>
       <c r="C320" t="n">
         <v>55202.6328125</v>
@@ -3956,7 +3956,7 @@
         <v>114531.3359375</v>
       </c>
       <c r="C321" t="n">
-        <v>55023.98046875</v>
+        <v>55023.984375</v>
       </c>
     </row>
     <row r="322">
@@ -4008,7 +4008,7 @@
         <v>45693</v>
       </c>
       <c r="B326" t="n">
-        <v>111930.0859375</v>
+        <v>111930.078125</v>
       </c>
       <c r="C326" t="n">
         <v>54934.65625</v>
@@ -4033,7 +4033,7 @@
         <v>111777.0703125</v>
       </c>
       <c r="C328" t="n">
-        <v>54309.3828125</v>
+        <v>54309.38671875</v>
       </c>
     </row>
     <row r="329">
@@ -4044,7 +4044,7 @@
         <v>108640.2734375</v>
       </c>
       <c r="C329" t="n">
-        <v>54130.73046875</v>
+        <v>54130.734375</v>
       </c>
     </row>
     <row r="330">
@@ -4055,7 +4055,7 @@
         <v>111241.515625</v>
       </c>
       <c r="C330" t="n">
-        <v>53952.08203125</v>
+        <v>53952.0859375</v>
       </c>
     </row>
     <row r="331">
@@ -4063,7 +4063,7 @@
         <v>45700</v>
       </c>
       <c r="B331" t="n">
-        <v>110935.5</v>
+        <v>110935.4921875</v>
       </c>
       <c r="C331" t="n">
         <v>54488.03515625</v>
@@ -4074,7 +4074,7 @@
         <v>45701</v>
       </c>
       <c r="B332" t="n">
-        <v>109481.8515625</v>
+        <v>109481.859375</v>
       </c>
       <c r="C332" t="n">
         <v>54220.0546875</v>
@@ -4085,7 +4085,7 @@
         <v>45702</v>
       </c>
       <c r="B333" t="n">
-        <v>110858.9765625</v>
+        <v>110858.984375</v>
       </c>
       <c r="C333" t="n">
         <v>53862.7578125</v>
@@ -4096,7 +4096,7 @@
         <v>45705</v>
       </c>
       <c r="B334" t="n">
-        <v>109864.390625</v>
+        <v>109864.3828125</v>
       </c>
       <c r="C334" t="n">
         <v>53594.78515625</v>
@@ -4121,7 +4121,7 @@
         <v>110170.421875</v>
       </c>
       <c r="C336" t="n">
-        <v>54309.3828125</v>
+        <v>54309.38671875</v>
       </c>
     </row>
     <row r="337">
@@ -4151,7 +4151,7 @@
         <v>45712</v>
       </c>
       <c r="B339" t="n">
-        <v>107492.6640625</v>
+        <v>107492.65625</v>
       </c>
       <c r="C339" t="n">
         <v>56989.12109375</v>
@@ -4173,7 +4173,7 @@
         <v>45714</v>
       </c>
       <c r="B341" t="n">
-        <v>108487.2578125</v>
+        <v>108487.265625</v>
       </c>
       <c r="C341" t="n">
         <v>56363.84765625</v>
@@ -4206,7 +4206,7 @@
         <v>45719</v>
       </c>
       <c r="B344" t="n">
-        <v>107492.6640625</v>
+        <v>107492.65625</v>
       </c>
       <c r="C344" t="n">
         <v>56453.171875</v>
@@ -4220,7 +4220,7 @@
         <v>107110.1328125</v>
       </c>
       <c r="C345" t="n">
-        <v>56721.14453125</v>
+        <v>56721.1484375</v>
       </c>
     </row>
     <row r="346">
@@ -4228,7 +4228,7 @@
         <v>45721</v>
       </c>
       <c r="B346" t="n">
-        <v>106421.5703125</v>
+        <v>106421.5625</v>
       </c>
       <c r="C346" t="n">
         <v>56006.55078125</v>
@@ -4250,7 +4250,7 @@
         <v>45723</v>
       </c>
       <c r="B348" t="n">
-        <v>108181.234375</v>
+        <v>108181.2265625</v>
       </c>
       <c r="C348" t="n">
         <v>56006.55078125</v>
@@ -4305,7 +4305,7 @@
         <v>45730</v>
       </c>
       <c r="B353" t="n">
-        <v>100530.5</v>
+        <v>100530.5078125</v>
       </c>
       <c r="C353" t="n">
         <v>55470.60546875</v>
@@ -4316,7 +4316,7 @@
         <v>45733</v>
       </c>
       <c r="B354" t="n">
-        <v>99459.40625</v>
+        <v>99459.3984375</v>
       </c>
       <c r="C354" t="n">
         <v>56274.5234375</v>
@@ -4327,7 +4327,7 @@
         <v>45734</v>
       </c>
       <c r="B355" t="n">
-        <v>99459.40625</v>
+        <v>99459.3984375</v>
       </c>
       <c r="C355" t="n">
         <v>55827.90234375</v>
@@ -4349,7 +4349,7 @@
         <v>45736</v>
       </c>
       <c r="B357" t="n">
-        <v>95634.0390625</v>
+        <v>95634.046875</v>
       </c>
       <c r="C357" t="n">
         <v>55202.6328125</v>
@@ -4360,7 +4360,7 @@
         <v>45737</v>
       </c>
       <c r="B358" t="n">
-        <v>97929.265625</v>
+        <v>97929.2578125</v>
       </c>
       <c r="C358" t="n">
         <v>54756.0078125</v>
@@ -4371,7 +4371,7 @@
         <v>45740</v>
       </c>
       <c r="B359" t="n">
-        <v>98694.3359375</v>
+        <v>98694.328125</v>
       </c>
       <c r="C359" t="n">
         <v>54845.33203125</v>
@@ -4393,7 +4393,7 @@
         <v>45742</v>
       </c>
       <c r="B361" t="n">
-        <v>94103.8984375</v>
+        <v>94103.90625</v>
       </c>
       <c r="C361" t="n">
         <v>54666.68359375</v>
@@ -4415,7 +4415,7 @@
         <v>45744</v>
       </c>
       <c r="B363" t="n">
-        <v>94868.9765625</v>
+        <v>94868.984375</v>
       </c>
       <c r="C363" t="n">
         <v>53862.7578125</v>
@@ -4429,7 +4429,7 @@
         <v>92573.75</v>
       </c>
       <c r="C364" t="n">
-        <v>54130.73046875</v>
+        <v>54130.734375</v>
       </c>
     </row>
     <row r="365">
@@ -4440,7 +4440,7 @@
         <v>92191.21875</v>
       </c>
       <c r="C365" t="n">
-        <v>54309.3828125</v>
+        <v>54309.38671875</v>
       </c>
     </row>
     <row r="366">
@@ -4473,7 +4473,7 @@
         <v>86453.1796875</v>
       </c>
       <c r="C368" t="n">
-        <v>52254.91796875</v>
+        <v>52254.9140625</v>
       </c>
     </row>
     <row r="369">
@@ -4484,7 +4484,7 @@
         <v>80409.109375</v>
       </c>
       <c r="C369" t="n">
-        <v>48681.93359375</v>
+        <v>48681.9296875</v>
       </c>
     </row>
     <row r="370">
@@ -4503,7 +4503,7 @@
         <v>45757</v>
       </c>
       <c r="B371" t="n">
-        <v>86147.140625</v>
+        <v>86147.1484375</v>
       </c>
       <c r="C371" t="n">
         <v>49664.5</v>
@@ -4517,7 +4517,7 @@
         <v>90661.078125</v>
       </c>
       <c r="C372" t="n">
-        <v>51361.671875</v>
+        <v>51361.66796875</v>
       </c>
     </row>
     <row r="373">
@@ -4539,7 +4539,7 @@
         <v>88748.390625</v>
       </c>
       <c r="C374" t="n">
-        <v>50289.7734375</v>
+        <v>50289.76953125</v>
       </c>
     </row>
     <row r="375">
@@ -4550,7 +4550,7 @@
         <v>82551.3125</v>
       </c>
       <c r="C375" t="n">
-        <v>50021.796875</v>
+        <v>50021.80078125</v>
       </c>
     </row>
     <row r="376">
@@ -4558,10 +4558,10 @@
         <v>45764</v>
       </c>
       <c r="B376" t="n">
-        <v>83698.9140625</v>
+        <v>83698.90625</v>
       </c>
       <c r="C376" t="n">
-        <v>50021.796875</v>
+        <v>50021.80078125</v>
       </c>
     </row>
     <row r="377">
@@ -4569,7 +4569,7 @@
         <v>45765</v>
       </c>
       <c r="B377" t="n">
-        <v>85382.0703125</v>
+        <v>85382.078125</v>
       </c>
       <c r="C377" t="n">
         <v>50557.75</v>
@@ -4580,7 +4580,7 @@
         <v>45768</v>
       </c>
       <c r="B378" t="n">
-        <v>85458.5859375</v>
+        <v>85458.59375</v>
       </c>
       <c r="C378" t="n">
         <v>50647.07421875</v>
@@ -4591,10 +4591,10 @@
         <v>45769</v>
       </c>
       <c r="B379" t="n">
-        <v>84463.984375</v>
+        <v>84463.9765625</v>
       </c>
       <c r="C379" t="n">
-        <v>50021.796875</v>
+        <v>50021.80078125</v>
       </c>
     </row>
     <row r="380">
@@ -4602,7 +4602,7 @@
         <v>45770</v>
       </c>
       <c r="B380" t="n">
-        <v>84463.984375</v>
+        <v>84463.9765625</v>
       </c>
       <c r="C380" t="n">
         <v>50379.09765625</v>
@@ -4616,7 +4616,7 @@
         <v>85688.1015625</v>
       </c>
       <c r="C381" t="n">
-        <v>50289.7734375</v>
+        <v>50289.76953125</v>
       </c>
     </row>
     <row r="382">
@@ -4627,7 +4627,7 @@
         <v>85994.1328125</v>
       </c>
       <c r="C382" t="n">
-        <v>52076.26953125</v>
+        <v>52076.265625</v>
       </c>
     </row>
     <row r="383">
@@ -4638,7 +4638,7 @@
         <v>83775.4296875</v>
       </c>
       <c r="C383" t="n">
-        <v>51361.671875</v>
+        <v>51361.66796875</v>
       </c>
     </row>
     <row r="384">
@@ -4646,7 +4646,7 @@
         <v>45776</v>
       </c>
       <c r="B384" t="n">
-        <v>83698.9140625</v>
+        <v>83698.90625</v>
       </c>
       <c r="C384" t="n">
         <v>51450.99609375</v>
@@ -4657,7 +4657,7 @@
         <v>45782</v>
       </c>
       <c r="B385" t="n">
-        <v>83086.859375</v>
+        <v>83086.8671875</v>
       </c>
       <c r="C385" t="n">
         <v>51450.99609375</v>
@@ -4668,7 +4668,7 @@
         <v>45783</v>
       </c>
       <c r="B386" t="n">
-        <v>83086.859375</v>
+        <v>83086.8671875</v>
       </c>
       <c r="C386" t="n">
         <v>50825.72265625</v>
@@ -4712,7 +4712,7 @@
         <v>45789</v>
       </c>
       <c r="B390" t="n">
-        <v>90508.0703125</v>
+        <v>90508.0625</v>
       </c>
       <c r="C390" t="n">
         <v>51272.34765625</v>
@@ -4723,7 +4723,7 @@
         <v>45790</v>
       </c>
       <c r="B391" t="n">
-        <v>90508.0703125</v>
+        <v>90508.0625</v>
       </c>
       <c r="C391" t="n">
         <v>52344.2421875</v>
@@ -4756,7 +4756,7 @@
         <v>45793</v>
       </c>
       <c r="B394" t="n">
-        <v>95634.0390625</v>
+        <v>95634.046875</v>
       </c>
       <c r="C394" t="n">
         <v>52529.203125</v>
@@ -4800,7 +4800,7 @@
         <v>45799</v>
       </c>
       <c r="B398" t="n">
-        <v>90508.0703125</v>
+        <v>90508.0625</v>
       </c>
       <c r="C398" t="n">
         <v>51234.46875</v>
@@ -4811,7 +4811,7 @@
         <v>45800</v>
       </c>
       <c r="B399" t="n">
-        <v>89360.4453125</v>
+        <v>89360.453125</v>
       </c>
       <c r="C399" t="n">
         <v>50864.54296875</v>
@@ -4822,7 +4822,7 @@
         <v>45803</v>
       </c>
       <c r="B400" t="n">
-        <v>89742.9921875</v>
+        <v>89742.984375</v>
       </c>
       <c r="C400" t="n">
         <v>51511.91015625</v>
@@ -4833,7 +4833,7 @@
         <v>45804</v>
       </c>
       <c r="B401" t="n">
-        <v>89742.9921875</v>
+        <v>89742.984375</v>
       </c>
       <c r="C401" t="n">
         <v>51511.91015625</v>
@@ -4866,7 +4866,7 @@
         <v>45807</v>
       </c>
       <c r="B404" t="n">
-        <v>89589.96875</v>
+        <v>89589.9765625</v>
       </c>
       <c r="C404" t="n">
         <v>50957.0234375</v>
@@ -4877,7 +4877,7 @@
         <v>45810</v>
       </c>
       <c r="B405" t="n">
-        <v>88824.8984375</v>
+        <v>88824.90625</v>
       </c>
       <c r="C405" t="n">
         <v>50494.62109375</v>
@@ -4888,7 +4888,7 @@
         <v>45811</v>
       </c>
       <c r="B406" t="n">
-        <v>88824.8984375</v>
+        <v>88824.90625</v>
       </c>
       <c r="C406" t="n">
         <v>50494.62109375</v>
@@ -4910,7 +4910,7 @@
         <v>45813</v>
       </c>
       <c r="B408" t="n">
-        <v>89589.96875</v>
+        <v>89589.9765625</v>
       </c>
       <c r="C408" t="n">
         <v>52621.68359375</v>
@@ -4921,7 +4921,7 @@
         <v>45814</v>
       </c>
       <c r="B409" t="n">
-        <v>89360.4453125</v>
+        <v>89360.453125</v>
       </c>
       <c r="C409" t="n">
         <v>52066.796875</v>
@@ -5064,7 +5064,7 @@
         <v>45833</v>
       </c>
       <c r="B422" t="n">
-        <v>89908.0078125</v>
+        <v>89908</v>
       </c>
       <c r="C422" t="n">
         <v>52159.27734375</v>
@@ -5130,7 +5130,7 @@
         <v>45842</v>
       </c>
       <c r="B428" t="n">
-        <v>91065.625</v>
+        <v>91065.6171875</v>
       </c>
       <c r="C428" t="n">
         <v>53176.5703125</v>
@@ -5141,7 +5141,7 @@
         <v>45845</v>
       </c>
       <c r="B429" t="n">
-        <v>95541.7265625</v>
+        <v>95541.71875</v>
       </c>
       <c r="C429" t="n">
         <v>53546.4921875</v>
@@ -5152,7 +5152,7 @@
         <v>45846</v>
       </c>
       <c r="B430" t="n">
-        <v>95541.7265625</v>
+        <v>95541.71875</v>
       </c>
       <c r="C430" t="n">
         <v>53546.4921875</v>
@@ -5174,7 +5174,7 @@
         <v>45848</v>
       </c>
       <c r="B432" t="n">
-        <v>94769.9921875</v>
+        <v>94769.984375</v>
       </c>
       <c r="C432" t="n">
         <v>55673.5546875</v>
@@ -5185,7 +5185,7 @@
         <v>45849</v>
       </c>
       <c r="B433" t="n">
-        <v>95618.8984375</v>
+        <v>95618.90625</v>
       </c>
       <c r="C433" t="n">
         <v>55211.1484375</v>
@@ -5196,7 +5196,7 @@
         <v>45852</v>
       </c>
       <c r="B434" t="n">
-        <v>98088.4765625</v>
+        <v>98088.46875</v>
       </c>
       <c r="C434" t="n">
         <v>55766.03515625</v>
@@ -5207,7 +5207,7 @@
         <v>45853</v>
       </c>
       <c r="B435" t="n">
-        <v>98088.4765625</v>
+        <v>98088.46875</v>
       </c>
       <c r="C435" t="n">
         <v>55766.03515625</v>
@@ -5229,7 +5229,7 @@
         <v>45855</v>
       </c>
       <c r="B437" t="n">
-        <v>97471.078125</v>
+        <v>97471.0859375</v>
       </c>
       <c r="C437" t="n">
         <v>55581.07421875</v>
@@ -5251,7 +5251,7 @@
         <v>45859</v>
       </c>
       <c r="B439" t="n">
-        <v>97891.6875</v>
+        <v>97891.6796875</v>
       </c>
       <c r="C439" t="n">
         <v>55488.59375</v>
@@ -5262,7 +5262,7 @@
         <v>45860</v>
       </c>
       <c r="B440" t="n">
-        <v>97891.6875</v>
+        <v>97891.6796875</v>
       </c>
       <c r="C440" t="n">
         <v>55488.59375</v>
@@ -5273,7 +5273,7 @@
         <v>45861</v>
       </c>
       <c r="B441" t="n">
-        <v>99489.1875</v>
+        <v>99489.1953125</v>
       </c>
       <c r="C441" t="n">
         <v>55673.5546875</v>
@@ -5284,7 +5284,7 @@
         <v>45862</v>
       </c>
       <c r="B442" t="n">
-        <v>99222.9453125</v>
+        <v>99222.9375</v>
       </c>
       <c r="C442" t="n">
         <v>57060.76953125</v>
@@ -5339,7 +5339,7 @@
         <v>45869</v>
       </c>
       <c r="B447" t="n">
-        <v>94164.171875</v>
+        <v>94164.1640625</v>
       </c>
       <c r="C447" t="n">
         <v>58170.54296875</v>
@@ -5416,7 +5416,7 @@
         <v>45880</v>
       </c>
       <c r="B454" t="n">
-        <v>94430.4140625</v>
+        <v>94430.421875</v>
       </c>
       <c r="C454" t="n">
         <v>56875.80859375</v>
@@ -5427,7 +5427,7 @@
         <v>45881</v>
       </c>
       <c r="B455" t="n">
-        <v>94430.4140625</v>
+        <v>94430.421875</v>
       </c>
       <c r="C455" t="n">
         <v>56875.80859375</v>
@@ -5449,7 +5449,7 @@
         <v>45883</v>
       </c>
       <c r="B457" t="n">
-        <v>93276.6640625</v>
+        <v>93276.65625</v>
       </c>
       <c r="C457" t="n">
         <v>56505.88671875</v>
@@ -5493,7 +5493,7 @@
         <v>45889</v>
       </c>
       <c r="B461" t="n">
-        <v>89016.640625</v>
+        <v>89016.6484375</v>
       </c>
       <c r="C461" t="n">
         <v>55950.99609375</v>
@@ -5526,7 +5526,7 @@
         <v>45894</v>
       </c>
       <c r="B464" t="n">
-        <v>87685.3828125</v>
+        <v>87685.390625</v>
       </c>
       <c r="C464" t="n">
         <v>54286.33984375</v>
@@ -5537,7 +5537,7 @@
         <v>45895</v>
       </c>
       <c r="B465" t="n">
-        <v>87685.3828125</v>
+        <v>87685.390625</v>
       </c>
       <c r="C465" t="n">
         <v>54286.33984375</v>
@@ -5548,7 +5548,7 @@
         <v>45896</v>
       </c>
       <c r="B466" t="n">
-        <v>88750.3984375</v>
+        <v>88750.390625</v>
       </c>
       <c r="C466" t="n">
         <v>55211.1484375</v>
@@ -5570,7 +5570,7 @@
         <v>45898</v>
       </c>
       <c r="B468" t="n">
-        <v>92744.15625</v>
+        <v>92744.1640625</v>
       </c>
       <c r="C468" t="n">
         <v>56413.40625</v>
@@ -5581,7 +5581,7 @@
         <v>45903</v>
       </c>
       <c r="B469" t="n">
-        <v>91590.40625</v>
+        <v>91590.3984375</v>
       </c>
       <c r="C469" t="n">
         <v>56875.80859375</v>
@@ -5592,7 +5592,7 @@
         <v>45904</v>
       </c>
       <c r="B470" t="n">
-        <v>91590.40625</v>
+        <v>91590.3984375</v>
       </c>
       <c r="C470" t="n">
         <v>56875.80859375</v>
@@ -5614,7 +5614,7 @@
         <v>45908</v>
       </c>
       <c r="B472" t="n">
-        <v>90436.65625</v>
+        <v>90436.6484375</v>
       </c>
       <c r="C472" t="n">
         <v>56043.4765625</v>
@@ -5625,7 +5625,7 @@
         <v>45909</v>
       </c>
       <c r="B473" t="n">
-        <v>90436.65625</v>
+        <v>90436.6484375</v>
       </c>
       <c r="C473" t="n">
         <v>56043.4765625</v>
@@ -5669,7 +5669,7 @@
         <v>45915</v>
       </c>
       <c r="B477" t="n">
-        <v>90436.65625</v>
+        <v>90436.6484375</v>
       </c>
       <c r="C477" t="n">
         <v>56598.3671875</v>
@@ -5680,7 +5680,7 @@
         <v>45916</v>
       </c>
       <c r="B478" t="n">
-        <v>90436.65625</v>
+        <v>90436.6484375</v>
       </c>
       <c r="C478" t="n">
         <v>58355.50390625</v>
@@ -5724,7 +5724,7 @@
         <v>45922</v>
       </c>
       <c r="B482" t="n">
-        <v>88484.140625</v>
+        <v>88484.1484375</v>
       </c>
       <c r="C482" t="n">
         <v>56783.328125</v>
@@ -5735,7 +5735,7 @@
         <v>45923</v>
       </c>
       <c r="B483" t="n">
-        <v>88484.140625</v>
+        <v>88484.1484375</v>
       </c>
       <c r="C483" t="n">
         <v>56783.328125</v>
@@ -5812,7 +5812,7 @@
         <v>45933</v>
       </c>
       <c r="B490" t="n">
-        <v>81739.109375</v>
+        <v>81739.1171875</v>
       </c>
       <c r="C490" t="n">
         <v>56598.3671875</v>
@@ -5867,7 +5867,7 @@
         <v>45940</v>
       </c>
       <c r="B495" t="n">
-        <v>83602.875</v>
+        <v>83602.8671875</v>
       </c>
       <c r="C495" t="n">
         <v>58170.54296875</v>
@@ -5878,7 +5878,7 @@
         <v>45943</v>
       </c>
       <c r="B496" t="n">
-        <v>83425.3671875</v>
+        <v>83425.375</v>
       </c>
       <c r="C496" t="n">
         <v>59187.83203125</v>
@@ -5889,7 +5889,7 @@
         <v>45944</v>
       </c>
       <c r="B497" t="n">
-        <v>83425.3671875</v>
+        <v>83425.375</v>
       </c>
       <c r="C497" t="n">
         <v>59187.83203125</v>
@@ -5900,7 +5900,7 @@
         <v>45945</v>
       </c>
       <c r="B498" t="n">
-        <v>82005.3671875</v>
+        <v>82005.359375</v>
       </c>
       <c r="C498" t="n">
         <v>58725.42578125</v>
@@ -5933,7 +5933,7 @@
         <v>45950</v>
       </c>
       <c r="B501" t="n">
-        <v>77212.8359375</v>
+        <v>77212.84375</v>
       </c>
       <c r="C501" t="n">
         <v>53254.71484375</v>
@@ -5944,7 +5944,7 @@
         <v>45951</v>
       </c>
       <c r="B502" t="n">
-        <v>77212.8359375</v>
+        <v>77212.84375</v>
       </c>
       <c r="C502" t="n">
         <v>53254.71484375</v>
@@ -5966,7 +5966,7 @@
         <v>45953</v>
       </c>
       <c r="B504" t="n">
-        <v>86087.8828125</v>
+        <v>86087.890625</v>
       </c>
       <c r="C504" t="n">
         <v>54513.46484375</v>
@@ -5977,7 +5977,7 @@
         <v>45954</v>
       </c>
       <c r="B505" t="n">
-        <v>84312.8671875</v>
+        <v>84312.875</v>
       </c>
       <c r="C505" t="n">
         <v>54803.9453125</v>
@@ -6010,7 +6010,7 @@
         <v>45959</v>
       </c>
       <c r="B508" t="n">
-        <v>90702.8984375</v>
+        <v>90702.90625</v>
       </c>
       <c r="C508" t="n">
         <v>55578.55859375</v>
@@ -6087,7 +6087,7 @@
         <v>45968</v>
       </c>
       <c r="B515" t="n">
-        <v>89637.8984375</v>
+        <v>89637.890625</v>
       </c>
       <c r="C515" t="n">
         <v>55772.2109375</v>
@@ -6098,7 +6098,7 @@
         <v>45971</v>
       </c>
       <c r="B516" t="n">
-        <v>85377.8828125</v>
+        <v>85377.875</v>
       </c>
       <c r="C516" t="n">
         <v>55191.25</v>
@@ -6109,7 +6109,7 @@
         <v>45972</v>
       </c>
       <c r="B517" t="n">
-        <v>85289.125</v>
+        <v>85289.1171875</v>
       </c>
       <c r="C517" t="n">
         <v>57030.9609375</v>
@@ -6142,7 +6142,7 @@
         <v>45975</v>
       </c>
       <c r="B520" t="n">
-        <v>88750.3984375</v>
+        <v>88750.390625</v>
       </c>
       <c r="C520" t="n">
         <v>60807.203125</v>
@@ -6153,7 +6153,7 @@
         <v>45978</v>
       </c>
       <c r="B521" t="n">
-        <v>89637.8984375</v>
+        <v>89637.890625</v>
       </c>
       <c r="C521" t="n">
         <v>60129.4140625</v>
@@ -6164,7 +6164,7 @@
         <v>45979</v>
       </c>
       <c r="B522" t="n">
-        <v>88750.3984375</v>
+        <v>88750.390625</v>
       </c>
       <c r="C522" t="n">
         <v>58773.83984375</v>
@@ -6219,7 +6219,7 @@
         <v>45986</v>
       </c>
       <c r="B527" t="n">
-        <v>88484.140625</v>
+        <v>88484.1484375</v>
       </c>
       <c r="C527" t="n">
         <v>59935.76171875</v>
@@ -8516,10 +8516,10 @@
         <v>45197</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.003181263382445065</v>
+        <v>-0.003181326376937466</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02349864296311999</v>
+        <v>-0.02349858363652735</v>
       </c>
     </row>
     <row r="3">
@@ -8527,10 +8527,10 @@
         <v>45198</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.01276598145681995</v>
+        <v>-0.0127659180595987</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.008021476046410125</v>
+        <v>-0.008021413830182178</v>
       </c>
     </row>
     <row r="4">
@@ -8538,10 +8538,10 @@
         <v>45201</v>
       </c>
       <c r="B4" t="n">
-        <v>0.004310310227901626</v>
+        <v>0.004310309951106372</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01886785589205453</v>
+        <v>0.01886779198934985</v>
       </c>
     </row>
     <row r="5">
@@ -8549,10 +8549,10 @@
         <v>45202</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.01072955994628411</v>
+        <v>-0.01072962320162407</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.02116390163102488</v>
+        <v>-0.02116396318888947</v>
       </c>
     </row>
     <row r="6">
@@ -8563,7 +8563,7 @@
         <v>0.003253786070724241</v>
       </c>
       <c r="C6" t="n">
-        <v>0.005405547160244994</v>
+        <v>0.005405421722510351</v>
       </c>
     </row>
     <row r="7">
@@ -8571,10 +8571,10 @@
         <v>45204</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.009729764275612451</v>
+        <v>-0.009729699850327123</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.02284965178328657</v>
+        <v>-0.02284946841888769</v>
       </c>
     </row>
     <row r="8">
@@ -8582,10 +8582,10 @@
         <v>45205</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0120087839096803</v>
+        <v>0.01200871807012671</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02063273533934695</v>
+        <v>0.02063279935274775</v>
       </c>
     </row>
     <row r="9">
@@ -8593,10 +8593,10 @@
         <v>45208</v>
       </c>
       <c r="B9" t="n">
-        <v>0.03128363579067028</v>
+        <v>0.03128370007695702</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.006738564760969123</v>
+        <v>-0.006738376180354222</v>
       </c>
     </row>
     <row r="10">
@@ -8604,10 +8604,10 @@
         <v>45209</v>
       </c>
       <c r="B10" t="n">
-        <v>0.007322195228576467</v>
+        <v>0.007322132435958251</v>
       </c>
       <c r="C10" t="n">
-        <v>0.009498182944226441</v>
+        <v>0.00949773853144853</v>
       </c>
     </row>
     <row r="11">
@@ -8626,10 +8626,10 @@
         <v>45211</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.006185548136007801</v>
+        <v>-0.006185486699523346</v>
       </c>
       <c r="C12" t="n">
-        <v>0.01478480020081285</v>
+        <v>0.01478492807667009</v>
       </c>
     </row>
     <row r="13">
@@ -8637,10 +8637,10 @@
         <v>45212</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.003112023640029715</v>
+        <v>-0.003112085266512299</v>
       </c>
       <c r="C13" t="n">
-        <v>0.003973521690161963</v>
+        <v>0.003973583574482076</v>
       </c>
     </row>
     <row r="14">
@@ -8648,7 +8648,7 @@
         <v>45215</v>
       </c>
       <c r="B14" t="n">
-        <v>0.007284160002976492</v>
+        <v>0.007284097991126171</v>
       </c>
       <c r="C14" t="n">
         <v>-0.007915590609347212</v>
@@ -8659,7 +8659,7 @@
         <v>45216</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.03822324543350308</v>
+        <v>-0.03822318622324017</v>
       </c>
       <c r="C15" t="n">
         <v>-0.005319102851377266</v>
@@ -8670,10 +8670,10 @@
         <v>45217</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.001074089242093734</v>
+        <v>-0.001074025232007725</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0120321829615011</v>
+        <v>-0.01203224517772905</v>
       </c>
     </row>
     <row r="17">
@@ -8681,10 +8681,10 @@
         <v>45218</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.01075269781833088</v>
+        <v>-0.01075276120821811</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.03382941265967676</v>
+        <v>-0.03382928884215664</v>
       </c>
     </row>
     <row r="18">
@@ -8695,7 +8695,7 @@
         <v>0.009782643477237896</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01260494863022288</v>
+        <v>0.01260488262974446</v>
       </c>
     </row>
     <row r="19">
@@ -8703,10 +8703,10 @@
         <v>45222</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.02045214253301275</v>
+        <v>-0.02045207838512575</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.02904560228947672</v>
+        <v>-0.02904553792192044</v>
       </c>
     </row>
     <row r="20">
@@ -8714,10 +8714,10 @@
         <v>45223</v>
       </c>
       <c r="B20" t="n">
-        <v>0.01098902106397115</v>
+        <v>0.01098895485709339</v>
       </c>
       <c r="C20" t="n">
-        <v>0.001424571967136412</v>
+        <v>0.001424505579622926</v>
       </c>
     </row>
     <row r="21">
@@ -8728,7 +8728,7 @@
         <v>-0.01195644189638079</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.01849229644870054</v>
+        <v>-0.01849216405115317</v>
       </c>
     </row>
     <row r="22">
@@ -8736,10 +8736,10 @@
         <v>45225</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.04510458704505382</v>
+        <v>-0.04510452148577515</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.02898546032741667</v>
+        <v>-0.02898559130950251</v>
       </c>
     </row>
     <row r="23">
@@ -8747,10 +8747,10 @@
         <v>45226</v>
       </c>
       <c r="B23" t="n">
-        <v>0.002304163284787553</v>
+        <v>0.002304094470619633</v>
       </c>
       <c r="C23" t="n">
-        <v>0.01492541771269495</v>
+        <v>0.01492534825337954</v>
       </c>
     </row>
     <row r="24">
@@ -8761,7 +8761,7 @@
         <v>-0.02298852621783709</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.005882370251927282</v>
+        <v>-0.005882302216647428</v>
       </c>
     </row>
     <row r="25">
@@ -8769,10 +8769,10 @@
         <v>45230</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.02352943321007783</v>
+        <v>-0.02352950331994774</v>
       </c>
       <c r="C25" t="n">
-        <v>0.005917177279531671</v>
+        <v>0.005917108436720886</v>
       </c>
     </row>
     <row r="26">
@@ -8780,10 +8780,10 @@
         <v>45231</v>
       </c>
       <c r="B26" t="n">
-        <v>0.02891571835991225</v>
+        <v>0.02891579223531093</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03529394776015571</v>
+        <v>0.0352941554891677</v>
       </c>
     </row>
     <row r="27">
@@ -8791,10 +8791,10 @@
         <v>45232</v>
       </c>
       <c r="B27" t="n">
-        <v>0.04215457589640081</v>
+        <v>0.04215464567788496</v>
       </c>
       <c r="C27" t="n">
-        <v>0.007102360898244564</v>
+        <v>0.007102293854499564</v>
       </c>
     </row>
     <row r="28">
@@ -8802,10 +8802,10 @@
         <v>45233</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.0224719296733753</v>
+        <v>-0.02247199512753784</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.01269390780905955</v>
+        <v>-0.01269397261441085</v>
       </c>
     </row>
     <row r="29">
@@ -8813,7 +8813,7 @@
         <v>45236</v>
       </c>
       <c r="B29" t="n">
-        <v>0.01724139466337782</v>
+        <v>0.01724132616523044</v>
       </c>
       <c r="C29" t="n">
         <v>0.01428575702445656</v>
@@ -8824,10 +8824,10 @@
         <v>45237</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.002259969788509508</v>
+        <v>-0.002259835266358867</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.002817040809337201</v>
+        <v>-0.002816909717112792</v>
       </c>
     </row>
     <row r="31">
@@ -8835,10 +8835,10 @@
         <v>45238</v>
       </c>
       <c r="B31" t="n">
-        <v>0.04869758742596964</v>
+        <v>0.04869758413938508</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008474733914849208</v>
+        <v>0.008474667069467978</v>
       </c>
     </row>
     <row r="32">
@@ -8846,10 +8846,10 @@
         <v>45239</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.001079824579185984</v>
+        <v>-0.00107988886540622</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.009804015502933194</v>
+        <v>-0.009804014863918131</v>
       </c>
     </row>
     <row r="33">
@@ -8857,10 +8857,10 @@
         <v>45240</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.01081082056166482</v>
+        <v>-0.01081075613637961</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.01555868001319116</v>
+        <v>-0.01555874481329644</v>
       </c>
     </row>
     <row r="34">
@@ -8868,7 +8868,7 @@
         <v>45243</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.001092936249010967</v>
+        <v>-0.001093001307211794</v>
       </c>
       <c r="C34" t="n">
         <v>-0.01293100652645029</v>
@@ -8879,10 +8879,10 @@
         <v>45244</v>
       </c>
       <c r="B35" t="n">
-        <v>0.01312906318210061</v>
+        <v>0.01312912838274816</v>
       </c>
       <c r="C35" t="n">
-        <v>0.002911284569006245</v>
+        <v>0.002911216828480612</v>
       </c>
     </row>
     <row r="36">
@@ -8890,10 +8890,10 @@
         <v>45245</v>
       </c>
       <c r="B36" t="n">
-        <v>-0.002159842225523678</v>
+        <v>-0.002159842086525532</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0261246918225766</v>
+        <v>0.02612482867492116</v>
       </c>
     </row>
     <row r="37">
@@ -8901,10 +8901,10 @@
         <v>45246</v>
       </c>
       <c r="B37" t="n">
-        <v>0.006493616218793852</v>
+        <v>0.006493615799987973</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.005657594110572872</v>
+        <v>-0.0056576595624096</v>
       </c>
     </row>
     <row r="38">
@@ -8912,7 +8912,7 @@
         <v>45247</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.02150539563666176</v>
+        <v>-0.02150539425861953</v>
       </c>
       <c r="C38" t="n">
         <v>-0.004267503948756857</v>
@@ -8923,10 +8923,10 @@
         <v>45250</v>
       </c>
       <c r="B39" t="n">
-        <v>-0.003296693221743086</v>
+        <v>-0.003296758493088858</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.009999896952143539</v>
+        <v>-0.009999963434631609</v>
       </c>
     </row>
     <row r="40">
@@ -8937,7 +8937,7 @@
         <v>0.01323045512594812</v>
       </c>
       <c r="C40" t="n">
-        <v>0.002885944065669666</v>
+        <v>0.002885944259472417</v>
       </c>
     </row>
     <row r="41">
@@ -8945,10 +8945,10 @@
         <v>45252</v>
       </c>
       <c r="B41" t="n">
-        <v>0.0119695167177285</v>
+        <v>0.01196958156363448</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.00143892012088298</v>
+        <v>-0.001438853256453432</v>
       </c>
     </row>
     <row r="42">
@@ -8956,7 +8956,7 @@
         <v>45253</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.02365594801611048</v>
+        <v>-0.02365594650026315</v>
       </c>
       <c r="C42" t="n">
         <v>-0.01008641871080129</v>
@@ -8967,7 +8967,7 @@
         <v>45254</v>
       </c>
       <c r="B43" t="n">
-        <v>0.004405251070301874</v>
+        <v>0.004405185149695567</v>
       </c>
       <c r="C43" t="n">
         <v>-0.005822433656961445</v>
@@ -8981,7 +8981,7 @@
         <v>-0.005482396098723807</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.002928334602957383</v>
+        <v>-0.002928130191206746</v>
       </c>
     </row>
     <row r="45">
@@ -8989,10 +8989,10 @@
         <v>45258</v>
       </c>
       <c r="B45" t="n">
-        <v>0.004410107906084759</v>
+        <v>0.004410173609931567</v>
       </c>
       <c r="C45" t="n">
-        <v>0.005873801524920896</v>
+        <v>0.005873595308668156</v>
       </c>
     </row>
     <row r="46">
@@ -9000,7 +9000,7 @@
         <v>45259</v>
       </c>
       <c r="B46" t="n">
-        <v>0.006586214498267573</v>
+        <v>0.006586214067427987</v>
       </c>
       <c r="C46" t="n">
         <v>-0.001459858378519141</v>
@@ -9011,7 +9011,7 @@
         <v>45260</v>
       </c>
       <c r="B47" t="n">
-        <v>0.002181040035254433</v>
+        <v>0.002180974906180966</v>
       </c>
       <c r="C47" t="n">
         <v>-0.01461992680783475</v>
@@ -9022,7 +9022,7 @@
         <v>45261</v>
       </c>
       <c r="B48" t="n">
-        <v>0.005440571515501924</v>
+        <v>0.005440636361408124</v>
       </c>
       <c r="C48" t="n">
         <v>0.01483684032748211</v>
@@ -9033,10 +9033,10 @@
         <v>45264</v>
       </c>
       <c r="B49" t="n">
-        <v>0.01298710344755527</v>
+        <v>0.01298703811493973</v>
       </c>
       <c r="C49" t="n">
-        <v>0.005847902685499839</v>
+        <v>0.005847970723133811</v>
       </c>
     </row>
     <row r="50">
@@ -9047,7 +9047,7 @@
         <v>0.01282053730826327</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0101744495744942</v>
+        <v>-0.01017431360214294</v>
       </c>
     </row>
     <row r="51">
@@ -9055,10 +9055,10 @@
         <v>45266</v>
       </c>
       <c r="B51" t="n">
-        <v>0.002109781959233281</v>
+        <v>0.002109719097009188</v>
       </c>
       <c r="C51" t="n">
-        <v>0.005873801524920896</v>
+        <v>0.005873595308668156</v>
       </c>
     </row>
     <row r="52">
@@ -9066,7 +9066,7 @@
         <v>45267</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.007368565067224164</v>
+        <v>-0.007368440069690396</v>
       </c>
       <c r="C52" t="n">
         <v>-0.001459858378519141</v>
@@ -9077,10 +9077,10 @@
         <v>45268</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.001060357931943701</v>
+        <v>-0.001060421060467776</v>
       </c>
       <c r="C53" t="n">
-        <v>0.008771888047066856</v>
+        <v>0.00877202412233502</v>
       </c>
     </row>
     <row r="54">
@@ -9088,10 +9088,10 @@
         <v>45271</v>
       </c>
       <c r="B54" t="n">
-        <v>0.00849262702643605</v>
+        <v>0.008492563763817129</v>
       </c>
       <c r="C54" t="n">
-        <v>0.01449279760971356</v>
+        <v>0.0144926607627589</v>
       </c>
     </row>
     <row r="55">
@@ -9099,7 +9099,7 @@
         <v>45272</v>
       </c>
       <c r="B55" t="n">
-        <v>0.01894737132643654</v>
+        <v>0.01894737251500289</v>
       </c>
       <c r="C55" t="n">
         <v>-0.008571454214673979</v>
@@ -9110,7 +9110,7 @@
         <v>45273</v>
       </c>
       <c r="B56" t="n">
-        <v>-0.01652903755331236</v>
+        <v>-0.01652897700747991</v>
       </c>
       <c r="C56" t="n">
         <v>-0.01729105140227805</v>
@@ -9121,10 +9121,10 @@
         <v>45275</v>
       </c>
       <c r="B57" t="n">
-        <v>0.01050427401040865</v>
+        <v>0.01050421141230951</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.00146634829937986</v>
+        <v>-0.001466143587904312</v>
       </c>
     </row>
     <row r="58">
@@ -9132,10 +9132,10 @@
         <v>45278</v>
       </c>
       <c r="B58" t="n">
-        <v>-0.02286905480863177</v>
+        <v>-0.02286899427791955</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.01615262959104935</v>
+        <v>-0.01615283129161826</v>
       </c>
     </row>
     <row r="59">
@@ -9157,7 +9157,7 @@
         <v>0.001057121208417833</v>
       </c>
       <c r="C60" t="n">
-        <v>0.01641782056533359</v>
+        <v>0.01641802894328004</v>
       </c>
     </row>
     <row r="61">
@@ -9165,10 +9165,10 @@
         <v>45281</v>
       </c>
       <c r="B61" t="n">
-        <v>0.004223830747229984</v>
+        <v>0.004223893675832757</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.004405231553302191</v>
+        <v>-0.004405367324878395</v>
       </c>
     </row>
     <row r="62">
@@ -9176,10 +9176,10 @@
         <v>45282</v>
       </c>
       <c r="B62" t="n">
-        <v>-0.005257628298425132</v>
+        <v>-0.00525769063287862</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.002949792776628435</v>
+        <v>-0.002949861213889626</v>
       </c>
     </row>
     <row r="63">
@@ -9190,7 +9190,7 @@
         <v>0.01479912996171651</v>
       </c>
       <c r="C63" t="n">
-        <v>0.004437951802459761</v>
+        <v>0.004437882959648753</v>
       </c>
     </row>
     <row r="64">
@@ -9201,7 +9201,7 @@
         <v>0.01249996197817538</v>
       </c>
       <c r="C64" t="n">
-        <v>0.001472689750937395</v>
+        <v>0.001472689851873543</v>
       </c>
     </row>
     <row r="65">
@@ -9209,10 +9209,10 @@
         <v>45287</v>
       </c>
       <c r="B65" t="n">
-        <v>-0.003086287860733949</v>
+        <v>-0.003086226550659044</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>1.368757132080844e-07</v>
       </c>
     </row>
     <row r="66">
@@ -9220,10 +9220,10 @@
         <v>45288</v>
       </c>
       <c r="B66" t="n">
-        <v>-0.003095965521690558</v>
+        <v>-0.003096026831166498</v>
       </c>
       <c r="C66" t="n">
-        <v>0.01481481025229137</v>
+        <v>0.01481467236270317</v>
       </c>
     </row>
     <row r="67">
@@ -9234,7 +9234,7 @@
         <v>-0.005176049406493743</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.0131387563267672</v>
+        <v>-0.0131386223353005</v>
       </c>
     </row>
     <row r="68">
@@ -9242,10 +9242,10 @@
         <v>45293</v>
       </c>
       <c r="B68" t="n">
-        <v>-0.002081179713443237</v>
+        <v>-0.00208124172529367</v>
       </c>
       <c r="C68" t="n">
-        <v>0.01035511601746775</v>
+        <v>0.01035497863660795</v>
       </c>
     </row>
     <row r="69">
@@ -9253,10 +9253,10 @@
         <v>45294</v>
       </c>
       <c r="B69" t="n">
-        <v>0.004170977969771839</v>
+        <v>0.004171040370142709</v>
       </c>
       <c r="C69" t="n">
-        <v>0.01024885129997521</v>
+        <v>0.01024898726565149</v>
       </c>
     </row>
     <row r="70">
@@ -9278,7 +9278,7 @@
         <v>0.002057627423947439</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.002898603508465158</v>
+        <v>-0.002898603314403392</v>
       </c>
     </row>
     <row r="72">
@@ -9286,10 +9286,10 @@
         <v>45299</v>
       </c>
       <c r="B72" t="n">
-        <v>-0.001026731735634945</v>
+        <v>-0.001026670551454223</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.008720888071931832</v>
+        <v>-0.008720954631067035</v>
       </c>
     </row>
     <row r="73">
@@ -9297,10 +9297,10 @@
         <v>45300</v>
       </c>
       <c r="B73" t="n">
-        <v>-0.0071940802506818</v>
+        <v>-0.00719414105712668</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.001466268508871216</v>
+        <v>-0.001466133038043105</v>
       </c>
     </row>
     <row r="74">
@@ -9311,7 +9311,7 @@
         <v>-0.01966877799570421</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.008810529655407628</v>
+        <v>-0.008810596294954398</v>
       </c>
     </row>
     <row r="75">
@@ -9319,10 +9319,10 @@
         <v>45302</v>
       </c>
       <c r="B75" t="n">
-        <v>0.00316795172117601</v>
+        <v>0.003167888792573237</v>
       </c>
       <c r="C75" t="n">
-        <v>0.005925965163627644</v>
+        <v>0.005925827882372836</v>
       </c>
     </row>
     <row r="76">
@@ -9330,10 +9330,10 @@
         <v>45303</v>
       </c>
       <c r="B76" t="n">
-        <v>-0.003157947495970648</v>
+        <v>-0.003157884964186897</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.01030929518383861</v>
+        <v>-0.01030922785054278</v>
       </c>
     </row>
     <row r="77">
@@ -9352,10 +9352,10 @@
         <v>45308</v>
       </c>
       <c r="B78" t="n">
-        <v>0.003144706929518071</v>
+        <v>0.003144644462652835</v>
       </c>
       <c r="C78" t="n">
-        <v>0.001492598955525448</v>
+        <v>0.001492461058356653</v>
       </c>
     </row>
     <row r="79">
@@ -9363,10 +9363,10 @@
         <v>45310</v>
       </c>
       <c r="B79" t="n">
-        <v>0.006269510684745461</v>
+        <v>0.006269573346199264</v>
       </c>
       <c r="C79" t="n">
-        <v>0.01341281905134717</v>
+        <v>0.01341288974401533</v>
       </c>
     </row>
     <row r="80">
@@ -9374,10 +9374,10 @@
         <v>45313</v>
       </c>
       <c r="B80" t="n">
-        <v>0.001038459705770878</v>
+        <v>0.001038521588835328</v>
       </c>
       <c r="C80" t="n">
-        <v>0.004411742826935239</v>
+        <v>0.004411743126645273</v>
       </c>
     </row>
     <row r="81">
@@ -9385,10 +9385,10 @@
         <v>45314</v>
       </c>
       <c r="B81" t="n">
-        <v>-0.008298812131903421</v>
+        <v>-0.008298811618880242</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.008784797321929716</v>
+        <v>-0.008784730279859154</v>
       </c>
     </row>
     <row r="82">
@@ -9396,10 +9396,10 @@
         <v>45315</v>
       </c>
       <c r="B82" t="n">
-        <v>-0.006276007045734278</v>
+        <v>-0.006276131326872991</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.005908390469905656</v>
+        <v>-0.005908458705578878</v>
       </c>
     </row>
     <row r="83">
@@ -9418,10 +9418,10 @@
         <v>45317</v>
       </c>
       <c r="B84" t="n">
-        <v>0.009473591568401885</v>
+        <v>0.009473592162679179</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.004457698913882924</v>
+        <v>-0.004457630578627803</v>
       </c>
     </row>
     <row r="85">
@@ -9440,10 +9440,10 @@
         <v>45321</v>
       </c>
       <c r="B86" t="n">
-        <v>-0.003128311153800745</v>
+        <v>-0.003128187065835064</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.001492461058356653</v>
+        <v>-0.001492530006941051</v>
       </c>
     </row>
     <row r="87">
@@ -9451,10 +9451,10 @@
         <v>45322</v>
       </c>
       <c r="B87" t="n">
-        <v>0.001046125846657864</v>
+        <v>0.00104600110908537</v>
       </c>
       <c r="C87" t="n">
-        <v>0.001494691827703676</v>
+        <v>0.001494760982560628</v>
       </c>
     </row>
     <row r="88">
@@ -9462,10 +9462,10 @@
         <v>45323</v>
       </c>
       <c r="B88" t="n">
-        <v>0.04388707296154659</v>
+        <v>0.04388720023653025</v>
       </c>
       <c r="C88" t="n">
-        <v>0.007462718983289651</v>
+        <v>0.007462787931874049</v>
       </c>
     </row>
     <row r="89">
@@ -9484,10 +9484,10 @@
         <v>45327</v>
       </c>
       <c r="B90" t="n">
-        <v>0.03603604570950258</v>
+        <v>0.03603586460072283</v>
       </c>
       <c r="C90" t="n">
-        <v>0.007407439345071598</v>
+        <v>0.007407301962427892</v>
       </c>
     </row>
     <row r="91">
@@ -9495,10 +9495,10 @@
         <v>45328</v>
       </c>
       <c r="B91" t="n">
-        <v>0.005797198914905044</v>
+        <v>0.005797199582489254</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.005882459638507642</v>
+        <v>-0.005882324168860475</v>
       </c>
     </row>
     <row r="92">
@@ -9506,7 +9506,7 @@
         <v>45329</v>
       </c>
       <c r="B92" t="n">
-        <v>0.007684855987234451</v>
+        <v>0.007684971359679604</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -9517,7 +9517,7 @@
         <v>45337</v>
       </c>
       <c r="B93" t="n">
-        <v>-0.008579743565504727</v>
+        <v>-0.008579516326656766</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -9528,10 +9528,10 @@
         <v>45338</v>
       </c>
       <c r="B94" t="n">
-        <v>0.01057702566836571</v>
+        <v>0.01057690864139582</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0355029229963173</v>
+        <v>0.0355029205701678</v>
       </c>
     </row>
     <row r="95">
@@ -9539,10 +9539,10 @@
         <v>45341</v>
       </c>
       <c r="B95" t="n">
-        <v>-0.0009513395868403496</v>
+        <v>-0.0009514528821594759</v>
       </c>
       <c r="C95" t="n">
-        <v>0.02714292436210375</v>
+        <v>0.02714285657719739</v>
       </c>
     </row>
     <row r="96">
@@ -9553,7 +9553,7 @@
         <v>-0.006666740070578991</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.005563255171187276</v>
+        <v>-0.005563190921462513</v>
       </c>
     </row>
     <row r="97">
@@ -9561,10 +9561,10 @@
         <v>45343</v>
       </c>
       <c r="B97" t="n">
-        <v>0.0153403548017701</v>
+        <v>0.01534024052873684</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.002797189062108241</v>
+        <v>-0.002797318099699964</v>
       </c>
     </row>
     <row r="98">
@@ -9572,10 +9572,10 @@
         <v>45344</v>
       </c>
       <c r="B98" t="n">
-        <v>-0.01227578761749581</v>
+        <v>-0.01227567645255101</v>
       </c>
       <c r="C98" t="n">
-        <v>0.004207617704545141</v>
+        <v>0.004207682767555454</v>
       </c>
     </row>
     <row r="99">
@@ -9583,10 +9583,10 @@
         <v>45345</v>
       </c>
       <c r="B99" t="n">
-        <v>-0.006692121286565489</v>
+        <v>-0.006692235231863353</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.008380040193998073</v>
+        <v>-0.008379911156153885</v>
       </c>
     </row>
     <row r="100">
@@ -9594,7 +9594,7 @@
         <v>45348</v>
       </c>
       <c r="B100" t="n">
-        <v>0.03946091786436567</v>
+        <v>0.0394611518170136</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -9605,10 +9605,10 @@
         <v>45349</v>
       </c>
       <c r="B101" t="n">
-        <v>-0.0009257944158119757</v>
+        <v>-0.0009259046717684516</v>
       </c>
       <c r="C101" t="n">
-        <v>0.01408456935722602</v>
+        <v>0.01408450246027093</v>
       </c>
     </row>
     <row r="102">
@@ -9616,10 +9616,10 @@
         <v>45350</v>
       </c>
       <c r="B102" t="n">
-        <v>0.005560797515259619</v>
+        <v>0.005560687054858349</v>
       </c>
       <c r="C102" t="n">
-        <v>0.002777764232785529</v>
+        <v>0.002777571573106652</v>
       </c>
     </row>
     <row r="103">
@@ -9627,10 +9627,10 @@
         <v>45351</v>
       </c>
       <c r="B103" t="n">
-        <v>0.004608298474409356</v>
+        <v>0.004608189131066975</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.002770069632438199</v>
+        <v>-0.002769878038605622</v>
       </c>
     </row>
     <row r="104">
@@ -9638,10 +9638,10 @@
         <v>45352</v>
       </c>
       <c r="B104" t="n">
-        <v>0.01651370850045453</v>
+        <v>0.01651382145753622</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.006944410581963822</v>
+        <v>-0.00694441013640712</v>
       </c>
     </row>
     <row r="105">
@@ -9649,10 +9649,10 @@
         <v>45355</v>
       </c>
       <c r="B105" t="n">
-        <v>0.005415252937340576</v>
+        <v>0.005415253519855723</v>
       </c>
       <c r="C105" t="n">
-        <v>0.006992972655270435</v>
+        <v>0.006992972203460512</v>
       </c>
     </row>
     <row r="106">
@@ -9660,10 +9660,10 @@
         <v>45356</v>
       </c>
       <c r="B106" t="n">
-        <v>-0.006283945222879228</v>
+        <v>-0.006283731915360247</v>
       </c>
       <c r="C106" t="n">
-        <v>0.01388894948490682</v>
+        <v>0.01388888443329961</v>
       </c>
     </row>
     <row r="107">
@@ -9671,10 +9671,10 @@
         <v>45357</v>
       </c>
       <c r="B107" t="n">
-        <v>-0.01445336329619629</v>
+        <v>-0.01445346940651981</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.01643827502526829</v>
+        <v>-0.01643840158841814</v>
       </c>
     </row>
     <row r="108">
@@ -9682,10 +9682,10 @@
         <v>45358</v>
       </c>
       <c r="B108" t="n">
-        <v>0.02016506986246003</v>
+        <v>0.02016496061701822</v>
       </c>
       <c r="C108" t="n">
-        <v>0.002785372662942986</v>
+        <v>0.002785566038986165</v>
       </c>
     </row>
     <row r="109">
@@ -9693,10 +9693,10 @@
         <v>45359</v>
       </c>
       <c r="B109" t="n">
-        <v>-0.0116803031820083</v>
+        <v>-0.01168019734675019</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.02777783480932405</v>
+        <v>-0.0277778330270847</v>
       </c>
     </row>
     <row r="110">
@@ -9707,7 +9707,7 @@
         <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>0.004285891620080085</v>
+        <v>0.004285825343592675</v>
       </c>
     </row>
     <row r="111">
@@ -9718,7 +9718,7 @@
         <v>0.01727276578680459</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.004267601144098743</v>
+        <v>-0.004267535432083136</v>
       </c>
     </row>
     <row r="112">
@@ -9726,10 +9726,10 @@
         <v>45364</v>
       </c>
       <c r="B112" t="n">
-        <v>0.04557642892329805</v>
+        <v>0.04557632241142873</v>
       </c>
       <c r="C112" t="n">
-        <v>0.01142851637101172</v>
+        <v>0.01142858161044824</v>
       </c>
     </row>
     <row r="113">
@@ -9740,7 +9740,7 @@
         <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.004237072209072212</v>
+        <v>-0.004237332647968772</v>
       </c>
     </row>
     <row r="114">
@@ -9748,10 +9748,10 @@
         <v>45366</v>
       </c>
       <c r="B114" t="n">
-        <v>-0.008547016383088746</v>
+        <v>-0.008546915384712528</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.01149436961457384</v>
+        <v>-0.01149424006970878</v>
       </c>
     </row>
     <row r="115">
@@ -9759,7 +9759,7 @@
         <v>45369</v>
       </c>
       <c r="B115" t="n">
-        <v>-0.02586199013359503</v>
+        <v>-0.02586209288081953</v>
       </c>
       <c r="C115" t="n">
         <v>-0.01308138060756903</v>
@@ -9770,7 +9770,7 @@
         <v>45370</v>
       </c>
       <c r="B116" t="n">
-        <v>-0.008849670464400217</v>
+        <v>-0.008849565922789959</v>
       </c>
       <c r="C116" t="n">
         <v>-0.001472752368446684</v>
@@ -9781,7 +9781,7 @@
         <v>45371</v>
       </c>
       <c r="B117" t="n">
-        <v>0.0223214499497979</v>
+        <v>0.02232155636656952</v>
       </c>
       <c r="C117" t="n">
         <v>0.002949849134192384</v>
@@ -9792,10 +9792,10 @@
         <v>45372</v>
       </c>
       <c r="B118" t="n">
-        <v>0.01484713384415359</v>
+        <v>0.01484702820541894</v>
       </c>
       <c r="C118" t="n">
-        <v>0.005882413301823375</v>
+        <v>0.005882346234437952</v>
       </c>
     </row>
     <row r="119">
@@ -9806,7 +9806,7 @@
         <v>-0.01118755681758155</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.008771985972076735</v>
+        <v>-0.008771919881771617</v>
       </c>
     </row>
     <row r="120">
@@ -9825,7 +9825,7 @@
         <v>45377</v>
       </c>
       <c r="B121" t="n">
-        <v>0.008772148095238297</v>
+        <v>0.008772043545418162</v>
       </c>
       <c r="C121" t="n">
         <v>0.00594352955718036</v>
@@ -9836,7 +9836,7 @@
         <v>45378</v>
       </c>
       <c r="B122" t="n">
-        <v>0.001739090420472156</v>
+        <v>0.001739194241392239</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -9847,7 +9847,7 @@
         <v>45379</v>
       </c>
       <c r="B123" t="n">
-        <v>0.01649288365984503</v>
+        <v>0.0164930905813272</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -9858,7 +9858,7 @@
         <v>45380</v>
       </c>
       <c r="B124" t="n">
-        <v>-0.005123607188826318</v>
+        <v>-0.005123809709925209</v>
       </c>
       <c r="C124" t="n">
         <v>-0.001477103182868755</v>
@@ -9869,7 +9869,7 @@
         <v>45383</v>
       </c>
       <c r="B125" t="n">
-        <v>0.002575150326229014</v>
+        <v>0.002574945713752275</v>
       </c>
       <c r="C125" t="n">
         <v>-0.008875729465455895</v>
@@ -9880,7 +9880,7 @@
         <v>45384</v>
       </c>
       <c r="B126" t="n">
-        <v>0.001712187234240492</v>
+        <v>0.001712289627157526</v>
       </c>
       <c r="C126" t="n">
         <v>0.004477606758973351</v>
@@ -9891,7 +9891,7 @@
         <v>45385</v>
       </c>
       <c r="B127" t="n">
-        <v>-0.01623924963263479</v>
+        <v>-0.01623904754880645</v>
       </c>
       <c r="C127" t="n">
         <v>-0.008915294335770541</v>
@@ -9902,7 +9902,7 @@
         <v>45386</v>
       </c>
       <c r="B128" t="n">
-        <v>-0.009557101543401392</v>
+        <v>-0.009557204104373662</v>
       </c>
       <c r="C128" t="n">
         <v>0.02248872948199576</v>
@@ -9924,7 +9924,7 @@
         <v>45390</v>
       </c>
       <c r="B130" t="n">
-        <v>-0.009674465976103108</v>
+        <v>-0.009674570801773807</v>
       </c>
       <c r="C130" t="n">
         <v>-0.01325477131602015</v>
@@ -9935,7 +9935,7 @@
         <v>45391</v>
       </c>
       <c r="B131" t="n">
-        <v>0.003552422121869681</v>
+        <v>0.003552422497892449</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -9946,7 +9946,7 @@
         <v>45392</v>
       </c>
       <c r="B132" t="n">
-        <v>0.0070795887064945</v>
+        <v>0.007079800403273273</v>
       </c>
       <c r="C132" t="n">
         <v>-0.002985139241038826</v>
@@ -9957,10 +9957,10 @@
         <v>45393</v>
       </c>
       <c r="B133" t="n">
-        <v>0.009666068603196853</v>
+        <v>0.009665962857298371</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.002993872161139888</v>
+        <v>-0.002993940433331788</v>
       </c>
     </row>
     <row r="134">
@@ -9968,10 +9968,10 @@
         <v>45394</v>
       </c>
       <c r="B134" t="n">
-        <v>0.005222019866330418</v>
+        <v>0.005221916135452087</v>
       </c>
       <c r="C134" t="n">
-        <v>0.001501431173562384</v>
+        <v>0.001501499753584712</v>
       </c>
     </row>
     <row r="135">
@@ -9979,10 +9979,10 @@
         <v>45397</v>
       </c>
       <c r="B135" t="n">
-        <v>-0.03376628227987877</v>
+        <v>-0.03376628576428964</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.0269865437529393</v>
+        <v>-0.02698647537839494</v>
       </c>
     </row>
     <row r="136">
@@ -9990,10 +9990,10 @@
         <v>45398</v>
       </c>
       <c r="B136" t="n">
-        <v>0.01254483521307037</v>
+        <v>0.01254483655283622</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.01386747285206236</v>
+        <v>-0.01386754214849084</v>
       </c>
     </row>
     <row r="137">
@@ -10001,7 +10001,7 @@
         <v>45399</v>
       </c>
       <c r="B137" t="n">
-        <v>-0.01061964674728755</v>
+        <v>-0.01061943691733613</v>
       </c>
       <c r="C137" t="n">
         <v>0.003124996437045224</v>
@@ -10012,7 +10012,7 @@
         <v>45401</v>
       </c>
       <c r="B138" t="n">
-        <v>-0.02504447117204112</v>
+        <v>-0.02504478832353352</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -10023,7 +10023,7 @@
         <v>45404</v>
       </c>
       <c r="B139" t="n">
-        <v>0.01192654902605272</v>
+        <v>0.01192655163428591</v>
       </c>
       <c r="C139" t="n">
         <v>-0.003115261256717461</v>
@@ -10034,10 +10034,10 @@
         <v>45405</v>
       </c>
       <c r="B140" t="n">
-        <v>0.01813216505087367</v>
+        <v>0.01813238508334591</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.007812562351709795</v>
+        <v>-0.007812491092612839</v>
       </c>
     </row>
     <row r="141">
@@ -10045,10 +10045,10 @@
         <v>45406</v>
       </c>
       <c r="B141" t="n">
-        <v>0.0694568191985192</v>
+        <v>0.069456925331014</v>
       </c>
       <c r="C141" t="n">
-        <v>0.007874079085527841</v>
+        <v>0.007874006699818414</v>
       </c>
     </row>
     <row r="142">
@@ -10056,7 +10056,7 @@
         <v>45407</v>
       </c>
       <c r="B142" t="n">
-        <v>0.02581212747925399</v>
+        <v>0.02581192643843599</v>
       </c>
       <c r="C142" t="n">
         <v>0.01093748752965795</v>
@@ -10070,7 +10070,7 @@
         <v>0</v>
       </c>
       <c r="C143" t="n">
-        <v>0.004636850421007921</v>
+        <v>0.004636779932874147</v>
       </c>
     </row>
     <row r="144">
@@ -10078,10 +10078,10 @@
         <v>45414</v>
       </c>
       <c r="B144" t="n">
-        <v>0.03327893502764279</v>
+        <v>0.0332791317321417</v>
       </c>
       <c r="C144" t="n">
-        <v>0.006153838813737877</v>
+        <v>0.006153839245508497</v>
       </c>
     </row>
     <row r="145">
@@ -10089,10 +10089,10 @@
         <v>45415</v>
       </c>
       <c r="B145" t="n">
-        <v>-0.01099748574861192</v>
+        <v>-0.01099748471895379</v>
       </c>
       <c r="C145" t="n">
-        <v>0.003058100350237458</v>
+        <v>0.003058100563489985</v>
       </c>
     </row>
     <row r="146">
@@ -10100,10 +10100,10 @@
         <v>45418</v>
       </c>
       <c r="B146" t="n">
-        <v>0.01350275336584295</v>
+        <v>0.01350256275197026</v>
       </c>
       <c r="C146" t="n">
-        <v>0.00304877688457883</v>
+        <v>0.003048846617605072</v>
       </c>
     </row>
     <row r="147">
@@ -10111,7 +10111,7 @@
         <v>45419</v>
       </c>
       <c r="B147" t="n">
-        <v>0.02899675935275225</v>
+        <v>0.02899685546781039</v>
       </c>
       <c r="C147" t="n">
         <v>0.0334346110610193</v>
@@ -10133,10 +10133,10 @@
         <v>45421</v>
       </c>
       <c r="B149" t="n">
-        <v>-0.005343570901394146</v>
+        <v>-0.005343479919120431</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.01914571362364781</v>
+        <v>-0.01914578078980689</v>
       </c>
     </row>
     <row r="150">
@@ -10144,10 +10144,10 @@
         <v>45422</v>
       </c>
       <c r="B150" t="n">
-        <v>0.005372278050056689</v>
+        <v>0.005372186087601261</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.001501568127970199</v>
+        <v>-0.001501568230793393</v>
       </c>
     </row>
     <row r="151">
@@ -10158,7 +10158,7 @@
         <v>-0.009923709543822157</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.01052630351723061</v>
+        <v>-0.01052623565894006</v>
       </c>
     </row>
     <row r="152">
@@ -10166,10 +10166,10 @@
         <v>45426</v>
       </c>
       <c r="B152" t="n">
-        <v>0.006168122837556966</v>
+        <v>0.006168030943351832</v>
       </c>
       <c r="C152" t="n">
-        <v>0.01063828533759703</v>
+        <v>0.01063821602783976</v>
       </c>
     </row>
     <row r="153">
@@ -10177,10 +10177,10 @@
         <v>45427</v>
       </c>
       <c r="B153" t="n">
-        <v>0.02758630515596527</v>
+        <v>0.02758639900632009</v>
       </c>
       <c r="C153" t="n">
-        <v>0.007518788226593243</v>
+        <v>0.007518857322419636</v>
       </c>
     </row>
     <row r="154">
@@ -10191,7 +10191,7 @@
         <v>0.009694212615861675</v>
       </c>
       <c r="C154" t="n">
-        <v>0.002985071172648901</v>
+        <v>0.002985139241038715</v>
       </c>
     </row>
     <row r="155">
@@ -10202,7 +10202,7 @@
         <v>-0.006647083299846868</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.002976187042503908</v>
+        <v>-0.002976254706323678</v>
       </c>
     </row>
     <row r="156">
@@ -10213,7 +10213,7 @@
         <v>-0.01115233861311593</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.008955145449556667</v>
+        <v>-0.008955213517946592</v>
       </c>
     </row>
     <row r="157">
@@ -10224,7 +10224,7 @@
         <v>0.02255641119115448</v>
       </c>
       <c r="C157" t="n">
-        <v>-0.003012181835889693</v>
+        <v>-0.003011975992381677</v>
       </c>
     </row>
     <row r="158">
@@ -10232,10 +10232,10 @@
         <v>45434</v>
       </c>
       <c r="B158" t="n">
-        <v>0.0147057199661158</v>
+        <v>0.01470580760345008</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.006042220521380703</v>
+        <v>-0.006042357470797843</v>
       </c>
     </row>
     <row r="159">
@@ -10243,7 +10243,7 @@
         <v>45435</v>
       </c>
       <c r="B159" t="n">
-        <v>-0.003623019426410967</v>
+        <v>-0.003623105480735189</v>
       </c>
       <c r="C159" t="n">
         <v>0.01823706057873786</v>
@@ -10287,10 +10287,10 @@
         <v>45441</v>
       </c>
       <c r="B163" t="n">
-        <v>-0.009489094149199517</v>
+        <v>-0.009489007151554429</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.007485021763809385</v>
+        <v>-0.007484953491617374</v>
       </c>
     </row>
     <row r="164">
@@ -10298,10 +10298,10 @@
         <v>45442</v>
       </c>
       <c r="B164" t="n">
-        <v>-0.005158407309794555</v>
+        <v>-0.005158406856726083</v>
       </c>
       <c r="C164" t="n">
-        <v>-0.009049695008473524</v>
+        <v>-0.009049831960091348</v>
       </c>
     </row>
     <row r="165">
@@ -10309,10 +10309,10 @@
         <v>45443</v>
       </c>
       <c r="B165" t="n">
-        <v>-0.002962983236159289</v>
+        <v>-0.002963071261060435</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.00456620465726354</v>
+        <v>-0.004566204974227883</v>
       </c>
     </row>
     <row r="166">
@@ -10334,7 +10334,7 @@
         <v>0.03343233392061884</v>
       </c>
       <c r="C167" t="n">
-        <v>0.009174301050712153</v>
+        <v>0.009174371424144345</v>
       </c>
     </row>
     <row r="168">
@@ -10356,7 +10356,7 @@
         <v>-0.003568882468740098</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.01897808070992224</v>
+        <v>-0.01897801413207922</v>
       </c>
     </row>
     <row r="170">
@@ -10367,7 +10367,7 @@
         <v>0.01719192374710232</v>
       </c>
       <c r="C170" t="n">
-        <v>0.008928561127511614</v>
+        <v>0.008928492655766673</v>
       </c>
     </row>
     <row r="171">
@@ -10378,7 +10378,7 @@
         <v>0.01408443611181509</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.008849547402576929</v>
+        <v>-0.008849480137352872</v>
       </c>
     </row>
     <row r="172">
@@ -10386,10 +10386,10 @@
         <v>45454</v>
       </c>
       <c r="B172" t="n">
-        <v>0.01736129389177643</v>
+        <v>0.01736121112317335</v>
       </c>
       <c r="C172" t="n">
-        <v>-0.01041665464876362</v>
+        <v>-0.01041678967343107</v>
       </c>
     </row>
     <row r="173">
@@ -10397,10 +10397,10 @@
         <v>45455</v>
       </c>
       <c r="B173" t="n">
-        <v>0.04437547069620451</v>
+        <v>0.044375555662584</v>
       </c>
       <c r="C173" t="n">
-        <v>0.007518788226593243</v>
+        <v>0.007518857322419636</v>
       </c>
     </row>
     <row r="174">
@@ -10408,10 +10408,10 @@
         <v>45456</v>
       </c>
       <c r="B174" t="n">
-        <v>-0.0151514207280784</v>
+        <v>-0.01515149862741372</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.001492467517934526</v>
+        <v>-0.00149253558632445</v>
       </c>
     </row>
     <row r="175">
@@ -10419,10 +10419,10 @@
         <v>45457</v>
       </c>
       <c r="B175" t="n">
-        <v>0.007692338114530406</v>
+        <v>0.007692338722977254</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.01046350167742838</v>
+        <v>-0.01046329788031775</v>
       </c>
     </row>
     <row r="176">
@@ -10430,10 +10430,10 @@
         <v>45460</v>
       </c>
       <c r="B176" t="n">
-        <v>-0.01679402183592549</v>
+        <v>-0.01679386616618905</v>
       </c>
       <c r="C176" t="n">
-        <v>-0.003021075815204055</v>
+        <v>-0.003021213180880333</v>
       </c>
     </row>
     <row r="177">
@@ -10441,10 +10441,10 @@
         <v>45461</v>
       </c>
       <c r="B177" t="n">
-        <v>-0.006211061611808733</v>
+        <v>-0.006211220785383609</v>
       </c>
       <c r="C177" t="n">
-        <v>-0.001515149735310084</v>
+        <v>-0.001515218835038024</v>
       </c>
     </row>
     <row r="178">
@@ -10452,10 +10452,10 @@
         <v>45462</v>
       </c>
       <c r="B178" t="n">
-        <v>0.02734365680037865</v>
+        <v>0.02734373933068213</v>
       </c>
       <c r="C178" t="n">
-        <v>-0.009104693385633578</v>
+        <v>-0.009104624811132056</v>
       </c>
     </row>
     <row r="179">
@@ -10474,7 +10474,7 @@
         <v>45464</v>
       </c>
       <c r="B180" t="n">
-        <v>0.0210053514843902</v>
+        <v>0.0210052743447644</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -10485,10 +10485,10 @@
         <v>45467</v>
       </c>
       <c r="B181" t="n">
-        <v>-0.02939026998651917</v>
+        <v>-0.02939012110178696</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.007575679576822258</v>
+        <v>-0.007575748676550198</v>
       </c>
     </row>
     <row r="182">
@@ -10496,7 +10496,7 @@
         <v>45468</v>
       </c>
       <c r="B182" t="n">
-        <v>-0.01589694869658254</v>
+        <v>-0.01589710313987769</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
@@ -10507,10 +10507,10 @@
         <v>45469</v>
       </c>
       <c r="B183" t="n">
-        <v>0.01384614532793149</v>
+        <v>0.01384622552091619</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.004580286185900562</v>
+        <v>-0.004580216877606902</v>
       </c>
     </row>
     <row r="184">
@@ -10532,7 +10532,7 @@
         <v>-0.01731932334490727</v>
       </c>
       <c r="C185" t="n">
-        <v>0.003062853340343397</v>
+        <v>0.003062783499884203</v>
       </c>
     </row>
     <row r="186">
@@ -10543,7 +10543,7 @@
         <v>-0.0145592963441451</v>
       </c>
       <c r="C186" t="n">
-        <v>0.007633508591961879</v>
+        <v>0.007633578750667835</v>
       </c>
     </row>
     <row r="187">
@@ -10551,10 +10551,10 @@
         <v>45475</v>
       </c>
       <c r="B187" t="n">
-        <v>-0.004665600388408242</v>
+        <v>-0.004665680347283763</v>
       </c>
       <c r="C187" t="n">
-        <v>0.003030230370892006</v>
+        <v>0.003030368570348108</v>
       </c>
     </row>
     <row r="188">
@@ -10562,7 +10562,7 @@
         <v>45476</v>
       </c>
       <c r="B188" t="n">
-        <v>0.0234375119245307</v>
+        <v>0.02343751380735237</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
@@ -10573,10 +10573,10 @@
         <v>45477</v>
       </c>
       <c r="B189" t="n">
-        <v>0.03664114539666974</v>
+        <v>0.03664130526074527</v>
       </c>
       <c r="C189" t="n">
-        <v>0.003021282488121502</v>
+        <v>0.003021075398954354</v>
       </c>
     </row>
     <row r="190">
@@ -10584,10 +10584,10 @@
         <v>45478</v>
       </c>
       <c r="B190" t="n">
-        <v>0.0213549509553268</v>
+        <v>0.02135487361881916</v>
       </c>
       <c r="C190" t="n">
-        <v>0.01204810919241583</v>
+        <v>0.01204824738685173</v>
       </c>
     </row>
     <row r="191">
@@ -10598,7 +10598,7 @@
         <v>0.0064888580481679</v>
       </c>
       <c r="C191" t="n">
-        <v>0.005952374085007817</v>
+        <v>0.005952305815243975</v>
       </c>
     </row>
     <row r="192">
@@ -10617,7 +10617,7 @@
         <v>45483</v>
       </c>
       <c r="B193" t="n">
-        <v>-0.02545460990420323</v>
+        <v>-0.02545453512084506</v>
       </c>
       <c r="C193" t="n">
         <v>-0.01037049288674219</v>
@@ -10628,10 +10628,10 @@
         <v>45484</v>
       </c>
       <c r="B194" t="n">
-        <v>-0.007462563444911252</v>
+        <v>-0.007462639608913135</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.007485021763809385</v>
+        <v>-0.007484953491617374</v>
       </c>
     </row>
     <row r="195">
@@ -10650,10 +10650,10 @@
         <v>45488</v>
       </c>
       <c r="B196" t="n">
-        <v>-0.008221250752759035</v>
+        <v>-0.008221173901402201</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.001508293965923002</v>
+        <v>-0.001508225075112057</v>
       </c>
     </row>
     <row r="197">
@@ -10661,10 +10661,10 @@
         <v>45489</v>
       </c>
       <c r="B197" t="n">
-        <v>0.009796472045746629</v>
+        <v>0.009796471286633635</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.001510503462115786</v>
+        <v>-0.001510641035921689</v>
       </c>
     </row>
     <row r="198">
@@ -10672,10 +10672,10 @@
         <v>45490</v>
       </c>
       <c r="B198" t="n">
-        <v>-0.01567154438129958</v>
+        <v>-0.0156716199153718</v>
       </c>
       <c r="C198" t="n">
-        <v>-0.006051430118497847</v>
+        <v>-0.006051499113687742</v>
       </c>
     </row>
     <row r="199">
@@ -10683,10 +10683,10 @@
         <v>45491</v>
       </c>
       <c r="B199" t="n">
-        <v>-0.03032604692658414</v>
+        <v>-0.03032596896819584</v>
       </c>
       <c r="C199" t="n">
-        <v>0.003044136438175693</v>
+        <v>0.003044136649485329</v>
       </c>
     </row>
     <row r="200">
@@ -10694,10 +10694,10 @@
         <v>45492</v>
       </c>
       <c r="B200" t="n">
-        <v>-0.01485542338282242</v>
+        <v>-0.01485550258498836</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.009104693385633578</v>
+        <v>-0.009104624811132056</v>
       </c>
     </row>
     <row r="201">
@@ -10705,10 +10705,10 @@
         <v>45495</v>
       </c>
       <c r="B201" t="n">
-        <v>-0.01507927155305522</v>
+        <v>-0.01507935316188513</v>
       </c>
       <c r="C201" t="n">
-        <v>0.001531391749942212</v>
+        <v>0.001531321909482797</v>
       </c>
     </row>
     <row r="202">
@@ -10716,10 +10716,10 @@
         <v>45496</v>
       </c>
       <c r="B202" t="n">
-        <v>0.01128123663651426</v>
+        <v>0.01128132042953722</v>
       </c>
       <c r="C202" t="n">
-        <v>0.007645250875593312</v>
+        <v>0.007645251408724851</v>
       </c>
     </row>
     <row r="203">
@@ -10730,7 +10730,7 @@
         <v>0.003983956675945866</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.004552346692816789</v>
+        <v>-0.004552347007860003</v>
       </c>
     </row>
     <row r="204">
@@ -10738,7 +10738,7 @@
         <v>45498</v>
       </c>
       <c r="B204" t="n">
-        <v>-0.007936458712134331</v>
+        <v>-0.007936540320964247</v>
       </c>
       <c r="C204" t="n">
         <v>0</v>
@@ -10749,10 +10749,10 @@
         <v>45502</v>
       </c>
       <c r="B205" t="n">
-        <v>0.03200004672464352</v>
+        <v>0.03200004935702205</v>
       </c>
       <c r="C205" t="n">
-        <v>0.02439021507663064</v>
+        <v>0.02439035581440874</v>
       </c>
     </row>
     <row r="206">
@@ -10760,10 +10760,10 @@
         <v>45503</v>
       </c>
       <c r="B206" t="n">
-        <v>-0.007751889169267723</v>
+        <v>-0.007751889787178112</v>
       </c>
       <c r="C206" t="n">
-        <v>0.007440467606259604</v>
+        <v>0.007440399235505435</v>
       </c>
     </row>
     <row r="207">
@@ -10771,7 +10771,7 @@
         <v>45504</v>
       </c>
       <c r="B207" t="n">
-        <v>0.004687470251433901</v>
+        <v>0.004687550961682607</v>
       </c>
       <c r="C207" t="n">
         <v>0.05760715886104273</v>
@@ -10785,7 +10785,7 @@
         <v>-0.02954896237766991</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.01815646630319168</v>
+        <v>-0.01815640260791396</v>
       </c>
     </row>
     <row r="209">
@@ -10793,10 +10793,10 @@
         <v>45506</v>
       </c>
       <c r="B209" t="n">
-        <v>-0.01282059627035848</v>
+        <v>-0.01282051387684002</v>
       </c>
       <c r="C209" t="n">
-        <v>0.01706968134765385</v>
+        <v>0.0170696802402901</v>
       </c>
     </row>
     <row r="210">
@@ -10804,10 +10804,10 @@
         <v>45509</v>
       </c>
       <c r="B210" t="n">
-        <v>-0.037337679003278</v>
+        <v>-0.03733775935050654</v>
       </c>
       <c r="C210" t="n">
-        <v>-0.02937065943402983</v>
+        <v>-0.02937072134500296</v>
       </c>
     </row>
     <row r="211">
@@ -10818,7 +10818,7 @@
         <v>0.0185498046544792</v>
       </c>
       <c r="C211" t="n">
-        <v>0.04755051058478954</v>
+        <v>0.04755044487034699</v>
       </c>
     </row>
     <row r="212">
@@ -10829,7 +10829,7 @@
         <v>0.009933797383254284</v>
       </c>
       <c r="C212" t="n">
-        <v>0.0151305932369894</v>
+        <v>0.01513078238074561</v>
       </c>
     </row>
     <row r="213">
@@ -10840,7 +10840,7 @@
         <v>-0.004918085982852261</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.0149050706754309</v>
+        <v>-0.01490525422277122</v>
       </c>
     </row>
     <row r="214">
@@ -10848,10 +10848,10 @@
         <v>45513</v>
       </c>
       <c r="B214" t="n">
-        <v>0.04530466303197356</v>
+        <v>0.04530483243414651</v>
       </c>
       <c r="C214" t="n">
-        <v>0.008253022342209482</v>
+        <v>0.008253022859934234</v>
       </c>
     </row>
     <row r="215">
@@ -10859,10 +10859,10 @@
         <v>45516</v>
       </c>
       <c r="B215" t="n">
-        <v>0.0244288576845777</v>
+        <v>0.02442861063553226</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.004092702639021728</v>
+        <v>-0.00409264067561832</v>
       </c>
     </row>
     <row r="216">
@@ -10870,10 +10870,10 @@
         <v>45517</v>
       </c>
       <c r="B216" t="n">
-        <v>-0.002307756802804484</v>
+        <v>-0.002307677887557591</v>
       </c>
       <c r="C216" t="n">
-        <v>0.0109588286276352</v>
+        <v>0.01095895357508714</v>
       </c>
     </row>
     <row r="217">
@@ -10884,7 +10884,7 @@
         <v>-0.001542010388313919</v>
       </c>
       <c r="C217" t="n">
-        <v>0.002710085882315694</v>
+        <v>0.00270990015786543</v>
       </c>
     </row>
     <row r="218">
@@ -10892,10 +10892,10 @@
         <v>45519</v>
       </c>
       <c r="B218" t="n">
-        <v>-0.006177567426401631</v>
+        <v>-0.006177646829581884</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.002702761167432621</v>
+        <v>-0.002702576445528959</v>
       </c>
     </row>
     <row r="219">
@@ -10903,7 +10903,7 @@
         <v>45520</v>
       </c>
       <c r="B219" t="n">
-        <v>0.01476300147793008</v>
+        <v>0.01476316245095433</v>
       </c>
       <c r="C219" t="n">
         <v>0</v>
@@ -10914,10 +10914,10 @@
         <v>45523</v>
       </c>
       <c r="B220" t="n">
-        <v>-0.0007657706955317423</v>
+        <v>-0.0007658493696249824</v>
       </c>
       <c r="C220" t="n">
-        <v>0.02981032674038753</v>
+        <v>0.02981026125953878</v>
       </c>
     </row>
     <row r="221">
@@ -10928,7 +10928,7 @@
         <v>0.007662866344280594</v>
       </c>
       <c r="C221" t="n">
-        <v>-0.005263151893970752</v>
+        <v>-0.005263271593455299</v>
       </c>
     </row>
     <row r="222">
@@ -10939,7 +10939,7 @@
         <v>0.01520910852796531</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.003968309745089438</v>
+        <v>-0.003968189334148886</v>
       </c>
     </row>
     <row r="223">
@@ -10950,7 +10950,7 @@
         <v>0.002247254015187217</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.01460809667514162</v>
+        <v>-0.01460821692139502</v>
       </c>
     </row>
     <row r="224">
@@ -10961,7 +10961,7 @@
         <v>-0.005231732970431002</v>
       </c>
       <c r="C224" t="n">
-        <v>0.009433766277189726</v>
+        <v>0.00943407417387232</v>
       </c>
     </row>
     <row r="225">
@@ -10972,7 +10972,7 @@
         <v>-0.01202103884593819</v>
       </c>
       <c r="C225" t="n">
-        <v>-0.02002655976189982</v>
+        <v>-0.0200268593290136</v>
       </c>
     </row>
     <row r="226">
@@ -10983,7 +10983,7 @@
         <v>0.01368820549472161</v>
       </c>
       <c r="C226" t="n">
-        <v>0.006811794659235426</v>
+        <v>0.006811919349022144</v>
       </c>
     </row>
     <row r="227">
@@ -10994,7 +10994,7 @@
         <v>0.003000808577556136</v>
       </c>
       <c r="C227" t="n">
-        <v>-0.00541259112140291</v>
+        <v>-0.005412652500266901</v>
       </c>
     </row>
     <row r="228">
@@ -11005,7 +11005,7 @@
         <v>0.008227322833380013</v>
       </c>
       <c r="C228" t="n">
-        <v>0.005442046695026681</v>
+        <v>0.005442108743765495</v>
       </c>
     </row>
     <row r="229">
@@ -11016,7 +11016,7 @@
         <v>-0.01335303220243333</v>
       </c>
       <c r="C229" t="n">
-        <v>0.005412837972980755</v>
+        <v>0.005412899351829425</v>
       </c>
     </row>
     <row r="230">
@@ -11024,10 +11024,10 @@
         <v>45540</v>
       </c>
       <c r="B230" t="n">
-        <v>-0.01804515300828835</v>
+        <v>-0.01804507569467062</v>
       </c>
       <c r="C230" t="n">
-        <v>0.005383635513346974</v>
+        <v>0.00538351209115806</v>
       </c>
     </row>
     <row r="231">
@@ -11035,10 +11035,10 @@
         <v>45541</v>
       </c>
       <c r="B231" t="n">
-        <v>0.01148537941709771</v>
+        <v>0.01148537851280351</v>
       </c>
       <c r="C231" t="n">
-        <v>0.009370744677733578</v>
+        <v>0.009370927833641796</v>
       </c>
     </row>
     <row r="232">
@@ -11046,10 +11046,10 @@
         <v>45544</v>
       </c>
       <c r="B232" t="n">
-        <v>-0.006055980455840992</v>
+        <v>-0.006056057824801009</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.007957490532859879</v>
+        <v>-0.007957610059263986</v>
       </c>
     </row>
     <row r="233">
@@ -11057,10 +11057,10 @@
         <v>45545</v>
       </c>
       <c r="B233" t="n">
-        <v>-0.009900928067613779</v>
+        <v>-0.009901006382251443</v>
       </c>
       <c r="C233" t="n">
-        <v>0.001336774906311344</v>
+        <v>0.001336957735844191</v>
       </c>
     </row>
     <row r="234">
@@ -11068,10 +11068,10 @@
         <v>45546</v>
       </c>
       <c r="B234" t="n">
-        <v>0.004615355410050759</v>
+        <v>0.004615513970685825</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.004005153641098547</v>
+        <v>-0.004005578888197192</v>
       </c>
     </row>
     <row r="235">
@@ -11079,10 +11079,10 @@
         <v>45547</v>
       </c>
       <c r="B235" t="n">
-        <v>0.0130168420737693</v>
+        <v>0.01301676231451054</v>
       </c>
       <c r="C235" t="n">
-        <v>0.001340419800945902</v>
+        <v>0.001340603448228395</v>
       </c>
     </row>
     <row r="236">
@@ -11093,7 +11093,7 @@
         <v>0.005291049703969763</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.02409635759066464</v>
+        <v>-0.02409641864263401</v>
       </c>
     </row>
     <row r="237">
@@ -11104,7 +11104,7 @@
         <v>-0.01428577834556899</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.01371752993875053</v>
+        <v>-0.01371740567805635</v>
       </c>
     </row>
     <row r="238">
@@ -11115,7 +11115,7 @@
         <v>0.01373004783304199</v>
       </c>
       <c r="C238" t="n">
-        <v>0.02086241312534365</v>
+        <v>0.02086228494301912</v>
       </c>
     </row>
     <row r="239">
@@ -11126,7 +11126,7 @@
         <v>0.01279149145502068</v>
       </c>
       <c r="C239" t="n">
-        <v>-0.001362458345079087</v>
+        <v>-0.001362458429733149</v>
       </c>
     </row>
     <row r="240">
@@ -11134,7 +11134,7 @@
         <v>45554</v>
       </c>
       <c r="B240" t="n">
-        <v>0.004457777167979238</v>
+        <v>0.004457700773388362</v>
       </c>
       <c r="C240" t="n">
         <v>0</v>
@@ -11145,10 +11145,10 @@
         <v>45555</v>
       </c>
       <c r="B241" t="n">
-        <v>0.0007395641895171501</v>
+        <v>0.0007396403013228969</v>
       </c>
       <c r="C241" t="n">
-        <v>-0.008185467496082954</v>
+        <v>-0.008185468005366681</v>
       </c>
     </row>
     <row r="242">
@@ -11156,10 +11156,10 @@
         <v>45558</v>
       </c>
       <c r="B242" t="n">
-        <v>-0.009608369291157159</v>
+        <v>-0.009608293291811343</v>
       </c>
       <c r="C242" t="n">
-        <v>0.002751028357911967</v>
+        <v>0.002751028530488142</v>
       </c>
     </row>
     <row r="243">
@@ -11167,10 +11167,10 @@
         <v>45559</v>
       </c>
       <c r="B243" t="n">
-        <v>0.003731473564105636</v>
+        <v>0.003731396541110765</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.00212920998333288</v>
+        <v>-0.002129084997679942</v>
       </c>
     </row>
     <row r="244">
@@ -11181,7 +11181,7 @@
         <v>0.002230392666538572</v>
       </c>
       <c r="C244" t="n">
-        <v>-0.009957389509858694</v>
+        <v>-0.009957451578507026</v>
       </c>
     </row>
     <row r="245">
@@ -11189,7 +11189,7 @@
         <v>45561</v>
       </c>
       <c r="B245" t="n">
-        <v>-0.003709175611787074</v>
+        <v>-0.003709099330540533</v>
       </c>
       <c r="C245" t="n">
         <v>0.01580464564864381</v>
@@ -11200,10 +11200,10 @@
         <v>45562</v>
       </c>
       <c r="B246" t="n">
-        <v>-0.0007446735284946104</v>
+        <v>-0.0007447500367130377</v>
       </c>
       <c r="C246" t="n">
-        <v>0.004243299810959389</v>
+        <v>0.004243237472746575</v>
       </c>
     </row>
     <row r="247">
@@ -11214,7 +11214,7 @@
         <v>0.002235608818950796</v>
       </c>
       <c r="C247" t="n">
-        <v>-0.01267604881910744</v>
+        <v>-0.01267592545634144</v>
       </c>
     </row>
     <row r="248">
@@ -11222,7 +11222,7 @@
         <v>45566</v>
       </c>
       <c r="B248" t="n">
-        <v>0.01040885588363727</v>
+        <v>0.0104087794322536</v>
       </c>
       <c r="C248" t="n">
         <v>0</v>
@@ -11233,7 +11233,7 @@
         <v>45567</v>
       </c>
       <c r="B249" t="n">
-        <v>-0.003679152759027859</v>
+        <v>-0.003679077373590967</v>
       </c>
       <c r="C249" t="n">
         <v>0</v>
@@ -11244,10 +11244,10 @@
         <v>45568</v>
       </c>
       <c r="B250" t="n">
-        <v>-0.01033982083324436</v>
+        <v>-0.01033974489002776</v>
       </c>
       <c r="C250" t="n">
-        <v>0.002853058347271897</v>
+        <v>0.002853058167895162</v>
       </c>
     </row>
     <row r="251">
@@ -11255,10 +11255,10 @@
         <v>45569</v>
       </c>
       <c r="B251" t="n">
-        <v>0.0007463407548171652</v>
+        <v>0.0007463406975454223</v>
       </c>
       <c r="C251" t="n">
-        <v>-0.02560459945280369</v>
+        <v>-0.02560466054048305</v>
       </c>
     </row>
     <row r="252">
@@ -11269,7 +11269,7 @@
         <v>0</v>
       </c>
       <c r="C252" t="n">
-        <v>-0.0204379593979136</v>
+        <v>-0.02043789505759552</v>
       </c>
     </row>
     <row r="253">
@@ -11277,10 +11277,10 @@
         <v>45574</v>
       </c>
       <c r="B253" t="n">
-        <v>0.009694273741121195</v>
+        <v>0.009694196318344783</v>
       </c>
       <c r="C253" t="n">
-        <v>0.01043225810689208</v>
+        <v>0.01043212605620303</v>
       </c>
     </row>
     <row r="254">
@@ -11291,7 +11291,7 @@
         <v>0.03101923467008327</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.001475019254360888</v>
+        <v>-0.001474824336447633</v>
       </c>
     </row>
     <row r="255">
@@ -11299,10 +11299,10 @@
         <v>45579</v>
       </c>
       <c r="B255" t="n">
-        <v>-0.01432670412735948</v>
+        <v>-0.01432663046896976</v>
       </c>
       <c r="C255" t="n">
-        <v>-0.007385535046039449</v>
+        <v>-0.007385599185044556</v>
       </c>
     </row>
     <row r="256">
@@ -11310,10 +11310,10 @@
         <v>45580</v>
       </c>
       <c r="B256" t="n">
-        <v>-0.004360437744606704</v>
+        <v>-0.004360437418755581</v>
       </c>
       <c r="C256" t="n">
-        <v>-0.005952297799970863</v>
+        <v>-0.005952428579579894</v>
       </c>
     </row>
     <row r="257">
@@ -11321,10 +11321,10 @@
         <v>45581</v>
       </c>
       <c r="B257" t="n">
-        <v>-0.005109456837155024</v>
+        <v>-0.005109531509940979</v>
       </c>
       <c r="C257" t="n">
-        <v>0.01047904310139613</v>
+        <v>0.01047910977050237</v>
       </c>
     </row>
     <row r="258">
@@ -11332,7 +11332,7 @@
         <v>45582</v>
       </c>
       <c r="B258" t="n">
-        <v>0.00513569746166409</v>
+        <v>0.005135772903418934</v>
       </c>
       <c r="C258" t="n">
         <v>0.001481444336731919</v>
@@ -11346,7 +11346,7 @@
         <v>0</v>
       </c>
       <c r="C259" t="n">
-        <v>-0.002958505811783807</v>
+        <v>-0.002958571008703226</v>
       </c>
     </row>
     <row r="260">
@@ -11354,10 +11354,10 @@
         <v>45586</v>
       </c>
       <c r="B260" t="n">
-        <v>-0.01094891113590635</v>
+        <v>-0.01094898537040467</v>
       </c>
       <c r="C260" t="n">
-        <v>-0.001483707660548061</v>
+        <v>-0.001483642367186788</v>
       </c>
     </row>
     <row r="261">
@@ -11387,7 +11387,7 @@
         <v>45589</v>
       </c>
       <c r="B263" t="n">
-        <v>0.0007452284804165821</v>
+        <v>0.0007453051027155322</v>
       </c>
       <c r="C263" t="n">
         <v>0.01634470808273436</v>
@@ -11398,7 +11398,7 @@
         <v>45590</v>
       </c>
       <c r="B264" t="n">
-        <v>-0.002233867455002758</v>
+        <v>-0.00223386728396624</v>
       </c>
       <c r="C264" t="n">
         <v>-0.005847999940720383</v>
@@ -11409,10 +11409,10 @@
         <v>45593</v>
       </c>
       <c r="B265" t="n">
-        <v>0.006716452900074055</v>
+        <v>0.006716375648021966</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.01176473562027014</v>
+        <v>-0.01176467080686083</v>
       </c>
     </row>
     <row r="266">
@@ -11423,7 +11423,7 @@
         <v>0.003706502279461565</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.002976116107485716</v>
+        <v>-0.002976247082287498</v>
       </c>
     </row>
     <row r="267">
@@ -11431,10 +11431,10 @@
         <v>45596</v>
       </c>
       <c r="B267" t="n">
-        <v>0.003692738909575333</v>
+        <v>0.003692662966358728</v>
       </c>
       <c r="C267" t="n">
-        <v>-0.01343289384542612</v>
+        <v>-0.01343276316750219</v>
       </c>
     </row>
     <row r="268">
@@ -11442,10 +11442,10 @@
         <v>45597</v>
       </c>
       <c r="B268" t="n">
-        <v>-0.009565872837282385</v>
+        <v>-0.0095657978972572</v>
       </c>
       <c r="C268" t="n">
-        <v>-0.004538464431192768</v>
+        <v>-0.004538597481431483</v>
       </c>
     </row>
     <row r="269">
@@ -11456,7 +11456,7 @@
         <v>-0.013372949530983</v>
       </c>
       <c r="C269" t="n">
-        <v>-0.003039571293184884</v>
+        <v>-0.003039504516355818</v>
       </c>
     </row>
     <row r="270">
@@ -11467,7 +11467,7 @@
         <v>0.01355420928772011</v>
       </c>
       <c r="C270" t="n">
-        <v>0.003048838455030234</v>
+        <v>0.003048771270401485</v>
       </c>
     </row>
     <row r="271">
@@ -11475,10 +11475,10 @@
         <v>45603</v>
       </c>
       <c r="B271" t="n">
-        <v>0.003714763376922114</v>
+        <v>0.003714686982331239</v>
       </c>
       <c r="C271" t="n">
-        <v>0.001519718666176173</v>
+        <v>0.001519785748388403</v>
       </c>
     </row>
     <row r="272">
@@ -11486,7 +11486,7 @@
         <v>45607</v>
       </c>
       <c r="B272" t="n">
-        <v>0.02368608488085222</v>
+        <v>0.0236861627955034</v>
       </c>
       <c r="C272" t="n">
         <v>-0.01062215589630744</v>
@@ -11500,7 +11500,7 @@
         <v>-0.01084599359735738</v>
       </c>
       <c r="C273" t="n">
-        <v>-0.004601314392799205</v>
+        <v>-0.00460124679599605</v>
       </c>
     </row>
     <row r="274">
@@ -11511,7 +11511,7 @@
         <v>0.007309971081375322</v>
       </c>
       <c r="C274" t="n">
-        <v>0.00154092936151895</v>
+        <v>0.001540861347605116</v>
       </c>
     </row>
     <row r="275">
@@ -11519,7 +11519,7 @@
         <v>45610</v>
       </c>
       <c r="B275" t="n">
-        <v>-0.01306240203254438</v>
+        <v>-0.01306232741199365</v>
       </c>
       <c r="C275" t="n">
         <v>0</v>
@@ -11530,7 +11530,7 @@
         <v>45611</v>
       </c>
       <c r="B276" t="n">
-        <v>-0.01544107956981666</v>
+        <v>-0.01544115401051438</v>
       </c>
       <c r="C276" t="n">
         <v>-0.02000004068287564</v>
@@ -11541,7 +11541,7 @@
         <v>45614</v>
       </c>
       <c r="B277" t="n">
-        <v>0.000746667641438048</v>
+        <v>0.0007467444353947972</v>
       </c>
       <c r="C277" t="n">
         <v>-0.007849304533823043</v>
@@ -11552,10 +11552,10 @@
         <v>45615</v>
       </c>
       <c r="B278" t="n">
-        <v>-0.02985063746294481</v>
+        <v>-0.02985078864561497</v>
       </c>
       <c r="C278" t="n">
-        <v>-0.003164477736694815</v>
+        <v>-0.003164547472640278</v>
       </c>
     </row>
     <row r="279">
@@ -11563,10 +11563,10 @@
         <v>45616</v>
       </c>
       <c r="B279" t="n">
-        <v>0.01846142164020326</v>
+        <v>0.01846158129603137</v>
       </c>
       <c r="C279" t="n">
-        <v>0.009523780208359423</v>
+        <v>0.009523780874617804</v>
       </c>
     </row>
     <row r="280">
@@ -11574,10 +11574,10 @@
         <v>45617</v>
       </c>
       <c r="B280" t="n">
-        <v>0.00453184922623362</v>
+        <v>0.004531771210286806</v>
       </c>
       <c r="C280" t="n">
-        <v>0.004716932100930826</v>
+        <v>0.004717001725157655</v>
       </c>
     </row>
     <row r="281">
@@ -11588,7 +11588,7 @@
         <v>0.006766951706512536</v>
       </c>
       <c r="C281" t="n">
-        <v>0.006259762126556101</v>
+        <v>0.006259831098571089</v>
       </c>
     </row>
     <row r="282">
@@ -11607,10 +11607,10 @@
         <v>45622</v>
       </c>
       <c r="B283" t="n">
-        <v>0.00970875277552552</v>
+        <v>0.009708675981568771</v>
       </c>
       <c r="C283" t="n">
-        <v>0.007776060852981326</v>
+        <v>0.007775991777039692</v>
       </c>
     </row>
     <row r="284">
@@ -11618,10 +11618,10 @@
         <v>45623</v>
       </c>
       <c r="B284" t="n">
-        <v>0.02736684117866628</v>
+        <v>0.02736691931562474</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.003086342502536921</v>
+        <v>-0.003086478530678449</v>
       </c>
     </row>
     <row r="285">
@@ -11632,7 +11632,7 @@
         <v>0.003599541046116705</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.001548085200562044</v>
+        <v>-0.001547880737863161</v>
       </c>
     </row>
     <row r="286">
@@ -11640,10 +11640,10 @@
         <v>45625</v>
       </c>
       <c r="B286" t="n">
-        <v>0.03515079664467868</v>
+        <v>0.03515072288059939</v>
       </c>
       <c r="C286" t="n">
-        <v>0.001550485484193675</v>
+        <v>0.001550280387012437</v>
       </c>
     </row>
     <row r="287">
@@ -11651,10 +11651,10 @@
         <v>45628</v>
       </c>
       <c r="B287" t="n">
-        <v>-0.007676261203380719</v>
+        <v>-0.007676190491121004</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.001548085200562044</v>
+        <v>-0.001547880737863161</v>
       </c>
     </row>
     <row r="288">
@@ -11662,10 +11662,10 @@
         <v>45629</v>
       </c>
       <c r="B288" t="n">
-        <v>0.01969065331106346</v>
+        <v>0.01969058150056791</v>
       </c>
       <c r="C288" t="n">
-        <v>-0.009302297931412795</v>
+        <v>-0.009302365626194908</v>
       </c>
     </row>
     <row r="289">
@@ -11673,10 +11673,10 @@
         <v>45630</v>
       </c>
       <c r="B289" t="n">
-        <v>-0.01034490480955153</v>
+        <v>-0.01034483511426931</v>
       </c>
       <c r="C289" t="n">
-        <v>-0.00938971216184914</v>
+        <v>-0.009389643189834262</v>
       </c>
     </row>
     <row r="290">
@@ -11687,7 +11687,7 @@
         <v>0.03484318375583495</v>
       </c>
       <c r="C290" t="n">
-        <v>0.01579781118825019</v>
+        <v>0.01579781008831538</v>
       </c>
     </row>
     <row r="291">
@@ -11698,7 +11698,7 @@
         <v>-0.01010101774145356</v>
       </c>
       <c r="C291" t="n">
-        <v>-0.00311041063260209</v>
+        <v>-0.003110478962352947</v>
       </c>
     </row>
     <row r="292">
@@ -11706,7 +11706,7 @@
         <v>45636</v>
       </c>
       <c r="B292" t="n">
-        <v>0.01700693149247479</v>
+        <v>0.01700686202680934</v>
       </c>
       <c r="C292" t="n">
         <v>-0.003120115472944107</v>
@@ -11717,10 +11717,10 @@
         <v>45637</v>
       </c>
       <c r="B293" t="n">
-        <v>0.00668887640291338</v>
+        <v>0.006688876859790582</v>
       </c>
       <c r="C293" t="n">
-        <v>0.00469485608092457</v>
+        <v>0.004694787108909804</v>
       </c>
     </row>
     <row r="294">
@@ -11728,10 +11728,10 @@
         <v>45638</v>
       </c>
       <c r="B294" t="n">
-        <v>-0.001993370494425606</v>
+        <v>-0.001993302779489725</v>
       </c>
       <c r="C294" t="n">
-        <v>0.006230579424870486</v>
+        <v>0.006230511202879097</v>
       </c>
     </row>
     <row r="295">
@@ -11739,10 +11739,10 @@
         <v>45639</v>
       </c>
       <c r="B295" t="n">
-        <v>-0.004660351927989526</v>
+        <v>-0.004660419913692149</v>
       </c>
       <c r="C295" t="n">
-        <v>-0.006191999679071358</v>
+        <v>-0.006191932299320579</v>
       </c>
     </row>
     <row r="296">
@@ -11750,10 +11750,10 @@
         <v>45642</v>
       </c>
       <c r="B296" t="n">
-        <v>0.002675468596337272</v>
+        <v>0.002675605387138624</v>
       </c>
       <c r="C296" t="n">
-        <v>0.01246109020002684</v>
+        <v>0.01246115970519623</v>
       </c>
     </row>
     <row r="297">
@@ -11761,7 +11761,7 @@
         <v>45644</v>
       </c>
       <c r="B297" t="n">
-        <v>-0.008005329301978059</v>
+        <v>-0.008005465000163192</v>
       </c>
       <c r="C297" t="n">
         <v>-0.004615404435247106</v>
@@ -11772,7 +11772,7 @@
         <v>45645</v>
       </c>
       <c r="B298" t="n">
-        <v>-0.004034931545841558</v>
+        <v>-0.004034863151417878</v>
       </c>
       <c r="C298" t="n">
         <v>-0.0123647910706095</v>
@@ -11783,7 +11783,7 @@
         <v>45646</v>
       </c>
       <c r="B299" t="n">
-        <v>0.009453143293220334</v>
+        <v>0.00945307434350906</v>
       </c>
       <c r="C299" t="n">
         <v>0.01721444930605176</v>
@@ -11794,7 +11794,7 @@
         <v>45649</v>
       </c>
       <c r="B300" t="n">
-        <v>0.002006567295241179</v>
+        <v>0.00200656743229799</v>
       </c>
       <c r="C300" t="n">
         <v>-0.009230876675286881</v>
@@ -11805,10 +11805,10 @@
         <v>45650</v>
       </c>
       <c r="B301" t="n">
-        <v>0.004005370760602478</v>
+        <v>0.004005371033637628</v>
       </c>
       <c r="C301" t="n">
-        <v>-0.001552756243275666</v>
+        <v>-0.001552687806753883</v>
       </c>
     </row>
     <row r="302">
@@ -11816,10 +11816,10 @@
         <v>45651</v>
       </c>
       <c r="B302" t="n">
-        <v>0.002659594511642993</v>
+        <v>0.002659594692216993</v>
       </c>
       <c r="C302" t="n">
-        <v>0.001555171044824943</v>
+        <v>0.001555102395281338</v>
       </c>
     </row>
     <row r="303">
@@ -11827,7 +11827,7 @@
         <v>45652</v>
       </c>
       <c r="B303" t="n">
-        <v>-0.006631349578164802</v>
+        <v>-0.006631350027207938</v>
       </c>
       <c r="C303" t="n">
         <v>-0.001564869507635458</v>
@@ -11838,7 +11838,7 @@
         <v>45653</v>
       </c>
       <c r="B304" t="n">
-        <v>-0.001335123586867493</v>
+        <v>-0.001335055510633287</v>
       </c>
       <c r="C304" t="n">
         <v>0</v>
@@ -11849,10 +11849,10 @@
         <v>45656</v>
       </c>
       <c r="B305" t="n">
-        <v>0.006016088362377214</v>
+        <v>0.006016020104002484</v>
       </c>
       <c r="C305" t="n">
-        <v>-0.007837022074182909</v>
+        <v>-0.007836953530399038</v>
       </c>
     </row>
     <row r="306">
@@ -11860,10 +11860,10 @@
         <v>45657</v>
       </c>
       <c r="B306" t="n">
-        <v>0.01328906877932234</v>
+        <v>0.0132890696809882</v>
       </c>
       <c r="C306" t="n">
-        <v>0.001579771409488062</v>
+        <v>0.001579702215147805</v>
       </c>
     </row>
     <row r="307">
@@ -11871,7 +11871,7 @@
         <v>45659</v>
       </c>
       <c r="B307" t="n">
-        <v>-0.003278780073647014</v>
+        <v>-0.003278646372503635</v>
       </c>
       <c r="C307" t="n">
         <v>-0.004731839004490812</v>
@@ -11882,7 +11882,7 @@
         <v>45660</v>
       </c>
       <c r="B308" t="n">
-        <v>-0.01973679039387122</v>
+        <v>-0.01973678906794163</v>
       </c>
       <c r="C308" t="n">
         <v>-0.001584778585286939</v>
@@ -11893,7 +11893,7 @@
         <v>45663</v>
       </c>
       <c r="B309" t="n">
-        <v>0.00201336946405628</v>
+        <v>0.002013369326073544</v>
       </c>
       <c r="C309" t="n">
         <v>-0.007936470474885993</v>
@@ -11904,7 +11904,7 @@
         <v>45664</v>
       </c>
       <c r="B310" t="n">
-        <v>0.005358379594931462</v>
+        <v>0.005358310832914492</v>
       </c>
       <c r="C310" t="n">
         <v>-0.01280000906804624</v>
@@ -11915,7 +11915,7 @@
         <v>45665</v>
       </c>
       <c r="B311" t="n">
-        <v>-0.01199202785569975</v>
+        <v>-0.01199195982470314</v>
       </c>
       <c r="C311" t="n">
         <v>0</v>
@@ -11926,7 +11926,7 @@
         <v>45666</v>
       </c>
       <c r="B312" t="n">
-        <v>0.003371638560841994</v>
+        <v>0.003371500615234835</v>
       </c>
       <c r="C312" t="n">
         <v>0.001620808723165945</v>
@@ -11937,7 +11937,7 @@
         <v>45670</v>
       </c>
       <c r="B313" t="n">
-        <v>-0.008064576452927352</v>
+        <v>-0.008064508381008473</v>
       </c>
       <c r="C313" t="n">
         <v>-0.006472531526958147</v>
@@ -11951,7 +11951,7 @@
         <v>-0.01693765873671738</v>
       </c>
       <c r="C314" t="n">
-        <v>0.003257313446442645</v>
+        <v>0.00325738466945924</v>
       </c>
     </row>
     <row r="315">
@@ -11962,7 +11962,7 @@
         <v>0.002756740262314095</v>
       </c>
       <c r="C315" t="n">
-        <v>0.00162336890186876</v>
+        <v>0.001623297794853595</v>
       </c>
     </row>
     <row r="316">
@@ -11981,7 +11981,7 @@
         <v>45674</v>
       </c>
       <c r="B317" t="n">
-        <v>0.02405495291222204</v>
+        <v>0.02405502309402374</v>
       </c>
       <c r="C317" t="n">
         <v>0.004862284416067286</v>
@@ -11992,10 +11992,10 @@
         <v>45677</v>
       </c>
       <c r="B318" t="n">
-        <v>0.006711391457743021</v>
+        <v>0.006711390997789835</v>
       </c>
       <c r="C318" t="n">
-        <v>-0.001612895489845667</v>
+        <v>-0.001612966023605722</v>
       </c>
     </row>
     <row r="319">
@@ -12003,10 +12003,10 @@
         <v>45678</v>
       </c>
       <c r="B319" t="n">
-        <v>-0.0006666717043166681</v>
+        <v>-0.0006666716589320831</v>
       </c>
       <c r="C319" t="n">
-        <v>-0.00161550112432296</v>
+        <v>-0.001615430590742095</v>
       </c>
     </row>
     <row r="320">
@@ -12014,10 +12014,10 @@
         <v>45679</v>
       </c>
       <c r="B320" t="n">
-        <v>-0.001334164782191505</v>
+        <v>-0.001334232813066993</v>
       </c>
       <c r="C320" t="n">
-        <v>-0.003236301144490805</v>
+        <v>-0.003236230382467342</v>
       </c>
     </row>
     <row r="321">
@@ -12028,7 +12028,7 @@
         <v>0.03072808062695187</v>
       </c>
       <c r="C321" t="n">
-        <v>0.006493546599249056</v>
+        <v>0.006493475146491567</v>
       </c>
     </row>
     <row r="322">
@@ -12069,7 +12069,7 @@
         <v>45693</v>
       </c>
       <c r="B325" t="n">
-        <v>0.0006839297941036993</v>
+        <v>0.0006838599483323105</v>
       </c>
       <c r="C325" t="n">
         <v>0.02159472770555926</v>
@@ -12080,7 +12080,7 @@
         <v>45694</v>
       </c>
       <c r="B326" t="n">
-        <v>0.001366994505708208</v>
+        <v>0.001367064399161011</v>
       </c>
       <c r="C326" t="n">
         <v>-0.01300821032260491</v>
@@ -12094,7 +12094,7 @@
         <v>-0.002730326468169952</v>
       </c>
       <c r="C327" t="n">
-        <v>0.001647510787564643</v>
+        <v>0.001647582831940442</v>
       </c>
     </row>
     <row r="328">
@@ -12105,7 +12105,7 @@
         <v>-0.02806297272088387</v>
       </c>
       <c r="C328" t="n">
-        <v>-0.003289529994601192</v>
+        <v>-0.003289529757998899</v>
       </c>
     </row>
     <row r="329">
@@ -12116,7 +12116,7 @@
         <v>0.023943627028852</v>
       </c>
       <c r="C329" t="n">
-        <v>-0.003300314552435846</v>
+        <v>-0.003300314314274466</v>
       </c>
     </row>
     <row r="330">
@@ -12124,10 +12124,10 @@
         <v>45700</v>
       </c>
       <c r="B330" t="n">
-        <v>-0.002750912042870701</v>
+        <v>-0.00275098227294579</v>
       </c>
       <c r="C330" t="n">
-        <v>0.009933872889086315</v>
+        <v>0.009933799767646745</v>
       </c>
     </row>
     <row r="331">
@@ -12135,7 +12135,7 @@
         <v>45701</v>
       </c>
       <c r="B331" t="n">
-        <v>-0.01310354609209852</v>
+        <v>-0.01310340616728067</v>
       </c>
       <c r="C331" t="n">
         <v>-0.00491815254452721</v>
@@ -12146,7 +12146,7 @@
         <v>45702</v>
       </c>
       <c r="B332" t="n">
-        <v>0.01257856877962871</v>
+        <v>0.01257856788203648</v>
       </c>
       <c r="C332" t="n">
         <v>-0.006589754972754935</v>
@@ -12157,7 +12157,7 @@
         <v>45705</v>
       </c>
       <c r="B333" t="n">
-        <v>-0.008971631962877424</v>
+        <v>-0.008971772275448431</v>
       </c>
       <c r="C333" t="n">
         <v>-0.004975100925630915</v>
@@ -12168,7 +12168,7 @@
         <v>45706</v>
       </c>
       <c r="B334" t="n">
-        <v>0.002089081127145231</v>
+        <v>0.002089152386098636</v>
       </c>
       <c r="C334" t="n">
         <v>0.004999976312410892</v>
@@ -12182,7 +12182,7 @@
         <v>0.0006950032713550769</v>
       </c>
       <c r="C335" t="n">
-        <v>0.008291907398331411</v>
+        <v>0.00829197992061137</v>
       </c>
     </row>
     <row r="336">
@@ -12193,7 +12193,7 @@
         <v>-0.006944496644190612</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.001644800960239223</v>
+        <v>-0.001644872767807559</v>
       </c>
     </row>
     <row r="337">
@@ -12212,7 +12212,7 @@
         <v>45712</v>
       </c>
       <c r="B338" t="n">
-        <v>-0.01056338813119995</v>
+        <v>-0.01056346004283781</v>
       </c>
       <c r="C338" t="n">
         <v>0.0390879038033447</v>
@@ -12223,7 +12223,7 @@
         <v>45713</v>
       </c>
       <c r="B339" t="n">
-        <v>-0.01067616460163956</v>
+        <v>-0.01067609269819303</v>
       </c>
       <c r="C339" t="n">
         <v>-0.01410658489850203</v>
@@ -12234,7 +12234,7 @@
         <v>45714</v>
       </c>
       <c r="B340" t="n">
-        <v>0.02014389038865017</v>
+        <v>0.02014396385233885</v>
       </c>
       <c r="C340" t="n">
         <v>0.003179635206141285</v>
@@ -12245,7 +12245,7 @@
         <v>45715</v>
       </c>
       <c r="B341" t="n">
-        <v>-0.003526119750958623</v>
+        <v>-0.003526191510092258</v>
       </c>
       <c r="C341" t="n">
         <v>-0.01426300726758234</v>
@@ -12267,7 +12267,7 @@
         <v>45719</v>
       </c>
       <c r="B343" t="n">
-        <v>0.001425527540171556</v>
+        <v>0.001425454757186806</v>
       </c>
       <c r="C343" t="n">
         <v>0.01607709355508713</v>
@@ -12278,10 +12278,10 @@
         <v>45720</v>
       </c>
       <c r="B344" t="n">
-        <v>-0.003558673080961028</v>
+        <v>-0.003558600660219513</v>
       </c>
       <c r="C344" t="n">
-        <v>0.004746813108098769</v>
+        <v>0.00474688230261644</v>
       </c>
     </row>
     <row r="345">
@@ -12289,10 +12289,10 @@
         <v>45721</v>
       </c>
       <c r="B345" t="n">
-        <v>-0.006428546785628098</v>
+        <v>-0.006428619724572315</v>
       </c>
       <c r="C345" t="n">
-        <v>-0.01259836619845178</v>
+        <v>-0.01259843419844364</v>
       </c>
     </row>
     <row r="346">
@@ -12300,7 +12300,7 @@
         <v>45722</v>
       </c>
       <c r="B346" t="n">
-        <v>0.01797259586927313</v>
+        <v>0.017972670599532</v>
       </c>
       <c r="C346" t="n">
         <v>0.003189777535091531</v>
@@ -12311,7 +12311,7 @@
         <v>45723</v>
       </c>
       <c r="B347" t="n">
-        <v>-0.001412367958740002</v>
+        <v>-0.001412440073519594</v>
       </c>
       <c r="C347" t="n">
         <v>-0.003179635206141285</v>
@@ -12322,7 +12322,7 @@
         <v>45726</v>
       </c>
       <c r="B348" t="n">
-        <v>-0.01485152447448213</v>
+        <v>-0.01485145333022997</v>
       </c>
       <c r="C348" t="n">
         <v>-0.003189777535091642</v>
@@ -12366,7 +12366,7 @@
         <v>45730</v>
       </c>
       <c r="B352" t="n">
-        <v>-0.03736276725108834</v>
+        <v>-0.03736269244191726</v>
       </c>
       <c r="C352" t="n">
         <v>0.001612895489845778</v>
@@ -12377,7 +12377,7 @@
         <v>45733</v>
       </c>
       <c r="B353" t="n">
-        <v>-0.01065441582405335</v>
+        <v>-0.01065457042152551</v>
       </c>
       <c r="C353" t="n">
         <v>0.01449268422359107</v>
@@ -12399,7 +12399,7 @@
         <v>45735</v>
       </c>
       <c r="B355" t="n">
-        <v>-0.04153846057169686</v>
+        <v>-0.0415383852848874</v>
       </c>
       <c r="C355" t="n">
         <v>-0.003199984774638454</v>
@@ -12410,7 +12410,7 @@
         <v>45736</v>
       </c>
       <c r="B356" t="n">
-        <v>0.003210215123996996</v>
+        <v>0.003210297077869129</v>
       </c>
       <c r="C356" t="n">
         <v>-0.008025643874802091</v>
@@ -12421,7 +12421,7 @@
         <v>45737</v>
       </c>
       <c r="B357" t="n">
-        <v>0.02400010064408131</v>
+        <v>0.0239999353002387</v>
       </c>
       <c r="C357" t="n">
         <v>-0.008090646718191818</v>
@@ -12432,7 +12432,7 @@
         <v>45740</v>
       </c>
       <c r="B358" t="n">
-        <v>0.007812478809242629</v>
+        <v>0.00781247943249852</v>
       </c>
       <c r="C358" t="n">
         <v>0.001631313573039694</v>
@@ -12443,7 +12443,7 @@
         <v>45741</v>
       </c>
       <c r="B359" t="n">
-        <v>-0.01937991154032637</v>
+        <v>-0.01937983391586107</v>
       </c>
       <c r="C359" t="n">
         <v>0</v>
@@ -12454,7 +12454,7 @@
         <v>45742</v>
       </c>
       <c r="B360" t="n">
-        <v>-0.02766795196435667</v>
+        <v>-0.02766787124140835</v>
       </c>
       <c r="C360" t="n">
         <v>-0.003257313446442645</v>
@@ -12465,7 +12465,7 @@
         <v>45743</v>
       </c>
       <c r="B361" t="n">
-        <v>0.02601629067074218</v>
+        <v>0.0260162054909383</v>
       </c>
       <c r="C361" t="n">
         <v>-0.001633979105332362</v>
@@ -12476,7 +12476,7 @@
         <v>45744</v>
       </c>
       <c r="B362" t="n">
-        <v>-0.01743261594509382</v>
+        <v>-0.01743253503025766</v>
       </c>
       <c r="C362" t="n">
         <v>-0.01309337004727518</v>
@@ -12487,10 +12487,10 @@
         <v>45747</v>
       </c>
       <c r="B363" t="n">
-        <v>-0.02419364734042317</v>
+        <v>-0.02419372769847894</v>
       </c>
       <c r="C363" t="n">
-        <v>0.004975100925630915</v>
+        <v>0.004975173447910874</v>
       </c>
     </row>
     <row r="364">
@@ -12501,7 +12501,7 @@
         <v>-0.004132178398304043</v>
       </c>
       <c r="C364" t="n">
-        <v>0.003300386715696213</v>
+        <v>0.003300386477529615</v>
       </c>
     </row>
     <row r="365">
@@ -12512,7 +12512,7 @@
         <v>0.0124481419224105</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.004934259028963273</v>
+        <v>-0.004934330599934422</v>
       </c>
     </row>
     <row r="366">
@@ -12534,7 +12534,7 @@
         <v>-0.00440514009484505</v>
       </c>
       <c r="C367" t="n">
-        <v>0.03539829515919446</v>
+        <v>0.0353982177593104</v>
       </c>
     </row>
     <row r="368">
@@ -12545,7 +12545,7 @@
         <v>-0.06991148659132418</v>
       </c>
       <c r="C368" t="n">
-        <v>-0.0683760402635547</v>
+        <v>-0.06837604537491915</v>
       </c>
     </row>
     <row r="369">
@@ -12556,7 +12556,7 @@
         <v>0.001902963808321667</v>
       </c>
       <c r="C369" t="n">
-        <v>-0.04587165974928942</v>
+        <v>-0.04587158318979689</v>
       </c>
     </row>
     <row r="370">
@@ -12564,7 +12564,7 @@
         <v>45757</v>
       </c>
       <c r="B370" t="n">
-        <v>0.06932557482812185</v>
+        <v>0.069325671802972</v>
       </c>
       <c r="C370" t="n">
         <v>0.06923077958128632</v>
@@ -12575,10 +12575,10 @@
         <v>45758</v>
       </c>
       <c r="B371" t="n">
-        <v>0.05239799565314951</v>
+        <v>0.05239790021343382</v>
       </c>
       <c r="C371" t="n">
-        <v>0.03417273656233322</v>
+        <v>0.03417265790957313</v>
       </c>
     </row>
     <row r="372">
@@ -12589,7 +12589,7 @@
         <v>0</v>
       </c>
       <c r="C372" t="n">
-        <v>-0.01043480866538671</v>
+        <v>-0.01043473340519407</v>
       </c>
     </row>
     <row r="373">
@@ -12600,7 +12600,7 @@
         <v>-0.02109711840579331</v>
       </c>
       <c r="C373" t="n">
-        <v>-0.01054484207484441</v>
+        <v>-0.01054491893061349</v>
       </c>
     </row>
     <row r="374">
@@ -12611,7 +12611,7 @@
         <v>-0.06982749863245763</v>
       </c>
       <c r="C374" t="n">
-        <v>-0.005328649229908389</v>
+        <v>-0.005328494294122521</v>
       </c>
     </row>
     <row r="375">
@@ -12619,7 +12619,7 @@
         <v>45764</v>
       </c>
       <c r="B375" t="n">
-        <v>0.01390167554876842</v>
+        <v>0.01390158091066085</v>
       </c>
       <c r="C375" t="n">
         <v>0</v>
@@ -12630,10 +12630,10 @@
         <v>45765</v>
       </c>
       <c r="B376" t="n">
-        <v>0.02010965457381131</v>
+        <v>0.02010984313191067</v>
       </c>
       <c r="C376" t="n">
-        <v>0.01071439169487043</v>
+        <v>0.01071431276722246</v>
       </c>
     </row>
     <row r="377">
@@ -12641,7 +12641,7 @@
         <v>45768</v>
       </c>
       <c r="B377" t="n">
-        <v>0.0008961556532882664</v>
+        <v>0.0008961555712896363</v>
       </c>
       <c r="C377" t="n">
         <v>0.001766775988844449</v>
@@ -12652,10 +12652,10 @@
         <v>45769</v>
       </c>
       <c r="B378" t="n">
-        <v>-0.01163840416488282</v>
+        <v>-0.01163858593799993</v>
       </c>
       <c r="C378" t="n">
-        <v>-0.01234577423069616</v>
+        <v>-0.01234569710383226</v>
       </c>
     </row>
     <row r="379">
@@ -12666,7 +12666,7 @@
         <v>0</v>
       </c>
       <c r="C379" t="n">
-        <v>0.0071429017662612</v>
+        <v>0.00714282311751413</v>
       </c>
     </row>
     <row r="380">
@@ -12674,10 +12674,10 @@
         <v>45771</v>
       </c>
       <c r="B380" t="n">
-        <v>0.01449277104979108</v>
+        <v>0.01449286488535373</v>
       </c>
       <c r="C380" t="n">
-        <v>-0.001773041259283459</v>
+        <v>-0.00177311879640063</v>
       </c>
     </row>
     <row r="381">
@@ -12688,7 +12688,7 @@
         <v>0.003571455597913831</v>
       </c>
       <c r="C381" t="n">
-        <v>0.03552404339164994</v>
+        <v>0.03552404615097449</v>
       </c>
     </row>
     <row r="382">
@@ -12699,7 +12699,7 @@
         <v>-0.02580063374599773</v>
       </c>
       <c r="C382" t="n">
-        <v>-0.01372213606470374</v>
+        <v>-0.01372213709400361</v>
       </c>
     </row>
     <row r="383">
@@ -12707,10 +12707,10 @@
         <v>45776</v>
       </c>
       <c r="B383" t="n">
-        <v>-0.0009133420775687684</v>
+        <v>-0.0009134353328350553</v>
       </c>
       <c r="C383" t="n">
-        <v>0.001739122101932056</v>
+        <v>0.001739198287998622</v>
       </c>
     </row>
     <row r="384">
@@ -12718,7 +12718,7 @@
         <v>45782</v>
       </c>
       <c r="B384" t="n">
-        <v>-0.007312576206699228</v>
+        <v>-0.007312390208205399</v>
       </c>
       <c r="C384" t="n">
         <v>0</v>
@@ -12740,7 +12740,7 @@
         <v>45784</v>
       </c>
       <c r="B386" t="n">
-        <v>0.0101288956079284</v>
+        <v>0.01012880062743071</v>
       </c>
       <c r="C386" t="n">
         <v>0</v>
@@ -12773,7 +12773,7 @@
         <v>45789</v>
       </c>
       <c r="B389" t="n">
-        <v>0.03499570949267494</v>
+        <v>0.03499562015363633</v>
       </c>
       <c r="C389" t="n">
         <v>0</v>
@@ -12795,7 +12795,7 @@
         <v>45791</v>
       </c>
       <c r="B391" t="n">
-        <v>0.01014360511532431</v>
+        <v>0.01014369230917955</v>
       </c>
       <c r="C391" t="n">
         <v>0.03356886345695553</v>
@@ -12817,7 +12817,7 @@
         <v>45793</v>
       </c>
       <c r="B393" t="n">
-        <v>-0.01029303067979492</v>
+        <v>-0.01029294982902484</v>
       </c>
       <c r="C393" t="n">
         <v>0.01067624752131158</v>
@@ -12828,7 +12828,7 @@
         <v>45796</v>
       </c>
       <c r="B394" t="n">
-        <v>-0.0543999231445198</v>
+        <v>-0.05440000039211978</v>
       </c>
       <c r="C394" t="n">
         <v>-0.01408457616879177</v>
@@ -12861,7 +12861,7 @@
         <v>45799</v>
       </c>
       <c r="B397" t="n">
-        <v>-0.007550221156758852</v>
+        <v>-0.007550306823306263</v>
       </c>
       <c r="C397" t="n">
         <v>-0.008944493814943888</v>
@@ -12872,7 +12872,7 @@
         <v>45800</v>
       </c>
       <c r="B398" t="n">
-        <v>-0.01267980850809836</v>
+        <v>-0.01267963696604379</v>
       </c>
       <c r="C398" t="n">
         <v>-0.007220252112987935</v>
@@ -12883,7 +12883,7 @@
         <v>45803</v>
       </c>
       <c r="B399" t="n">
-        <v>0.004280941905137281</v>
+        <v>0.00428076667723376</v>
       </c>
       <c r="C399" t="n">
         <v>0.01272727817288621</v>
@@ -12905,7 +12905,7 @@
         <v>45805</v>
       </c>
       <c r="B401" t="n">
-        <v>0.01449268801716141</v>
+        <v>0.01449277633296897</v>
       </c>
       <c r="C401" t="n">
         <v>-0.005385966185459723</v>
@@ -12927,7 +12927,7 @@
         <v>45807</v>
       </c>
       <c r="B403" t="n">
-        <v>-0.01097972681603443</v>
+        <v>-0.01097964057065459</v>
       </c>
       <c r="C403" t="n">
         <v>-0.001811584083556195</v>
@@ -12938,7 +12938,7 @@
         <v>45810</v>
       </c>
       <c r="B404" t="n">
-        <v>-0.008539687234794369</v>
+        <v>-0.008539686490109388</v>
       </c>
       <c r="C404" t="n">
         <v>-0.009074359382807096</v>
@@ -12960,7 +12960,7 @@
         <v>45812</v>
       </c>
       <c r="B406" t="n">
-        <v>0.01119724049782977</v>
+        <v>0.01119715155905388</v>
       </c>
       <c r="C406" t="n">
         <v>0.01648350075653937</v>
@@ -12971,7 +12971,7 @@
         <v>45813</v>
       </c>
       <c r="B407" t="n">
-        <v>-0.002555385606287652</v>
+        <v>-0.002555298626281233</v>
       </c>
       <c r="C407" t="n">
         <v>0.02522523537259103</v>
@@ -12982,7 +12982,7 @@
         <v>45814</v>
       </c>
       <c r="B408" t="n">
-        <v>-0.002561932331291317</v>
+        <v>-0.002561932107883469</v>
       </c>
       <c r="C408" t="n">
         <v>-0.01054483020790131</v>
@@ -12993,7 +12993,7 @@
         <v>45817</v>
       </c>
       <c r="B409" t="n">
-        <v>-0.005136937947149978</v>
+        <v>-0.005137024924861011</v>
       </c>
       <c r="C409" t="n">
         <v>-0.01776203944752464</v>
@@ -13125,7 +13125,7 @@
         <v>45833</v>
       </c>
       <c r="B421" t="n">
-        <v>0.005176891690114926</v>
+        <v>0.005176804345898844</v>
       </c>
       <c r="C421" t="n">
         <v>0.008944569375609834</v>
@@ -13136,7 +13136,7 @@
         <v>45834</v>
       </c>
       <c r="B422" t="n">
-        <v>0.005150229509763626</v>
+        <v>0.005150316851670667</v>
       </c>
       <c r="C422" t="n">
         <v>0.007092233636828205</v>
@@ -13191,7 +13191,7 @@
         <v>45842</v>
       </c>
       <c r="B427" t="n">
-        <v>-0.006733969435792075</v>
+        <v>-0.006734054647867027</v>
       </c>
       <c r="C427" t="n">
         <v>0</v>
@@ -13202,7 +13202,7 @@
         <v>45845</v>
       </c>
       <c r="B428" t="n">
-        <v>0.04915248275625417</v>
+        <v>0.04915248697303509</v>
       </c>
       <c r="C428" t="n">
         <v>0.006956482391137664</v>
@@ -13224,7 +13224,7 @@
         <v>45847</v>
       </c>
       <c r="B430" t="n">
-        <v>0.005654270332309919</v>
+        <v>0.005654352565224396</v>
       </c>
       <c r="C430" t="n">
         <v>0.0189983120684698</v>
@@ -13235,7 +13235,7 @@
         <v>45848</v>
       </c>
       <c r="B431" t="n">
-        <v>-0.01365452292553992</v>
+        <v>-0.01365460423634157</v>
       </c>
       <c r="C431" t="n">
         <v>0.02033893961117328</v>
@@ -13246,7 +13246,7 @@
         <v>45849</v>
       </c>
       <c r="B432" t="n">
-        <v>0.008957542682080932</v>
+        <v>0.008957708293386046</v>
       </c>
       <c r="C432" t="n">
         <v>-0.008305671383757041</v>
@@ -13257,7 +13257,7 @@
         <v>45852</v>
       </c>
       <c r="B433" t="n">
-        <v>0.0258273015622974</v>
+        <v>0.02582713604298315</v>
       </c>
       <c r="C433" t="n">
         <v>0.01005026583314317</v>
@@ -13279,7 +13279,7 @@
         <v>45854</v>
       </c>
       <c r="B435" t="n">
-        <v>-0.008654574851706398</v>
+        <v>-0.008654495893534841</v>
       </c>
       <c r="C435" t="n">
         <v>-0.003316730999106565</v>
@@ -13290,7 +13290,7 @@
         <v>45855</v>
       </c>
       <c r="B436" t="n">
-        <v>0.002380878924665986</v>
+        <v>0.002380959267479277</v>
       </c>
       <c r="C436" t="n">
         <v>0</v>
@@ -13301,7 +13301,7 @@
         <v>45856</v>
       </c>
       <c r="B437" t="n">
-        <v>0.005542429332803689</v>
+        <v>0.005542348736592428</v>
       </c>
       <c r="C437" t="n">
         <v>0</v>
@@ -13312,7 +13312,7 @@
         <v>45859</v>
       </c>
       <c r="B438" t="n">
-        <v>-0.001220442763019913</v>
+        <v>-0.001220522473212804</v>
       </c>
       <c r="C438" t="n">
         <v>-0.001663884155711393</v>
@@ -13334,7 +13334,7 @@
         <v>45861</v>
       </c>
       <c r="B440" t="n">
-        <v>0.01631905671255285</v>
+        <v>0.01631921763013722</v>
       </c>
       <c r="C440" t="n">
         <v>0.003333314560706402</v>
@@ -13345,7 +13345,7 @@
         <v>45862</v>
       </c>
       <c r="B441" t="n">
-        <v>-0.002676091685842708</v>
+        <v>-0.002676248527929803</v>
       </c>
       <c r="C441" t="n">
         <v>0.0249169439877972</v>
@@ -13356,7 +13356,7 @@
         <v>45863</v>
       </c>
       <c r="B442" t="n">
-        <v>-0.00626123131643963</v>
+        <v>-0.006261153072594783</v>
       </c>
       <c r="C442" t="n">
         <v>0.03241493426998088</v>
@@ -13400,7 +13400,7 @@
         <v>45869</v>
       </c>
       <c r="B446" t="n">
-        <v>0.0009434751192380908</v>
+        <v>0.0009433920741612756</v>
       </c>
       <c r="C446" t="n">
         <v>-0.004746808794464985</v>
@@ -13411,7 +13411,7 @@
         <v>45870</v>
       </c>
       <c r="B447" t="n">
-        <v>-0.01979272570329715</v>
+        <v>-0.0197926443786296</v>
       </c>
       <c r="C447" t="n">
         <v>-0.02702700887792286</v>
@@ -13477,7 +13477,7 @@
         <v>45880</v>
       </c>
       <c r="B453" t="n">
-        <v>0.001883230898116262</v>
+        <v>0.001883313786800178</v>
       </c>
       <c r="C453" t="n">
         <v>0.009852160716518732</v>
@@ -13499,7 +13499,7 @@
         <v>45882</v>
       </c>
       <c r="B455" t="n">
-        <v>0.01033838326552128</v>
+        <v>0.01033829967732536</v>
       </c>
       <c r="C455" t="n">
         <v>0.004878089988693102</v>
@@ -13510,7 +13510,7 @@
         <v>45883</v>
       </c>
       <c r="B456" t="n">
-        <v>-0.02232556456104762</v>
+        <v>-0.02232564644735435</v>
       </c>
       <c r="C456" t="n">
         <v>-0.01132686493339286</v>
@@ -13521,7 +13521,7 @@
         <v>45884</v>
       </c>
       <c r="B457" t="n">
-        <v>-0.01236920106541251</v>
+        <v>-0.0123691183451915</v>
       </c>
       <c r="C457" t="n">
         <v>0.009819911600747799</v>
@@ -13554,7 +13554,7 @@
         <v>45889</v>
       </c>
       <c r="B460" t="n">
-        <v>-0.001990041035837331</v>
+        <v>-0.001989953446003057</v>
       </c>
       <c r="C460" t="n">
         <v>-0.003294874573832152</v>
@@ -13565,7 +13565,7 @@
         <v>45890</v>
       </c>
       <c r="B461" t="n">
-        <v>-0.02592220731201067</v>
+        <v>-0.02592229280144309</v>
       </c>
       <c r="C461" t="n">
         <v>-0.008264416650870854</v>
@@ -13587,7 +13587,7 @@
         <v>45894</v>
       </c>
       <c r="B463" t="n">
-        <v>-0.02851537222851008</v>
+        <v>-0.02851528567219463</v>
       </c>
       <c r="C463" t="n">
         <v>-0.02329451874039579</v>
@@ -13609,7 +13609,7 @@
         <v>45896</v>
       </c>
       <c r="B465" t="n">
-        <v>0.01214587415644131</v>
+        <v>0.01214569488040063</v>
       </c>
       <c r="C465" t="n">
         <v>0.0170357514691879</v>
@@ -13620,7 +13620,7 @@
         <v>45897</v>
       </c>
       <c r="B466" t="n">
-        <v>0.04999995158472448</v>
+        <v>0.0500000440138908</v>
       </c>
       <c r="C466" t="n">
         <v>0.01340033086048775</v>
@@ -13631,7 +13631,7 @@
         <v>45898</v>
       </c>
       <c r="B467" t="n">
-        <v>-0.00476196743927948</v>
+        <v>-0.004761883603300543</v>
       </c>
       <c r="C467" t="n">
         <v>0.008264556281986524</v>
@@ -13642,7 +13642,7 @@
         <v>45903</v>
       </c>
       <c r="B468" t="n">
-        <v>-0.01244013689541756</v>
+        <v>-0.01244030432170895</v>
       </c>
       <c r="C468" t="n">
         <v>0.008196674770901691</v>
@@ -13664,7 +13664,7 @@
         <v>45905</v>
       </c>
       <c r="B470" t="n">
-        <v>0.01744186839983586</v>
+        <v>0.01744195518583891</v>
       </c>
       <c r="C470" t="n">
         <v>0.004878089988693102</v>
@@ -13675,7 +13675,7 @@
         <v>45908</v>
       </c>
       <c r="B471" t="n">
-        <v>-0.02952376217644237</v>
+        <v>-0.02952384601242131</v>
       </c>
       <c r="C471" t="n">
         <v>-0.01941757061759597</v>
@@ -13697,7 +13697,7 @@
         <v>45910</v>
       </c>
       <c r="B473" t="n">
-        <v>0.00196261333467862</v>
+        <v>0.00196269989066078</v>
       </c>
       <c r="C473" t="n">
         <v>-0.004950467445405504</v>
@@ -13730,7 +13730,7 @@
         <v>45915</v>
       </c>
       <c r="B476" t="n">
-        <v>-0.0009803015400288162</v>
+        <v>-0.0009803878417754541</v>
       </c>
       <c r="C476" t="n">
         <v>0</v>
@@ -13752,7 +13752,7 @@
         <v>45917</v>
       </c>
       <c r="B478" t="n">
-        <v>0.01570159776888036</v>
+        <v>0.01570168551172424</v>
       </c>
       <c r="C478" t="n">
         <v>0.02535656816325638</v>
@@ -13785,7 +13785,7 @@
         <v>45922</v>
       </c>
       <c r="B481" t="n">
-        <v>-0.03203886349472673</v>
+        <v>-0.03203877803086475</v>
       </c>
       <c r="C481" t="n">
         <v>-0.03459119893660156</v>
@@ -13807,7 +13807,7 @@
         <v>45924</v>
       </c>
       <c r="B483" t="n">
-        <v>-0.01705116647845617</v>
+        <v>-0.01705125326561407</v>
       </c>
       <c r="C483" t="n">
         <v>0.003257310615764508</v>
@@ -13873,7 +13873,7 @@
         <v>45933</v>
       </c>
       <c r="B489" t="n">
-        <v>-0.0139186621436348</v>
+        <v>-0.0139185678954773</v>
       </c>
       <c r="C489" t="n">
         <v>-0.01449273982268573</v>
@@ -13884,7 +13884,7 @@
         <v>45936</v>
       </c>
       <c r="B490" t="n">
-        <v>0.03691642407254947</v>
+        <v>0.036916324965661</v>
       </c>
       <c r="C490" t="n">
         <v>0.0196078011857399</v>
@@ -13928,7 +13928,7 @@
         <v>45940</v>
       </c>
       <c r="B494" t="n">
-        <v>-0.003174588980152104</v>
+        <v>-0.003174682131237172</v>
       </c>
       <c r="C494" t="n">
         <v>-0.007886391196715525</v>
@@ -13939,7 +13939,7 @@
         <v>45943</v>
       </c>
       <c r="B495" t="n">
-        <v>-0.002123226174937209</v>
+        <v>-0.002123039477843869</v>
       </c>
       <c r="C495" t="n">
         <v>0.01748804481757205</v>
@@ -13961,7 +13961,7 @@
         <v>45945</v>
       </c>
       <c r="B497" t="n">
-        <v>-0.01702120167848375</v>
+        <v>-0.01702138737764136</v>
       </c>
       <c r="C497" t="n">
         <v>-0.007812522171041114</v>
@@ -13972,7 +13972,7 @@
         <v>45946</v>
       </c>
       <c r="B498" t="n">
-        <v>-0.03030308515439206</v>
+        <v>-0.03030299277314763</v>
       </c>
       <c r="C498" t="n">
         <v>0.04863976015499571</v>
@@ -13994,7 +13994,7 @@
         <v>45950</v>
       </c>
       <c r="B500" t="n">
-        <v>-0.03118055437106904</v>
+        <v>-0.03118045634459676</v>
       </c>
       <c r="C500" t="n">
         <v>-0.1013072343504389</v>
@@ -14016,7 +14016,7 @@
         <v>45952</v>
       </c>
       <c r="B502" t="n">
-        <v>0.06896562191175515</v>
+        <v>0.06896551375236704</v>
       </c>
       <c r="C502" t="n">
         <v>0.02727274661053714</v>
@@ -14027,7 +14027,7 @@
         <v>45953</v>
       </c>
       <c r="B503" t="n">
-        <v>0.04301075065261228</v>
+        <v>0.04301084530613641</v>
       </c>
       <c r="C503" t="n">
         <v>-0.003539801651150531</v>
@@ -14038,7 +14038,7 @@
         <v>45954</v>
       </c>
       <c r="B504" t="n">
-        <v>-0.02061864651574707</v>
+        <v>-0.02061864464459917</v>
       </c>
       <c r="C504" t="n">
         <v>0.005328600366580893</v>
@@ -14049,7 +14049,7 @@
         <v>45957</v>
       </c>
       <c r="B505" t="n">
-        <v>0.03157899516190033</v>
+        <v>0.0315788995749462</v>
       </c>
       <c r="C505" t="n">
         <v>0.007067094992733391</v>
@@ -14071,7 +14071,7 @@
         <v>45959</v>
       </c>
       <c r="B507" t="n">
-        <v>0.04285713387471612</v>
+        <v>0.04285722369898304</v>
       </c>
       <c r="C507" t="n">
         <v>0.00701757241863521</v>
@@ -14082,7 +14082,7 @@
         <v>45960</v>
       </c>
       <c r="B508" t="n">
-        <v>-0.004892260282131633</v>
+        <v>-0.004892345993599334</v>
       </c>
       <c r="C508" t="n">
         <v>0.001742114606780865</v>
@@ -14148,7 +14148,7 @@
         <v>45968</v>
       </c>
       <c r="B514" t="n">
-        <v>0.007984084717516104</v>
+        <v>0.007983996865437826</v>
       </c>
       <c r="C514" t="n">
         <v>-0.006896579546669446</v>
@@ -14159,7 +14159,7 @@
         <v>45971</v>
       </c>
       <c r="B515" t="n">
-        <v>-0.04752471554172255</v>
+        <v>-0.04752471968379723</v>
       </c>
       <c r="C515" t="n">
         <v>-0.0104166739624334</v>
@@ -14170,7 +14170,7 @@
         <v>45972</v>
       </c>
       <c r="B516" t="n">
-        <v>-0.001039587883608251</v>
+        <v>-0.001039587978735712</v>
       </c>
       <c r="C516" t="n">
         <v>0.03333338051774515</v>
@@ -14181,7 +14181,7 @@
         <v>45973</v>
       </c>
       <c r="B517" t="n">
-        <v>0.04682629159931007</v>
+        <v>0.0468263874888053</v>
       </c>
       <c r="C517" t="n">
         <v>0.01528007744696791</v>
@@ -14203,7 +14203,7 @@
         <v>45975</v>
       </c>
       <c r="B519" t="n">
-        <v>0.01112238531244514</v>
+        <v>0.01112229630559258</v>
       </c>
       <c r="C519" t="n">
         <v>0.01618126315257618</v>
@@ -14214,7 +14214,7 @@
         <v>45978</v>
       </c>
       <c r="B520" t="n">
-        <v>0.009999955105835401</v>
+        <v>0.009999955986109255</v>
       </c>
       <c r="C520" t="n">
         <v>-0.0111465258664617</v>
@@ -14225,7 +14225,7 @@
         <v>45979</v>
       </c>
       <c r="B521" t="n">
-        <v>-0.009900946089435703</v>
+        <v>-0.009900946952364764</v>
       </c>
       <c r="C521" t="n">
         <v>-0.02254427786941315</v>
@@ -14236,7 +14236,7 @@
         <v>45980</v>
       </c>
       <c r="B522" t="n">
-        <v>-0.02000008626721839</v>
+        <v>-0.02000000000000002</v>
       </c>
       <c r="C522" t="n">
         <v>0.00329493956009741</v>
@@ -14280,7 +14280,7 @@
         <v>45986</v>
       </c>
       <c r="B526" t="n">
-        <v>-0.004989998040898613</v>
+        <v>-0.004989910188820446</v>
       </c>
       <c r="C526" t="n">
         <v>-0.01746030841396373</v>
@@ -14291,7 +14291,7 @@
         <v>45987</v>
       </c>
       <c r="B527" t="n">
-        <v>-0.007021120486810362</v>
+        <v>-0.007021208159547654</v>
       </c>
       <c r="C527" t="n">
         <v>0.01453959007544214</v>
@@ -16614,31 +16614,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02360804854460236</v>
+        <v>0.02360804251446819</v>
       </c>
       <c r="C2" t="n">
-        <v>5.949228233239794</v>
+        <v>5.949226713645983</v>
       </c>
       <c r="D2" t="n">
-        <v>1.586567957823126</v>
+        <v>1.586565744698598</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0003483920214204917</v>
+        <v>0.0003483920797748125</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08779478939796391</v>
+        <v>0.08779480410325276</v>
       </c>
       <c r="G2" t="n">
-        <v>1.866526242570652</v>
+        <v>1.866526398888621</v>
       </c>
       <c r="H2" t="n">
-        <v>29.63018552050661</v>
+        <v>29.63018800197744</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04009346521802291</v>
+        <v>0.04009345639449882</v>
       </c>
       <c r="J2" t="n">
-        <v>20.02335267082486</v>
+        <v>20.02335046751637</v>
       </c>
     </row>
     <row r="3">
@@ -16648,31 +16648,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002164758214700105</v>
+        <v>0.002164765508247972</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5455190701044267</v>
+        <v>0.545520908078489</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.468029911637304</v>
+        <v>-2.468027868927347</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0002420833828221582</v>
+        <v>0.0002420833626095284</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06100501247118386</v>
+        <v>0.06100500737760115</v>
       </c>
       <c r="G3" t="n">
-        <v>1.555902898069665</v>
+        <v>1.555902833115</v>
       </c>
       <c r="H3" t="n">
-        <v>24.69919279474207</v>
+        <v>24.69919176361874</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02849124673597093</v>
+        <v>0.02849124341881984</v>
       </c>
       <c r="J3" t="n">
-        <v>16.87935032398194</v>
+        <v>16.87934934137565</v>
       </c>
     </row>
     <row r="4">

--- a/Adjusted_Close_FPT_VNM.xlsx
+++ b/Adjusted_Close_FPT_VNM.xlsx
@@ -447,7 +447,7 @@
         <v>61812.12109375</v>
       </c>
       <c r="C2" t="n">
-        <v>64295.9296875</v>
+        <v>64295.93359375</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         <v>45197</v>
       </c>
       <c r="B3" t="n">
-        <v>61615.4765625</v>
+        <v>61615.48046875</v>
       </c>
       <c r="C3" t="n">
         <v>62785.06640625</v>
@@ -477,10 +477,10 @@
         <v>45201</v>
       </c>
       <c r="B5" t="n">
-        <v>61091.08984375</v>
+        <v>61091.0859375</v>
       </c>
       <c r="C5" t="n">
-        <v>63456.5546875</v>
+        <v>63456.546875</v>
       </c>
     </row>
     <row r="6">
@@ -488,10 +488,10 @@
         <v>45202</v>
       </c>
       <c r="B6" t="n">
-        <v>60435.60546875</v>
+        <v>60435.6015625</v>
       </c>
       <c r="C6" t="n">
-        <v>62113.5625</v>
+        <v>62113.56640625</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +502,7 @@
         <v>60632.25</v>
       </c>
       <c r="C7" t="n">
-        <v>62449.3125</v>
+        <v>62449.32421875</v>
       </c>
     </row>
     <row r="8">
@@ -510,10 +510,10 @@
         <v>45204</v>
       </c>
       <c r="B8" t="n">
-        <v>60042.31640625</v>
+        <v>60042.3125</v>
       </c>
       <c r="C8" t="n">
-        <v>61022.37890625</v>
+        <v>61022.3828125</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         <v>45205</v>
       </c>
       <c r="B9" t="n">
-        <v>60763.34765625</v>
+        <v>60763.34375</v>
       </c>
       <c r="C9" t="n">
         <v>62281.44140625</v>
@@ -535,7 +535,7 @@
         <v>62664.25</v>
       </c>
       <c r="C10" t="n">
-        <v>61861.765625</v>
+        <v>61861.75390625</v>
       </c>
     </row>
     <row r="11">
@@ -546,7 +546,7 @@
         <v>63123.0859375</v>
       </c>
       <c r="C11" t="n">
-        <v>62449.3125</v>
+        <v>62449.32421875</v>
       </c>
     </row>
     <row r="12">
@@ -554,10 +554,10 @@
         <v>45210</v>
       </c>
       <c r="B12" t="n">
-        <v>63581.92578125</v>
+        <v>63581.9296875</v>
       </c>
       <c r="C12" t="n">
-        <v>62449.3125</v>
+        <v>62449.32421875</v>
       </c>
     </row>
     <row r="13">
@@ -565,10 +565,10 @@
         <v>45211</v>
       </c>
       <c r="B13" t="n">
-        <v>63188.640625</v>
+        <v>63188.63671875</v>
       </c>
       <c r="C13" t="n">
-        <v>63372.62109375</v>
+        <v>63372.62890625</v>
       </c>
     </row>
     <row r="14">
@@ -576,7 +576,7 @@
         <v>45212</v>
       </c>
       <c r="B14" t="n">
-        <v>62991.9921875</v>
+        <v>62991.98828125</v>
       </c>
       <c r="C14" t="n">
         <v>63624.4375</v>
@@ -609,10 +609,10 @@
         <v>45217</v>
       </c>
       <c r="B17" t="n">
-        <v>60959.99609375</v>
+        <v>60959.9921875</v>
       </c>
       <c r="C17" t="n">
-        <v>62029.62109375</v>
+        <v>62029.62890625</v>
       </c>
     </row>
     <row r="18">
@@ -623,7 +623,7 @@
         <v>60304.5078125</v>
       </c>
       <c r="C18" t="n">
-        <v>59931.203125</v>
+        <v>59931.19140625</v>
       </c>
     </row>
     <row r="19">
@@ -634,7 +634,7 @@
         <v>60894.4453125</v>
       </c>
       <c r="C19" t="n">
-        <v>60686.62890625</v>
+        <v>60686.6328125</v>
       </c>
     </row>
     <row r="20">
@@ -642,10 +642,10 @@
         <v>45222</v>
       </c>
       <c r="B20" t="n">
-        <v>59649.02734375</v>
+        <v>59649.01953125</v>
       </c>
       <c r="C20" t="n">
-        <v>58923.953125</v>
+        <v>58923.94921875</v>
       </c>
     </row>
     <row r="21">
@@ -664,10 +664,10 @@
         <v>45224</v>
       </c>
       <c r="B22" t="n">
-        <v>59583.48046875</v>
+        <v>59583.4765625</v>
       </c>
       <c r="C22" t="n">
-        <v>57916.70703125</v>
+        <v>57916.6953125</v>
       </c>
     </row>
     <row r="23">
@@ -675,7 +675,7 @@
         <v>45225</v>
       </c>
       <c r="B23" t="n">
-        <v>56895.99609375</v>
+        <v>56895.9921875</v>
       </c>
       <c r="C23" t="n">
         <v>56237.95703125</v>
@@ -689,7 +689,7 @@
         <v>57027.08984375</v>
       </c>
       <c r="C24" t="n">
-        <v>57077.328125</v>
+        <v>57077.33203125</v>
       </c>
     </row>
     <row r="25">
@@ -697,10 +697,10 @@
         <v>45229</v>
       </c>
       <c r="B25" t="n">
-        <v>55716.12109375</v>
+        <v>55716.1171875</v>
       </c>
       <c r="C25" t="n">
-        <v>56741.58203125</v>
+        <v>56741.578125</v>
       </c>
     </row>
     <row r="26">
@@ -708,10 +708,10 @@
         <v>45230</v>
       </c>
       <c r="B26" t="n">
-        <v>54405.1484375</v>
+        <v>54405.15234375</v>
       </c>
       <c r="C26" t="n">
-        <v>57077.328125</v>
+        <v>57077.33203125</v>
       </c>
     </row>
     <row r="27">
@@ -722,7 +722,7 @@
         <v>55978.31640625</v>
       </c>
       <c r="C27" t="n">
-        <v>59091.82421875</v>
+        <v>59091.828125</v>
       </c>
     </row>
     <row r="28">
@@ -730,10 +730,10 @@
         <v>45232</v>
       </c>
       <c r="B28" t="n">
-        <v>58338.0625</v>
+        <v>58338.05859375</v>
       </c>
       <c r="C28" t="n">
-        <v>59511.51171875</v>
+        <v>59511.5078125</v>
       </c>
     </row>
     <row r="29">
@@ -752,10 +752,10 @@
         <v>45236</v>
       </c>
       <c r="B30" t="n">
-        <v>58010.3125</v>
+        <v>58010.31640625</v>
       </c>
       <c r="C30" t="n">
-        <v>59595.44921875</v>
+        <v>59595.453125</v>
       </c>
     </row>
     <row r="31">
@@ -766,7 +766,7 @@
         <v>57879.21875</v>
       </c>
       <c r="C31" t="n">
-        <v>59427.57421875</v>
+        <v>59427.5703125</v>
       </c>
     </row>
     <row r="32">
@@ -777,7 +777,7 @@
         <v>60697.796875</v>
       </c>
       <c r="C32" t="n">
-        <v>59931.203125</v>
+        <v>59931.19140625</v>
       </c>
     </row>
     <row r="33">
@@ -796,10 +796,10 @@
         <v>45240</v>
       </c>
       <c r="B34" t="n">
-        <v>59976.76953125</v>
+        <v>59976.765625</v>
       </c>
       <c r="C34" t="n">
-        <v>58420.32421875</v>
+        <v>58420.328125</v>
       </c>
     </row>
     <row r="35">
@@ -807,7 +807,7 @@
         <v>45243</v>
       </c>
       <c r="B35" t="n">
-        <v>59911.21484375</v>
+        <v>59911.21875</v>
       </c>
       <c r="C35" t="n">
         <v>57664.890625</v>
@@ -840,7 +840,7 @@
         <v>45246</v>
       </c>
       <c r="B38" t="n">
-        <v>60959.99609375</v>
+        <v>60959.9921875</v>
       </c>
       <c r="C38" t="n">
         <v>59007.890625</v>
@@ -851,7 +851,7 @@
         <v>45247</v>
       </c>
       <c r="B39" t="n">
-        <v>59649.02734375</v>
+        <v>59649.01953125</v>
       </c>
       <c r="C39" t="n">
         <v>58756.07421875</v>
@@ -862,10 +862,10 @@
         <v>45250</v>
       </c>
       <c r="B40" t="n">
-        <v>59452.37890625</v>
+        <v>59452.375</v>
       </c>
       <c r="C40" t="n">
-        <v>58168.515625</v>
+        <v>58168.51171875</v>
       </c>
     </row>
     <row r="41">
@@ -876,7 +876,7 @@
         <v>60238.9609375</v>
       </c>
       <c r="C41" t="n">
-        <v>58336.38671875</v>
+        <v>58336.39453125</v>
       </c>
     </row>
     <row r="42">
@@ -884,10 +884,10 @@
         <v>45252</v>
       </c>
       <c r="B42" t="n">
-        <v>60959.99609375</v>
+        <v>60959.9921875</v>
       </c>
       <c r="C42" t="n">
-        <v>58252.44921875</v>
+        <v>58252.4453125</v>
       </c>
     </row>
     <row r="43">
@@ -906,10 +906,10 @@
         <v>45254</v>
       </c>
       <c r="B44" t="n">
-        <v>59780.1171875</v>
+        <v>59780.12109375</v>
       </c>
       <c r="C44" t="n">
-        <v>57329.140625</v>
+        <v>57329.13671875</v>
       </c>
     </row>
     <row r="45">
@@ -917,7 +917,7 @@
         <v>45257</v>
       </c>
       <c r="B45" t="n">
-        <v>59452.37890625</v>
+        <v>59452.375</v>
       </c>
       <c r="C45" t="n">
         <v>57161.2734375</v>
@@ -931,7 +931,7 @@
         <v>59714.57421875</v>
       </c>
       <c r="C46" t="n">
-        <v>57497.015625</v>
+        <v>57497.01953125</v>
       </c>
     </row>
     <row r="47">
@@ -972,10 +972,10 @@
         <v>45264</v>
       </c>
       <c r="B50" t="n">
-        <v>61353.28125</v>
+        <v>61353.28515625</v>
       </c>
       <c r="C50" t="n">
-        <v>57748.828125</v>
+        <v>57748.82421875</v>
       </c>
     </row>
     <row r="51">
@@ -983,7 +983,7 @@
         <v>45265</v>
       </c>
       <c r="B51" t="n">
-        <v>62139.86328125</v>
+        <v>62139.8671875</v>
       </c>
       <c r="C51" t="n">
         <v>57161.2734375</v>
@@ -997,7 +997,7 @@
         <v>62270.9609375</v>
       </c>
       <c r="C52" t="n">
-        <v>57497.015625</v>
+        <v>57497.01953125</v>
       </c>
     </row>
     <row r="53">
@@ -1019,7 +1019,7 @@
         <v>61746.57421875</v>
       </c>
       <c r="C54" t="n">
-        <v>57916.70703125</v>
+        <v>57916.6953125</v>
       </c>
     </row>
     <row r="55">
@@ -1041,7 +1041,7 @@
         <v>63450.83203125</v>
       </c>
       <c r="C56" t="n">
-        <v>58252.44921875</v>
+        <v>58252.4453125</v>
       </c>
     </row>
     <row r="57">
@@ -1052,7 +1052,7 @@
         <v>62402.0546875</v>
       </c>
       <c r="C57" t="n">
-        <v>57245.203125</v>
+        <v>57245.2109375</v>
       </c>
     </row>
     <row r="58">
@@ -1060,7 +1060,7 @@
         <v>45275</v>
       </c>
       <c r="B58" t="n">
-        <v>63057.5390625</v>
+        <v>63057.54296875</v>
       </c>
       <c r="C58" t="n">
         <v>57161.2734375</v>
@@ -1071,7 +1071,7 @@
         <v>45278</v>
       </c>
       <c r="B59" t="n">
-        <v>61615.4765625</v>
+        <v>61615.48046875</v>
       </c>
       <c r="C59" t="n">
         <v>56237.95703125</v>
@@ -1104,10 +1104,10 @@
         <v>45281</v>
       </c>
       <c r="B62" t="n">
-        <v>62336.51171875</v>
+        <v>62336.50390625</v>
       </c>
       <c r="C62" t="n">
-        <v>56909.45703125</v>
+        <v>56909.453125</v>
       </c>
     </row>
     <row r="63">
@@ -1118,7 +1118,7 @@
         <v>62008.765625</v>
       </c>
       <c r="C63" t="n">
-        <v>56741.58203125</v>
+        <v>56741.578125</v>
       </c>
     </row>
     <row r="64">
@@ -1140,7 +1140,7 @@
         <v>63713.01953125</v>
       </c>
       <c r="C65" t="n">
-        <v>57077.328125</v>
+        <v>57077.33203125</v>
       </c>
     </row>
     <row r="66">
@@ -1148,10 +1148,10 @@
         <v>45287</v>
       </c>
       <c r="B66" t="n">
-        <v>63516.38671875</v>
+        <v>63516.375</v>
       </c>
       <c r="C66" t="n">
-        <v>57077.3359375</v>
+        <v>57077.33203125</v>
       </c>
     </row>
     <row r="67">
@@ -1170,10 +1170,10 @@
         <v>45289</v>
       </c>
       <c r="B68" t="n">
-        <v>62991.9921875</v>
+        <v>62991.98828125</v>
       </c>
       <c r="C68" t="n">
-        <v>57161.890625</v>
+        <v>57161.88671875</v>
       </c>
     </row>
     <row r="69">
@@ -1217,7 +1217,7 @@
         <v>63844.1171875</v>
       </c>
       <c r="C72" t="n">
-        <v>58176.59765625</v>
+        <v>58176.59375</v>
       </c>
     </row>
     <row r="73">
@@ -1225,10 +1225,10 @@
         <v>45299</v>
       </c>
       <c r="B73" t="n">
-        <v>63778.5703125</v>
+        <v>63778.56640625</v>
       </c>
       <c r="C73" t="n">
-        <v>57669.2421875</v>
+        <v>57669.24609375</v>
       </c>
     </row>
     <row r="74">
@@ -1239,7 +1239,7 @@
         <v>63319.73828125</v>
       </c>
       <c r="C74" t="n">
-        <v>57584.69140625</v>
+        <v>57584.6875</v>
       </c>
     </row>
     <row r="75">
@@ -1250,7 +1250,7 @@
         <v>62074.31640625</v>
       </c>
       <c r="C75" t="n">
-        <v>57077.3359375</v>
+        <v>57077.33203125</v>
       </c>
     </row>
     <row r="76">
@@ -1272,7 +1272,7 @@
         <v>62074.31640625</v>
       </c>
       <c r="C77" t="n">
-        <v>56823.65625</v>
+        <v>56823.65234375</v>
       </c>
     </row>
     <row r="78">
@@ -1291,10 +1291,10 @@
         <v>45308</v>
       </c>
       <c r="B79" t="n">
-        <v>62729.796875</v>
+        <v>62729.80078125</v>
       </c>
       <c r="C79" t="n">
-        <v>56739.08984375</v>
+        <v>56739.09765625</v>
       </c>
     </row>
     <row r="80">
@@ -1305,7 +1305,7 @@
         <v>63123.0859375</v>
       </c>
       <c r="C80" t="n">
-        <v>57500.125</v>
+        <v>57500.12890625</v>
       </c>
     </row>
     <row r="81">
@@ -1313,7 +1313,7 @@
         <v>45313</v>
       </c>
       <c r="B81" t="n">
-        <v>63188.640625</v>
+        <v>63188.63671875</v>
       </c>
       <c r="C81" t="n">
         <v>57753.80078125</v>
@@ -1327,7 +1327,7 @@
         <v>62664.25</v>
       </c>
       <c r="C82" t="n">
-        <v>57246.44921875</v>
+        <v>57246.4453125</v>
       </c>
     </row>
     <row r="83">
@@ -1382,7 +1382,7 @@
         <v>62664.25</v>
       </c>
       <c r="C87" t="n">
-        <v>56569.9765625</v>
+        <v>56569.98046875</v>
       </c>
     </row>
     <row r="88">
@@ -1390,7 +1390,7 @@
         <v>45322</v>
       </c>
       <c r="B88" t="n">
-        <v>62729.796875</v>
+        <v>62729.80078125</v>
       </c>
       <c r="C88" t="n">
         <v>56654.53515625</v>
@@ -1401,10 +1401,10 @@
         <v>45323</v>
       </c>
       <c r="B89" t="n">
-        <v>65482.83203125</v>
+        <v>65482.8359375</v>
       </c>
       <c r="C89" t="n">
-        <v>57077.3359375</v>
+        <v>57077.33203125</v>
       </c>
     </row>
     <row r="90">
@@ -1412,10 +1412,10 @@
         <v>45324</v>
       </c>
       <c r="B90" t="n">
-        <v>65482.83203125</v>
+        <v>65482.8359375</v>
       </c>
       <c r="C90" t="n">
-        <v>57077.3359375</v>
+        <v>57077.33203125</v>
       </c>
     </row>
     <row r="91">
@@ -1423,10 +1423,10 @@
         <v>45327</v>
       </c>
       <c r="B91" t="n">
-        <v>67842.5625</v>
+        <v>67842.5703125</v>
       </c>
       <c r="C91" t="n">
-        <v>57500.125</v>
+        <v>57500.12890625</v>
       </c>
     </row>
     <row r="92">
@@ -1434,10 +1434,10 @@
         <v>45328</v>
       </c>
       <c r="B92" t="n">
-        <v>68235.859375</v>
+        <v>68235.8671875</v>
       </c>
       <c r="C92" t="n">
-        <v>57161.890625</v>
+        <v>57161.88671875</v>
       </c>
     </row>
     <row r="93">
@@ -1445,10 +1445,10 @@
         <v>45329</v>
       </c>
       <c r="B93" t="n">
-        <v>68760.25</v>
+        <v>68760.2421875</v>
       </c>
       <c r="C93" t="n">
-        <v>57161.890625</v>
+        <v>57161.88671875</v>
       </c>
     </row>
     <row r="94">
@@ -1456,10 +1456,10 @@
         <v>45337</v>
       </c>
       <c r="B94" t="n">
-        <v>68170.3203125</v>
+        <v>68170.3125</v>
       </c>
       <c r="C94" t="n">
-        <v>57161.890625</v>
+        <v>57161.88671875</v>
       </c>
     </row>
     <row r="95">
@@ -1467,7 +1467,7 @@
         <v>45338</v>
       </c>
       <c r="B95" t="n">
-        <v>68891.3515625</v>
+        <v>68891.34375</v>
       </c>
       <c r="C95" t="n">
         <v>59191.3046875</v>
@@ -1489,7 +1489,7 @@
         <v>45342</v>
       </c>
       <c r="B97" t="n">
-        <v>68366.9609375</v>
+        <v>68366.953125</v>
       </c>
       <c r="C97" t="n">
         <v>60459.6953125</v>
@@ -1500,10 +1500,10 @@
         <v>45343</v>
       </c>
       <c r="B98" t="n">
-        <v>69415.7265625</v>
+        <v>69415.734375</v>
       </c>
       <c r="C98" t="n">
-        <v>60290.5703125</v>
+        <v>60290.57421875</v>
       </c>
     </row>
     <row r="99">
@@ -1511,7 +1511,7 @@
         <v>45344</v>
       </c>
       <c r="B99" t="n">
-        <v>68563.6015625</v>
+        <v>68563.609375</v>
       </c>
       <c r="C99" t="n">
         <v>60544.25390625</v>
@@ -1522,10 +1522,10 @@
         <v>45345</v>
       </c>
       <c r="B100" t="n">
-        <v>68104.7578125</v>
+        <v>68104.765625</v>
       </c>
       <c r="C100" t="n">
-        <v>60036.8984375</v>
+        <v>60036.89453125</v>
       </c>
     </row>
     <row r="101">
@@ -1533,10 +1533,10 @@
         <v>45348</v>
       </c>
       <c r="B101" t="n">
-        <v>70792.25</v>
+        <v>70792.2421875</v>
       </c>
       <c r="C101" t="n">
-        <v>60036.8984375</v>
+        <v>60036.89453125</v>
       </c>
     </row>
     <row r="102">
@@ -1544,10 +1544,10 @@
         <v>45349</v>
       </c>
       <c r="B102" t="n">
-        <v>70726.703125</v>
+        <v>70726.6953125</v>
       </c>
       <c r="C102" t="n">
-        <v>60882.48828125</v>
+        <v>60882.484375</v>
       </c>
     </row>
     <row r="103">
@@ -1555,10 +1555,10 @@
         <v>45350</v>
       </c>
       <c r="B103" t="n">
-        <v>71119.9921875</v>
+        <v>71120</v>
       </c>
       <c r="C103" t="n">
-        <v>61051.59375</v>
+        <v>61051.60546875</v>
       </c>
     </row>
     <row r="104">
@@ -1569,7 +1569,7 @@
         <v>71447.7265625</v>
       </c>
       <c r="C104" t="n">
-        <v>60882.48828125</v>
+        <v>60882.484375</v>
       </c>
     </row>
     <row r="105">
@@ -1588,10 +1588,10 @@
         <v>45355</v>
       </c>
       <c r="B106" t="n">
-        <v>73020.8984375</v>
+        <v>73020.90625</v>
       </c>
       <c r="C106" t="n">
-        <v>60882.48828125</v>
+        <v>60882.484375</v>
       </c>
     </row>
     <row r="107">
@@ -1602,7 +1602,7 @@
         <v>72562.0546875</v>
       </c>
       <c r="C107" t="n">
-        <v>61728.078125</v>
+        <v>61728.07421875</v>
       </c>
     </row>
     <row r="108">
@@ -1610,10 +1610,10 @@
         <v>45357</v>
       </c>
       <c r="B108" t="n">
-        <v>71513.28125</v>
+        <v>71513.2734375</v>
       </c>
       <c r="C108" t="n">
-        <v>60713.3671875</v>
+        <v>60713.36328125</v>
       </c>
     </row>
     <row r="109">
@@ -1624,7 +1624,7 @@
         <v>72955.34375</v>
       </c>
       <c r="C109" t="n">
-        <v>60882.48828125</v>
+        <v>60882.484375</v>
       </c>
     </row>
     <row r="110">
@@ -1665,10 +1665,10 @@
         <v>45364</v>
       </c>
       <c r="B113" t="n">
-        <v>76691.59375</v>
+        <v>76691.609375</v>
       </c>
       <c r="C113" t="n">
-        <v>59867.77734375</v>
+        <v>59867.7734375</v>
       </c>
     </row>
     <row r="114">
@@ -1676,10 +1676,10 @@
         <v>45365</v>
       </c>
       <c r="B114" t="n">
-        <v>76691.59375</v>
+        <v>76691.609375</v>
       </c>
       <c r="C114" t="n">
-        <v>59614.09765625</v>
+        <v>59614.09375</v>
       </c>
     </row>
     <row r="115">
@@ -1690,7 +1690,7 @@
         <v>76036.1171875</v>
       </c>
       <c r="C115" t="n">
-        <v>58928.87890625</v>
+        <v>58928.875</v>
       </c>
     </row>
     <row r="116">
@@ -1698,7 +1698,7 @@
         <v>45369</v>
       </c>
       <c r="B116" t="n">
-        <v>74069.6640625</v>
+        <v>74069.671875</v>
       </c>
       <c r="C116" t="n">
         <v>58158.0078125</v>
@@ -1720,10 +1720,10 @@
         <v>45371</v>
       </c>
       <c r="B118" t="n">
-        <v>75052.8984375</v>
+        <v>75052.890625</v>
       </c>
       <c r="C118" t="n">
-        <v>58243.66015625</v>
+        <v>58243.6640625</v>
       </c>
     </row>
     <row r="119">
@@ -1731,7 +1731,7 @@
         <v>45372</v>
       </c>
       <c r="B119" t="n">
-        <v>76167.2109375</v>
+        <v>76167.203125</v>
       </c>
       <c r="C119" t="n">
         <v>58586.26953125</v>
@@ -1742,7 +1742,7 @@
         <v>45373</v>
       </c>
       <c r="B120" t="n">
-        <v>75315.0859375</v>
+        <v>75315.078125</v>
       </c>
       <c r="C120" t="n">
         <v>58072.35546875</v>
@@ -1753,10 +1753,10 @@
         <v>45376</v>
       </c>
       <c r="B121" t="n">
-        <v>74725.140625</v>
+        <v>74725.15625</v>
       </c>
       <c r="C121" t="n">
-        <v>57644.09375</v>
+        <v>57644.08984375</v>
       </c>
     </row>
     <row r="122">
@@ -1786,7 +1786,7 @@
         <v>45379</v>
       </c>
       <c r="B124" t="n">
-        <v>76757.15625</v>
+        <v>76757.1484375</v>
       </c>
       <c r="C124" t="n">
         <v>57986.703125</v>
@@ -1797,7 +1797,7 @@
         <v>45380</v>
       </c>
       <c r="B125" t="n">
-        <v>76363.8671875</v>
+        <v>76363.875</v>
       </c>
       <c r="C125" t="n">
         <v>57901.05078125</v>
@@ -1808,7 +1808,7 @@
         <v>45383</v>
       </c>
       <c r="B126" t="n">
-        <v>76560.5</v>
+        <v>76560.515625</v>
       </c>
       <c r="C126" t="n">
         <v>57387.13671875</v>
@@ -1819,10 +1819,10 @@
         <v>45384</v>
       </c>
       <c r="B127" t="n">
-        <v>76691.59375</v>
+        <v>76691.609375</v>
       </c>
       <c r="C127" t="n">
-        <v>57644.09375</v>
+        <v>57644.08984375</v>
       </c>
     </row>
     <row r="128">
@@ -1830,7 +1830,7 @@
         <v>45385</v>
       </c>
       <c r="B128" t="n">
-        <v>75446.1953125</v>
+        <v>75446.1796875</v>
       </c>
       <c r="C128" t="n">
         <v>57130.1796875</v>
@@ -1841,10 +1841,10 @@
         <v>45386</v>
       </c>
       <c r="B129" t="n">
-        <v>74725.140625</v>
+        <v>74725.15625</v>
       </c>
       <c r="C129" t="n">
-        <v>58414.96484375</v>
+        <v>58414.96875</v>
       </c>
     </row>
     <row r="130">
@@ -1852,7 +1852,7 @@
         <v>45387</v>
       </c>
       <c r="B130" t="n">
-        <v>74528.5</v>
+        <v>74528.5078125</v>
       </c>
       <c r="C130" t="n">
         <v>58158.0078125</v>
@@ -1874,7 +1874,7 @@
         <v>45391</v>
       </c>
       <c r="B132" t="n">
-        <v>74069.6640625</v>
+        <v>74069.671875</v>
       </c>
       <c r="C132" t="n">
         <v>57387.13671875</v>
@@ -1885,10 +1885,10 @@
         <v>45392</v>
       </c>
       <c r="B133" t="n">
-        <v>74594.0625</v>
+        <v>74594.046875</v>
       </c>
       <c r="C133" t="n">
-        <v>57215.828125</v>
+        <v>57215.83203125</v>
       </c>
     </row>
     <row r="134">
@@ -1896,10 +1896,10 @@
         <v>45393</v>
       </c>
       <c r="B134" t="n">
-        <v>75315.0859375</v>
+        <v>75315.078125</v>
       </c>
       <c r="C134" t="n">
-        <v>57044.52734375</v>
+        <v>57044.53125</v>
       </c>
     </row>
     <row r="135">
@@ -1907,7 +1907,7 @@
         <v>45394</v>
       </c>
       <c r="B135" t="n">
-        <v>75708.375</v>
+        <v>75708.3828125</v>
       </c>
       <c r="C135" t="n">
         <v>57130.1796875</v>
@@ -1918,7 +1918,7 @@
         <v>45397</v>
       </c>
       <c r="B136" t="n">
-        <v>73151.984375</v>
+        <v>73151.9921875</v>
       </c>
       <c r="C136" t="n">
         <v>55588.4375</v>
@@ -1929,7 +1929,7 @@
         <v>45398</v>
       </c>
       <c r="B137" t="n">
-        <v>74069.6640625</v>
+        <v>74069.671875</v>
       </c>
       <c r="C137" t="n">
         <v>54817.5625</v>
@@ -1943,7 +1943,7 @@
         <v>73283.0859375</v>
       </c>
       <c r="C138" t="n">
-        <v>54988.8671875</v>
+        <v>54988.86328125</v>
       </c>
     </row>
     <row r="139">
@@ -1954,7 +1954,7 @@
         <v>71447.7265625</v>
       </c>
       <c r="C139" t="n">
-        <v>54988.8671875</v>
+        <v>54988.86328125</v>
       </c>
     </row>
     <row r="140">
@@ -1973,7 +1973,7 @@
         <v>45405</v>
       </c>
       <c r="B141" t="n">
-        <v>73610.8203125</v>
+        <v>73610.828125</v>
       </c>
       <c r="C141" t="n">
         <v>54389.30078125</v>
@@ -1984,7 +1984,7 @@
         <v>45406</v>
       </c>
       <c r="B142" t="n">
-        <v>78723.6015625</v>
+        <v>78723.6171875</v>
       </c>
       <c r="C142" t="n">
         <v>54817.5625</v>
@@ -1995,7 +1995,7 @@
         <v>45407</v>
       </c>
       <c r="B143" t="n">
-        <v>80755.609375</v>
+        <v>80755.6015625</v>
       </c>
       <c r="C143" t="n">
         <v>55417.12890625</v>
@@ -2006,10 +2006,10 @@
         <v>45408</v>
       </c>
       <c r="B144" t="n">
-        <v>80755.609375</v>
+        <v>80755.6015625</v>
       </c>
       <c r="C144" t="n">
-        <v>55674.0859375</v>
+        <v>55674.08984375</v>
       </c>
     </row>
     <row r="145">
@@ -2017,10 +2017,10 @@
         <v>45414</v>
       </c>
       <c r="B145" t="n">
-        <v>83443.0859375</v>
+        <v>83443.09375</v>
       </c>
       <c r="C145" t="n">
-        <v>56016.6953125</v>
+        <v>56016.69921875</v>
       </c>
     </row>
     <row r="146">
@@ -2028,7 +2028,7 @@
         <v>45415</v>
       </c>
       <c r="B146" t="n">
-        <v>82525.421875</v>
+        <v>82525.40625</v>
       </c>
       <c r="C146" t="n">
         <v>56188</v>
@@ -2039,7 +2039,7 @@
         <v>45418</v>
       </c>
       <c r="B147" t="n">
-        <v>83639.7265625</v>
+        <v>83639.734375</v>
       </c>
       <c r="C147" t="n">
         <v>56359.30859375</v>
@@ -2053,7 +2053,7 @@
         <v>86065.015625</v>
       </c>
       <c r="C148" t="n">
-        <v>58243.66015625</v>
+        <v>58243.6640625</v>
       </c>
     </row>
     <row r="149">
@@ -2075,7 +2075,7 @@
         <v>85409.5390625</v>
       </c>
       <c r="C150" t="n">
-        <v>57044.52734375</v>
+        <v>57044.53125</v>
       </c>
     </row>
     <row r="151">
@@ -2094,7 +2094,7 @@
         <v>45425</v>
       </c>
       <c r="B152" t="n">
-        <v>85016.2421875</v>
+        <v>85016.25</v>
       </c>
       <c r="C152" t="n">
         <v>56359.30859375</v>
@@ -2116,7 +2116,7 @@
         <v>45427</v>
       </c>
       <c r="B154" t="n">
-        <v>87900.3828125</v>
+        <v>87900.375</v>
       </c>
       <c r="C154" t="n">
         <v>57387.13671875</v>
@@ -2127,10 +2127,10 @@
         <v>45428</v>
       </c>
       <c r="B155" t="n">
-        <v>88752.5078125</v>
+        <v>88752.5</v>
       </c>
       <c r="C155" t="n">
-        <v>57558.4453125</v>
+        <v>57558.44140625</v>
       </c>
     </row>
     <row r="156">
@@ -2138,7 +2138,7 @@
         <v>45429</v>
       </c>
       <c r="B156" t="n">
-        <v>88162.5625</v>
+        <v>88162.578125</v>
       </c>
       <c r="C156" t="n">
         <v>57387.13671875</v>
@@ -2163,7 +2163,7 @@
         <v>89145.796875</v>
       </c>
       <c r="C158" t="n">
-        <v>56701.921875</v>
+        <v>56701.9140625</v>
       </c>
     </row>
     <row r="159">
@@ -2171,7 +2171,7 @@
         <v>45434</v>
       </c>
       <c r="B159" t="n">
-        <v>90456.7578125</v>
+        <v>90456.75</v>
       </c>
       <c r="C159" t="n">
         <v>56359.30859375</v>
@@ -2182,7 +2182,7 @@
         <v>45435</v>
       </c>
       <c r="B160" t="n">
-        <v>90129.0234375</v>
+        <v>90129.015625</v>
       </c>
       <c r="C160" t="n">
         <v>57387.13671875</v>
@@ -2196,7 +2196,7 @@
         <v>86458.3125</v>
       </c>
       <c r="C161" t="n">
-        <v>56530.61328125</v>
+        <v>56530.609375</v>
       </c>
     </row>
     <row r="162">
@@ -2204,10 +2204,10 @@
         <v>45439</v>
       </c>
       <c r="B162" t="n">
-        <v>87048.25</v>
+        <v>87048.2421875</v>
       </c>
       <c r="C162" t="n">
-        <v>56616.265625</v>
+        <v>56616.26171875</v>
       </c>
     </row>
     <row r="163">
@@ -2215,10 +2215,10 @@
         <v>45440</v>
       </c>
       <c r="B163" t="n">
-        <v>89801.28125</v>
+        <v>89801.2890625</v>
       </c>
       <c r="C163" t="n">
-        <v>57215.828125</v>
+        <v>57215.83203125</v>
       </c>
     </row>
     <row r="164">
@@ -2226,10 +2226,10 @@
         <v>45441</v>
       </c>
       <c r="B164" t="n">
-        <v>88949.15625</v>
+        <v>88949.1484375</v>
       </c>
       <c r="C164" t="n">
-        <v>56787.5703125</v>
+        <v>56787.56640625</v>
       </c>
     </row>
     <row r="165">
@@ -2237,10 +2237,10 @@
         <v>45442</v>
       </c>
       <c r="B165" t="n">
-        <v>88490.3203125</v>
+        <v>88490.3125</v>
       </c>
       <c r="C165" t="n">
-        <v>56273.65234375</v>
+        <v>56273.65625</v>
       </c>
     </row>
     <row r="166">
@@ -2248,10 +2248,10 @@
         <v>45443</v>
       </c>
       <c r="B166" t="n">
-        <v>88228.1171875</v>
+        <v>88228.125</v>
       </c>
       <c r="C166" t="n">
-        <v>56016.6953125</v>
+        <v>56016.69921875</v>
       </c>
     </row>
     <row r="167">
@@ -2259,10 +2259,10 @@
         <v>45446</v>
       </c>
       <c r="B167" t="n">
-        <v>88228.1171875</v>
+        <v>88228.125</v>
       </c>
       <c r="C167" t="n">
-        <v>56016.6953125</v>
+        <v>56016.69921875</v>
       </c>
     </row>
     <row r="168">
@@ -2270,10 +2270,10 @@
         <v>45447</v>
       </c>
       <c r="B168" t="n">
-        <v>91177.7890625</v>
+        <v>91177.8046875</v>
       </c>
       <c r="C168" t="n">
-        <v>56530.61328125</v>
+        <v>56530.609375</v>
       </c>
     </row>
     <row r="169">
@@ -2295,7 +2295,7 @@
         <v>91505.5390625</v>
       </c>
       <c r="C170" t="n">
-        <v>57558.4453125</v>
+        <v>57558.44140625</v>
       </c>
     </row>
     <row r="171">
@@ -2314,10 +2314,10 @@
         <v>45453</v>
       </c>
       <c r="B172" t="n">
-        <v>94389.65625</v>
+        <v>94389.6640625</v>
       </c>
       <c r="C172" t="n">
-        <v>57558.4453125</v>
+        <v>57558.44140625</v>
       </c>
     </row>
     <row r="173">
@@ -2336,7 +2336,7 @@
         <v>45455</v>
       </c>
       <c r="B174" t="n">
-        <v>100289.6875</v>
+        <v>100289.6953125</v>
       </c>
       <c r="C174" t="n">
         <v>57387.13671875</v>
@@ -2350,7 +2350,7 @@
         <v>98770.1484375</v>
       </c>
       <c r="C175" t="n">
-        <v>57301.484375</v>
+        <v>57301.48828125</v>
       </c>
     </row>
     <row r="176">
@@ -2361,7 +2361,7 @@
         <v>99529.921875</v>
       </c>
       <c r="C176" t="n">
-        <v>56701.921875</v>
+        <v>56701.9140625</v>
       </c>
     </row>
     <row r="177">
@@ -2369,10 +2369,10 @@
         <v>45460</v>
       </c>
       <c r="B177" t="n">
-        <v>97858.4296875</v>
+        <v>97858.421875</v>
       </c>
       <c r="C177" t="n">
-        <v>56530.61328125</v>
+        <v>56530.609375</v>
       </c>
     </row>
     <row r="178">
@@ -2383,7 +2383,7 @@
         <v>97250.609375</v>
       </c>
       <c r="C178" t="n">
-        <v>56444.95703125</v>
+        <v>56444.9609375</v>
       </c>
     </row>
     <row r="179">
@@ -2391,7 +2391,7 @@
         <v>45462</v>
       </c>
       <c r="B179" t="n">
-        <v>99909.8046875</v>
+        <v>99909.8125</v>
       </c>
       <c r="C179" t="n">
         <v>55931.046875</v>
@@ -2402,10 +2402,10 @@
         <v>45463</v>
       </c>
       <c r="B180" t="n">
-        <v>101277.390625</v>
+        <v>101277.3984375</v>
       </c>
       <c r="C180" t="n">
-        <v>56530.61328125</v>
+        <v>56530.609375</v>
       </c>
     </row>
     <row r="181">
@@ -2416,7 +2416,7 @@
         <v>103404.75</v>
       </c>
       <c r="C181" t="n">
-        <v>56530.61328125</v>
+        <v>56530.609375</v>
       </c>
     </row>
     <row r="182">
@@ -2424,7 +2424,7 @@
         <v>45467</v>
       </c>
       <c r="B182" t="n">
-        <v>100365.671875</v>
+        <v>100365.65625</v>
       </c>
       <c r="C182" t="n">
         <v>56102.3515625</v>
@@ -2468,7 +2468,7 @@
         <v>45471</v>
       </c>
       <c r="B186" t="n">
-        <v>99150.03125</v>
+        <v>99150.0390625</v>
       </c>
       <c r="C186" t="n">
         <v>56102.3515625</v>
@@ -2482,7 +2482,7 @@
         <v>97706.4765625</v>
       </c>
       <c r="C187" t="n">
-        <v>56530.61328125</v>
+        <v>56530.609375</v>
       </c>
     </row>
     <row r="188">
@@ -2493,7 +2493,7 @@
         <v>97250.609375</v>
       </c>
       <c r="C188" t="n">
-        <v>56701.921875</v>
+        <v>56701.9140625</v>
       </c>
     </row>
     <row r="189">
@@ -2504,7 +2504,7 @@
         <v>99529.921875</v>
       </c>
       <c r="C189" t="n">
-        <v>56701.921875</v>
+        <v>56701.9140625</v>
       </c>
     </row>
     <row r="190">
@@ -2512,7 +2512,7 @@
         <v>45477</v>
       </c>
       <c r="B190" t="n">
-        <v>103176.828125</v>
+        <v>103176.8203125</v>
       </c>
       <c r="C190" t="n">
         <v>56873.22265625</v>
@@ -2526,7 +2526,7 @@
         <v>105380.15625</v>
       </c>
       <c r="C191" t="n">
-        <v>57558.4453125</v>
+        <v>57558.44140625</v>
       </c>
     </row>
     <row r="192">
@@ -2556,10 +2556,10 @@
         <v>45483</v>
       </c>
       <c r="B194" t="n">
-        <v>101809.234375</v>
+        <v>101809.2265625</v>
       </c>
       <c r="C194" t="n">
-        <v>57215.828125</v>
+        <v>57215.83203125</v>
       </c>
     </row>
     <row r="195">
@@ -2570,7 +2570,7 @@
         <v>101049.46875</v>
       </c>
       <c r="C195" t="n">
-        <v>56787.5703125</v>
+        <v>56787.56640625</v>
       </c>
     </row>
     <row r="196">
@@ -2581,7 +2581,7 @@
         <v>101657.28125</v>
       </c>
       <c r="C196" t="n">
-        <v>56787.5703125</v>
+        <v>56787.56640625</v>
       </c>
     </row>
     <row r="197">
@@ -2589,10 +2589,10 @@
         <v>45488</v>
       </c>
       <c r="B197" t="n">
-        <v>100821.5390625</v>
+        <v>100821.53125</v>
       </c>
       <c r="C197" t="n">
-        <v>56701.921875</v>
+        <v>56701.9140625</v>
       </c>
     </row>
     <row r="198">
@@ -2600,10 +2600,10 @@
         <v>45489</v>
       </c>
       <c r="B198" t="n">
-        <v>101809.234375</v>
+        <v>101809.2265625</v>
       </c>
       <c r="C198" t="n">
-        <v>56616.265625</v>
+        <v>56616.26171875</v>
       </c>
     </row>
     <row r="199">
@@ -2611,10 +2611,10 @@
         <v>45490</v>
       </c>
       <c r="B199" t="n">
-        <v>100213.71875</v>
+        <v>100213.7109375</v>
       </c>
       <c r="C199" t="n">
-        <v>56273.65234375</v>
+        <v>56273.65625</v>
       </c>
     </row>
     <row r="200">
@@ -2622,10 +2622,10 @@
         <v>45491</v>
       </c>
       <c r="B200" t="n">
-        <v>97174.640625</v>
+        <v>97174.6328125</v>
       </c>
       <c r="C200" t="n">
-        <v>56444.95703125</v>
+        <v>56444.9609375</v>
       </c>
     </row>
     <row r="201">
@@ -2633,7 +2633,7 @@
         <v>45492</v>
       </c>
       <c r="B201" t="n">
-        <v>95731.0625</v>
+        <v>95731.0703125</v>
       </c>
       <c r="C201" t="n">
         <v>55931.046875</v>
@@ -2644,10 +2644,10 @@
         <v>45495</v>
       </c>
       <c r="B202" t="n">
-        <v>94287.5</v>
+        <v>94287.515625</v>
       </c>
       <c r="C202" t="n">
-        <v>56016.6953125</v>
+        <v>56016.69921875</v>
       </c>
     </row>
     <row r="203">
@@ -2658,7 +2658,7 @@
         <v>95351.1875</v>
       </c>
       <c r="C203" t="n">
-        <v>56444.95703125</v>
+        <v>56444.9609375</v>
       </c>
     </row>
     <row r="204">
@@ -2666,7 +2666,7 @@
         <v>45497</v>
       </c>
       <c r="B204" t="n">
-        <v>95731.0625</v>
+        <v>95731.0703125</v>
       </c>
       <c r="C204" t="n">
         <v>56188</v>
@@ -2677,7 +2677,7 @@
         <v>45498</v>
       </c>
       <c r="B205" t="n">
-        <v>94971.2890625</v>
+        <v>94971.296875</v>
       </c>
       <c r="C205" t="n">
         <v>56188</v>
@@ -2691,7 +2691,7 @@
         <v>98010.375</v>
       </c>
       <c r="C206" t="n">
-        <v>57558.4453125</v>
+        <v>57558.44140625</v>
       </c>
     </row>
     <row r="207">
@@ -2721,7 +2721,7 @@
         <v>45505</v>
       </c>
       <c r="B209" t="n">
-        <v>94819.3515625</v>
+        <v>94819.34375</v>
       </c>
       <c r="C209" t="n">
         <v>60213.671875</v>
@@ -2732,7 +2732,7 @@
         <v>45506</v>
       </c>
       <c r="B210" t="n">
-        <v>93603.71875</v>
+        <v>93603.7109375</v>
       </c>
       <c r="C210" t="n">
         <v>61241.5</v>
@@ -2743,7 +2743,7 @@
         <v>45509</v>
       </c>
       <c r="B211" t="n">
-        <v>90108.765625</v>
+        <v>90108.7578125</v>
       </c>
       <c r="C211" t="n">
         <v>59442.79296875</v>
@@ -2757,7 +2757,7 @@
         <v>91780.265625</v>
       </c>
       <c r="C212" t="n">
-        <v>62269.32421875</v>
+        <v>62269.33203125</v>
       </c>
     </row>
     <row r="213">
@@ -2768,7 +2768,7 @@
         <v>92691.9921875</v>
       </c>
       <c r="C213" t="n">
-        <v>63211.5078125</v>
+        <v>63211.50390625</v>
       </c>
     </row>
     <row r="214">
@@ -2776,10 +2776,10 @@
         <v>45512</v>
       </c>
       <c r="B214" t="n">
-        <v>92236.125</v>
+        <v>92236.1328125</v>
       </c>
       <c r="C214" t="n">
-        <v>62269.32421875</v>
+        <v>62269.33203125</v>
       </c>
     </row>
     <row r="215">
@@ -2787,10 +2787,10 @@
         <v>45513</v>
       </c>
       <c r="B215" t="n">
-        <v>96414.8671875</v>
+        <v>96414.8515625</v>
       </c>
       <c r="C215" t="n">
-        <v>62783.234375</v>
+        <v>62783.23046875</v>
       </c>
     </row>
     <row r="216">
@@ -2801,7 +2801,7 @@
         <v>98770.1484375</v>
       </c>
       <c r="C216" t="n">
-        <v>62526.28515625</v>
+        <v>62526.28125</v>
       </c>
     </row>
     <row r="217">
@@ -2812,7 +2812,7 @@
         <v>98542.21875</v>
       </c>
       <c r="C217" t="n">
-        <v>63211.5078125</v>
+        <v>63211.50390625</v>
       </c>
     </row>
     <row r="218">
@@ -2823,7 +2823,7 @@
         <v>98390.265625</v>
       </c>
       <c r="C218" t="n">
-        <v>63382.8046875</v>
+        <v>63382.80078125</v>
       </c>
     </row>
     <row r="219">
@@ -2831,10 +2831,10 @@
         <v>45519</v>
       </c>
       <c r="B219" t="n">
-        <v>97782.4453125</v>
+        <v>97782.453125</v>
       </c>
       <c r="C219" t="n">
-        <v>63211.5078125</v>
+        <v>63211.50390625</v>
       </c>
     </row>
     <row r="220">
@@ -2842,10 +2842,10 @@
         <v>45520</v>
       </c>
       <c r="B220" t="n">
-        <v>99226.0234375</v>
+        <v>99226.0078125</v>
       </c>
       <c r="C220" t="n">
-        <v>63211.5078125</v>
+        <v>63211.50390625</v>
       </c>
     </row>
     <row r="221">
@@ -2853,10 +2853,10 @@
         <v>45523</v>
       </c>
       <c r="B221" t="n">
-        <v>99150.03125</v>
+        <v>99150.0390625</v>
       </c>
       <c r="C221" t="n">
-        <v>65095.859375</v>
+        <v>65095.85546875</v>
       </c>
     </row>
     <row r="222">
@@ -2864,10 +2864,10 @@
         <v>45524</v>
       </c>
       <c r="B222" t="n">
-        <v>99909.8046875</v>
+        <v>99909.8125</v>
       </c>
       <c r="C222" t="n">
-        <v>64753.2421875</v>
+        <v>64753.23828125</v>
       </c>
     </row>
     <row r="223">
@@ -2875,10 +2875,10 @@
         <v>45525</v>
       </c>
       <c r="B223" t="n">
-        <v>101429.34375</v>
+        <v>101429.3515625</v>
       </c>
       <c r="C223" t="n">
-        <v>64496.2890625</v>
+        <v>64496.29296875</v>
       </c>
     </row>
     <row r="224">
@@ -2889,7 +2889,7 @@
         <v>101657.28125</v>
       </c>
       <c r="C224" t="n">
-        <v>63554.11328125</v>
+        <v>63554.1171875</v>
       </c>
     </row>
     <row r="225">
@@ -2908,7 +2908,7 @@
         <v>45530</v>
       </c>
       <c r="B226" t="n">
-        <v>99909.8046875</v>
+        <v>99909.8125</v>
       </c>
       <c r="C226" t="n">
         <v>62868.890625</v>
@@ -2919,7 +2919,7 @@
         <v>45532</v>
       </c>
       <c r="B227" t="n">
-        <v>101277.390625</v>
+        <v>101277.3984375</v>
       </c>
       <c r="C227" t="n">
         <v>63297.1484375</v>
@@ -2930,10 +2930,10 @@
         <v>45533</v>
       </c>
       <c r="B228" t="n">
-        <v>101581.3046875</v>
+        <v>101581.3125</v>
       </c>
       <c r="C228" t="n">
-        <v>62954.54296875</v>
+        <v>62954.5390625</v>
       </c>
     </row>
     <row r="229">
@@ -2963,10 +2963,10 @@
         <v>45540</v>
       </c>
       <c r="B231" t="n">
-        <v>99226.0234375</v>
+        <v>99226.0078125</v>
       </c>
       <c r="C231" t="n">
-        <v>63982.375</v>
+        <v>63982.3828125</v>
       </c>
     </row>
     <row r="232">
@@ -2974,10 +2974,10 @@
         <v>45541</v>
       </c>
       <c r="B232" t="n">
-        <v>100365.671875</v>
+        <v>100365.65625</v>
       </c>
       <c r="C232" t="n">
-        <v>64581.94921875</v>
+        <v>64581.9453125</v>
       </c>
     </row>
     <row r="233">
@@ -2985,10 +2985,10 @@
         <v>45544</v>
       </c>
       <c r="B233" t="n">
-        <v>99757.8515625</v>
+        <v>99757.859375</v>
       </c>
       <c r="C233" t="n">
-        <v>64068.03125</v>
+        <v>64068.02734375</v>
       </c>
     </row>
     <row r="234">
@@ -3007,10 +3007,10 @@
         <v>45546</v>
       </c>
       <c r="B235" t="n">
-        <v>99226.0234375</v>
+        <v>99226.0078125</v>
       </c>
       <c r="C235" t="n">
-        <v>63896.71484375</v>
+        <v>63896.72265625</v>
       </c>
     </row>
     <row r="236">
@@ -3021,7 +3021,7 @@
         <v>100517.625</v>
       </c>
       <c r="C236" t="n">
-        <v>63982.375</v>
+        <v>63982.3828125</v>
       </c>
     </row>
     <row r="237">
@@ -3051,7 +3051,7 @@
         <v>45552</v>
       </c>
       <c r="B239" t="n">
-        <v>100973.4921875</v>
+        <v>100973.484375</v>
       </c>
       <c r="C239" t="n">
         <v>62868.890625</v>
@@ -3062,10 +3062,10 @@
         <v>45553</v>
       </c>
       <c r="B240" t="n">
-        <v>102265.09375</v>
+        <v>102265.1015625</v>
       </c>
       <c r="C240" t="n">
-        <v>62783.234375</v>
+        <v>62783.23046875</v>
       </c>
     </row>
     <row r="241">
@@ -3073,10 +3073,10 @@
         <v>45554</v>
       </c>
       <c r="B241" t="n">
-        <v>102720.9609375</v>
+        <v>102720.953125</v>
       </c>
       <c r="C241" t="n">
-        <v>62783.234375</v>
+        <v>62783.23046875</v>
       </c>
     </row>
     <row r="242">
@@ -3087,7 +3087,7 @@
         <v>102796.9375</v>
       </c>
       <c r="C242" t="n">
-        <v>62269.32421875</v>
+        <v>62269.33203125</v>
       </c>
     </row>
     <row r="243">
@@ -3095,7 +3095,7 @@
         <v>45558</v>
       </c>
       <c r="B243" t="n">
-        <v>101809.234375</v>
+        <v>101809.2265625</v>
       </c>
       <c r="C243" t="n">
         <v>62440.62890625</v>
@@ -3128,10 +3128,10 @@
         <v>45561</v>
       </c>
       <c r="B246" t="n">
-        <v>102037.171875</v>
+        <v>102037.1640625</v>
       </c>
       <c r="C246" t="n">
-        <v>62662.20703125</v>
+        <v>62662.2109375</v>
       </c>
     </row>
     <row r="247">
@@ -3142,7 +3142,7 @@
         <v>101961.1796875</v>
       </c>
       <c r="C247" t="n">
-        <v>62928.09765625</v>
+        <v>62928.10546875</v>
       </c>
     </row>
     <row r="248">
@@ -3153,7 +3153,7 @@
         <v>102189.125</v>
       </c>
       <c r="C248" t="n">
-        <v>62130.42578125</v>
+        <v>62130.41796875</v>
       </c>
     </row>
     <row r="249">
@@ -3161,10 +3161,10 @@
         <v>45566</v>
       </c>
       <c r="B249" t="n">
-        <v>103252.7890625</v>
+        <v>103252.796875</v>
       </c>
       <c r="C249" t="n">
-        <v>62130.42578125</v>
+        <v>62130.41796875</v>
       </c>
     </row>
     <row r="250">
@@ -3175,7 +3175,7 @@
         <v>102872.9140625</v>
       </c>
       <c r="C250" t="n">
-        <v>62130.42578125</v>
+        <v>62130.41796875</v>
       </c>
     </row>
     <row r="251">
@@ -3183,7 +3183,7 @@
         <v>45568</v>
       </c>
       <c r="B251" t="n">
-        <v>101809.234375</v>
+        <v>101809.2265625</v>
       </c>
       <c r="C251" t="n">
         <v>62307.6875</v>
@@ -3194,10 +3194,10 @@
         <v>45569</v>
       </c>
       <c r="B252" t="n">
-        <v>101885.21875</v>
+        <v>101885.2109375</v>
       </c>
       <c r="C252" t="n">
-        <v>60712.3203125</v>
+        <v>60712.31640625</v>
       </c>
     </row>
     <row r="253">
@@ -3205,7 +3205,7 @@
         <v>45572</v>
       </c>
       <c r="B253" t="n">
-        <v>101885.21875</v>
+        <v>101885.2109375</v>
       </c>
       <c r="C253" t="n">
         <v>59471.48828125</v>
@@ -3219,7 +3219,7 @@
         <v>102872.9140625</v>
       </c>
       <c r="C254" t="n">
-        <v>60091.90234375</v>
+        <v>60091.90625</v>
       </c>
     </row>
     <row r="255">
@@ -3230,7 +3230,7 @@
         <v>106063.953125</v>
       </c>
       <c r="C255" t="n">
-        <v>60003.27734375</v>
+        <v>60003.26953125</v>
       </c>
     </row>
     <row r="256">
@@ -3241,7 +3241,7 @@
         <v>104544.4140625</v>
       </c>
       <c r="C256" t="n">
-        <v>59560.1171875</v>
+        <v>59560.11328125</v>
       </c>
     </row>
     <row r="257">
@@ -3249,10 +3249,10 @@
         <v>45580</v>
       </c>
       <c r="B257" t="n">
-        <v>104088.5546875</v>
+        <v>104088.546875</v>
       </c>
       <c r="C257" t="n">
-        <v>59205.58984375</v>
+        <v>59205.59375</v>
       </c>
     </row>
     <row r="258">
@@ -3260,7 +3260,7 @@
         <v>45581</v>
       </c>
       <c r="B258" t="n">
-        <v>103556.7109375</v>
+        <v>103556.703125</v>
       </c>
       <c r="C258" t="n">
         <v>59826.01171875</v>
@@ -3271,10 +3271,10 @@
         <v>45582</v>
       </c>
       <c r="B259" t="n">
-        <v>104088.5546875</v>
+        <v>104088.546875</v>
       </c>
       <c r="C259" t="n">
-        <v>59914.640625</v>
+        <v>59914.64453125</v>
       </c>
     </row>
     <row r="260">
@@ -3282,10 +3282,10 @@
         <v>45583</v>
       </c>
       <c r="B260" t="n">
-        <v>104088.5546875</v>
+        <v>104088.546875</v>
       </c>
       <c r="C260" t="n">
-        <v>59737.37890625</v>
+        <v>59737.38671875</v>
       </c>
     </row>
     <row r="261">
@@ -3326,7 +3326,7 @@
         <v>45589</v>
       </c>
       <c r="B264" t="n">
-        <v>102037.171875</v>
+        <v>102037.1640625</v>
       </c>
       <c r="C264" t="n">
         <v>60623.69140625</v>
@@ -3337,7 +3337,7 @@
         <v>45590</v>
       </c>
       <c r="B265" t="n">
-        <v>101809.234375</v>
+        <v>101809.2265625</v>
       </c>
       <c r="C265" t="n">
         <v>60269.1640625</v>
@@ -3351,7 +3351,7 @@
         <v>102493.0234375</v>
       </c>
       <c r="C266" t="n">
-        <v>59560.1171875</v>
+        <v>59560.11328125</v>
       </c>
     </row>
     <row r="267">
@@ -3362,7 +3362,7 @@
         <v>102872.9140625</v>
       </c>
       <c r="C267" t="n">
-        <v>59382.8515625</v>
+        <v>59382.85546875</v>
       </c>
     </row>
     <row r="268">
@@ -3370,7 +3370,7 @@
         <v>45596</v>
       </c>
       <c r="B268" t="n">
-        <v>103252.7890625</v>
+        <v>103252.796875</v>
       </c>
       <c r="C268" t="n">
         <v>58585.17578125</v>
@@ -3381,7 +3381,7 @@
         <v>45597</v>
       </c>
       <c r="B269" t="n">
-        <v>102265.09375</v>
+        <v>102265.1015625</v>
       </c>
       <c r="C269" t="n">
         <v>58319.28125</v>
@@ -3395,7 +3395,7 @@
         <v>100897.5078125</v>
       </c>
       <c r="C270" t="n">
-        <v>58142.01953125</v>
+        <v>58142.0234375</v>
       </c>
     </row>
     <row r="271">
@@ -3403,7 +3403,7 @@
         <v>45602</v>
       </c>
       <c r="B271" t="n">
-        <v>102265.09375</v>
+        <v>102265.1015625</v>
       </c>
       <c r="C271" t="n">
         <v>58319.28125</v>
@@ -3414,7 +3414,7 @@
         <v>45603</v>
       </c>
       <c r="B272" t="n">
-        <v>102644.9765625</v>
+        <v>102644.984375</v>
       </c>
       <c r="C272" t="n">
         <v>58407.9140625</v>
@@ -3436,7 +3436,7 @@
         <v>45608</v>
       </c>
       <c r="B274" t="n">
-        <v>103936.5859375</v>
+        <v>103936.59375</v>
       </c>
       <c r="C274" t="n">
         <v>57521.6015625</v>
@@ -3480,10 +3480,10 @@
         <v>45614</v>
       </c>
       <c r="B278" t="n">
-        <v>101809.234375</v>
+        <v>101809.2265625</v>
       </c>
       <c r="C278" t="n">
-        <v>56014.87109375</v>
+        <v>56014.875</v>
       </c>
     </row>
     <row r="279">
@@ -3494,7 +3494,7 @@
         <v>98770.1484375</v>
       </c>
       <c r="C279" t="n">
-        <v>55837.609375</v>
+        <v>55837.61328125</v>
       </c>
     </row>
     <row r="280">
@@ -3502,7 +3502,7 @@
         <v>45616</v>
       </c>
       <c r="B280" t="n">
-        <v>100593.6015625</v>
+        <v>100593.609375</v>
       </c>
       <c r="C280" t="n">
         <v>56369.39453125</v>
@@ -3546,10 +3546,10 @@
         <v>45622</v>
       </c>
       <c r="B284" t="n">
-        <v>102720.9609375</v>
+        <v>102720.953125</v>
       </c>
       <c r="C284" t="n">
-        <v>57432.96875</v>
+        <v>57432.97265625</v>
       </c>
     </row>
     <row r="285">
@@ -3560,7 +3560,7 @@
         <v>105532.1171875</v>
       </c>
       <c r="C285" t="n">
-        <v>57255.703125</v>
+        <v>57255.70703125</v>
       </c>
     </row>
     <row r="286">
@@ -3571,7 +3571,7 @@
         <v>105911.984375</v>
       </c>
       <c r="C286" t="n">
-        <v>57167.078125</v>
+        <v>57167.07421875</v>
       </c>
     </row>
     <row r="287">
@@ -3579,10 +3579,10 @@
         <v>45625</v>
       </c>
       <c r="B287" t="n">
-        <v>109634.8671875</v>
+        <v>109634.875</v>
       </c>
       <c r="C287" t="n">
-        <v>57255.703125</v>
+        <v>57255.70703125</v>
       </c>
     </row>
     <row r="288">
@@ -3593,7 +3593,7 @@
         <v>108793.2890625</v>
       </c>
       <c r="C288" t="n">
-        <v>57167.078125</v>
+        <v>57167.07421875</v>
       </c>
     </row>
     <row r="289">
@@ -3634,7 +3634,7 @@
         <v>45635</v>
       </c>
       <c r="B292" t="n">
-        <v>112465.6328125</v>
+        <v>112465.640625</v>
       </c>
       <c r="C292" t="n">
         <v>56812.55078125</v>
@@ -3659,7 +3659,7 @@
         <v>115143.3828125</v>
       </c>
       <c r="C294" t="n">
-        <v>56901.1796875</v>
+        <v>56901.18359375</v>
       </c>
     </row>
     <row r="295">
@@ -3670,7 +3670,7 @@
         <v>114913.8671875</v>
       </c>
       <c r="C295" t="n">
-        <v>57255.703125</v>
+        <v>57255.70703125</v>
       </c>
     </row>
     <row r="296">
@@ -3681,7 +3681,7 @@
         <v>114378.3203125</v>
       </c>
       <c r="C296" t="n">
-        <v>56901.1796875</v>
+        <v>56901.18359375</v>
       </c>
     </row>
     <row r="297">
@@ -3700,7 +3700,7 @@
         <v>45644</v>
       </c>
       <c r="B298" t="n">
-        <v>113766.25</v>
+        <v>113766.2578125</v>
       </c>
       <c r="C298" t="n">
         <v>57344.33984375</v>
@@ -3736,7 +3736,7 @@
         <v>114607.828125</v>
       </c>
       <c r="C301" t="n">
-        <v>57078.44140625</v>
+        <v>57078.4453125</v>
       </c>
     </row>
     <row r="302">
@@ -3744,7 +3744,7 @@
         <v>45650</v>
       </c>
       <c r="B302" t="n">
-        <v>115066.875</v>
+        <v>115066.8828125</v>
       </c>
       <c r="C302" t="n">
         <v>56989.81640625</v>
@@ -3755,10 +3755,10 @@
         <v>45651</v>
       </c>
       <c r="B303" t="n">
-        <v>115372.90625</v>
+        <v>115372.8984375</v>
       </c>
       <c r="C303" t="n">
-        <v>57078.44140625</v>
+        <v>57078.4453125</v>
       </c>
     </row>
     <row r="304">
@@ -3791,7 +3791,7 @@
         <v>115143.3828125</v>
       </c>
       <c r="C306" t="n">
-        <v>56542.5</v>
+        <v>56542.49609375</v>
       </c>
     </row>
     <row r="307">
@@ -3802,7 +3802,7 @@
         <v>116673.53125</v>
       </c>
       <c r="C307" t="n">
-        <v>56631.8203125</v>
+        <v>56631.82421875</v>
       </c>
     </row>
     <row r="308">
@@ -3821,7 +3821,7 @@
         <v>45660</v>
       </c>
       <c r="B309" t="n">
-        <v>113995.7890625</v>
+        <v>113995.78125</v>
       </c>
       <c r="C309" t="n">
         <v>56274.5234375</v>
@@ -3854,7 +3854,7 @@
         <v>45665</v>
       </c>
       <c r="B312" t="n">
-        <v>113460.234375</v>
+        <v>113460.2265625</v>
       </c>
       <c r="C312" t="n">
         <v>55113.3046875</v>
@@ -3868,7 +3868,7 @@
         <v>113842.765625</v>
       </c>
       <c r="C313" t="n">
-        <v>55202.6328125</v>
+        <v>55202.62890625</v>
       </c>
     </row>
     <row r="314">
@@ -3890,7 +3890,7 @@
         <v>111012</v>
       </c>
       <c r="C315" t="n">
-        <v>55023.984375</v>
+        <v>55023.98046875</v>
       </c>
     </row>
     <row r="316">
@@ -3920,7 +3920,7 @@
         <v>45674</v>
       </c>
       <c r="B318" t="n">
-        <v>113995.7890625</v>
+        <v>113995.78125</v>
       </c>
       <c r="C318" t="n">
         <v>55381.28125</v>
@@ -3945,7 +3945,7 @@
         <v>114684.3515625</v>
       </c>
       <c r="C320" t="n">
-        <v>55202.6328125</v>
+        <v>55202.62890625</v>
       </c>
     </row>
     <row r="321">
@@ -3953,10 +3953,10 @@
         <v>45679</v>
       </c>
       <c r="B321" t="n">
-        <v>114531.3359375</v>
+        <v>114531.328125</v>
       </c>
       <c r="C321" t="n">
-        <v>55023.984375</v>
+        <v>55023.98046875</v>
       </c>
     </row>
     <row r="322">
@@ -3989,7 +3989,7 @@
         <v>111318.03125</v>
       </c>
       <c r="C324" t="n">
-        <v>54041.40625</v>
+        <v>54041.41015625</v>
       </c>
     </row>
     <row r="325">
@@ -4011,7 +4011,7 @@
         <v>111930.078125</v>
       </c>
       <c r="C326" t="n">
-        <v>54934.65625</v>
+        <v>54934.65234375</v>
       </c>
     </row>
     <row r="327">
@@ -4022,7 +4022,7 @@
         <v>112083.09375</v>
       </c>
       <c r="C327" t="n">
-        <v>54220.0546875</v>
+        <v>54220.05859375</v>
       </c>
     </row>
     <row r="328">
@@ -4033,7 +4033,7 @@
         <v>111777.0703125</v>
       </c>
       <c r="C328" t="n">
-        <v>54309.38671875</v>
+        <v>54309.3828125</v>
       </c>
     </row>
     <row r="329">
@@ -4055,7 +4055,7 @@
         <v>111241.515625</v>
       </c>
       <c r="C330" t="n">
-        <v>53952.0859375</v>
+        <v>53952.08203125</v>
       </c>
     </row>
     <row r="331">
@@ -4066,7 +4066,7 @@
         <v>110935.4921875</v>
       </c>
       <c r="C331" t="n">
-        <v>54488.03515625</v>
+        <v>54488.03125</v>
       </c>
     </row>
     <row r="332">
@@ -4074,10 +4074,10 @@
         <v>45701</v>
       </c>
       <c r="B332" t="n">
-        <v>109481.859375</v>
+        <v>109481.8515625</v>
       </c>
       <c r="C332" t="n">
-        <v>54220.0546875</v>
+        <v>54220.05859375</v>
       </c>
     </row>
     <row r="333">
@@ -4088,7 +4088,7 @@
         <v>110858.984375</v>
       </c>
       <c r="C333" t="n">
-        <v>53862.7578125</v>
+        <v>53862.76171875</v>
       </c>
     </row>
     <row r="334">
@@ -4096,7 +4096,7 @@
         <v>45705</v>
       </c>
       <c r="B334" t="n">
-        <v>109864.3828125</v>
+        <v>109864.390625</v>
       </c>
       <c r="C334" t="n">
         <v>53594.78515625</v>
@@ -4107,10 +4107,10 @@
         <v>45706</v>
       </c>
       <c r="B335" t="n">
-        <v>110093.90625</v>
+        <v>110093.9140625</v>
       </c>
       <c r="C335" t="n">
-        <v>53862.7578125</v>
+        <v>53862.76171875</v>
       </c>
     </row>
     <row r="336">
@@ -4121,7 +4121,7 @@
         <v>110170.421875</v>
       </c>
       <c r="C336" t="n">
-        <v>54309.38671875</v>
+        <v>54309.3828125</v>
       </c>
     </row>
     <row r="337">
@@ -4132,7 +4132,7 @@
         <v>109405.34375</v>
       </c>
       <c r="C337" t="n">
-        <v>54220.0546875</v>
+        <v>54220.05859375</v>
       </c>
     </row>
     <row r="338">
@@ -4151,7 +4151,7 @@
         <v>45712</v>
       </c>
       <c r="B339" t="n">
-        <v>107492.65625</v>
+        <v>107492.6640625</v>
       </c>
       <c r="C339" t="n">
         <v>56989.12109375</v>
@@ -4173,7 +4173,7 @@
         <v>45714</v>
       </c>
       <c r="B341" t="n">
-        <v>108487.265625</v>
+        <v>108487.2578125</v>
       </c>
       <c r="C341" t="n">
         <v>56363.84765625</v>
@@ -4206,10 +4206,10 @@
         <v>45719</v>
       </c>
       <c r="B344" t="n">
-        <v>107492.65625</v>
+        <v>107492.6640625</v>
       </c>
       <c r="C344" t="n">
-        <v>56453.171875</v>
+        <v>56453.17578125</v>
       </c>
     </row>
     <row r="345">
@@ -4217,10 +4217,10 @@
         <v>45720</v>
       </c>
       <c r="B345" t="n">
-        <v>107110.1328125</v>
+        <v>107110.125</v>
       </c>
       <c r="C345" t="n">
-        <v>56721.1484375</v>
+        <v>56721.14453125</v>
       </c>
     </row>
     <row r="346">
@@ -4228,7 +4228,7 @@
         <v>45721</v>
       </c>
       <c r="B346" t="n">
-        <v>106421.5625</v>
+        <v>106421.5703125</v>
       </c>
       <c r="C346" t="n">
         <v>56006.55078125</v>
@@ -4239,7 +4239,7 @@
         <v>45722</v>
       </c>
       <c r="B347" t="n">
-        <v>108334.2421875</v>
+        <v>108334.25</v>
       </c>
       <c r="C347" t="n">
         <v>56185.19921875</v>
@@ -4250,7 +4250,7 @@
         <v>45723</v>
       </c>
       <c r="B348" t="n">
-        <v>108181.2265625</v>
+        <v>108181.234375</v>
       </c>
       <c r="C348" t="n">
         <v>56006.55078125</v>
@@ -4308,7 +4308,7 @@
         <v>100530.5078125</v>
       </c>
       <c r="C353" t="n">
-        <v>55470.60546875</v>
+        <v>55470.6015625</v>
       </c>
     </row>
     <row r="354">
@@ -4338,7 +4338,7 @@
         <v>45735</v>
       </c>
       <c r="B356" t="n">
-        <v>95328.015625</v>
+        <v>95328.0078125</v>
       </c>
       <c r="C356" t="n">
         <v>55649.25390625</v>
@@ -4349,10 +4349,10 @@
         <v>45736</v>
       </c>
       <c r="B357" t="n">
-        <v>95634.046875</v>
+        <v>95634.0390625</v>
       </c>
       <c r="C357" t="n">
-        <v>55202.6328125</v>
+        <v>55202.62890625</v>
       </c>
     </row>
     <row r="358">
@@ -4415,10 +4415,10 @@
         <v>45744</v>
       </c>
       <c r="B363" t="n">
-        <v>94868.984375</v>
+        <v>94868.9765625</v>
       </c>
       <c r="C363" t="n">
-        <v>53862.7578125</v>
+        <v>53862.76171875</v>
       </c>
     </row>
     <row r="364">
@@ -4426,7 +4426,7 @@
         <v>45747</v>
       </c>
       <c r="B364" t="n">
-        <v>92573.75</v>
+        <v>92573.7578125</v>
       </c>
       <c r="C364" t="n">
         <v>54130.734375</v>
@@ -4437,10 +4437,10 @@
         <v>45748</v>
       </c>
       <c r="B365" t="n">
-        <v>92191.21875</v>
+        <v>92191.2109375</v>
       </c>
       <c r="C365" t="n">
-        <v>54309.38671875</v>
+        <v>54309.3828125</v>
       </c>
     </row>
     <row r="366">
@@ -4451,7 +4451,7 @@
         <v>93338.828125</v>
       </c>
       <c r="C366" t="n">
-        <v>54041.40625</v>
+        <v>54041.41015625</v>
       </c>
     </row>
     <row r="367">
@@ -4459,7 +4459,7 @@
         <v>45750</v>
       </c>
       <c r="B367" t="n">
-        <v>86835.703125</v>
+        <v>86835.7109375</v>
       </c>
       <c r="C367" t="n">
         <v>50468.421875</v>
@@ -4470,10 +4470,10 @@
         <v>45751</v>
       </c>
       <c r="B368" t="n">
-        <v>86453.1796875</v>
+        <v>86453.171875</v>
       </c>
       <c r="C368" t="n">
-        <v>52254.9140625</v>
+        <v>52254.91796875</v>
       </c>
     </row>
     <row r="369">
@@ -4481,10 +4481,10 @@
         <v>45755</v>
       </c>
       <c r="B369" t="n">
-        <v>80409.109375</v>
+        <v>80409.1015625</v>
       </c>
       <c r="C369" t="n">
-        <v>48681.9296875</v>
+        <v>48681.93359375</v>
       </c>
     </row>
     <row r="370">
@@ -4495,7 +4495,7 @@
         <v>80562.125</v>
       </c>
       <c r="C370" t="n">
-        <v>46448.8125</v>
+        <v>46448.81640625</v>
       </c>
     </row>
     <row r="371">
@@ -4539,7 +4539,7 @@
         <v>88748.390625</v>
       </c>
       <c r="C374" t="n">
-        <v>50289.76953125</v>
+        <v>50289.7734375</v>
       </c>
     </row>
     <row r="375">
@@ -4580,10 +4580,10 @@
         <v>45768</v>
       </c>
       <c r="B378" t="n">
-        <v>85458.59375</v>
+        <v>85458.5859375</v>
       </c>
       <c r="C378" t="n">
-        <v>50647.07421875</v>
+        <v>50647.0703125</v>
       </c>
     </row>
     <row r="379">
@@ -4591,7 +4591,7 @@
         <v>45769</v>
       </c>
       <c r="B379" t="n">
-        <v>84463.9765625</v>
+        <v>84463.984375</v>
       </c>
       <c r="C379" t="n">
         <v>50021.80078125</v>
@@ -4602,7 +4602,7 @@
         <v>45770</v>
       </c>
       <c r="B380" t="n">
-        <v>84463.9765625</v>
+        <v>84463.984375</v>
       </c>
       <c r="C380" t="n">
         <v>50379.09765625</v>
@@ -4616,7 +4616,7 @@
         <v>85688.1015625</v>
       </c>
       <c r="C381" t="n">
-        <v>50289.76953125</v>
+        <v>50289.7734375</v>
       </c>
     </row>
     <row r="382">
@@ -4627,7 +4627,7 @@
         <v>85994.1328125</v>
       </c>
       <c r="C382" t="n">
-        <v>52076.265625</v>
+        <v>52076.26953125</v>
       </c>
     </row>
     <row r="383">
@@ -4657,7 +4657,7 @@
         <v>45782</v>
       </c>
       <c r="B385" t="n">
-        <v>83086.8671875</v>
+        <v>83086.859375</v>
       </c>
       <c r="C385" t="n">
         <v>51450.99609375</v>
@@ -4668,7 +4668,7 @@
         <v>45783</v>
       </c>
       <c r="B386" t="n">
-        <v>83086.8671875</v>
+        <v>83086.859375</v>
       </c>
       <c r="C386" t="n">
         <v>50825.72265625</v>
@@ -4748,7 +4748,7 @@
         <v>96628.640625</v>
       </c>
       <c r="C393" t="n">
-        <v>51974.3125</v>
+        <v>51974.31640625</v>
       </c>
     </row>
     <row r="394">
@@ -4756,7 +4756,7 @@
         <v>45793</v>
       </c>
       <c r="B394" t="n">
-        <v>95634.046875</v>
+        <v>95634.0390625</v>
       </c>
       <c r="C394" t="n">
         <v>52529.203125</v>
@@ -4767,10 +4767,10 @@
         <v>45796</v>
       </c>
       <c r="B395" t="n">
-        <v>90431.5546875</v>
+        <v>90431.546875</v>
       </c>
       <c r="C395" t="n">
-        <v>51789.3515625</v>
+        <v>51789.35546875</v>
       </c>
     </row>
     <row r="396">
@@ -4778,10 +4778,10 @@
         <v>45797</v>
       </c>
       <c r="B396" t="n">
-        <v>90431.5546875</v>
+        <v>90431.546875</v>
       </c>
       <c r="C396" t="n">
-        <v>51789.3515625</v>
+        <v>51789.35546875</v>
       </c>
     </row>
     <row r="397">
@@ -4858,7 +4858,7 @@
         <v>90584.5625</v>
       </c>
       <c r="C403" t="n">
-        <v>51049.50390625</v>
+        <v>51049.5078125</v>
       </c>
     </row>
     <row r="404">
@@ -4866,10 +4866,10 @@
         <v>45807</v>
       </c>
       <c r="B404" t="n">
-        <v>89589.9765625</v>
+        <v>89589.96875</v>
       </c>
       <c r="C404" t="n">
-        <v>50957.0234375</v>
+        <v>50957.02734375</v>
       </c>
     </row>
     <row r="405">
@@ -4877,7 +4877,7 @@
         <v>45810</v>
       </c>
       <c r="B405" t="n">
-        <v>88824.90625</v>
+        <v>88824.8984375</v>
       </c>
       <c r="C405" t="n">
         <v>50494.62109375</v>
@@ -4888,7 +4888,7 @@
         <v>45811</v>
       </c>
       <c r="B406" t="n">
-        <v>88824.90625</v>
+        <v>88824.8984375</v>
       </c>
       <c r="C406" t="n">
         <v>50494.62109375</v>
@@ -4902,7 +4902,7 @@
         <v>89819.4921875</v>
       </c>
       <c r="C407" t="n">
-        <v>51326.94921875</v>
+        <v>51326.9453125</v>
       </c>
     </row>
     <row r="408">
@@ -4910,7 +4910,7 @@
         <v>45813</v>
       </c>
       <c r="B408" t="n">
-        <v>89589.9765625</v>
+        <v>89589.96875</v>
       </c>
       <c r="C408" t="n">
         <v>52621.68359375</v>
@@ -4932,7 +4932,7 @@
         <v>45817</v>
       </c>
       <c r="B410" t="n">
-        <v>88901.40625</v>
+        <v>88901.4140625</v>
       </c>
       <c r="C410" t="n">
         <v>51141.984375</v>
@@ -4943,7 +4943,7 @@
         <v>45818</v>
       </c>
       <c r="B411" t="n">
-        <v>88901.40625</v>
+        <v>88901.4140625</v>
       </c>
       <c r="C411" t="n">
         <v>51141.984375</v>
@@ -4968,7 +4968,7 @@
         <v>90988.4453125</v>
       </c>
       <c r="C413" t="n">
-        <v>51049.50390625</v>
+        <v>51049.5078125</v>
       </c>
     </row>
     <row r="414">
@@ -5012,7 +5012,7 @@
         <v>91683.015625</v>
       </c>
       <c r="C417" t="n">
-        <v>51974.3125</v>
+        <v>51974.31640625</v>
       </c>
     </row>
     <row r="418">
@@ -5023,7 +5023,7 @@
         <v>90293.875</v>
       </c>
       <c r="C418" t="n">
-        <v>51789.3515625</v>
+        <v>51789.35546875</v>
       </c>
     </row>
     <row r="419">
@@ -5100,7 +5100,7 @@
         <v>91219.96875</v>
       </c>
       <c r="C425" t="n">
-        <v>53638.97265625</v>
+        <v>53638.9765625</v>
       </c>
     </row>
     <row r="426">
@@ -5111,7 +5111,7 @@
         <v>91219.96875</v>
       </c>
       <c r="C426" t="n">
-        <v>53638.97265625</v>
+        <v>53638.9765625</v>
       </c>
     </row>
     <row r="427">
@@ -5122,7 +5122,7 @@
         <v>91683.015625</v>
       </c>
       <c r="C427" t="n">
-        <v>53176.5703125</v>
+        <v>53176.56640625</v>
       </c>
     </row>
     <row r="428">
@@ -5133,7 +5133,7 @@
         <v>91065.6171875</v>
       </c>
       <c r="C428" t="n">
-        <v>53176.5703125</v>
+        <v>53176.56640625</v>
       </c>
     </row>
     <row r="429">
@@ -5166,7 +5166,7 @@
         <v>96081.9453125</v>
       </c>
       <c r="C431" t="n">
-        <v>54563.78515625</v>
+        <v>54563.78125</v>
       </c>
     </row>
     <row r="432">
@@ -5188,7 +5188,7 @@
         <v>95618.90625</v>
       </c>
       <c r="C433" t="n">
-        <v>55211.1484375</v>
+        <v>55211.15234375</v>
       </c>
     </row>
     <row r="434">
@@ -5199,7 +5199,7 @@
         <v>98088.46875</v>
       </c>
       <c r="C434" t="n">
-        <v>55766.03515625</v>
+        <v>55766.0390625</v>
       </c>
     </row>
     <row r="435">
@@ -5210,7 +5210,7 @@
         <v>98088.46875</v>
       </c>
       <c r="C435" t="n">
-        <v>55766.03515625</v>
+        <v>55766.0390625</v>
       </c>
     </row>
     <row r="436">
@@ -5331,7 +5331,7 @@
         <v>94075.4140625</v>
       </c>
       <c r="C446" t="n">
-        <v>58447.984375</v>
+        <v>58447.98828125</v>
       </c>
     </row>
     <row r="447">
@@ -5419,7 +5419,7 @@
         <v>94430.421875</v>
       </c>
       <c r="C454" t="n">
-        <v>56875.80859375</v>
+        <v>56875.8046875</v>
       </c>
     </row>
     <row r="455">
@@ -5430,7 +5430,7 @@
         <v>94430.421875</v>
       </c>
       <c r="C455" t="n">
-        <v>56875.80859375</v>
+        <v>56875.8046875</v>
       </c>
     </row>
     <row r="456">
@@ -5441,7 +5441,7 @@
         <v>95406.671875</v>
       </c>
       <c r="C456" t="n">
-        <v>57153.25390625</v>
+        <v>57153.25</v>
       </c>
     </row>
     <row r="457">
@@ -5474,7 +5474,7 @@
         <v>89194.140625</v>
       </c>
       <c r="C459" t="n">
-        <v>56135.95703125</v>
+        <v>56135.9609375</v>
       </c>
     </row>
     <row r="460">
@@ -5485,7 +5485,7 @@
         <v>89194.140625</v>
       </c>
       <c r="C460" t="n">
-        <v>56135.95703125</v>
+        <v>56135.9609375</v>
       </c>
     </row>
     <row r="461">
@@ -5496,7 +5496,7 @@
         <v>89016.6484375</v>
       </c>
       <c r="C461" t="n">
-        <v>55950.99609375</v>
+        <v>55951</v>
       </c>
     </row>
     <row r="462">
@@ -5551,7 +5551,7 @@
         <v>88750.390625</v>
       </c>
       <c r="C466" t="n">
-        <v>55211.1484375</v>
+        <v>55211.15234375</v>
       </c>
     </row>
     <row r="467">
@@ -5562,7 +5562,7 @@
         <v>93187.9140625</v>
       </c>
       <c r="C467" t="n">
-        <v>55950.99609375</v>
+        <v>55951</v>
       </c>
     </row>
     <row r="468">
@@ -5573,7 +5573,7 @@
         <v>92744.1640625</v>
       </c>
       <c r="C468" t="n">
-        <v>56413.40625</v>
+        <v>56413.40234375</v>
       </c>
     </row>
     <row r="469">
@@ -5584,7 +5584,7 @@
         <v>91590.3984375</v>
       </c>
       <c r="C469" t="n">
-        <v>56875.80859375</v>
+        <v>56875.8046875</v>
       </c>
     </row>
     <row r="470">
@@ -5595,7 +5595,7 @@
         <v>91590.3984375</v>
       </c>
       <c r="C470" t="n">
-        <v>56875.80859375</v>
+        <v>56875.8046875</v>
       </c>
     </row>
     <row r="471">
@@ -5606,7 +5606,7 @@
         <v>93187.9140625</v>
       </c>
       <c r="C471" t="n">
-        <v>57153.25390625</v>
+        <v>57153.25</v>
       </c>
     </row>
     <row r="472">
@@ -5617,7 +5617,7 @@
         <v>90436.6484375</v>
       </c>
       <c r="C472" t="n">
-        <v>56043.4765625</v>
+        <v>56043.48046875</v>
       </c>
     </row>
     <row r="473">
@@ -5628,7 +5628,7 @@
         <v>90436.6484375</v>
       </c>
       <c r="C473" t="n">
-        <v>56043.4765625</v>
+        <v>56043.48046875</v>
       </c>
     </row>
     <row r="474">
@@ -5639,7 +5639,7 @@
         <v>90614.1484375</v>
       </c>
       <c r="C474" t="n">
-        <v>55766.03515625</v>
+        <v>55766.0390625</v>
       </c>
     </row>
     <row r="475">
@@ -5771,7 +5771,7 @@
         <v>84756.625</v>
       </c>
       <c r="C486" t="n">
-        <v>55766.03515625</v>
+        <v>55766.0390625</v>
       </c>
     </row>
     <row r="487">
@@ -5782,7 +5782,7 @@
         <v>84756.625</v>
       </c>
       <c r="C487" t="n">
-        <v>55766.03515625</v>
+        <v>55766.0390625</v>
       </c>
     </row>
     <row r="488">
@@ -5804,7 +5804,7 @@
         <v>82892.8671875</v>
       </c>
       <c r="C489" t="n">
-        <v>57430.6953125</v>
+        <v>57430.69140625</v>
       </c>
     </row>
     <row r="490">
@@ -5859,7 +5859,7 @@
         <v>83869.125</v>
       </c>
       <c r="C494" t="n">
-        <v>58632.9453125</v>
+        <v>58632.94921875</v>
       </c>
     </row>
     <row r="495">
@@ -5881,7 +5881,7 @@
         <v>83425.375</v>
       </c>
       <c r="C496" t="n">
-        <v>59187.83203125</v>
+        <v>59187.8359375</v>
       </c>
     </row>
     <row r="497">
@@ -5892,7 +5892,7 @@
         <v>83425.375</v>
       </c>
       <c r="C497" t="n">
-        <v>59187.83203125</v>
+        <v>59187.8359375</v>
       </c>
     </row>
     <row r="498">
@@ -8516,10 +8516,10 @@
         <v>45197</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.003181326376937466</v>
+        <v>-0.003181263181403438</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02349858363652735</v>
+        <v>-0.02349864296311999</v>
       </c>
     </row>
     <row r="3">
@@ -8527,7 +8527,7 @@
         <v>45198</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.0127659180595987</v>
+        <v>-0.01276598064749224</v>
       </c>
       <c r="C3" t="n">
         <v>-0.008021413830182178</v>
@@ -8538,10 +8538,10 @@
         <v>45201</v>
       </c>
       <c r="B4" t="n">
-        <v>0.004310309951106372</v>
+        <v>0.004310245734096219</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01886779198934985</v>
+        <v>0.0188676665506986</v>
       </c>
     </row>
     <row r="5">
@@ -8549,10 +8549,10 @@
         <v>45202</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.01072962320162407</v>
+        <v>-0.01072962388769128</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.02116396318888947</v>
+        <v>-0.02116378112089001</v>
       </c>
     </row>
     <row r="6">
@@ -8560,10 +8560,10 @@
         <v>45203</v>
       </c>
       <c r="B6" t="n">
-        <v>0.003253786070724241</v>
+        <v>0.003253850915947876</v>
       </c>
       <c r="C6" t="n">
-        <v>0.005405421722510351</v>
+        <v>0.005405547160244994</v>
       </c>
     </row>
     <row r="7">
@@ -8571,10 +8571,10 @@
         <v>45204</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.009729699850327123</v>
+        <v>-0.009729764275612451</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.02284946841888769</v>
+        <v>-0.02284958923256963</v>
       </c>
     </row>
     <row r="8">
@@ -8582,10 +8582,10 @@
         <v>45205</v>
       </c>
       <c r="B8" t="n">
-        <v>0.01200871807012671</v>
+        <v>0.01200871885139332</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02063279935274775</v>
+        <v>0.02063273401857546</v>
       </c>
     </row>
     <row r="9">
@@ -8593,10 +8593,10 @@
         <v>45208</v>
       </c>
       <c r="B9" t="n">
-        <v>0.03128370007695702</v>
+        <v>0.03128376637436125</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.006738376180354222</v>
+        <v>-0.006738564338330866</v>
       </c>
     </row>
     <row r="10">
@@ -8607,7 +8607,7 @@
         <v>0.007322132435958251</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00949773853144853</v>
+        <v>0.00949811919963417</v>
       </c>
     </row>
     <row r="11">
@@ -8615,7 +8615,7 @@
         <v>45210</v>
       </c>
       <c r="B11" t="n">
-        <v>0.007268970408137454</v>
+        <v>0.007269032291201905</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -8626,10 +8626,10 @@
         <v>45211</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.006185486699523346</v>
+        <v>-0.006185609192470243</v>
       </c>
       <c r="C12" t="n">
-        <v>0.01478492807667009</v>
+        <v>0.01478486275152968</v>
       </c>
     </row>
     <row r="13">
@@ -8637,10 +8637,10 @@
         <v>45212</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.003112085266512299</v>
+        <v>-0.003112085458897851</v>
       </c>
       <c r="C13" t="n">
-        <v>0.003973583574482076</v>
+        <v>0.0039734598058494</v>
       </c>
     </row>
     <row r="14">
@@ -8648,7 +8648,7 @@
         <v>45215</v>
       </c>
       <c r="B14" t="n">
-        <v>0.007284097991126171</v>
+        <v>0.007284160454680944</v>
       </c>
       <c r="C14" t="n">
         <v>-0.007915590609347212</v>
@@ -8670,10 +8670,10 @@
         <v>45217</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.001074025232007725</v>
+        <v>-0.001074089242093734</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.01203224517772905</v>
+        <v>-0.01203212074527327</v>
       </c>
     </row>
     <row r="17">
@@ -8681,10 +8681,10 @@
         <v>45218</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.01075276120821811</v>
+        <v>-0.01075269781833088</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.03382928884215664</v>
+        <v>-0.03382959945111919</v>
       </c>
     </row>
     <row r="18">
@@ -8695,7 +8695,7 @@
         <v>0.009782643477237896</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01260488262974446</v>
+        <v>0.01260514581012018</v>
       </c>
     </row>
     <row r="19">
@@ -8703,10 +8703,10 @@
         <v>45222</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.02045207838512575</v>
+        <v>-0.02045220668089975</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.02904553792192044</v>
+        <v>-0.02904566478743453</v>
       </c>
     </row>
     <row r="20">
@@ -8714,10 +8714,10 @@
         <v>45223</v>
       </c>
       <c r="B20" t="n">
-        <v>0.01098895485709339</v>
+        <v>0.01098908727085757</v>
       </c>
       <c r="C20" t="n">
-        <v>0.001424505579622926</v>
+        <v>0.001424571967136412</v>
       </c>
     </row>
     <row r="21">
@@ -8725,10 +8725,10 @@
         <v>45224</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.01195644189638079</v>
+        <v>-0.01195650667180381</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.01849216405115317</v>
+        <v>-0.01849236264747434</v>
       </c>
     </row>
     <row r="22">
@@ -8736,10 +8736,10 @@
         <v>45225</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.04510452148577515</v>
+        <v>-0.04510452444279522</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.02898559130950251</v>
+        <v>-0.02898539483636042</v>
       </c>
     </row>
     <row r="23">
@@ -8747,10 +8747,10 @@
         <v>45226</v>
       </c>
       <c r="B23" t="n">
-        <v>0.002304094470619633</v>
+        <v>0.002304163284787553</v>
       </c>
       <c r="C23" t="n">
-        <v>0.01492534825337954</v>
+        <v>0.01492541771269495</v>
       </c>
     </row>
     <row r="24">
@@ -8758,10 +8758,10 @@
         <v>45229</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.02298852621783709</v>
+        <v>-0.02298859471598447</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.005882302216647428</v>
+        <v>-0.005882438689779224</v>
       </c>
     </row>
     <row r="25">
@@ -8769,10 +8769,10 @@
         <v>45230</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.02352950331994774</v>
+        <v>-0.02352936474984868</v>
       </c>
       <c r="C25" t="n">
-        <v>0.005917108436720886</v>
+        <v>0.005917246529702602</v>
       </c>
     </row>
     <row r="26">
@@ -8780,10 +8780,10 @@
         <v>45231</v>
       </c>
       <c r="B26" t="n">
-        <v>0.02891579223531093</v>
+        <v>0.02891571835991225</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0352941554891677</v>
+        <v>0.03529415307371164</v>
       </c>
     </row>
     <row r="27">
@@ -8791,10 +8791,10 @@
         <v>45232</v>
       </c>
       <c r="B27" t="n">
-        <v>0.04215464567788496</v>
+        <v>0.04215457589640081</v>
       </c>
       <c r="C27" t="n">
-        <v>0.007102293854499564</v>
+        <v>0.007102161175522204</v>
       </c>
     </row>
     <row r="28">
@@ -8802,10 +8802,10 @@
         <v>45233</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.02247199512753784</v>
+        <v>-0.0224719296733753</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.01269397261441085</v>
+        <v>-0.01269390780905955</v>
       </c>
     </row>
     <row r="29">
@@ -8813,10 +8813,10 @@
         <v>45236</v>
       </c>
       <c r="B29" t="n">
-        <v>0.01724132616523044</v>
+        <v>0.01724139466337782</v>
       </c>
       <c r="C29" t="n">
-        <v>0.01428575702445656</v>
+        <v>0.01428582350694452</v>
       </c>
     </row>
     <row r="30">
@@ -8824,10 +8824,10 @@
         <v>45237</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.002259835266358867</v>
+        <v>-0.002259902451348772</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.002816909717112792</v>
+        <v>-0.002817040624691125</v>
       </c>
     </row>
     <row r="31">
@@ -8838,7 +8838,7 @@
         <v>0.04869758413938508</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008474667069467978</v>
+        <v>0.008474536163967539</v>
       </c>
     </row>
     <row r="32">
@@ -8849,7 +8849,7 @@
         <v>-0.00107988886540622</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.009804014863918131</v>
+        <v>-0.009803821244219857</v>
       </c>
     </row>
     <row r="33">
@@ -8857,10 +8857,10 @@
         <v>45240</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.01081075613637961</v>
+        <v>-0.01081082056166482</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.01555874481329644</v>
+        <v>-0.01555867898905283</v>
       </c>
     </row>
     <row r="34">
@@ -8868,10 +8868,10 @@
         <v>45243</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.001093001307211794</v>
+        <v>-0.00109287111962364</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.01293100652645029</v>
+        <v>-0.01293107252639214</v>
       </c>
     </row>
     <row r="35">
@@ -8879,7 +8879,7 @@
         <v>45244</v>
       </c>
       <c r="B35" t="n">
-        <v>0.01312912838274816</v>
+        <v>0.01312906232607736</v>
       </c>
       <c r="C35" t="n">
         <v>0.002911216828480612</v>
@@ -8901,7 +8901,7 @@
         <v>45246</v>
       </c>
       <c r="B37" t="n">
-        <v>0.006493615799987973</v>
+        <v>0.006493551304975975</v>
       </c>
       <c r="C37" t="n">
         <v>-0.0056576595624096</v>
@@ -8912,7 +8912,7 @@
         <v>45247</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.02150539425861953</v>
+        <v>-0.02150545971557416</v>
       </c>
       <c r="C38" t="n">
         <v>-0.004267503948756857</v>
@@ -8923,10 +8923,10 @@
         <v>45250</v>
       </c>
       <c r="B39" t="n">
-        <v>-0.003296758493088858</v>
+        <v>-0.00329669343763439</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.009999963434631609</v>
+        <v>-0.01000002991711957</v>
       </c>
     </row>
     <row r="40">
@@ -8934,10 +8934,10 @@
         <v>45251</v>
       </c>
       <c r="B40" t="n">
-        <v>0.01323045512594812</v>
+        <v>0.01323052169909111</v>
       </c>
       <c r="C40" t="n">
-        <v>0.002885944259472417</v>
+        <v>0.002886145915366178</v>
       </c>
     </row>
     <row r="41">
@@ -8945,10 +8945,10 @@
         <v>45252</v>
       </c>
       <c r="B41" t="n">
-        <v>0.01196958156363448</v>
+        <v>0.0119695167177285</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.001438853256453432</v>
+        <v>-0.001439053946075242</v>
       </c>
     </row>
     <row r="42">
@@ -8956,10 +8956,10 @@
         <v>45253</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.02365594650026315</v>
+        <v>-0.02365588393719809</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.01008641871080129</v>
+        <v>-0.01008635232989818</v>
       </c>
     </row>
     <row r="43">
@@ -8967,10 +8967,10 @@
         <v>45254</v>
       </c>
       <c r="B43" t="n">
-        <v>0.004405185149695567</v>
+        <v>0.004405250781178705</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.005822433656961445</v>
+        <v>-0.005822501397487079</v>
       </c>
     </row>
     <row r="44">
@@ -8978,10 +8978,10 @@
         <v>45257</v>
       </c>
       <c r="B44" t="n">
-        <v>-0.005482396098723807</v>
+        <v>-0.005482526427740275</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.002928130191206746</v>
+        <v>-0.002928062253466646</v>
       </c>
     </row>
     <row r="45">
@@ -8989,10 +8989,10 @@
         <v>45258</v>
       </c>
       <c r="B45" t="n">
-        <v>0.004410173609931567</v>
+        <v>0.004410239603548138</v>
       </c>
       <c r="C45" t="n">
-        <v>0.005873595308668156</v>
+        <v>0.005873663646019045</v>
       </c>
     </row>
     <row r="46">
@@ -9003,7 +9003,7 @@
         <v>0.006586214067427987</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.001459858378519141</v>
+        <v>-0.001459926217642904</v>
       </c>
     </row>
     <row r="47">
@@ -9033,10 +9033,10 @@
         <v>45264</v>
       </c>
       <c r="B49" t="n">
-        <v>0.01298703811493973</v>
+        <v>0.01298710260995195</v>
       </c>
       <c r="C49" t="n">
-        <v>0.005847970723133811</v>
+        <v>0.005847902685499839</v>
       </c>
     </row>
     <row r="50">
@@ -9044,10 +9044,10 @@
         <v>45265</v>
       </c>
       <c r="B50" t="n">
-        <v>0.01282053730826327</v>
+        <v>0.01282053649200354</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.01017431360214294</v>
+        <v>-0.0101742466482847</v>
       </c>
     </row>
     <row r="51">
@@ -9055,10 +9055,10 @@
         <v>45266</v>
       </c>
       <c r="B51" t="n">
-        <v>0.002109719097009188</v>
+        <v>0.002109656102167623</v>
       </c>
       <c r="C51" t="n">
-        <v>0.005873595308668156</v>
+        <v>0.005873663646019045</v>
       </c>
     </row>
     <row r="52">
@@ -9069,7 +9069,7 @@
         <v>-0.007368440069690396</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.001459858378519141</v>
+        <v>-0.001459926217642904</v>
       </c>
     </row>
     <row r="53">
@@ -9080,7 +9080,7 @@
         <v>-0.001060421060467776</v>
       </c>
       <c r="C53" t="n">
-        <v>0.00877202412233502</v>
+        <v>0.008771820009432663</v>
       </c>
     </row>
     <row r="54">
@@ -9091,7 +9091,7 @@
         <v>0.008492563763817129</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0144926607627589</v>
+        <v>0.01449286603320465</v>
       </c>
     </row>
     <row r="55">
@@ -9102,7 +9102,7 @@
         <v>0.01894737251500289</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.008571454214673979</v>
+        <v>-0.008571520697161938</v>
       </c>
     </row>
     <row r="56">
@@ -9113,7 +9113,7 @@
         <v>-0.01652897700747991</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.01729105140227805</v>
+        <v>-0.01729085138995645</v>
       </c>
     </row>
     <row r="57">
@@ -9121,10 +9121,10 @@
         <v>45275</v>
       </c>
       <c r="B57" t="n">
-        <v>0.01050421141230951</v>
+        <v>0.01050427401040865</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.001466143587904312</v>
+        <v>-0.001466279862111786</v>
       </c>
     </row>
     <row r="58">
@@ -9132,7 +9132,7 @@
         <v>45278</v>
       </c>
       <c r="B58" t="n">
-        <v>-0.02286899427791955</v>
+        <v>-0.02286899286124511</v>
       </c>
       <c r="C58" t="n">
         <v>-0.01615283129161826</v>
@@ -9143,7 +9143,7 @@
         <v>45279</v>
       </c>
       <c r="B59" t="n">
-        <v>0.006382959029799462</v>
+        <v>0.006382895227920349</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -9165,10 +9165,10 @@
         <v>45281</v>
       </c>
       <c r="B61" t="n">
-        <v>0.004223893675832757</v>
+        <v>0.004223767818627211</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.004405367324878395</v>
+        <v>-0.004405435662229285</v>
       </c>
     </row>
     <row r="62">
@@ -9176,10 +9176,10 @@
         <v>45282</v>
       </c>
       <c r="B62" t="n">
-        <v>-0.00525769063287862</v>
+        <v>-0.005257565963963873</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.002949861213889626</v>
+        <v>-0.002949861416367328</v>
       </c>
     </row>
     <row r="63">
@@ -9190,7 +9190,7 @@
         <v>0.01479912996171651</v>
       </c>
       <c r="C63" t="n">
-        <v>0.004437882959648753</v>
+        <v>0.004437952107980703</v>
       </c>
     </row>
     <row r="64">
@@ -9201,7 +9201,7 @@
         <v>0.01249996197817538</v>
       </c>
       <c r="C64" t="n">
-        <v>0.001472689851873543</v>
+        <v>0.001472758390518081</v>
       </c>
     </row>
     <row r="65">
@@ -9209,10 +9209,10 @@
         <v>45287</v>
       </c>
       <c r="B65" t="n">
-        <v>-0.003086226550659044</v>
+        <v>-0.003086410480883761</v>
       </c>
       <c r="C65" t="n">
-        <v>1.368757132080844e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -9220,10 +9220,10 @@
         <v>45288</v>
       </c>
       <c r="B66" t="n">
-        <v>-0.003096026831166498</v>
+        <v>-0.003095842902716028</v>
       </c>
       <c r="C66" t="n">
-        <v>0.01481467236270317</v>
+        <v>0.01481474181443931</v>
       </c>
     </row>
     <row r="67">
@@ -9231,10 +9231,10 @@
         <v>45289</v>
       </c>
       <c r="B67" t="n">
-        <v>-0.005176049406493743</v>
+        <v>-0.005176111097367708</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.0131386223353005</v>
+        <v>-0.01313868977406463</v>
       </c>
     </row>
     <row r="68">
@@ -9242,10 +9242,10 @@
         <v>45293</v>
       </c>
       <c r="B68" t="n">
-        <v>-0.00208124172529367</v>
+        <v>-0.002081179842501002</v>
       </c>
       <c r="C68" t="n">
-        <v>0.01035497863660795</v>
+        <v>0.01035504768085005</v>
       </c>
     </row>
     <row r="69">
@@ -9278,7 +9278,7 @@
         <v>0.002057627423947439</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.002898603314403392</v>
+        <v>-0.002898670264474212</v>
       </c>
     </row>
     <row r="72">
@@ -9286,10 +9286,10 @@
         <v>45299</v>
       </c>
       <c r="B72" t="n">
-        <v>-0.001026670551454223</v>
+        <v>-0.001026731735634945</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.008720954631067035</v>
+        <v>-0.008720820927230699</v>
       </c>
     </row>
     <row r="73">
@@ -9297,10 +9297,10 @@
         <v>45300</v>
       </c>
       <c r="B73" t="n">
-        <v>-0.00719414105712668</v>
+        <v>-0.0071940802506818</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.001466133038043105</v>
+        <v>-0.001466268409552995</v>
       </c>
     </row>
     <row r="74">
@@ -9311,7 +9311,7 @@
         <v>-0.01966877799570421</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.008810596294954398</v>
+        <v>-0.008810596892620093</v>
       </c>
     </row>
     <row r="75">
@@ -9322,7 +9322,7 @@
         <v>0.003167888792573237</v>
       </c>
       <c r="C75" t="n">
-        <v>0.005925827882372836</v>
+        <v>0.005925896725775814</v>
       </c>
     </row>
     <row r="76">
@@ -9333,7 +9333,7 @@
         <v>-0.003157884964186897</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.01030922785054278</v>
+        <v>-0.01030929588522822</v>
       </c>
     </row>
     <row r="77">
@@ -9344,7 +9344,7 @@
         <v>0.007391719539803221</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.002976244488843482</v>
+        <v>-0.002976175950059279</v>
       </c>
     </row>
     <row r="78">
@@ -9352,10 +9352,10 @@
         <v>45308</v>
       </c>
       <c r="B78" t="n">
-        <v>0.003144644462652835</v>
+        <v>0.003144706929518071</v>
       </c>
       <c r="C78" t="n">
-        <v>0.001492461058356653</v>
+        <v>0.001492598955525448</v>
       </c>
     </row>
     <row r="79">
@@ -9363,10 +9363,10 @@
         <v>45310</v>
       </c>
       <c r="B79" t="n">
-        <v>0.006269573346199264</v>
+        <v>0.006269510684745461</v>
       </c>
       <c r="C79" t="n">
-        <v>0.01341288974401533</v>
+        <v>0.01341281905134717</v>
       </c>
     </row>
     <row r="80">
@@ -9374,10 +9374,10 @@
         <v>45313</v>
       </c>
       <c r="B80" t="n">
-        <v>0.001038521588835328</v>
+        <v>0.001038459705770878</v>
       </c>
       <c r="C80" t="n">
-        <v>0.004411743126645273</v>
+        <v>0.004411674892304873</v>
       </c>
     </row>
     <row r="81">
@@ -9385,10 +9385,10 @@
         <v>45314</v>
       </c>
       <c r="B81" t="n">
-        <v>-0.008298811618880242</v>
+        <v>-0.008298750313035286</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.008784730279859154</v>
+        <v>-0.008784797916100318</v>
       </c>
     </row>
     <row r="82">
@@ -9399,7 +9399,7 @@
         <v>-0.006276131326872991</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.005908458705578878</v>
+        <v>-0.005908390873068714</v>
       </c>
     </row>
     <row r="83">
@@ -9443,7 +9443,7 @@
         <v>-0.003128187065835064</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.001492530006941051</v>
+        <v>-0.001492461058356653</v>
       </c>
     </row>
     <row r="87">
@@ -9451,10 +9451,10 @@
         <v>45322</v>
       </c>
       <c r="B87" t="n">
-        <v>0.00104600110908537</v>
+        <v>0.00104606344526581</v>
       </c>
       <c r="C87" t="n">
-        <v>0.001494760982560628</v>
+        <v>0.001494691827703676</v>
       </c>
     </row>
     <row r="88">
@@ -9462,10 +9462,10 @@
         <v>45323</v>
       </c>
       <c r="B88" t="n">
-        <v>0.04388720023653025</v>
+        <v>0.04388719750362879</v>
       </c>
       <c r="C88" t="n">
-        <v>0.007462787931874049</v>
+        <v>0.007462718983289651</v>
       </c>
     </row>
     <row r="89">
@@ -9484,10 +9484,10 @@
         <v>45327</v>
       </c>
       <c r="B90" t="n">
-        <v>0.03603586460072283</v>
+        <v>0.03603592210411044</v>
       </c>
       <c r="C90" t="n">
-        <v>0.007407301962427892</v>
+        <v>0.007407439345071598</v>
       </c>
     </row>
     <row r="91">
@@ -9495,10 +9495,10 @@
         <v>45328</v>
       </c>
       <c r="B91" t="n">
-        <v>0.005797199582489254</v>
+        <v>0.005797198914905044</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.005882324168860475</v>
+        <v>-0.005882459638507642</v>
       </c>
     </row>
     <row r="92">
@@ -9506,7 +9506,7 @@
         <v>45329</v>
       </c>
       <c r="B92" t="n">
-        <v>0.007684971359679604</v>
+        <v>0.007684741494661695</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -9517,7 +9517,7 @@
         <v>45337</v>
       </c>
       <c r="B93" t="n">
-        <v>-0.008579516326656766</v>
+        <v>-0.008579517301456563</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -9528,10 +9528,10 @@
         <v>45338</v>
       </c>
       <c r="B94" t="n">
-        <v>0.01057690864139582</v>
+        <v>0.01057690985353776</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0355029205701678</v>
+        <v>0.03550299133293522</v>
       </c>
     </row>
     <row r="95">
@@ -9539,7 +9539,7 @@
         <v>45341</v>
       </c>
       <c r="B95" t="n">
-        <v>-0.0009514528821594759</v>
+        <v>-0.0009513395868403496</v>
       </c>
       <c r="C95" t="n">
         <v>0.02714285657719739</v>
@@ -9550,7 +9550,7 @@
         <v>45342</v>
       </c>
       <c r="B96" t="n">
-        <v>-0.006666740070578991</v>
+        <v>-0.006666853581783649</v>
       </c>
       <c r="C96" t="n">
         <v>-0.005563190921462513</v>
@@ -9561,10 +9561,10 @@
         <v>45343</v>
       </c>
       <c r="B97" t="n">
-        <v>0.01534024052873684</v>
+        <v>0.01534047082780532</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.002797318099699964</v>
+        <v>-0.002797253490542051</v>
       </c>
     </row>
     <row r="98">
@@ -9572,10 +9572,10 @@
         <v>45344</v>
       </c>
       <c r="B98" t="n">
-        <v>-0.01227567645255101</v>
+        <v>-0.01227567507096616</v>
       </c>
       <c r="C98" t="n">
-        <v>0.004207682767555454</v>
+        <v>0.004207617704545141</v>
       </c>
     </row>
     <row r="99">
@@ -9583,10 +9583,10 @@
         <v>45345</v>
       </c>
       <c r="B99" t="n">
-        <v>-0.006692235231863353</v>
+        <v>-0.006692234469314662</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.008379911156153885</v>
+        <v>-0.008379975675075979</v>
       </c>
     </row>
     <row r="100">
@@ -9594,7 +9594,7 @@
         <v>45348</v>
       </c>
       <c r="B100" t="n">
-        <v>0.0394611518170136</v>
+        <v>0.03946091786436567</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -9605,10 +9605,10 @@
         <v>45349</v>
       </c>
       <c r="B101" t="n">
-        <v>-0.0009259046717684516</v>
+        <v>-0.000925904773949604</v>
       </c>
       <c r="C101" t="n">
-        <v>0.01408450246027093</v>
+        <v>0.01408450337666722</v>
       </c>
     </row>
     <row r="102">
@@ -9616,10 +9616,10 @@
         <v>45350</v>
       </c>
       <c r="B102" t="n">
-        <v>0.005560687054858349</v>
+        <v>0.005560908589920865</v>
       </c>
       <c r="C102" t="n">
-        <v>0.002777571573106652</v>
+        <v>0.002777828393275117</v>
       </c>
     </row>
     <row r="103">
@@ -9627,10 +9627,10 @@
         <v>45351</v>
       </c>
       <c r="B103" t="n">
-        <v>0.004608189131066975</v>
+        <v>0.004608078775309332</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.002769878038605622</v>
+        <v>-0.002770133437957956</v>
       </c>
     </row>
     <row r="104">
@@ -9641,7 +9641,7 @@
         <v>0.01651382145753622</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.00694441013640712</v>
+        <v>-0.006944346421474346</v>
       </c>
     </row>
     <row r="105">
@@ -9649,10 +9649,10 @@
         <v>45355</v>
       </c>
       <c r="B105" t="n">
-        <v>0.005415253519855723</v>
+        <v>0.005415361089152082</v>
       </c>
       <c r="C105" t="n">
-        <v>0.006992972203460512</v>
+        <v>0.006992907594302489</v>
       </c>
     </row>
     <row r="106">
@@ -9660,10 +9660,10 @@
         <v>45356</v>
       </c>
       <c r="B106" t="n">
-        <v>-0.006283731915360247</v>
+        <v>-0.00628383823297185</v>
       </c>
       <c r="C106" t="n">
-        <v>0.01388888443329961</v>
+        <v>0.01388888532441723</v>
       </c>
     </row>
     <row r="107">
@@ -9671,10 +9671,10 @@
         <v>45357</v>
       </c>
       <c r="B107" t="n">
-        <v>-0.01445346940651981</v>
+        <v>-0.01445357707298589</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.01643840158841814</v>
+        <v>-0.01643840262866614</v>
       </c>
     </row>
     <row r="108">
@@ -9682,10 +9682,10 @@
         <v>45358</v>
       </c>
       <c r="B108" t="n">
-        <v>0.02016496061701822</v>
+        <v>0.0201650720654023</v>
       </c>
       <c r="C108" t="n">
-        <v>0.002785566038986165</v>
+        <v>0.002785566218207247</v>
       </c>
     </row>
     <row r="109">
@@ -9696,7 +9696,7 @@
         <v>-0.01168019734675019</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.0277778330270847</v>
+        <v>-0.02777777064883447</v>
       </c>
     </row>
     <row r="110">
@@ -9726,10 +9726,10 @@
         <v>45364</v>
       </c>
       <c r="B112" t="n">
-        <v>0.04557632241142873</v>
+        <v>0.0455765354351676</v>
       </c>
       <c r="C112" t="n">
-        <v>0.01142858161044824</v>
+        <v>0.01142851561680236</v>
       </c>
     </row>
     <row r="113">
@@ -9740,7 +9740,7 @@
         <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.004237332647968772</v>
+        <v>-0.004237332924446169</v>
       </c>
     </row>
     <row r="114">
@@ -9748,10 +9748,10 @@
         <v>45366</v>
       </c>
       <c r="B114" t="n">
-        <v>-0.008546915384712528</v>
+        <v>-0.008547117381444314</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.01149424006970878</v>
+        <v>-0.01149424082287587</v>
       </c>
     </row>
     <row r="115">
@@ -9759,10 +9759,10 @@
         <v>45369</v>
       </c>
       <c r="B115" t="n">
-        <v>-0.02586209288081953</v>
+        <v>-0.02586199013359503</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.01308138060756903</v>
+        <v>-0.01308131518716416</v>
       </c>
     </row>
     <row r="116">
@@ -9770,7 +9770,7 @@
         <v>45370</v>
       </c>
       <c r="B116" t="n">
-        <v>-0.008849565922789959</v>
+        <v>-0.008849670464400217</v>
       </c>
       <c r="C116" t="n">
         <v>-0.001472752368446684</v>
@@ -9781,10 +9781,10 @@
         <v>45371</v>
       </c>
       <c r="B117" t="n">
-        <v>0.02232155636656952</v>
+        <v>0.0223214499497979</v>
       </c>
       <c r="C117" t="n">
-        <v>0.002949849134192384</v>
+        <v>0.002949916399416219</v>
       </c>
     </row>
     <row r="118">
@@ -9792,10 +9792,10 @@
         <v>45372</v>
       </c>
       <c r="B118" t="n">
-        <v>0.01484702820541894</v>
+        <v>0.01484702975089447</v>
       </c>
       <c r="C118" t="n">
-        <v>0.005882346234437952</v>
+        <v>0.005882278772543437</v>
       </c>
     </row>
     <row r="119">
@@ -9803,7 +9803,7 @@
         <v>45373</v>
       </c>
       <c r="B119" t="n">
-        <v>-0.01118755681758155</v>
+        <v>-0.01118755796509363</v>
       </c>
       <c r="C119" t="n">
         <v>-0.008771919881771617</v>
@@ -9814,10 +9814,10 @@
         <v>45376</v>
       </c>
       <c r="B120" t="n">
-        <v>-0.007833029799495517</v>
+        <v>-0.007832719419355927</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.007374622835480737</v>
+        <v>-0.007374690100704795</v>
       </c>
     </row>
     <row r="121">
@@ -9825,10 +9825,10 @@
         <v>45377</v>
       </c>
       <c r="B121" t="n">
-        <v>0.008772043545418162</v>
+        <v>0.008771832611591313</v>
       </c>
       <c r="C121" t="n">
-        <v>0.00594352955718036</v>
+        <v>0.005943597724913152</v>
       </c>
     </row>
     <row r="122">
@@ -9847,7 +9847,7 @@
         <v>45379</v>
       </c>
       <c r="B123" t="n">
-        <v>0.0164930905813272</v>
+        <v>0.01649298712058611</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -9858,7 +9858,7 @@
         <v>45380</v>
       </c>
       <c r="B124" t="n">
-        <v>-0.005123809709925209</v>
+        <v>-0.005123606667335023</v>
       </c>
       <c r="C124" t="n">
         <v>-0.001477103182868755</v>
@@ -9869,7 +9869,7 @@
         <v>45383</v>
       </c>
       <c r="B125" t="n">
-        <v>0.002574945713752275</v>
+        <v>0.002575047756547155</v>
       </c>
       <c r="C125" t="n">
         <v>-0.008875729465455895</v>
@@ -9880,10 +9880,10 @@
         <v>45384</v>
       </c>
       <c r="B126" t="n">
-        <v>0.001712289627157526</v>
+        <v>0.001712289277701728</v>
       </c>
       <c r="C126" t="n">
-        <v>0.004477606758973351</v>
+        <v>0.004477538690583316</v>
       </c>
     </row>
     <row r="127">
@@ -9891,10 +9891,10 @@
         <v>45385</v>
       </c>
       <c r="B127" t="n">
-        <v>-0.01623904754880645</v>
+        <v>-0.01623945171642183</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.008915294335770541</v>
+        <v>-0.008915227174945528</v>
       </c>
     </row>
     <row r="128">
@@ -9902,10 +9902,10 @@
         <v>45386</v>
       </c>
       <c r="B128" t="n">
-        <v>-0.009557204104373662</v>
+        <v>-0.009556791881133009</v>
       </c>
       <c r="C128" t="n">
-        <v>0.02248872948199576</v>
+        <v>0.02248879785654001</v>
       </c>
     </row>
     <row r="129">
@@ -9913,10 +9913,10 @@
         <v>45387</v>
       </c>
       <c r="B129" t="n">
-        <v>-0.002631518968787439</v>
+        <v>-0.002631622968336078</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.004398821978876755</v>
+        <v>-0.004398888555427027</v>
       </c>
     </row>
     <row r="130">
@@ -9924,7 +9924,7 @@
         <v>45390</v>
       </c>
       <c r="B130" t="n">
-        <v>-0.009674570801773807</v>
+        <v>-0.009674674613290302</v>
       </c>
       <c r="C130" t="n">
         <v>-0.01325477131602015</v>
@@ -9935,7 +9935,7 @@
         <v>45391</v>
       </c>
       <c r="B131" t="n">
-        <v>0.003552422497892449</v>
+        <v>0.003552528347613881</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -9946,10 +9946,10 @@
         <v>45392</v>
       </c>
       <c r="B132" t="n">
-        <v>0.007079800403273273</v>
+        <v>0.007079483231476003</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.002985139241038826</v>
+        <v>-0.002985071172648901</v>
       </c>
     </row>
     <row r="133">
@@ -9957,10 +9957,10 @@
         <v>45393</v>
       </c>
       <c r="B133" t="n">
-        <v>0.009665962857298371</v>
+        <v>0.009666069615558825</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.002993940433331788</v>
+        <v>-0.00299394022892896</v>
       </c>
     </row>
     <row r="134">
@@ -9968,10 +9968,10 @@
         <v>45394</v>
       </c>
       <c r="B134" t="n">
-        <v>0.005221916135452087</v>
+        <v>0.005222124138903883</v>
       </c>
       <c r="C134" t="n">
-        <v>0.001501499753584712</v>
+        <v>0.001501431173562384</v>
       </c>
     </row>
     <row r="135">
@@ -9979,7 +9979,7 @@
         <v>45397</v>
       </c>
       <c r="B135" t="n">
-        <v>-0.03376628576428964</v>
+        <v>-0.03376628227987877</v>
       </c>
       <c r="C135" t="n">
         <v>-0.02698647537839494</v>
@@ -9990,7 +9990,7 @@
         <v>45398</v>
       </c>
       <c r="B136" t="n">
-        <v>0.01254483655283622</v>
+        <v>0.01254483521307037</v>
       </c>
       <c r="C136" t="n">
         <v>-0.01386754214849084</v>
@@ -10001,10 +10001,10 @@
         <v>45399</v>
       </c>
       <c r="B137" t="n">
-        <v>-0.01061943691733613</v>
+        <v>-0.01061954127226916</v>
       </c>
       <c r="C137" t="n">
-        <v>0.003124996437045224</v>
+        <v>0.003124925177948157</v>
       </c>
     </row>
     <row r="138">
@@ -10026,7 +10026,7 @@
         <v>0.01192655163428591</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.003115261256717461</v>
+        <v>-0.003115190440905358</v>
       </c>
     </row>
     <row r="140">
@@ -10034,7 +10034,7 @@
         <v>45405</v>
       </c>
       <c r="B140" t="n">
-        <v>0.01813238508334591</v>
+        <v>0.01813249314027598</v>
       </c>
       <c r="C140" t="n">
         <v>-0.007812491092612839</v>
@@ -10045,7 +10045,7 @@
         <v>45406</v>
       </c>
       <c r="B141" t="n">
-        <v>0.069456925331014</v>
+        <v>0.0694570240918615</v>
       </c>
       <c r="C141" t="n">
         <v>0.007874006699818414</v>
@@ -10056,7 +10056,7 @@
         <v>45407</v>
       </c>
       <c r="B142" t="n">
-        <v>0.02581192643843599</v>
+        <v>0.02581162359651645</v>
       </c>
       <c r="C142" t="n">
         <v>0.01093748752965795</v>
@@ -10070,7 +10070,7 @@
         <v>0</v>
       </c>
       <c r="C143" t="n">
-        <v>0.004636779932874147</v>
+        <v>0.004636850421007921</v>
       </c>
     </row>
     <row r="144">
@@ -10078,10 +10078,10 @@
         <v>45414</v>
       </c>
       <c r="B144" t="n">
-        <v>0.0332791317321417</v>
+        <v>0.03327932843667858</v>
       </c>
       <c r="C144" t="n">
-        <v>0.006153839245508497</v>
+        <v>0.006153838813737877</v>
       </c>
     </row>
     <row r="145">
@@ -10089,10 +10089,10 @@
         <v>45415</v>
       </c>
       <c r="B145" t="n">
-        <v>-0.01099748471895379</v>
+        <v>-0.01099776456934165</v>
       </c>
       <c r="C145" t="n">
-        <v>0.003058100563489985</v>
+        <v>0.003058030616567731</v>
       </c>
     </row>
     <row r="146">
@@ -10100,7 +10100,7 @@
         <v>45418</v>
       </c>
       <c r="B146" t="n">
-        <v>0.01350256275197026</v>
+        <v>0.01350284931193535</v>
       </c>
       <c r="C146" t="n">
         <v>0.003048846617605072</v>
@@ -10111,10 +10111,10 @@
         <v>45419</v>
       </c>
       <c r="B147" t="n">
-        <v>0.02899685546781039</v>
+        <v>0.02899675935275225</v>
       </c>
       <c r="C147" t="n">
-        <v>0.0334346110610193</v>
+        <v>0.03343468037077679</v>
       </c>
     </row>
     <row r="148">
@@ -10125,7 +10125,7 @@
         <v>-0.002284791602859881</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.001470586558609432</v>
+        <v>-0.001470653527361976</v>
       </c>
     </row>
     <row r="149">
@@ -10136,7 +10136,7 @@
         <v>-0.005343479919120431</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.01914578078980689</v>
+        <v>-0.01914571362364781</v>
       </c>
     </row>
     <row r="150">
@@ -10147,7 +10147,7 @@
         <v>0.005372186087601261</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.001501568230793393</v>
+        <v>-0.001501636605174106</v>
       </c>
     </row>
     <row r="151">
@@ -10155,7 +10155,7 @@
         <v>45425</v>
       </c>
       <c r="B151" t="n">
-        <v>-0.009923709543822157</v>
+        <v>-0.009923618561548442</v>
       </c>
       <c r="C151" t="n">
         <v>-0.01052623565894006</v>
@@ -10166,7 +10166,7 @@
         <v>45426</v>
       </c>
       <c r="B152" t="n">
-        <v>0.006168030943351832</v>
+        <v>0.006167938482348978</v>
       </c>
       <c r="C152" t="n">
         <v>0.01063821602783976</v>
@@ -10177,7 +10177,7 @@
         <v>45427</v>
       </c>
       <c r="B153" t="n">
-        <v>0.02758639900632009</v>
+        <v>0.02758630767544656</v>
       </c>
       <c r="C153" t="n">
         <v>0.007518857322419636</v>
@@ -10188,10 +10188,10 @@
         <v>45428</v>
       </c>
       <c r="B154" t="n">
-        <v>0.009694212615861675</v>
+        <v>0.00969421347747379</v>
       </c>
       <c r="C154" t="n">
-        <v>0.002985139241038715</v>
+        <v>0.002985071172648901</v>
       </c>
     </row>
     <row r="155">
@@ -10199,10 +10199,10 @@
         <v>45429</v>
       </c>
       <c r="B155" t="n">
-        <v>-0.006647083299846868</v>
+        <v>-0.006646819807892723</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.002976254706323678</v>
+        <v>-0.002976187042503908</v>
       </c>
     </row>
     <row r="156">
@@ -10210,7 +10210,7 @@
         <v>45432</v>
       </c>
       <c r="B156" t="n">
-        <v>-0.01115233861311593</v>
+        <v>-0.01115251386598448</v>
       </c>
       <c r="C156" t="n">
         <v>-0.008955213517946592</v>
@@ -10224,7 +10224,7 @@
         <v>0.02255641119115448</v>
       </c>
       <c r="C157" t="n">
-        <v>-0.003011975992381677</v>
+        <v>-0.00301211335931173</v>
       </c>
     </row>
     <row r="158">
@@ -10232,10 +10232,10 @@
         <v>45434</v>
       </c>
       <c r="B158" t="n">
-        <v>0.01470580760345008</v>
+        <v>0.0147057199661158</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.006042357470797843</v>
+        <v>-0.006042220521380703</v>
       </c>
     </row>
     <row r="159">
@@ -10243,7 +10243,7 @@
         <v>45435</v>
       </c>
       <c r="B159" t="n">
-        <v>-0.003623105480735189</v>
+        <v>-0.00362310579365277</v>
       </c>
       <c r="C159" t="n">
         <v>0.01823706057873786</v>
@@ -10254,10 +10254,10 @@
         <v>45436</v>
       </c>
       <c r="B160" t="n">
-        <v>-0.0407272906939401</v>
+        <v>-0.04072720754293713</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.01492535586324439</v>
+        <v>-0.01492542393163432</v>
       </c>
     </row>
     <row r="161">
@@ -10265,10 +10265,10 @@
         <v>45439</v>
       </c>
       <c r="B161" t="n">
-        <v>0.006823375138162779</v>
+        <v>0.006823284776695138</v>
       </c>
       <c r="C161" t="n">
-        <v>0.001515149735310084</v>
+        <v>0.001515149840006558</v>
       </c>
     </row>
     <row r="162">
@@ -10276,10 +10276,10 @@
         <v>45440</v>
       </c>
       <c r="B162" t="n">
-        <v>0.03162649737358314</v>
+        <v>0.03162667971020028</v>
       </c>
       <c r="C162" t="n">
-        <v>0.01058993371218131</v>
+        <v>0.01059007243322529</v>
       </c>
     </row>
     <row r="163">
@@ -10287,10 +10287,10 @@
         <v>45441</v>
       </c>
       <c r="B163" t="n">
-        <v>-0.009489007151554429</v>
+        <v>-0.00948918032130841</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.007484953491617374</v>
+        <v>-0.007485089524977839</v>
       </c>
     </row>
     <row r="164">
@@ -10298,10 +10298,10 @@
         <v>45442</v>
       </c>
       <c r="B164" t="n">
-        <v>-0.005158406856726083</v>
+        <v>-0.005158407309794555</v>
       </c>
       <c r="C164" t="n">
-        <v>-0.009049831960091348</v>
+        <v>-0.009049695008473524</v>
       </c>
     </row>
     <row r="165">
@@ -10309,10 +10309,10 @@
         <v>45443</v>
       </c>
       <c r="B165" t="n">
-        <v>-0.002963071261060435</v>
+        <v>-0.002962894949659067</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.004566204974227883</v>
+        <v>-0.00456620465726354</v>
       </c>
     </row>
     <row r="166">
@@ -10331,10 +10331,10 @@
         <v>45447</v>
       </c>
       <c r="B167" t="n">
-        <v>0.03343233392061884</v>
+        <v>0.03343241950908515</v>
       </c>
       <c r="C167" t="n">
-        <v>0.009174371424144345</v>
+        <v>0.009174231317042425</v>
       </c>
     </row>
     <row r="168">
@@ -10342,10 +10342,10 @@
         <v>45448</v>
       </c>
       <c r="B168" t="n">
-        <v>0.007189165192968971</v>
+        <v>0.0071889925925126</v>
       </c>
       <c r="C168" t="n">
-        <v>0.03787874338275099</v>
+        <v>0.03787881509989477</v>
       </c>
     </row>
     <row r="169">
@@ -10356,7 +10356,7 @@
         <v>-0.003568882468740098</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.01897801413207922</v>
+        <v>-0.01897808070992224</v>
       </c>
     </row>
     <row r="170">
@@ -10367,7 +10367,7 @@
         <v>0.01719192374710232</v>
       </c>
       <c r="C170" t="n">
-        <v>0.008928492655766673</v>
+        <v>0.008928561127511614</v>
       </c>
     </row>
     <row r="171">
@@ -10375,10 +10375,10 @@
         <v>45453</v>
       </c>
       <c r="B171" t="n">
-        <v>0.01408443611181509</v>
+        <v>0.01408452004616723</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.008849480137352872</v>
+        <v>-0.008849547402576929</v>
       </c>
     </row>
     <row r="172">
@@ -10386,10 +10386,10 @@
         <v>45454</v>
       </c>
       <c r="B172" t="n">
-        <v>0.01736121112317335</v>
+        <v>0.01736112691761393</v>
       </c>
       <c r="C172" t="n">
-        <v>-0.01041678967343107</v>
+        <v>-0.01041672251456927</v>
       </c>
     </row>
     <row r="173">
@@ -10397,7 +10397,7 @@
         <v>45455</v>
       </c>
       <c r="B173" t="n">
-        <v>0.044375555662584</v>
+        <v>0.04437563701874581</v>
       </c>
       <c r="C173" t="n">
         <v>0.007518857322419636</v>
@@ -10408,10 +10408,10 @@
         <v>45456</v>
       </c>
       <c r="B174" t="n">
-        <v>-0.01515149862741372</v>
+        <v>-0.0151515753464514</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.00149253558632445</v>
+        <v>-0.001492467517934526</v>
       </c>
     </row>
     <row r="175">
@@ -10422,7 +10422,7 @@
         <v>0.007692338722977254</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.01046329788031775</v>
+        <v>-0.01046350167742838</v>
       </c>
     </row>
     <row r="176">
@@ -10430,10 +10430,10 @@
         <v>45460</v>
       </c>
       <c r="B176" t="n">
-        <v>-0.01679386616618905</v>
+        <v>-0.01679394466017203</v>
       </c>
       <c r="C176" t="n">
-        <v>-0.003021213180880333</v>
+        <v>-0.003021144706176537</v>
       </c>
     </row>
     <row r="177">
@@ -10441,10 +10441,10 @@
         <v>45461</v>
       </c>
       <c r="B177" t="n">
-        <v>-0.006211220785383609</v>
+        <v>-0.006211141446531787</v>
       </c>
       <c r="C177" t="n">
-        <v>-0.001515218835038024</v>
+        <v>-0.001515080740273733</v>
       </c>
     </row>
     <row r="178">
@@ -10452,10 +10452,10 @@
         <v>45462</v>
       </c>
       <c r="B178" t="n">
-        <v>0.02734373933068213</v>
+        <v>0.02734381966436916</v>
       </c>
       <c r="C178" t="n">
-        <v>-0.009104624811132056</v>
+        <v>-0.009104693385633578</v>
       </c>
     </row>
     <row r="179">
@@ -10463,10 +10463,10 @@
         <v>45463</v>
       </c>
       <c r="B179" t="n">
-        <v>0.01368820549472161</v>
+        <v>0.01368820442436514</v>
       </c>
       <c r="C179" t="n">
-        <v>0.01071974224959482</v>
+        <v>0.01071967240913541</v>
       </c>
     </row>
     <row r="180">
@@ -10474,7 +10474,7 @@
         <v>45464</v>
       </c>
       <c r="B180" t="n">
-        <v>0.0210052743447644</v>
+        <v>0.02100519558480585</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -10485,10 +10485,10 @@
         <v>45467</v>
       </c>
       <c r="B181" t="n">
-        <v>-0.02939012110178696</v>
+        <v>-0.02939027220703105</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.007575748676550198</v>
+        <v>-0.007575680100299631</v>
       </c>
     </row>
     <row r="182">
@@ -10496,7 +10496,7 @@
         <v>45468</v>
       </c>
       <c r="B182" t="n">
-        <v>-0.01589710313987769</v>
+        <v>-0.01589694993400692</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
@@ -10529,7 +10529,7 @@
         <v>45471</v>
       </c>
       <c r="B185" t="n">
-        <v>-0.01731932334490727</v>
+        <v>-0.01731924591484812</v>
       </c>
       <c r="C185" t="n">
         <v>0.003062783499884203</v>
@@ -10540,10 +10540,10 @@
         <v>45474</v>
       </c>
       <c r="B186" t="n">
-        <v>-0.0145592963441451</v>
+        <v>-0.01455937399167373</v>
       </c>
       <c r="C186" t="n">
-        <v>0.007633578750667835</v>
+        <v>0.007633509123461613</v>
       </c>
     </row>
     <row r="187">
@@ -10554,7 +10554,7 @@
         <v>-0.004665680347283763</v>
       </c>
       <c r="C187" t="n">
-        <v>0.003030368570348108</v>
+        <v>0.003030299680012893</v>
       </c>
     </row>
     <row r="188">
@@ -10573,10 +10573,10 @@
         <v>45477</v>
       </c>
       <c r="B189" t="n">
-        <v>0.03664130526074527</v>
+        <v>0.03664122676676218</v>
       </c>
       <c r="C189" t="n">
-        <v>0.003021075398954354</v>
+        <v>0.003021213597149019</v>
       </c>
     </row>
     <row r="190">
@@ -10584,10 +10584,10 @@
         <v>45478</v>
       </c>
       <c r="B190" t="n">
-        <v>0.02135487361881916</v>
+        <v>0.0213549509553268</v>
       </c>
       <c r="C190" t="n">
-        <v>0.01204824738685173</v>
+        <v>0.01204817870338659</v>
       </c>
     </row>
     <row r="191">
@@ -10598,7 +10598,7 @@
         <v>0.0064888580481679</v>
       </c>
       <c r="C191" t="n">
-        <v>0.005952305815243975</v>
+        <v>0.005952374085007817</v>
       </c>
     </row>
     <row r="192">
@@ -10617,10 +10617,10 @@
         <v>45483</v>
       </c>
       <c r="B193" t="n">
-        <v>-0.02545453512084506</v>
+        <v>-0.02545460990420323</v>
       </c>
       <c r="C193" t="n">
-        <v>-0.01037049288674219</v>
+        <v>-0.0103704253225666</v>
       </c>
     </row>
     <row r="194">
@@ -10628,10 +10628,10 @@
         <v>45484</v>
       </c>
       <c r="B194" t="n">
-        <v>-0.007462639608913135</v>
+        <v>-0.007462563444911252</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.007484953491617374</v>
+        <v>-0.007485089524977839</v>
       </c>
     </row>
     <row r="195">
@@ -10650,10 +10650,10 @@
         <v>45488</v>
       </c>
       <c r="B196" t="n">
-        <v>-0.008221173901402201</v>
+        <v>-0.008221250752759035</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.001508225075112057</v>
+        <v>-0.001508293965923002</v>
       </c>
     </row>
     <row r="197">
@@ -10661,10 +10661,10 @@
         <v>45489</v>
       </c>
       <c r="B197" t="n">
-        <v>0.009796471286633635</v>
+        <v>0.009796472045746629</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.001510641035921689</v>
+        <v>-0.001510572353088269</v>
       </c>
     </row>
     <row r="198">
@@ -10672,10 +10672,10 @@
         <v>45490</v>
       </c>
       <c r="B198" t="n">
-        <v>-0.0156716199153718</v>
+        <v>-0.0156716211179595</v>
       </c>
       <c r="C198" t="n">
-        <v>-0.006051499113687742</v>
+        <v>-0.006051361540822753</v>
       </c>
     </row>
     <row r="199">
@@ -10683,10 +10683,10 @@
         <v>45491</v>
       </c>
       <c r="B199" t="n">
-        <v>-0.03032596896819584</v>
+        <v>-0.03032597133235959</v>
       </c>
       <c r="C199" t="n">
-        <v>0.003044136649485329</v>
+        <v>0.003044136438175693</v>
       </c>
     </row>
     <row r="200">
@@ -10694,10 +10694,10 @@
         <v>45492</v>
       </c>
       <c r="B200" t="n">
-        <v>-0.01485550258498836</v>
+        <v>-0.01485534298632629</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.009104624811132056</v>
+        <v>-0.009104693385633578</v>
       </c>
     </row>
     <row r="201">
@@ -10705,10 +10705,10 @@
         <v>45495</v>
       </c>
       <c r="B201" t="n">
-        <v>-0.01507935316188513</v>
+        <v>-0.0150792703224536</v>
       </c>
       <c r="C201" t="n">
-        <v>0.001531321909482797</v>
+        <v>0.001531391749942212</v>
       </c>
     </row>
     <row r="202">
@@ -10716,10 +10716,10 @@
         <v>45496</v>
       </c>
       <c r="B202" t="n">
-        <v>0.01128132042953722</v>
+        <v>0.01128115284350506</v>
       </c>
       <c r="C202" t="n">
-        <v>0.007645251408724851</v>
+        <v>0.007645250875593312</v>
       </c>
     </row>
     <row r="203">
@@ -10727,10 +10727,10 @@
         <v>45497</v>
       </c>
       <c r="B203" t="n">
-        <v>0.003983956675945866</v>
+        <v>0.00398403860990193</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.004552347007860003</v>
+        <v>-0.004552415897400075</v>
       </c>
     </row>
     <row r="204">
@@ -10738,7 +10738,7 @@
         <v>45498</v>
       </c>
       <c r="B204" t="n">
-        <v>-0.007936540320964247</v>
+        <v>-0.007936539673272569</v>
       </c>
       <c r="C204" t="n">
         <v>0</v>
@@ -10749,10 +10749,10 @@
         <v>45502</v>
       </c>
       <c r="B205" t="n">
-        <v>0.03200004935702205</v>
+        <v>0.03199996446294717</v>
       </c>
       <c r="C205" t="n">
-        <v>0.02439035581440874</v>
+        <v>0.02439028629333673</v>
       </c>
     </row>
     <row r="206">
@@ -10763,7 +10763,7 @@
         <v>-0.007751889787178112</v>
       </c>
       <c r="C206" t="n">
-        <v>0.007440399235505435</v>
+        <v>0.007440467606259604</v>
       </c>
     </row>
     <row r="207">
@@ -10782,7 +10782,7 @@
         <v>45505</v>
       </c>
       <c r="B208" t="n">
-        <v>-0.02954896237766991</v>
+        <v>-0.02954904233654543</v>
       </c>
       <c r="C208" t="n">
         <v>-0.01815640260791396</v>
@@ -10793,7 +10793,7 @@
         <v>45506</v>
       </c>
       <c r="B209" t="n">
-        <v>-0.01282051387684002</v>
+        <v>-0.01282051493316727</v>
       </c>
       <c r="C209" t="n">
         <v>0.0170696802402901</v>
@@ -10804,7 +10804,7 @@
         <v>45509</v>
       </c>
       <c r="B210" t="n">
-        <v>-0.03733775935050654</v>
+        <v>-0.03733776246684928</v>
       </c>
       <c r="C210" t="n">
         <v>-0.02937072134500296</v>
@@ -10815,10 +10815,10 @@
         <v>45510</v>
       </c>
       <c r="B211" t="n">
-        <v>0.0185498046544792</v>
+        <v>0.01854989296354637</v>
       </c>
       <c r="C211" t="n">
-        <v>0.04755044487034699</v>
+        <v>0.04755057629923209</v>
       </c>
     </row>
     <row r="212">
@@ -10829,7 +10829,7 @@
         <v>0.009933797383254284</v>
       </c>
       <c r="C212" t="n">
-        <v>0.01513078238074561</v>
+        <v>0.01513059228782421</v>
       </c>
     </row>
     <row r="213">
@@ -10837,10 +10837,10 @@
         <v>45512</v>
       </c>
       <c r="B213" t="n">
-        <v>-0.004918085982852261</v>
+        <v>-0.004918001698333008</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.01490525422277122</v>
+        <v>-0.01490506975434958</v>
       </c>
     </row>
     <row r="214">
@@ -10848,10 +10848,10 @@
         <v>45513</v>
       </c>
       <c r="B214" t="n">
-        <v>0.04530483243414651</v>
+        <v>0.04530457449354053</v>
       </c>
       <c r="C214" t="n">
-        <v>0.008253022859934234</v>
+        <v>0.008252833629917466</v>
       </c>
     </row>
     <row r="215">
@@ -10859,10 +10859,10 @@
         <v>45516</v>
       </c>
       <c r="B215" t="n">
-        <v>0.02442861063553226</v>
+        <v>0.02442877665453036</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.00409264067561832</v>
+        <v>-0.00409264093025441</v>
       </c>
     </row>
     <row r="216">
@@ -10873,7 +10873,7 @@
         <v>-0.002307677887557591</v>
       </c>
       <c r="C216" t="n">
-        <v>0.01095895357508714</v>
+        <v>0.0109589542597337</v>
       </c>
     </row>
     <row r="217">
@@ -10884,7 +10884,7 @@
         <v>-0.001542010388313919</v>
       </c>
       <c r="C217" t="n">
-        <v>0.00270990015786543</v>
+        <v>0.002709900325327697</v>
       </c>
     </row>
     <row r="218">
@@ -10892,10 +10892,10 @@
         <v>45519</v>
       </c>
       <c r="B218" t="n">
-        <v>-0.006177646829581884</v>
+        <v>-0.006177567426401631</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.002702576445528959</v>
+        <v>-0.002702576612087393</v>
       </c>
     </row>
     <row r="219">
@@ -10903,7 +10903,7 @@
         <v>45520</v>
       </c>
       <c r="B219" t="n">
-        <v>0.01476316245095433</v>
+        <v>0.0147629215811822</v>
       </c>
       <c r="C219" t="n">
         <v>0</v>
@@ -10914,10 +10914,10 @@
         <v>45523</v>
       </c>
       <c r="B220" t="n">
-        <v>-0.0007658493696249824</v>
+        <v>-0.0007656132870280663</v>
       </c>
       <c r="C220" t="n">
-        <v>0.02981026125953878</v>
+        <v>0.02981026310170876</v>
       </c>
     </row>
     <row r="221">
@@ -10925,10 +10925,10 @@
         <v>45524</v>
       </c>
       <c r="B221" t="n">
-        <v>0.007662866344280594</v>
+        <v>0.007662865740487135</v>
       </c>
       <c r="C221" t="n">
-        <v>-0.005263271593455299</v>
+        <v>-0.005263271909291989</v>
       </c>
     </row>
     <row r="222">
@@ -10936,10 +10936,10 @@
         <v>45525</v>
       </c>
       <c r="B222" t="n">
-        <v>0.01520910852796531</v>
+        <v>0.01520910733868108</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.003968189334148886</v>
+        <v>-0.003968068923193901</v>
       </c>
     </row>
     <row r="223">
@@ -10947,10 +10947,10 @@
         <v>45526</v>
       </c>
       <c r="B223" t="n">
-        <v>0.002247254015187217</v>
+        <v>0.002247176818039209</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.01460821692139502</v>
+        <v>-0.0146082160366412</v>
       </c>
     </row>
     <row r="224">
@@ -10961,7 +10961,7 @@
         <v>-0.005231732970431002</v>
       </c>
       <c r="C224" t="n">
-        <v>0.00943407417387232</v>
+        <v>0.009434012130655978</v>
       </c>
     </row>
     <row r="225">
@@ -10969,7 +10969,7 @@
         <v>45530</v>
       </c>
       <c r="B225" t="n">
-        <v>-0.01202103884593819</v>
+        <v>-0.012020961590401</v>
       </c>
       <c r="C225" t="n">
         <v>-0.0200268593290136</v>
@@ -10980,7 +10980,7 @@
         <v>45532</v>
       </c>
       <c r="B226" t="n">
-        <v>0.01368820549472161</v>
+        <v>0.01368820442436514</v>
       </c>
       <c r="C226" t="n">
         <v>0.006811919349022144</v>
@@ -10991,10 +10991,10 @@
         <v>45533</v>
       </c>
       <c r="B227" t="n">
-        <v>0.003000808577556136</v>
+        <v>0.003000808346074857</v>
       </c>
       <c r="C227" t="n">
-        <v>-0.005412652500266901</v>
+        <v>-0.005412714213157588</v>
       </c>
     </row>
     <row r="228">
@@ -11002,10 +11002,10 @@
         <v>45534</v>
       </c>
       <c r="B228" t="n">
-        <v>0.008227322833380013</v>
+        <v>0.008227245291795082</v>
       </c>
       <c r="C228" t="n">
-        <v>0.005442108743765495</v>
+        <v>0.005442171130184414</v>
       </c>
     </row>
     <row r="229">
@@ -11024,10 +11024,10 @@
         <v>45540</v>
       </c>
       <c r="B230" t="n">
-        <v>-0.01804507569467062</v>
+        <v>-0.01804523032190608</v>
       </c>
       <c r="C230" t="n">
-        <v>0.00538351209115806</v>
+        <v>0.005383634852444974</v>
       </c>
     </row>
     <row r="231">
@@ -11035,10 +11035,10 @@
         <v>45541</v>
       </c>
       <c r="B231" t="n">
-        <v>0.01148537851280351</v>
+        <v>0.01148538032139235</v>
       </c>
       <c r="C231" t="n">
-        <v>0.009370927833641796</v>
+        <v>0.009370743533528847</v>
       </c>
     </row>
     <row r="232">
@@ -11046,10 +11046,10 @@
         <v>45544</v>
       </c>
       <c r="B232" t="n">
-        <v>-0.006056057824801009</v>
+        <v>-0.00605582524649706</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.007957610059263986</v>
+        <v>-0.007957610540581417</v>
       </c>
     </row>
     <row r="233">
@@ -11057,10 +11057,10 @@
         <v>45545</v>
       </c>
       <c r="B233" t="n">
-        <v>-0.009901006382251443</v>
+        <v>-0.009901083921489251</v>
       </c>
       <c r="C233" t="n">
-        <v>0.001336957735844191</v>
+        <v>0.0013370187877082</v>
       </c>
     </row>
     <row r="234">
@@ -11068,10 +11068,10 @@
         <v>45546</v>
       </c>
       <c r="B234" t="n">
-        <v>0.004615513970685825</v>
+        <v>0.004615355775115182</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.004005578888197192</v>
+        <v>-0.004005457110318078</v>
       </c>
     </row>
     <row r="235">
@@ -11079,10 +11079,10 @@
         <v>45547</v>
       </c>
       <c r="B235" t="n">
-        <v>0.01301676231451054</v>
+        <v>0.01301692183304071</v>
       </c>
       <c r="C235" t="n">
-        <v>0.001340603448228395</v>
+        <v>0.001340603284315955</v>
       </c>
     </row>
     <row r="236">
@@ -11093,7 +11093,7 @@
         <v>0.005291049703969763</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.02409641864263401</v>
+        <v>-0.02409653780429066</v>
       </c>
     </row>
     <row r="237">
@@ -11112,7 +11112,7 @@
         <v>45552</v>
       </c>
       <c r="B238" t="n">
-        <v>0.01373004783304199</v>
+        <v>0.0137299693989319</v>
       </c>
       <c r="C238" t="n">
         <v>0.02086228494301912</v>
@@ -11123,10 +11123,10 @@
         <v>45553</v>
       </c>
       <c r="B239" t="n">
-        <v>0.01279149145502068</v>
+        <v>0.01279164718831671</v>
       </c>
       <c r="C239" t="n">
-        <v>-0.001362458429733149</v>
+        <v>-0.001362520563007008</v>
       </c>
     </row>
     <row r="240">
@@ -11134,7 +11134,7 @@
         <v>45554</v>
       </c>
       <c r="B240" t="n">
-        <v>0.004457700773388362</v>
+        <v>0.004457547643673898</v>
       </c>
       <c r="C240" t="n">
         <v>0</v>
@@ -11145,10 +11145,10 @@
         <v>45555</v>
       </c>
       <c r="B241" t="n">
-        <v>0.0007396403013228969</v>
+        <v>0.0007397164131404121</v>
       </c>
       <c r="C241" t="n">
-        <v>-0.008185468005366681</v>
+        <v>-0.008185281860508709</v>
       </c>
     </row>
     <row r="242">
@@ -11156,10 +11156,10 @@
         <v>45558</v>
       </c>
       <c r="B242" t="n">
-        <v>-0.009608293291811343</v>
+        <v>-0.009608369291157159</v>
       </c>
       <c r="C242" t="n">
-        <v>0.002751028530488142</v>
+        <v>0.002750902722290949</v>
       </c>
     </row>
     <row r="243">
@@ -11167,7 +11167,7 @@
         <v>45559</v>
       </c>
       <c r="B243" t="n">
-        <v>0.003731396541110765</v>
+        <v>0.003731473564105636</v>
       </c>
       <c r="C243" t="n">
         <v>-0.002129084997679942</v>
@@ -11189,10 +11189,10 @@
         <v>45561</v>
       </c>
       <c r="B245" t="n">
-        <v>-0.003709099330540533</v>
+        <v>-0.003709175611787074</v>
       </c>
       <c r="C245" t="n">
-        <v>0.01580464564864381</v>
+        <v>0.01580470897209008</v>
       </c>
     </row>
     <row r="246">
@@ -11200,10 +11200,10 @@
         <v>45562</v>
       </c>
       <c r="B246" t="n">
-        <v>-0.0007447500367130377</v>
+        <v>-0.0007446735284946104</v>
       </c>
       <c r="C246" t="n">
-        <v>0.004243237472746575</v>
+        <v>0.004243299546439649</v>
       </c>
     </row>
     <row r="247">
@@ -11214,7 +11214,7 @@
         <v>0.002235608818950796</v>
       </c>
       <c r="C247" t="n">
-        <v>-0.01267592545634144</v>
+        <v>-0.01267617218185813</v>
       </c>
     </row>
     <row r="248">
@@ -11222,7 +11222,7 @@
         <v>45566</v>
       </c>
       <c r="B248" t="n">
-        <v>0.0104087794322536</v>
+        <v>0.01040885588363727</v>
       </c>
       <c r="C248" t="n">
         <v>0</v>
@@ -11233,7 +11233,7 @@
         <v>45567</v>
       </c>
       <c r="B249" t="n">
-        <v>-0.003679077373590967</v>
+        <v>-0.003679152759027859</v>
       </c>
       <c r="C249" t="n">
         <v>0</v>
@@ -11244,10 +11244,10 @@
         <v>45568</v>
       </c>
       <c r="B250" t="n">
-        <v>-0.01033974489002776</v>
+        <v>-0.01033982083324436</v>
       </c>
       <c r="C250" t="n">
-        <v>0.002853058167895162</v>
+        <v>0.002853184270209752</v>
       </c>
     </row>
     <row r="251">
@@ -11255,10 +11255,10 @@
         <v>45569</v>
       </c>
       <c r="B251" t="n">
-        <v>0.0007463406975454223</v>
+        <v>0.0007463407548171652</v>
       </c>
       <c r="C251" t="n">
-        <v>-0.02560466054048305</v>
+        <v>-0.02560472323338914</v>
       </c>
     </row>
     <row r="252">
@@ -11269,7 +11269,7 @@
         <v>0</v>
       </c>
       <c r="C252" t="n">
-        <v>-0.02043789505759552</v>
+        <v>-0.02043783203225402</v>
       </c>
     </row>
     <row r="253">
@@ -11277,10 +11277,10 @@
         <v>45574</v>
       </c>
       <c r="B253" t="n">
-        <v>0.009694196318344783</v>
+        <v>0.009694273741121195</v>
       </c>
       <c r="C253" t="n">
-        <v>0.01043212605620303</v>
+        <v>0.01043219173893783</v>
       </c>
     </row>
     <row r="254">
@@ -11291,7 +11291,7 @@
         <v>0.03101923467008327</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.001474824336447633</v>
+        <v>-0.001475019254360888</v>
       </c>
     </row>
     <row r="255">
@@ -11302,7 +11302,7 @@
         <v>-0.01432663046896976</v>
       </c>
       <c r="C255" t="n">
-        <v>-0.007385599185044556</v>
+        <v>-0.007385535046039449</v>
       </c>
     </row>
     <row r="256">
@@ -11310,10 +11310,10 @@
         <v>45580</v>
       </c>
       <c r="B256" t="n">
-        <v>-0.004360437418755581</v>
+        <v>-0.004360512147760121</v>
       </c>
       <c r="C256" t="n">
-        <v>-0.005952428579579894</v>
+        <v>-0.005952297799970863</v>
       </c>
     </row>
     <row r="257">
@@ -11321,10 +11321,10 @@
         <v>45581</v>
       </c>
       <c r="B257" t="n">
-        <v>-0.005109531509940979</v>
+        <v>-0.005109531893443542</v>
       </c>
       <c r="C257" t="n">
-        <v>0.01047910977050237</v>
+        <v>0.01047904310139613</v>
       </c>
     </row>
     <row r="258">
@@ -11332,10 +11332,10 @@
         <v>45582</v>
       </c>
       <c r="B258" t="n">
-        <v>0.005135772903418934</v>
+        <v>0.005135773290870782</v>
       </c>
       <c r="C258" t="n">
-        <v>0.001481444336731919</v>
+        <v>0.001481509630236966</v>
       </c>
     </row>
     <row r="259">
@@ -11346,7 +11346,7 @@
         <v>0</v>
       </c>
       <c r="C259" t="n">
-        <v>-0.002958571008703226</v>
+        <v>-0.002958505618898322</v>
       </c>
     </row>
     <row r="260">
@@ -11354,10 +11354,10 @@
         <v>45586</v>
       </c>
       <c r="B260" t="n">
-        <v>-0.01094898537040467</v>
+        <v>-0.01094891113590635</v>
       </c>
       <c r="C260" t="n">
-        <v>-0.001483642367186788</v>
+        <v>-0.001483772953900897</v>
       </c>
     </row>
     <row r="261">
@@ -11387,7 +11387,7 @@
         <v>45589</v>
       </c>
       <c r="B263" t="n">
-        <v>0.0007453051027155322</v>
+        <v>0.0007452284804165821</v>
       </c>
       <c r="C263" t="n">
         <v>0.01634470808273436</v>
@@ -11398,7 +11398,7 @@
         <v>45590</v>
       </c>
       <c r="B264" t="n">
-        <v>-0.00223386728396624</v>
+        <v>-0.002233867455002758</v>
       </c>
       <c r="C264" t="n">
         <v>-0.005847999940720383</v>
@@ -11409,10 +11409,10 @@
         <v>45593</v>
       </c>
       <c r="B265" t="n">
-        <v>0.006716375648021966</v>
+        <v>0.006716452900074055</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.01176467080686083</v>
+        <v>-0.01176473562027014</v>
       </c>
     </row>
     <row r="266">
@@ -11423,7 +11423,7 @@
         <v>0.003706502279461565</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.002976247082287498</v>
+        <v>-0.002976116107485716</v>
       </c>
     </row>
     <row r="267">
@@ -11431,10 +11431,10 @@
         <v>45596</v>
       </c>
       <c r="B267" t="n">
-        <v>0.003692662966358728</v>
+        <v>0.003692738909575333</v>
       </c>
       <c r="C267" t="n">
-        <v>-0.01343276316750219</v>
+        <v>-0.0134328280646554</v>
       </c>
     </row>
     <row r="268">
@@ -11442,7 +11442,7 @@
         <v>45597</v>
       </c>
       <c r="B268" t="n">
-        <v>-0.0095657978972572</v>
+        <v>-0.009565797173472501</v>
       </c>
       <c r="C268" t="n">
         <v>-0.004538597481431483</v>
@@ -11453,10 +11453,10 @@
         <v>45600</v>
       </c>
       <c r="B269" t="n">
-        <v>-0.013372949530983</v>
+        <v>-0.01337302490394721</v>
       </c>
       <c r="C269" t="n">
-        <v>-0.003039504516355818</v>
+        <v>-0.003039437535934941</v>
       </c>
     </row>
     <row r="270">
@@ -11464,10 +11464,10 @@
         <v>45602</v>
       </c>
       <c r="B270" t="n">
-        <v>0.01355420928772011</v>
+        <v>0.01355428671777936</v>
       </c>
       <c r="C270" t="n">
-        <v>0.003048771270401485</v>
+        <v>0.003048703880946801</v>
       </c>
     </row>
     <row r="271">
@@ -11475,7 +11475,7 @@
         <v>45603</v>
       </c>
       <c r="B271" t="n">
-        <v>0.003714686982331239</v>
+        <v>0.00371468669854913</v>
       </c>
       <c r="C271" t="n">
         <v>0.001519785748388403</v>
@@ -11486,7 +11486,7 @@
         <v>45607</v>
       </c>
       <c r="B272" t="n">
-        <v>0.0236861627955034</v>
+        <v>0.02368608488085222</v>
       </c>
       <c r="C272" t="n">
         <v>-0.01062215589630744</v>
@@ -11497,7 +11497,7 @@
         <v>45608</v>
       </c>
       <c r="B273" t="n">
-        <v>-0.01084599359735738</v>
+        <v>-0.01084591924658274</v>
       </c>
       <c r="C273" t="n">
         <v>-0.00460124679599605</v>
@@ -11508,7 +11508,7 @@
         <v>45609</v>
       </c>
       <c r="B274" t="n">
-        <v>0.007309971081375322</v>
+        <v>0.007309895365894548</v>
       </c>
       <c r="C274" t="n">
         <v>0.001540861347605116</v>
@@ -11541,10 +11541,10 @@
         <v>45614</v>
       </c>
       <c r="B277" t="n">
-        <v>0.0007467444353947972</v>
+        <v>0.000746667641438048</v>
       </c>
       <c r="C277" t="n">
-        <v>-0.007849304533823043</v>
+        <v>-0.007849235345256167</v>
       </c>
     </row>
     <row r="278">
@@ -11552,10 +11552,10 @@
         <v>45615</v>
       </c>
       <c r="B278" t="n">
-        <v>-0.02985078864561497</v>
+        <v>-0.02985071419960483</v>
       </c>
       <c r="C278" t="n">
-        <v>-0.003164547472640278</v>
+        <v>-0.003164547251957583</v>
       </c>
     </row>
     <row r="279">
@@ -11563,10 +11563,10 @@
         <v>45616</v>
       </c>
       <c r="B279" t="n">
-        <v>0.01846158129603137</v>
+        <v>0.0184616603938168</v>
       </c>
       <c r="C279" t="n">
-        <v>0.009523780874617804</v>
+        <v>0.009523710251035489</v>
       </c>
     </row>
     <row r="280">
@@ -11574,7 +11574,7 @@
         <v>45617</v>
       </c>
       <c r="B280" t="n">
-        <v>0.004531771210286806</v>
+        <v>0.004531693194351982</v>
       </c>
       <c r="C280" t="n">
         <v>0.004717001725157655</v>
@@ -11607,10 +11607,10 @@
         <v>45622</v>
       </c>
       <c r="B283" t="n">
-        <v>0.009708675981568771</v>
+        <v>0.009708599187612021</v>
       </c>
       <c r="C283" t="n">
-        <v>0.007775991777039692</v>
+        <v>0.007776060319987232</v>
       </c>
     </row>
     <row r="284">
@@ -11618,10 +11618,10 @@
         <v>45623</v>
       </c>
       <c r="B284" t="n">
-        <v>0.02736691931562474</v>
+        <v>0.02736699745259497</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.003086478530678449</v>
+        <v>-0.003086478320754482</v>
       </c>
     </row>
     <row r="285">
@@ -11632,7 +11632,7 @@
         <v>0.003599541046116705</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.001547880737863161</v>
+        <v>-0.00154801708153951</v>
       </c>
     </row>
     <row r="286">
@@ -11640,10 +11640,10 @@
         <v>45625</v>
       </c>
       <c r="B286" t="n">
-        <v>0.03515072288059939</v>
+        <v>0.03515079664467868</v>
       </c>
       <c r="C286" t="n">
-        <v>0.001550280387012437</v>
+        <v>0.001550417153777017</v>
       </c>
     </row>
     <row r="287">
@@ -11651,10 +11651,10 @@
         <v>45628</v>
       </c>
       <c r="B287" t="n">
-        <v>-0.007676190491121004</v>
+        <v>-0.007676261203380719</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.001547880737863161</v>
+        <v>-0.00154801708153951</v>
       </c>
     </row>
     <row r="288">
@@ -11665,7 +11665,7 @@
         <v>0.01969058150056791</v>
       </c>
       <c r="C288" t="n">
-        <v>-0.009302365626194908</v>
+        <v>-0.009302297931412795</v>
       </c>
     </row>
     <row r="289">
@@ -11695,7 +11695,7 @@
         <v>45635</v>
       </c>
       <c r="B291" t="n">
-        <v>-0.01010101774145356</v>
+        <v>-0.01010094897746228</v>
       </c>
       <c r="C291" t="n">
         <v>-0.003110478962352947</v>
@@ -11706,7 +11706,7 @@
         <v>45636</v>
       </c>
       <c r="B292" t="n">
-        <v>0.01700686202680934</v>
+        <v>0.01700679137975603</v>
       </c>
       <c r="C292" t="n">
         <v>-0.003120115472944107</v>
@@ -11720,7 +11720,7 @@
         <v>0.006688876859790582</v>
       </c>
       <c r="C293" t="n">
-        <v>0.004694787108909804</v>
+        <v>0.00469485608092457</v>
       </c>
     </row>
     <row r="294">
@@ -11731,7 +11731,7 @@
         <v>-0.001993302779489725</v>
       </c>
       <c r="C294" t="n">
-        <v>0.006230511202879097</v>
+        <v>0.006230510775156128</v>
       </c>
     </row>
     <row r="295">
@@ -11742,7 +11742,7 @@
         <v>-0.004660419913692149</v>
       </c>
       <c r="C295" t="n">
-        <v>-0.006191932299320579</v>
+        <v>-0.006191931876878276</v>
       </c>
     </row>
     <row r="296">
@@ -11753,7 +11753,7 @@
         <v>0.002675605387138624</v>
       </c>
       <c r="C296" t="n">
-        <v>0.01246115970519623</v>
+        <v>0.01246109020002684</v>
       </c>
     </row>
     <row r="297">
@@ -11761,7 +11761,7 @@
         <v>45644</v>
       </c>
       <c r="B297" t="n">
-        <v>-0.008005465000163192</v>
+        <v>-0.008005396878402071</v>
       </c>
       <c r="C297" t="n">
         <v>-0.004615404435247106</v>
@@ -11772,7 +11772,7 @@
         <v>45645</v>
       </c>
       <c r="B298" t="n">
-        <v>-0.004034863151417878</v>
+        <v>-0.004034931545841558</v>
       </c>
       <c r="C298" t="n">
         <v>-0.0123647910706095</v>
@@ -11797,7 +11797,7 @@
         <v>0.00200656743229799</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.009230876675286881</v>
+        <v>-0.009230808870494212</v>
       </c>
     </row>
     <row r="301">
@@ -11805,10 +11805,10 @@
         <v>45650</v>
       </c>
       <c r="B301" t="n">
-        <v>0.004005371033637628</v>
+        <v>0.004005439200883476</v>
       </c>
       <c r="C301" t="n">
-        <v>-0.001552687806753883</v>
+        <v>-0.001552756137010447</v>
       </c>
     </row>
     <row r="302">
@@ -11816,10 +11816,10 @@
         <v>45651</v>
       </c>
       <c r="B302" t="n">
-        <v>0.002659594692216993</v>
+        <v>0.002659458721052221</v>
       </c>
       <c r="C302" t="n">
-        <v>0.001555102395281338</v>
+        <v>0.001555170938228878</v>
       </c>
     </row>
     <row r="303">
@@ -11827,10 +11827,10 @@
         <v>45652</v>
       </c>
       <c r="B303" t="n">
-        <v>-0.006631350027207938</v>
+        <v>-0.006631282761041635</v>
       </c>
       <c r="C303" t="n">
-        <v>-0.001564869507635458</v>
+        <v>-0.001564937837058356</v>
       </c>
     </row>
     <row r="304">
@@ -11852,7 +11852,7 @@
         <v>0.006016020104002484</v>
       </c>
       <c r="C305" t="n">
-        <v>-0.007836953530399038</v>
+        <v>-0.007837022074182909</v>
       </c>
     </row>
     <row r="306">
@@ -11863,7 +11863,7 @@
         <v>0.0132890696809882</v>
       </c>
       <c r="C306" t="n">
-        <v>0.001579702215147805</v>
+        <v>0.001579840494694285</v>
       </c>
     </row>
     <row r="307">
@@ -11874,7 +11874,7 @@
         <v>-0.003278646372503635</v>
       </c>
       <c r="C307" t="n">
-        <v>-0.004731839004490812</v>
+        <v>-0.004731907654341061</v>
       </c>
     </row>
     <row r="308">
@@ -11882,7 +11882,7 @@
         <v>45660</v>
       </c>
       <c r="B308" t="n">
-        <v>-0.01973678906794163</v>
+        <v>-0.01973685624854893</v>
       </c>
       <c r="C308" t="n">
         <v>-0.001584778585286939</v>
@@ -11893,7 +11893,7 @@
         <v>45663</v>
       </c>
       <c r="B309" t="n">
-        <v>0.002013369326073544</v>
+        <v>0.002013437997294254</v>
       </c>
       <c r="C309" t="n">
         <v>-0.007936470474885993</v>
@@ -11915,7 +11915,7 @@
         <v>45665</v>
       </c>
       <c r="B311" t="n">
-        <v>-0.01199195982470314</v>
+        <v>-0.01199202785569975</v>
       </c>
       <c r="C311" t="n">
         <v>0</v>
@@ -11926,10 +11926,10 @@
         <v>45666</v>
       </c>
       <c r="B312" t="n">
-        <v>0.003371500615234835</v>
+        <v>0.003371569704113675</v>
       </c>
       <c r="C312" t="n">
-        <v>0.001620808723165945</v>
+        <v>0.001620737846450782</v>
       </c>
     </row>
     <row r="313">
@@ -11940,7 +11940,7 @@
         <v>-0.008064508381008473</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.006472531526958147</v>
+        <v>-0.006472461222939097</v>
       </c>
     </row>
     <row r="314">
@@ -11951,7 +11951,7 @@
         <v>-0.01693765873671738</v>
       </c>
       <c r="C314" t="n">
-        <v>0.00325738466945924</v>
+        <v>0.003257313446442645</v>
       </c>
     </row>
     <row r="315">
@@ -11962,7 +11962,7 @@
         <v>0.002756740262314095</v>
       </c>
       <c r="C315" t="n">
-        <v>0.001623297794853595</v>
+        <v>0.00162336890186876</v>
       </c>
     </row>
     <row r="316">
@@ -11981,7 +11981,7 @@
         <v>45674</v>
       </c>
       <c r="B317" t="n">
-        <v>0.02405502309402374</v>
+        <v>0.02405495291222204</v>
       </c>
       <c r="C317" t="n">
         <v>0.004862284416067286</v>
@@ -11992,7 +11992,7 @@
         <v>45677</v>
       </c>
       <c r="B318" t="n">
-        <v>0.006711390997789835</v>
+        <v>0.006711459990980995</v>
       </c>
       <c r="C318" t="n">
         <v>-0.001612966023605722</v>
@@ -12006,7 +12006,7 @@
         <v>-0.0006666716589320831</v>
       </c>
       <c r="C319" t="n">
-        <v>-0.001615430590742095</v>
+        <v>-0.001615501238454442</v>
       </c>
     </row>
     <row r="320">
@@ -12014,10 +12014,10 @@
         <v>45679</v>
       </c>
       <c r="B320" t="n">
-        <v>-0.001334232813066993</v>
+        <v>-0.001334300934828114</v>
       </c>
       <c r="C320" t="n">
-        <v>-0.003236230382467342</v>
+        <v>-0.003236230611469604</v>
       </c>
     </row>
     <row r="321">
@@ -12025,10 +12025,10 @@
         <v>45680</v>
       </c>
       <c r="B321" t="n">
-        <v>0.03072808062695187</v>
+        <v>0.03072815093577708</v>
       </c>
       <c r="C321" t="n">
-        <v>0.006493475146491567</v>
+        <v>0.006493546599249056</v>
       </c>
     </row>
     <row r="322">
@@ -12050,7 +12050,7 @@
         <v>-0.05149933608918289</v>
       </c>
       <c r="C323" t="n">
-        <v>-0.02733126996454138</v>
+        <v>-0.02733119965757691</v>
       </c>
     </row>
     <row r="324">
@@ -12061,7 +12061,7 @@
         <v>0.004811032691525385</v>
       </c>
       <c r="C324" t="n">
-        <v>-0.004958654388272921</v>
+        <v>-0.004958726312381589</v>
       </c>
     </row>
     <row r="325">
@@ -12072,7 +12072,7 @@
         <v>0.0006838599483323105</v>
       </c>
       <c r="C325" t="n">
-        <v>0.02159472770555926</v>
+        <v>0.021594655062811</v>
       </c>
     </row>
     <row r="326">
@@ -12083,7 +12083,7 @@
         <v>0.001367064399161011</v>
       </c>
       <c r="C326" t="n">
-        <v>-0.01300821032260491</v>
+        <v>-0.01300806903315732</v>
       </c>
     </row>
     <row r="327">
@@ -12094,7 +12094,7 @@
         <v>-0.002730326468169952</v>
       </c>
       <c r="C327" t="n">
-        <v>0.001647582831940442</v>
+        <v>0.001647438624500008</v>
       </c>
     </row>
     <row r="328">
@@ -12105,7 +12105,7 @@
         <v>-0.02806297272088387</v>
       </c>
       <c r="C328" t="n">
-        <v>-0.003289529757998899</v>
+        <v>-0.003289458068724049</v>
       </c>
     </row>
     <row r="329">
@@ -12116,7 +12116,7 @@
         <v>0.023943627028852</v>
       </c>
       <c r="C329" t="n">
-        <v>-0.003300314314274466</v>
+        <v>-0.003300386477529615</v>
       </c>
     </row>
     <row r="330">
@@ -12127,7 +12127,7 @@
         <v>-0.00275098227294579</v>
       </c>
       <c r="C330" t="n">
-        <v>0.009933799767646745</v>
+        <v>0.009933800486875866</v>
       </c>
     </row>
     <row r="331">
@@ -12135,10 +12135,10 @@
         <v>45701</v>
       </c>
       <c r="B331" t="n">
-        <v>-0.01310340616728067</v>
+        <v>-0.01310347659109046</v>
       </c>
       <c r="C331" t="n">
-        <v>-0.00491815254452721</v>
+        <v>-0.004918009516998278</v>
       </c>
     </row>
     <row r="332">
@@ -12146,10 +12146,10 @@
         <v>45702</v>
       </c>
       <c r="B332" t="n">
-        <v>0.01257856788203648</v>
+        <v>0.01257864013848753</v>
       </c>
       <c r="C332" t="n">
-        <v>-0.006589754972754935</v>
+        <v>-0.006589754498000255</v>
       </c>
     </row>
     <row r="333">
@@ -12157,10 +12157,10 @@
         <v>45705</v>
       </c>
       <c r="B333" t="n">
-        <v>-0.008971772275448431</v>
+        <v>-0.008971701803036636</v>
       </c>
       <c r="C333" t="n">
-        <v>-0.004975100925630915</v>
+        <v>-0.004975173087099938</v>
       </c>
     </row>
     <row r="334">
@@ -12168,10 +12168,10 @@
         <v>45706</v>
       </c>
       <c r="B334" t="n">
-        <v>0.002089152386098636</v>
+        <v>0.002089152237538361</v>
       </c>
       <c r="C334" t="n">
-        <v>0.004999976312410892</v>
+        <v>0.005000049197300571</v>
       </c>
     </row>
     <row r="335">
@@ -12179,10 +12179,10 @@
         <v>45707</v>
       </c>
       <c r="B335" t="n">
-        <v>0.0006950032713550769</v>
+        <v>0.0006949322598936991</v>
       </c>
       <c r="C335" t="n">
-        <v>0.00829197992061137</v>
+        <v>0.008291834274708698</v>
       </c>
     </row>
     <row r="336">
@@ -12193,7 +12193,7 @@
         <v>-0.006944496644190612</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.001644872767807559</v>
+        <v>-0.001644729034361969</v>
       </c>
     </row>
     <row r="337">
@@ -12204,7 +12204,7 @@
         <v>-0.00699298851661434</v>
       </c>
       <c r="C337" t="n">
-        <v>0.01153221529107307</v>
+        <v>0.01153214241587119</v>
       </c>
     </row>
     <row r="338">
@@ -12212,7 +12212,7 @@
         <v>45712</v>
       </c>
       <c r="B338" t="n">
-        <v>-0.01056346004283781</v>
+        <v>-0.01056338813119995</v>
       </c>
       <c r="C338" t="n">
         <v>0.0390879038033447</v>
@@ -12223,7 +12223,7 @@
         <v>45713</v>
       </c>
       <c r="B339" t="n">
-        <v>-0.01067609269819303</v>
+        <v>-0.01067616460163956</v>
       </c>
       <c r="C339" t="n">
         <v>-0.01410658489850203</v>
@@ -12234,7 +12234,7 @@
         <v>45714</v>
       </c>
       <c r="B340" t="n">
-        <v>0.02014396385233885</v>
+        <v>0.02014389038865017</v>
       </c>
       <c r="C340" t="n">
         <v>0.003179635206141285</v>
@@ -12245,7 +12245,7 @@
         <v>45715</v>
       </c>
       <c r="B341" t="n">
-        <v>-0.003526191510092258</v>
+        <v>-0.003526119750958623</v>
       </c>
       <c r="C341" t="n">
         <v>-0.01426300726758234</v>
@@ -12267,10 +12267,10 @@
         <v>45719</v>
       </c>
       <c r="B343" t="n">
-        <v>0.001425454757186806</v>
+        <v>0.001425527540171556</v>
       </c>
       <c r="C343" t="n">
-        <v>0.01607709355508713</v>
+        <v>0.0160771638620516</v>
       </c>
     </row>
     <row r="344">
@@ -12278,10 +12278,10 @@
         <v>45720</v>
       </c>
       <c r="B344" t="n">
-        <v>-0.003558600660219513</v>
+        <v>-0.003558745760339321</v>
       </c>
       <c r="C344" t="n">
-        <v>0.00474688230261644</v>
+        <v>0.004746743585132496</v>
       </c>
     </row>
     <row r="345">
@@ -12289,10 +12289,10 @@
         <v>45721</v>
       </c>
       <c r="B345" t="n">
-        <v>-0.006428619724572315</v>
+        <v>-0.006428474315570032</v>
       </c>
       <c r="C345" t="n">
-        <v>-0.01259843419844364</v>
+        <v>-0.01259836619845178</v>
       </c>
     </row>
     <row r="346">
@@ -12300,7 +12300,7 @@
         <v>45722</v>
       </c>
       <c r="B346" t="n">
-        <v>0.017972670599532</v>
+        <v>0.01797266928014252</v>
       </c>
       <c r="C346" t="n">
         <v>0.003189777535091531</v>
@@ -12311,7 +12311,7 @@
         <v>45723</v>
       </c>
       <c r="B347" t="n">
-        <v>-0.001412440073519594</v>
+        <v>-0.001412439971661739</v>
       </c>
       <c r="C347" t="n">
         <v>-0.003179635206141285</v>
@@ -12322,7 +12322,7 @@
         <v>45726</v>
       </c>
       <c r="B348" t="n">
-        <v>-0.01485145333022997</v>
+        <v>-0.01485152447448213</v>
       </c>
       <c r="C348" t="n">
         <v>-0.003189777535091642</v>
@@ -12369,7 +12369,7 @@
         <v>-0.03736269244191726</v>
       </c>
       <c r="C352" t="n">
-        <v>0.001612895489845778</v>
+        <v>0.001612824956085612</v>
       </c>
     </row>
     <row r="353">
@@ -12380,7 +12380,7 @@
         <v>-0.01065457042152551</v>
       </c>
       <c r="C353" t="n">
-        <v>0.01449268422359107</v>
+        <v>0.01449275566435326</v>
       </c>
     </row>
     <row r="354">
@@ -12399,7 +12399,7 @@
         <v>45735</v>
       </c>
       <c r="B355" t="n">
-        <v>-0.0415383852848874</v>
+        <v>-0.04153846383452797</v>
       </c>
       <c r="C355" t="n">
         <v>-0.003199984774638454</v>
@@ -12410,10 +12410,10 @@
         <v>45736</v>
       </c>
       <c r="B356" t="n">
-        <v>0.003210297077869129</v>
+        <v>0.00321029734096534</v>
       </c>
       <c r="C356" t="n">
-        <v>-0.008025643874802091</v>
+        <v>-0.008025714068914724</v>
       </c>
     </row>
     <row r="357">
@@ -12421,10 +12421,10 @@
         <v>45737</v>
       </c>
       <c r="B357" t="n">
-        <v>0.0239999353002387</v>
+        <v>0.02400001895245696</v>
       </c>
       <c r="C357" t="n">
-        <v>-0.008090646718191818</v>
+        <v>-0.008090576528673843</v>
       </c>
     </row>
     <row r="358">
@@ -12476,10 +12476,10 @@
         <v>45744</v>
       </c>
       <c r="B362" t="n">
-        <v>-0.01743253503025766</v>
+        <v>-0.01743261594509382</v>
       </c>
       <c r="C362" t="n">
-        <v>-0.01309337004727518</v>
+        <v>-0.01309329847455631</v>
       </c>
     </row>
     <row r="363">
@@ -12487,10 +12487,10 @@
         <v>45747</v>
       </c>
       <c r="B363" t="n">
-        <v>-0.02419372769847894</v>
+        <v>-0.02419356499000391</v>
       </c>
       <c r="C363" t="n">
-        <v>0.004975173447910874</v>
+        <v>0.004975100564825308</v>
       </c>
     </row>
     <row r="364">
@@ -12498,10 +12498,10 @@
         <v>45748</v>
       </c>
       <c r="B364" t="n">
-        <v>-0.004132178398304043</v>
+        <v>-0.004132346833913947</v>
       </c>
       <c r="C364" t="n">
-        <v>0.003300386477529615</v>
+        <v>0.003300314314274466</v>
       </c>
     </row>
     <row r="365">
@@ -12509,10 +12509,10 @@
         <v>45749</v>
       </c>
       <c r="B365" t="n">
-        <v>0.0124481419224105</v>
+        <v>0.01244822771964693</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.004934330599934422</v>
+        <v>-0.004934187103086018</v>
       </c>
     </row>
     <row r="366">
@@ -12520,10 +12520,10 @@
         <v>45750</v>
       </c>
       <c r="B366" t="n">
-        <v>-0.06967223748825058</v>
+        <v>-0.0696721537878211</v>
       </c>
       <c r="C366" t="n">
-        <v>-0.06611568097379039</v>
+        <v>-0.06611574847731427</v>
       </c>
     </row>
     <row r="367">
@@ -12531,10 +12531,10 @@
         <v>45751</v>
       </c>
       <c r="B367" t="n">
-        <v>-0.00440514009484505</v>
+        <v>-0.004405319636011651</v>
       </c>
       <c r="C367" t="n">
-        <v>0.0353982177593104</v>
+        <v>0.03539829515919446</v>
       </c>
     </row>
     <row r="368">
@@ -12542,10 +12542,10 @@
         <v>45755</v>
       </c>
       <c r="B368" t="n">
-        <v>-0.06991148659132418</v>
+        <v>-0.06991149290900434</v>
       </c>
       <c r="C368" t="n">
-        <v>-0.06837604537491915</v>
+        <v>-0.0683760402635547</v>
       </c>
     </row>
     <row r="369">
@@ -12553,10 +12553,10 @@
         <v>45756</v>
       </c>
       <c r="B369" t="n">
-        <v>0.001902963808321667</v>
+        <v>0.001903061152611629</v>
       </c>
       <c r="C369" t="n">
-        <v>-0.04587158318979689</v>
+        <v>-0.04587157950905008</v>
       </c>
     </row>
     <row r="370">
@@ -12567,7 +12567,7 @@
         <v>0.069325671802972</v>
       </c>
       <c r="C370" t="n">
-        <v>0.06923077958128632</v>
+        <v>0.06923068966117518</v>
       </c>
     </row>
     <row r="371">
@@ -12600,7 +12600,7 @@
         <v>-0.02109711840579331</v>
       </c>
       <c r="C373" t="n">
-        <v>-0.01054491893061349</v>
+        <v>-0.01054484207484441</v>
       </c>
     </row>
     <row r="374">
@@ -12611,7 +12611,7 @@
         <v>-0.06982749863245763</v>
       </c>
       <c r="C374" t="n">
-        <v>-0.005328494294122521</v>
+        <v>-0.005328571555070494</v>
       </c>
     </row>
     <row r="375">
@@ -12641,10 +12641,10 @@
         <v>45768</v>
       </c>
       <c r="B377" t="n">
-        <v>0.0008961555712896363</v>
+        <v>0.0008960640708228773</v>
       </c>
       <c r="C377" t="n">
-        <v>0.001766775988844449</v>
+        <v>0.001766698725714555</v>
       </c>
     </row>
     <row r="378">
@@ -12652,10 +12652,10 @@
         <v>45769</v>
       </c>
       <c r="B378" t="n">
-        <v>-0.01163858593799993</v>
+        <v>-0.01163840416488282</v>
       </c>
       <c r="C378" t="n">
-        <v>-0.01234569710383226</v>
+        <v>-0.01234562092914737</v>
       </c>
     </row>
     <row r="379">
@@ -12674,10 +12674,10 @@
         <v>45771</v>
       </c>
       <c r="B380" t="n">
-        <v>0.01449286488535373</v>
+        <v>0.01449277104979108</v>
       </c>
       <c r="C380" t="n">
-        <v>-0.00177311879640063</v>
+        <v>-0.001773041259283459</v>
       </c>
     </row>
     <row r="381">
@@ -12688,7 +12688,7 @@
         <v>0.003571455597913831</v>
       </c>
       <c r="C381" t="n">
-        <v>0.03552404615097449</v>
+        <v>0.03552404339164994</v>
       </c>
     </row>
     <row r="382">
@@ -12699,7 +12699,7 @@
         <v>-0.02580063374599773</v>
       </c>
       <c r="C382" t="n">
-        <v>-0.01372213709400361</v>
+        <v>-0.01372221107487703</v>
       </c>
     </row>
     <row r="383">
@@ -12718,7 +12718,7 @@
         <v>45782</v>
       </c>
       <c r="B384" t="n">
-        <v>-0.007312390208205399</v>
+        <v>-0.007312483548732152</v>
       </c>
       <c r="C384" t="n">
         <v>0</v>
@@ -12740,7 +12740,7 @@
         <v>45784</v>
       </c>
       <c r="B386" t="n">
-        <v>0.01012880062743071</v>
+        <v>0.0101288956079284</v>
       </c>
       <c r="C386" t="n">
         <v>0</v>
@@ -12809,7 +12809,7 @@
         <v>0.05690376633394423</v>
       </c>
       <c r="C392" t="n">
-        <v>-0.03931630670515629</v>
+        <v>-0.03931623450274524</v>
       </c>
     </row>
     <row r="393">
@@ -12817,10 +12817,10 @@
         <v>45793</v>
       </c>
       <c r="B393" t="n">
-        <v>-0.01029294982902484</v>
+        <v>-0.01029303067979492</v>
       </c>
       <c r="C393" t="n">
-        <v>0.01067624752131158</v>
+        <v>0.01067617156159995</v>
       </c>
     </row>
     <row r="394">
@@ -12828,10 +12828,10 @@
         <v>45796</v>
       </c>
       <c r="B394" t="n">
-        <v>-0.05440000039211978</v>
+        <v>-0.05440000483614416</v>
       </c>
       <c r="C394" t="n">
-        <v>-0.01408457616879177</v>
+        <v>-0.01408450180539456</v>
       </c>
     </row>
     <row r="395">
@@ -12850,10 +12850,10 @@
         <v>45798</v>
       </c>
       <c r="B396" t="n">
-        <v>0.008460214082836703</v>
+        <v>0.008460301205037934</v>
       </c>
       <c r="C396" t="n">
-        <v>-0.001785704318741921</v>
+        <v>-0.001785779609784988</v>
       </c>
     </row>
     <row r="397">
@@ -12919,7 +12919,7 @@
         <v>-0.005042054880636693</v>
       </c>
       <c r="C402" t="n">
-        <v>-0.003610164177802688</v>
+        <v>-0.003610087935185247</v>
       </c>
     </row>
     <row r="403">
@@ -12927,10 +12927,10 @@
         <v>45807</v>
       </c>
       <c r="B403" t="n">
-        <v>-0.01097964057065459</v>
+        <v>-0.01097972681603443</v>
       </c>
       <c r="C403" t="n">
-        <v>-0.001811584083556195</v>
+        <v>-0.001811583944935857</v>
       </c>
     </row>
     <row r="404">
@@ -12938,10 +12938,10 @@
         <v>45810</v>
       </c>
       <c r="B404" t="n">
-        <v>-0.008539686490109388</v>
+        <v>-0.008539687234794369</v>
       </c>
       <c r="C404" t="n">
-        <v>-0.009074359382807096</v>
+        <v>-0.009074435344916476</v>
       </c>
     </row>
     <row r="405">
@@ -12960,10 +12960,10 @@
         <v>45812</v>
       </c>
       <c r="B406" t="n">
-        <v>0.01119715155905388</v>
+        <v>0.01119724049782977</v>
       </c>
       <c r="C406" t="n">
-        <v>0.01648350075653937</v>
+        <v>0.01648342339681452</v>
       </c>
     </row>
     <row r="407">
@@ -12971,10 +12971,10 @@
         <v>45813</v>
       </c>
       <c r="B407" t="n">
-        <v>-0.002555298626281233</v>
+        <v>-0.002555385606287652</v>
       </c>
       <c r="C407" t="n">
-        <v>0.02522523537259103</v>
+        <v>0.02522531339761391</v>
       </c>
     </row>
     <row r="408">
@@ -12982,7 +12982,7 @@
         <v>45814</v>
       </c>
       <c r="B408" t="n">
-        <v>-0.002561932107883469</v>
+        <v>-0.002561845128448037</v>
       </c>
       <c r="C408" t="n">
         <v>-0.01054483020790131</v>
@@ -12993,7 +12993,7 @@
         <v>45817</v>
       </c>
       <c r="B409" t="n">
-        <v>-0.005137024924861011</v>
+        <v>-0.005136937498043781</v>
       </c>
       <c r="C409" t="n">
         <v>-0.01776203944752464</v>
@@ -13015,7 +13015,7 @@
         <v>45819</v>
       </c>
       <c r="B411" t="n">
-        <v>-0.004302870630913058</v>
+        <v>-0.004302958131026657</v>
       </c>
       <c r="C411" t="n">
         <v>0</v>
@@ -13029,7 +13029,7 @@
         <v>0.02789879912617499</v>
       </c>
       <c r="C412" t="n">
-        <v>-0.001808308181236895</v>
+        <v>-0.00180823180074341</v>
       </c>
     </row>
     <row r="413">
@@ -13040,7 +13040,7 @@
         <v>-0.007633610071196339</v>
       </c>
       <c r="C413" t="n">
-        <v>0.01268116510375616</v>
+        <v>0.01268108761455067</v>
       </c>
     </row>
     <row r="414">
@@ -13073,7 +13073,7 @@
         <v>-0.001680705438613761</v>
       </c>
       <c r="C416" t="n">
-        <v>-0.001776263963808478</v>
+        <v>-0.001776188939988432</v>
       </c>
     </row>
     <row r="417">
@@ -13084,7 +13084,7 @@
         <v>-0.01515155904864462</v>
       </c>
       <c r="C417" t="n">
-        <v>-0.003558699068891058</v>
+        <v>-0.003558698801428783</v>
       </c>
     </row>
     <row r="418">
@@ -13095,7 +13095,7 @@
         <v>-0.008547004849443041</v>
       </c>
       <c r="C418" t="n">
-        <v>0.001785704318741921</v>
+        <v>0.001785628758322666</v>
       </c>
     </row>
     <row r="419">
@@ -13161,7 +13161,7 @@
         <v>0.01025644042854523</v>
       </c>
       <c r="C424" t="n">
-        <v>0.02836878476571347</v>
+        <v>0.02836885965651326</v>
       </c>
     </row>
     <row r="425">
@@ -13183,7 +13183,7 @@
         <v>0.005076156913285557</v>
       </c>
       <c r="C426" t="n">
-        <v>-0.008620641314540878</v>
+        <v>-0.008620786336428377</v>
       </c>
     </row>
     <row r="427">
@@ -13205,7 +13205,7 @@
         <v>0.04915248697303509</v>
       </c>
       <c r="C428" t="n">
-        <v>0.006956482391137664</v>
+        <v>0.006956556360256494</v>
       </c>
     </row>
     <row r="429">
@@ -13227,7 +13227,7 @@
         <v>0.005654352565224396</v>
       </c>
       <c r="C430" t="n">
-        <v>0.0189983120684698</v>
+        <v>0.01899823911784604</v>
       </c>
     </row>
     <row r="431">
@@ -13238,7 +13238,7 @@
         <v>-0.01365460423634157</v>
       </c>
       <c r="C431" t="n">
-        <v>0.02033893961117328</v>
+        <v>0.02033901265777827</v>
       </c>
     </row>
     <row r="432">
@@ -13249,7 +13249,7 @@
         <v>0.008957708293386046</v>
       </c>
       <c r="C432" t="n">
-        <v>-0.008305671383757041</v>
+        <v>-0.008305601220283121</v>
       </c>
     </row>
     <row r="433">
@@ -13260,7 +13260,7 @@
         <v>0.02582713604298315</v>
       </c>
       <c r="C433" t="n">
-        <v>0.01005026583314317</v>
+        <v>0.01005026512207574</v>
       </c>
     </row>
     <row r="434">
@@ -13282,7 +13282,7 @@
         <v>-0.008654495893534841</v>
       </c>
       <c r="C435" t="n">
-        <v>-0.003316730999106565</v>
+        <v>-0.003316800813891407</v>
       </c>
     </row>
     <row r="436">
@@ -13392,7 +13392,7 @@
         <v>-0.04761907398256338</v>
       </c>
       <c r="C445" t="n">
-        <v>-0.001579769976149614</v>
+        <v>-0.001579703248801079</v>
       </c>
     </row>
     <row r="446">
@@ -13403,7 +13403,7 @@
         <v>0.0009433920741612756</v>
       </c>
       <c r="C446" t="n">
-        <v>-0.004746808794464985</v>
+        <v>-0.004746875310146503</v>
       </c>
     </row>
     <row r="447">
@@ -13480,7 +13480,7 @@
         <v>0.001883313786800178</v>
       </c>
       <c r="C453" t="n">
-        <v>0.009852160716518732</v>
+        <v>0.009852091359526804</v>
       </c>
     </row>
     <row r="454">
@@ -13502,7 +13502,7 @@
         <v>0.01033829967732536</v>
       </c>
       <c r="C455" t="n">
-        <v>0.004878089988693102</v>
+        <v>0.004878090323721995</v>
       </c>
     </row>
     <row r="456">
@@ -13513,7 +13513,7 @@
         <v>-0.02232564644735435</v>
       </c>
       <c r="C456" t="n">
-        <v>-0.01132686493339286</v>
+        <v>-0.01132679736060505</v>
       </c>
     </row>
     <row r="457">
@@ -13535,7 +13535,7 @@
         <v>-0.03179193692665339</v>
       </c>
       <c r="C458" t="n">
-        <v>-0.01620750136384885</v>
+        <v>-0.01620743290613202</v>
       </c>
     </row>
     <row r="459">
@@ -13557,7 +13557,7 @@
         <v>-0.001989953446003057</v>
       </c>
       <c r="C460" t="n">
-        <v>-0.003294874573832152</v>
+        <v>-0.003294874344556553</v>
       </c>
     </row>
     <row r="461">
@@ -13568,7 +13568,7 @@
         <v>-0.02592229280144309</v>
       </c>
       <c r="C461" t="n">
-        <v>-0.008264416650870854</v>
+        <v>-0.008264485889438955</v>
       </c>
     </row>
     <row r="462">
@@ -13612,7 +13612,7 @@
         <v>0.01214569488040063</v>
       </c>
       <c r="C465" t="n">
-        <v>0.0170357514691879</v>
+        <v>0.01703582342559562</v>
       </c>
     </row>
     <row r="466">
@@ -13623,7 +13623,7 @@
         <v>0.0500000440138908</v>
       </c>
       <c r="C466" t="n">
-        <v>0.01340033086048775</v>
+        <v>0.01340032991239948</v>
       </c>
     </row>
     <row r="467">
@@ -13634,7 +13634,7 @@
         <v>-0.004761883603300543</v>
       </c>
       <c r="C467" t="n">
-        <v>0.008264556281986524</v>
+        <v>0.008264416073886061</v>
       </c>
     </row>
     <row r="468">
@@ -13645,7 +13645,7 @@
         <v>-0.01244030432170895</v>
       </c>
       <c r="C468" t="n">
-        <v>0.008196674770901691</v>
+        <v>0.008196675338466353</v>
       </c>
     </row>
     <row r="469">
@@ -13667,7 +13667,7 @@
         <v>0.01744195518583891</v>
       </c>
       <c r="C470" t="n">
-        <v>0.004878089988693102</v>
+        <v>0.004878090323721995</v>
       </c>
     </row>
     <row r="471">
@@ -13678,7 +13678,7 @@
         <v>-0.02952384601242131</v>
       </c>
       <c r="C471" t="n">
-        <v>-0.01941757061759597</v>
+        <v>-0.01941743525083872</v>
       </c>
     </row>
     <row r="472">
@@ -13700,7 +13700,7 @@
         <v>0.00196269989066078</v>
       </c>
       <c r="C473" t="n">
-        <v>-0.004950467445405504</v>
+        <v>-0.004950467100356182</v>
       </c>
     </row>
     <row r="474">
@@ -13711,7 +13711,7 @@
         <v>-0.008814848605578685</v>
       </c>
       <c r="C474" t="n">
-        <v>-0.008291897544883575</v>
+        <v>-0.008291967011172408</v>
       </c>
     </row>
     <row r="475">
@@ -13832,7 +13832,7 @@
         <v>-0.0402010041359786</v>
       </c>
       <c r="C485" t="n">
-        <v>-0.02741940417545752</v>
+        <v>-0.02741933604899061</v>
       </c>
     </row>
     <row r="486">
@@ -13854,7 +13854,7 @@
         <v>-0.02617798682403882</v>
       </c>
       <c r="C487" t="n">
-        <v>-0.004975096498659792</v>
+        <v>-0.004975166197281</v>
       </c>
     </row>
     <row r="488">
@@ -13865,7 +13865,7 @@
         <v>0.004301056134556447</v>
       </c>
       <c r="C488" t="n">
-        <v>0.03500001407947018</v>
+        <v>0.03499994368211934</v>
       </c>
     </row>
     <row r="489">
@@ -13876,7 +13876,7 @@
         <v>-0.0139185678954773</v>
       </c>
       <c r="C489" t="n">
-        <v>-0.01449273982268573</v>
+        <v>-0.01449267279166733</v>
       </c>
     </row>
     <row r="490">
@@ -13920,7 +13920,7 @@
         <v>-0.01047115785934138</v>
       </c>
       <c r="C493" t="n">
-        <v>0.03257324374204251</v>
+        <v>0.03257331253424134</v>
       </c>
     </row>
     <row r="494">
@@ -13931,7 +13931,7 @@
         <v>-0.003174682131237172</v>
       </c>
       <c r="C494" t="n">
-        <v>-0.007886391196715525</v>
+        <v>-0.007886457293404092</v>
       </c>
     </row>
     <row r="495">
@@ -13942,7 +13942,7 @@
         <v>-0.002123039477843869</v>
       </c>
       <c r="C495" t="n">
-        <v>0.01748804481757205</v>
+        <v>0.01748811196925737</v>
       </c>
     </row>
     <row r="496">
@@ -13964,7 +13964,7 @@
         <v>-0.01702138737764136</v>
       </c>
       <c r="C497" t="n">
-        <v>-0.007812522171041114</v>
+        <v>-0.007812587652947567</v>
       </c>
     </row>
     <row r="498">
@@ -16614,31 +16614,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02360804251446819</v>
+        <v>0.02360804560066293</v>
       </c>
       <c r="C2" t="n">
-        <v>5.949226713645983</v>
+        <v>5.949227491367058</v>
       </c>
       <c r="D2" t="n">
         <v>1.586565744698598</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0003483920797748125</v>
+        <v>0.0003483921433027945</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08779480410325276</v>
+        <v>0.0877948201123042</v>
       </c>
       <c r="G2" t="n">
-        <v>1.866526398888621</v>
+        <v>1.866526569065639</v>
       </c>
       <c r="H2" t="n">
-        <v>29.63018800197744</v>
+        <v>29.63019070345383</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04009345639449882</v>
+        <v>0.04009346306422304</v>
       </c>
       <c r="J2" t="n">
-        <v>20.02335046751637</v>
+        <v>20.02335213300286</v>
       </c>
     </row>
     <row r="3">
@@ -16648,31 +16648,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002164765508247972</v>
+        <v>0.002164758707399229</v>
       </c>
       <c r="C3" t="n">
-        <v>0.545520908078489</v>
+        <v>0.5455191942646057</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.468027868927347</v>
+        <v>-2.468029911637304</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0002420833626095284</v>
+        <v>0.0002420833930276994</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06100500737760115</v>
+        <v>0.06100501504298026</v>
       </c>
       <c r="G3" t="n">
-        <v>1.555902833115</v>
+        <v>1.555902930865867</v>
       </c>
       <c r="H3" t="n">
-        <v>24.69919176361874</v>
+        <v>24.69919331536564</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02849124341881984</v>
+        <v>0.0284912437319472</v>
       </c>
       <c r="J3" t="n">
-        <v>16.87934934137565</v>
+        <v>16.87934943413022</v>
       </c>
     </row>
     <row r="4">
